--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="165">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,261 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Chilean Primera Division</t>
+  </si>
+  <si>
+    <t>Costa Rican Primera Division</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
+    <t>Bulgarian A League</t>
+  </si>
+  <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
+    <t>Portuguese Segunda Liga</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Dutch Eerste Divisie</t>
+  </si>
+  <si>
+    <t>Uruguayan Segunda Division</t>
+  </si>
+  <si>
+    <t>Icelandic Urvalsdeild</t>
+  </si>
+  <si>
+    <t>Portuguese Primeira Liga</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>01:15:00</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>15:45:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
+    <t>Universidad de Chile</t>
+  </si>
+  <si>
+    <t>Cs Herediano</t>
+  </si>
+  <si>
+    <t>Guayaquil City</t>
+  </si>
+  <si>
+    <t>America de Cali S.A</t>
+  </si>
+  <si>
+    <t>Polissya Zhytomyr</t>
+  </si>
+  <si>
+    <t>MSK Povazska Bystrica</t>
+  </si>
+  <si>
+    <t>Karpaty</t>
+  </si>
+  <si>
+    <t>Botosani</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Norrby IF</t>
+  </si>
+  <si>
+    <t>Sirius</t>
+  </si>
+  <si>
+    <t>Vasteras SK</t>
+  </si>
+  <si>
+    <t>Benfica B</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>Lusitania Futebol Clube</t>
+  </si>
+  <si>
+    <t>Jong AZ Alkmaar</t>
+  </si>
+  <si>
+    <t>Jong PSV Eindhoven</t>
+  </si>
+  <si>
+    <t>Botev Plovdiv</t>
+  </si>
+  <si>
+    <t>ACS Sepsi OSK</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Tecnico Universitario</t>
+  </si>
+  <si>
+    <t>CA Rentistas</t>
+  </si>
+  <si>
+    <t>Fram</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Palestino</t>
+  </si>
+  <si>
+    <t>Ld Alajuelense</t>
+  </si>
+  <si>
+    <t>Emelec</t>
+  </si>
+  <si>
+    <t>Atletico Nacional Medellin</t>
+  </si>
+  <si>
+    <t>Fc Kharkiv</t>
+  </si>
+  <si>
+    <t>Zlate Moravce</t>
+  </si>
+  <si>
+    <t>LNZ-Lebedyn</t>
+  </si>
+  <si>
+    <t>FC Hunedoara</t>
+  </si>
+  <si>
+    <t>Panevezys</t>
+  </si>
+  <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
+    <t>Orebro</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Djurgardens</t>
+  </si>
+  <si>
+    <t>Leixoes</t>
+  </si>
+  <si>
+    <t>Odds BK</t>
+  </si>
+  <si>
+    <t>OB</t>
+  </si>
+  <si>
+    <t>Porto B</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>FCSB</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Mushuc Runa</t>
+  </si>
+  <si>
+    <t>Plaza Colonia</t>
+  </si>
+  <si>
+    <t>KR Reykjavik</t>
+  </si>
+  <si>
+    <t>CD Nacional Funchal</t>
+  </si>
+  <si>
+    <t>2026-08-08 01:34:43</t>
   </si>
 </sst>
 </file>
@@ -585,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1083,6298 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2">
+        <v>1.77</v>
+      </c>
+      <c r="G2">
+        <v>1.96</v>
+      </c>
+      <c r="H2">
+        <v>4.5</v>
+      </c>
+      <c r="I2">
+        <v>5.8</v>
+      </c>
+      <c r="J2">
+        <v>3.7</v>
+      </c>
+      <c r="K2">
+        <v>4.6</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>3.75</v>
+      </c>
+      <c r="O2">
+        <v>1.3</v>
+      </c>
+      <c r="P2">
+        <v>1.92</v>
+      </c>
+      <c r="Q2">
+        <v>1.3</v>
+      </c>
+      <c r="R2">
+        <v>1.31</v>
+      </c>
+      <c r="S2">
+        <v>2.78</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.89</v>
+      </c>
+      <c r="V2">
+        <v>1.2</v>
+      </c>
+      <c r="W2">
+        <v>2.04</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>6.8</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>15.5</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>40</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3">
+        <v>2.48</v>
+      </c>
+      <c r="G3">
+        <v>2.94</v>
+      </c>
+      <c r="H3">
+        <v>3.05</v>
+      </c>
+      <c r="I3">
+        <v>3.8</v>
+      </c>
+      <c r="J3">
+        <v>2.92</v>
+      </c>
+      <c r="K3">
+        <v>3.75</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>1.53</v>
+      </c>
+      <c r="O3">
+        <v>1.02</v>
+      </c>
+      <c r="P3">
+        <v>1.53</v>
+      </c>
+      <c r="Q3">
+        <v>2.38</v>
+      </c>
+      <c r="R3">
+        <v>1.18</v>
+      </c>
+      <c r="S3">
+        <v>4.4</v>
+      </c>
+      <c r="T3">
+        <v>1.01</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
+        <v>1.35</v>
+      </c>
+      <c r="W3">
+        <v>1.51</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3">
+        <v>1.01</v>
+      </c>
+      <c r="AR3">
+        <v>1.01</v>
+      </c>
+      <c r="AS3">
+        <v>1.01</v>
+      </c>
+      <c r="AT3">
+        <v>1.01</v>
+      </c>
+      <c r="AU3">
+        <v>1.01</v>
+      </c>
+      <c r="AV3">
+        <v>1.01</v>
+      </c>
+      <c r="AW3">
+        <v>1.01</v>
+      </c>
+      <c r="AX3">
+        <v>1.01</v>
+      </c>
+      <c r="AY3">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3">
+        <v>1.01</v>
+      </c>
+      <c r="BA3">
+        <v>1.01</v>
+      </c>
+      <c r="BB3">
+        <v>1.01</v>
+      </c>
+      <c r="BC3">
+        <v>1.01</v>
+      </c>
+      <c r="BD3">
+        <v>1.01</v>
+      </c>
+      <c r="BE3">
+        <v>1.01</v>
+      </c>
+      <c r="BF3">
+        <v>1.01</v>
+      </c>
+      <c r="BG3">
+        <v>1.01</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4">
+        <v>1.06</v>
+      </c>
+      <c r="G4">
+        <v>3.45</v>
+      </c>
+      <c r="H4">
+        <v>2.56</v>
+      </c>
+      <c r="I4">
+        <v>110</v>
+      </c>
+      <c r="J4">
+        <v>3.1</v>
+      </c>
+      <c r="K4">
+        <v>110</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>1.49</v>
+      </c>
+      <c r="O4">
+        <v>1.5</v>
+      </c>
+      <c r="P4">
+        <v>1.25</v>
+      </c>
+      <c r="Q4">
+        <v>2.56</v>
+      </c>
+      <c r="R4">
+        <v>1.18</v>
+      </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.49</v>
+      </c>
+      <c r="W4">
+        <v>1.4</v>
+      </c>
+      <c r="X4">
+        <v>10.5</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>7.6</v>
+      </c>
+      <c r="AQ4">
+        <v>1.1</v>
+      </c>
+      <c r="AR4">
+        <v>1.1</v>
+      </c>
+      <c r="AS4">
+        <v>1.1</v>
+      </c>
+      <c r="AT4">
+        <v>1.1</v>
+      </c>
+      <c r="AU4">
+        <v>1.1</v>
+      </c>
+      <c r="AV4">
+        <v>1.1</v>
+      </c>
+      <c r="AW4">
+        <v>1.1</v>
+      </c>
+      <c r="AX4">
+        <v>1.1</v>
+      </c>
+      <c r="AY4">
+        <v>1.1</v>
+      </c>
+      <c r="AZ4">
+        <v>1.1</v>
+      </c>
+      <c r="BA4">
+        <v>1.1</v>
+      </c>
+      <c r="BB4">
+        <v>1.1</v>
+      </c>
+      <c r="BC4">
+        <v>1.1</v>
+      </c>
+      <c r="BD4">
+        <v>1.1</v>
+      </c>
+      <c r="BE4">
+        <v>1.1</v>
+      </c>
+      <c r="BF4">
+        <v>1.1</v>
+      </c>
+      <c r="BG4">
+        <v>1.1</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5">
+        <v>2.46</v>
+      </c>
+      <c r="G5">
+        <v>2.68</v>
+      </c>
+      <c r="H5">
+        <v>3.05</v>
+      </c>
+      <c r="I5">
+        <v>3.35</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3.6</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.07</v>
+      </c>
+      <c r="N5">
+        <v>3.2</v>
+      </c>
+      <c r="O5">
+        <v>1.39</v>
+      </c>
+      <c r="P5">
+        <v>1.75</v>
+      </c>
+      <c r="Q5">
+        <v>2.12</v>
+      </c>
+      <c r="R5">
+        <v>1.28</v>
+      </c>
+      <c r="S5">
+        <v>4</v>
+      </c>
+      <c r="T5">
+        <v>1.74</v>
+      </c>
+      <c r="U5">
+        <v>1.88</v>
+      </c>
+      <c r="V5">
+        <v>1.42</v>
+      </c>
+      <c r="W5">
+        <v>1.6</v>
+      </c>
+      <c r="X5">
+        <v>12</v>
+      </c>
+      <c r="Y5">
+        <v>11.5</v>
+      </c>
+      <c r="Z5">
+        <v>22</v>
+      </c>
+      <c r="AA5">
+        <v>65</v>
+      </c>
+      <c r="AB5">
+        <v>9.6</v>
+      </c>
+      <c r="AC5">
+        <v>7.8</v>
+      </c>
+      <c r="AD5">
+        <v>14</v>
+      </c>
+      <c r="AE5">
+        <v>48</v>
+      </c>
+      <c r="AF5">
+        <v>16</v>
+      </c>
+      <c r="AG5">
+        <v>12</v>
+      </c>
+      <c r="AH5">
+        <v>19</v>
+      </c>
+      <c r="AI5">
+        <v>65</v>
+      </c>
+      <c r="AJ5">
+        <v>38</v>
+      </c>
+      <c r="AK5">
+        <v>32</v>
+      </c>
+      <c r="AL5">
+        <v>55</v>
+      </c>
+      <c r="AM5">
+        <v>130</v>
+      </c>
+      <c r="AN5">
+        <v>27</v>
+      </c>
+      <c r="AO5">
+        <v>50</v>
+      </c>
+      <c r="AP5">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR5">
+        <v>19</v>
+      </c>
+      <c r="AS5">
+        <v>38</v>
+      </c>
+      <c r="AT5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU5">
+        <v>6.6</v>
+      </c>
+      <c r="AV5">
+        <v>12</v>
+      </c>
+      <c r="AW5">
+        <v>34</v>
+      </c>
+      <c r="AX5">
+        <v>13.5</v>
+      </c>
+      <c r="AY5">
+        <v>10.5</v>
+      </c>
+      <c r="AZ5">
+        <v>16.5</v>
+      </c>
+      <c r="BA5">
+        <v>38</v>
+      </c>
+      <c r="BB5">
+        <v>26</v>
+      </c>
+      <c r="BC5">
+        <v>8.4</v>
+      </c>
+      <c r="BD5">
+        <v>34</v>
+      </c>
+      <c r="BE5">
+        <v>10.5</v>
+      </c>
+      <c r="BF5">
+        <v>20</v>
+      </c>
+      <c r="BG5">
+        <v>32</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F6">
+        <v>1.04</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>1.04</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1.01</v>
+      </c>
+      <c r="K6">
+        <v>330</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.04</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F7">
+        <v>1.99</v>
+      </c>
+      <c r="G7">
+        <v>2.76</v>
+      </c>
+      <c r="H7">
+        <v>2.68</v>
+      </c>
+      <c r="I7">
+        <v>4.1</v>
+      </c>
+      <c r="J7">
+        <v>2.52</v>
+      </c>
+      <c r="K7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.85</v>
+      </c>
+      <c r="Q7">
+        <v>1.68</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F8">
+        <v>1.04</v>
+      </c>
+      <c r="G8">
+        <v>1000</v>
+      </c>
+      <c r="H8">
+        <v>1.04</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>1.01</v>
+      </c>
+      <c r="K8">
+        <v>330</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.12</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F9">
+        <v>2.1</v>
+      </c>
+      <c r="G9">
+        <v>2.66</v>
+      </c>
+      <c r="H9">
+        <v>2.98</v>
+      </c>
+      <c r="I9">
+        <v>4.3</v>
+      </c>
+      <c r="J9">
+        <v>3.2</v>
+      </c>
+      <c r="K9">
+        <v>5.4</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.7</v>
+      </c>
+      <c r="Q9">
+        <v>1.87</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10">
+        <v>1.04</v>
+      </c>
+      <c r="G10">
+        <v>1000</v>
+      </c>
+      <c r="H10">
+        <v>1.04</v>
+      </c>
+      <c r="I10">
+        <v>1000</v>
+      </c>
+      <c r="J10">
+        <v>1.01</v>
+      </c>
+      <c r="K10">
+        <v>330</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1.04</v>
+      </c>
+      <c r="Q10">
+        <v>1.01</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11">
+        <v>1.11</v>
+      </c>
+      <c r="G11">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>1.09</v>
+      </c>
+      <c r="I11">
+        <v>1000</v>
+      </c>
+      <c r="J11">
+        <v>1.09</v>
+      </c>
+      <c r="K11">
+        <v>950</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.57</v>
+      </c>
+      <c r="Q11">
+        <v>1.01</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12">
+        <v>2.3</v>
+      </c>
+      <c r="G12">
+        <v>2.48</v>
+      </c>
+      <c r="H12">
+        <v>3.1</v>
+      </c>
+      <c r="I12">
+        <v>3.55</v>
+      </c>
+      <c r="J12">
+        <v>3.4</v>
+      </c>
+      <c r="K12">
+        <v>3.9</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2</v>
+      </c>
+      <c r="Q12">
+        <v>1.81</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13">
+        <v>1.35</v>
+      </c>
+      <c r="G13">
+        <v>1.36</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>11</v>
+      </c>
+      <c r="J13">
+        <v>5.5</v>
+      </c>
+      <c r="K13">
+        <v>6.4</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>3.2</v>
+      </c>
+      <c r="Q13">
+        <v>1.4</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14">
+        <v>4.1</v>
+      </c>
+      <c r="G14">
+        <v>4.5</v>
+      </c>
+      <c r="H14">
+        <v>1.84</v>
+      </c>
+      <c r="I14">
+        <v>1.96</v>
+      </c>
+      <c r="J14">
+        <v>4</v>
+      </c>
+      <c r="K14">
+        <v>4.5</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.25</v>
+      </c>
+      <c r="Q14">
+        <v>1.55</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15">
+        <v>2.22</v>
+      </c>
+      <c r="G15">
+        <v>2.52</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15">
+        <v>3.45</v>
+      </c>
+      <c r="J15">
+        <v>3.55</v>
+      </c>
+      <c r="K15">
+        <v>110</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.04</v>
+      </c>
+      <c r="N15">
+        <v>1.01</v>
+      </c>
+      <c r="O15">
+        <v>1.26</v>
+      </c>
+      <c r="P15">
+        <v>2</v>
+      </c>
+      <c r="Q15">
+        <v>1.78</v>
+      </c>
+      <c r="R15">
+        <v>1.37</v>
+      </c>
+      <c r="S15">
+        <v>2.96</v>
+      </c>
+      <c r="T15">
+        <v>1.01</v>
+      </c>
+      <c r="U15">
+        <v>1.01</v>
+      </c>
+      <c r="V15">
+        <v>1.44</v>
+      </c>
+      <c r="W15">
+        <v>1.66</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>1.01</v>
+      </c>
+      <c r="AR15">
+        <v>1.01</v>
+      </c>
+      <c r="AS15">
+        <v>1.01</v>
+      </c>
+      <c r="AT15">
+        <v>1.01</v>
+      </c>
+      <c r="AU15">
+        <v>1.01</v>
+      </c>
+      <c r="AV15">
+        <v>1.01</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>1.01</v>
+      </c>
+      <c r="AY15">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15">
+        <v>1.01</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
+        <v>1.01</v>
+      </c>
+      <c r="BC15">
+        <v>1.01</v>
+      </c>
+      <c r="BD15">
+        <v>1.01</v>
+      </c>
+      <c r="BE15">
+        <v>1.01</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16">
+        <v>2.92</v>
+      </c>
+      <c r="G16">
+        <v>4.1</v>
+      </c>
+      <c r="H16">
+        <v>1.95</v>
+      </c>
+      <c r="I16">
+        <v>2.52</v>
+      </c>
+      <c r="J16">
+        <v>3.65</v>
+      </c>
+      <c r="K16">
+        <v>7</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>2.88</v>
+      </c>
+      <c r="Q16">
+        <v>1.28</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17">
+        <v>2.72</v>
+      </c>
+      <c r="G17">
+        <v>2.82</v>
+      </c>
+      <c r="H17">
+        <v>2.54</v>
+      </c>
+      <c r="I17">
+        <v>2.58</v>
+      </c>
+      <c r="J17">
+        <v>3.95</v>
+      </c>
+      <c r="K17">
+        <v>4.2</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>2.6</v>
+      </c>
+      <c r="Q17">
+        <v>1.53</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.24</v>
+      </c>
+      <c r="Q18">
+        <v>1.01</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" t="s">
+        <v>155</v>
+      </c>
+      <c r="F19">
+        <v>1.92</v>
+      </c>
+      <c r="G19">
+        <v>2.56</v>
+      </c>
+      <c r="H19">
+        <v>2.92</v>
+      </c>
+      <c r="I19">
+        <v>4</v>
+      </c>
+      <c r="J19">
+        <v>2.9</v>
+      </c>
+      <c r="K19">
+        <v>9</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>2.42</v>
+      </c>
+      <c r="Q19">
+        <v>1.37</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20">
+        <v>3.55</v>
+      </c>
+      <c r="G20">
+        <v>4.6</v>
+      </c>
+      <c r="H20">
+        <v>1.88</v>
+      </c>
+      <c r="I20">
+        <v>2.12</v>
+      </c>
+      <c r="J20">
+        <v>3.2</v>
+      </c>
+      <c r="K20">
+        <v>5.4</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>2.46</v>
+      </c>
+      <c r="Q20">
+        <v>1.5</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21">
+        <v>1.11</v>
+      </c>
+      <c r="G21">
+        <v>110</v>
+      </c>
+      <c r="H21">
+        <v>1.11</v>
+      </c>
+      <c r="I21">
+        <v>1000</v>
+      </c>
+      <c r="J21">
+        <v>1.04</v>
+      </c>
+      <c r="K21">
+        <v>950</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.03</v>
+      </c>
+      <c r="N21">
+        <v>1.26</v>
+      </c>
+      <c r="O21">
+        <v>1.26</v>
+      </c>
+      <c r="P21">
+        <v>1.25</v>
+      </c>
+      <c r="Q21">
+        <v>1.26</v>
+      </c>
+      <c r="R21">
+        <v>1.18</v>
+      </c>
+      <c r="S21">
+        <v>1.26</v>
+      </c>
+      <c r="T21">
+        <v>1.01</v>
+      </c>
+      <c r="U21">
+        <v>1.01</v>
+      </c>
+      <c r="V21">
+        <v>1.01</v>
+      </c>
+      <c r="W21">
+        <v>1.1</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>1000</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>1000</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>13.5</v>
+      </c>
+      <c r="AQ21">
+        <v>16</v>
+      </c>
+      <c r="AR21">
+        <v>34</v>
+      </c>
+      <c r="AS21">
+        <v>40</v>
+      </c>
+      <c r="AT21">
+        <v>6.8</v>
+      </c>
+      <c r="AU21">
+        <v>7.8</v>
+      </c>
+      <c r="AV21">
+        <v>18.5</v>
+      </c>
+      <c r="AW21">
+        <v>40</v>
+      </c>
+      <c r="AX21">
+        <v>7.6</v>
+      </c>
+      <c r="AY21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ21">
+        <v>17</v>
+      </c>
+      <c r="BA21">
+        <v>40</v>
+      </c>
+      <c r="BB21">
+        <v>11</v>
+      </c>
+      <c r="BC21">
+        <v>12</v>
+      </c>
+      <c r="BD21">
+        <v>25</v>
+      </c>
+      <c r="BE21">
+        <v>40</v>
+      </c>
+      <c r="BF21">
+        <v>1.01</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.01</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.01</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>1.01</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.01</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.01</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.01</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.01</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" t="s">
+        <v>158</v>
+      </c>
+      <c r="F22">
+        <v>3.7</v>
+      </c>
+      <c r="G22">
+        <v>4.9</v>
+      </c>
+      <c r="H22">
+        <v>1.93</v>
+      </c>
+      <c r="I22">
+        <v>2.16</v>
+      </c>
+      <c r="J22">
+        <v>3.55</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>3.75</v>
+      </c>
+      <c r="O22">
+        <v>1.3</v>
+      </c>
+      <c r="P22">
+        <v>1.94</v>
+      </c>
+      <c r="Q22">
+        <v>1.84</v>
+      </c>
+      <c r="R22">
+        <v>1.34</v>
+      </c>
+      <c r="S22">
+        <v>3.1</v>
+      </c>
+      <c r="T22">
+        <v>1.01</v>
+      </c>
+      <c r="U22">
+        <v>1.01</v>
+      </c>
+      <c r="V22">
+        <v>1.86</v>
+      </c>
+      <c r="W22">
+        <v>1.26</v>
+      </c>
+      <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>1000</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22">
+        <v>1.01</v>
+      </c>
+      <c r="AR22">
+        <v>1.01</v>
+      </c>
+      <c r="AS22">
+        <v>1.01</v>
+      </c>
+      <c r="AT22">
+        <v>1.01</v>
+      </c>
+      <c r="AU22">
+        <v>1.01</v>
+      </c>
+      <c r="AV22">
+        <v>1.01</v>
+      </c>
+      <c r="AW22">
+        <v>1.01</v>
+      </c>
+      <c r="AX22">
+        <v>1.01</v>
+      </c>
+      <c r="AY22">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22">
+        <v>1.01</v>
+      </c>
+      <c r="BA22">
+        <v>1.01</v>
+      </c>
+      <c r="BB22">
+        <v>1.01</v>
+      </c>
+      <c r="BC22">
+        <v>1.01</v>
+      </c>
+      <c r="BD22">
+        <v>1.01</v>
+      </c>
+      <c r="BE22">
+        <v>1.01</v>
+      </c>
+      <c r="BF22">
+        <v>1.01</v>
+      </c>
+      <c r="BG22">
+        <v>1.01</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.01</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.01</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.01</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.01</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.01</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.01</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.01</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23">
+        <v>1.04</v>
+      </c>
+      <c r="G23">
+        <v>1000</v>
+      </c>
+      <c r="H23">
+        <v>1.04</v>
+      </c>
+      <c r="I23">
+        <v>1000</v>
+      </c>
+      <c r="J23">
+        <v>1.04</v>
+      </c>
+      <c r="K23">
+        <v>950</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1.24</v>
+      </c>
+      <c r="Q23">
+        <v>1.01</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24">
+        <v>2.72</v>
+      </c>
+      <c r="G24">
+        <v>3.3</v>
+      </c>
+      <c r="H24">
+        <v>2.62</v>
+      </c>
+      <c r="I24">
+        <v>3.15</v>
+      </c>
+      <c r="J24">
+        <v>2.62</v>
+      </c>
+      <c r="K24">
+        <v>4</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1.65</v>
+      </c>
+      <c r="Q24">
+        <v>2.16</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25">
+        <v>3.5</v>
+      </c>
+      <c r="G25">
+        <v>4.4</v>
+      </c>
+      <c r="H25">
+        <v>2.08</v>
+      </c>
+      <c r="I25">
+        <v>2.6</v>
+      </c>
+      <c r="J25">
+        <v>3.05</v>
+      </c>
+      <c r="K25">
+        <v>3.4</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.62</v>
+      </c>
+      <c r="Q25">
+        <v>2.26</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>1.24</v>
+      </c>
+      <c r="Q26">
+        <v>1.01</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27">
+        <v>1.85</v>
+      </c>
+      <c r="G27">
+        <v>2.08</v>
+      </c>
+      <c r="H27">
+        <v>4.6</v>
+      </c>
+      <c r="I27">
+        <v>5.2</v>
+      </c>
+      <c r="J27">
+        <v>3.3</v>
+      </c>
+      <c r="K27">
+        <v>4.9</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>1.68</v>
+      </c>
+      <c r="Q27">
+        <v>2.18</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <v>0</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+      <c r="BG27">
+        <v>0</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <v>0</v>
+      </c>
+      <c r="BK27">
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <v>0</v>
+      </c>
+      <c r="BN27">
+        <v>0</v>
+      </c>
+      <c r="BO27">
+        <v>0</v>
+      </c>
+      <c r="BP27">
+        <v>0</v>
+      </c>
+      <c r="BQ27">
+        <v>0</v>
+      </c>
+      <c r="BR27">
+        <v>0</v>
+      </c>
+      <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
+        <v>0</v>
+      </c>
+      <c r="BU27">
+        <v>0</v>
+      </c>
+      <c r="BV27">
+        <v>0</v>
+      </c>
+      <c r="BW27">
+        <v>0</v>
+      </c>
+      <c r="BX27">
+        <v>0</v>
+      </c>
+      <c r="BY27">
+        <v>0</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -508,7 +508,7 @@
     <t>CD Nacional Funchal</t>
   </si>
   <si>
-    <t>2026-08-08 01:34:43</t>
+    <t>2026-08-08 03:59:30</t>
   </si>
 </sst>
 </file>
@@ -1102,16 +1102,16 @@
         <v>138</v>
       </c>
       <c r="F2">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G2">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="H2">
         <v>4.5</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J2">
         <v>3.7</v>
@@ -1150,10 +1150,10 @@
         <v>1.89</v>
       </c>
       <c r="V2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1368,7 +1368,7 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="O3">
         <v>1.02</v>
@@ -1586,10 +1586,10 @@
         <v>140</v>
       </c>
       <c r="F4">
-        <v>1.06</v>
+        <v>2.06</v>
       </c>
       <c r="G4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H4">
         <v>2.56</v>
@@ -1598,10 +1598,10 @@
         <v>110</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>1.06</v>
       </c>
       <c r="K4">
-        <v>110</v>
+        <v>6.6</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1610,10 +1610,10 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="O4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P4">
         <v>1.25</v>
@@ -1634,7 +1634,7 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
         <v>1.4</v>
@@ -1828,40 +1828,40 @@
         <v>141</v>
       </c>
       <c r="F5">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H5">
+        <v>3.1</v>
+      </c>
+      <c r="I5">
+        <v>3.45</v>
+      </c>
+      <c r="J5">
         <v>3.05</v>
       </c>
-      <c r="I5">
-        <v>3.35</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
       <c r="K5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
         <v>3.2</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
         <v>1.28</v>
@@ -1870,16 +1870,16 @@
         <v>4</v>
       </c>
       <c r="T5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U5">
         <v>1.88</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W5">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X5">
         <v>12</v>
@@ -1918,10 +1918,10 @@
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL5">
         <v>55</v>
@@ -1957,7 +1957,7 @@
         <v>12</v>
       </c>
       <c r="AW5">
-        <v>34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX5">
         <v>13.5</v>
@@ -1978,7 +1978,7 @@
         <v>8.4</v>
       </c>
       <c r="BD5">
-        <v>34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE5">
         <v>10.5</v>
@@ -1987,7 +1987,7 @@
         <v>20</v>
       </c>
       <c r="BG5">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -3280,22 +3280,22 @@
         <v>147</v>
       </c>
       <c r="F11">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="G11">
-        <v>13</v>
+        <v>2.2</v>
       </c>
       <c r="H11">
-        <v>1.09</v>
+        <v>3.7</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J11">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3310,10 +3310,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>3.1</v>
       </c>
       <c r="I12">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J12">
         <v>3.4</v>
@@ -4248,22 +4248,22 @@
         <v>151</v>
       </c>
       <c r="F15">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G15">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H15">
         <v>3</v>
       </c>
       <c r="I15">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J15">
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>110</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4296,10 +4296,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4762,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q17">
         <v>1.53</v>
@@ -5228,10 +5228,10 @@
         <v>4</v>
       </c>
       <c r="J19">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="K19">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5700,22 +5700,22 @@
         <v>157</v>
       </c>
       <c r="F21">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="G21">
-        <v>110</v>
+        <v>1.86</v>
       </c>
       <c r="H21">
-        <v>1.11</v>
+        <v>5.8</v>
       </c>
       <c r="I21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J21">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="K21">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5724,22 +5724,22 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>1.26</v>
+        <v>1.87</v>
       </c>
       <c r="O21">
         <v>1.26</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="Q21">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="R21">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S21">
-        <v>1.26</v>
+        <v>2.56</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5748,10 +5748,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>2.14</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6184,22 +6184,22 @@
         <v>159</v>
       </c>
       <c r="F23">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G23">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H23">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I23">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J23">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6214,10 +6214,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q23">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6438,7 +6438,7 @@
         <v>3.15</v>
       </c>
       <c r="J24">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="K24">
         <v>4</v>
@@ -7152,10 +7152,10 @@
         <v>163</v>
       </c>
       <c r="F27">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G27">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H27">
         <v>4.6</v>
@@ -7164,10 +7164,10 @@
         <v>5.2</v>
       </c>
       <c r="J27">
-        <v>3.3</v>
+        <v>1.26</v>
       </c>
       <c r="K27">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="L27">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -508,7 +508,7 @@
     <t>CD Nacional Funchal</t>
   </si>
   <si>
-    <t>2026-08-08 03:59:30</t>
+    <t>2026-08-08 06:24:27</t>
   </si>
 </sst>
 </file>
@@ -1102,22 +1102,22 @@
         <v>138</v>
       </c>
       <c r="F2">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="G2">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>2.06</v>
       </c>
       <c r="I2">
-        <v>5.7</v>
+        <v>110</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>1.06</v>
       </c>
       <c r="K2">
-        <v>4.6</v>
+        <v>110</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1150,10 +1150,10 @@
         <v>1.89</v>
       </c>
       <c r="V2">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1350,7 +1350,7 @@
         <v>2.94</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>3.8</v>
@@ -1586,7 +1586,7 @@
         <v>140</v>
       </c>
       <c r="F4">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="G4">
         <v>3.5</v>
@@ -1598,10 +1598,10 @@
         <v>110</v>
       </c>
       <c r="J4">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="K4">
-        <v>6.6</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1634,7 +1634,7 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
         <v>1.4</v>
@@ -1831,7 +1831,7 @@
         <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H5">
         <v>3.1</v>
@@ -1840,7 +1840,7 @@
         <v>3.45</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
         <v>3.55</v>
@@ -1849,25 +1849,25 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O5">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T5">
         <v>1.75</v>
@@ -1945,7 +1945,7 @@
         <v>19</v>
       </c>
       <c r="AS5">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AT5">
         <v>8.199999999999999</v>
@@ -2312,40 +2312,40 @@
         <v>143</v>
       </c>
       <c r="F7">
+        <v>2.2</v>
+      </c>
+      <c r="G7">
+        <v>2.52</v>
+      </c>
+      <c r="H7">
+        <v>3.05</v>
+      </c>
+      <c r="I7">
+        <v>3.85</v>
+      </c>
+      <c r="J7">
+        <v>3.5</v>
+      </c>
+      <c r="K7">
+        <v>4.5</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>1.99</v>
       </c>
-      <c r="G7">
-        <v>2.76</v>
-      </c>
-      <c r="H7">
-        <v>2.68</v>
-      </c>
-      <c r="I7">
-        <v>4.1</v>
-      </c>
-      <c r="J7">
-        <v>2.52</v>
-      </c>
-      <c r="K7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>1.85</v>
-      </c>
       <c r="Q7">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -3280,13 +3280,13 @@
         <v>147</v>
       </c>
       <c r="F11">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G11">
         <v>2.2</v>
       </c>
       <c r="H11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I11">
         <v>4.8</v>
@@ -3295,7 +3295,7 @@
         <v>3.45</v>
       </c>
       <c r="K11">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3310,10 +3310,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q11">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>3.5</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
         <v>3.9</v>
@@ -3764,13 +3764,13 @@
         <v>149</v>
       </c>
       <c r="F13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="G13">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="H13">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I13">
         <v>11</v>
@@ -3794,10 +3794,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4012,13 +4012,13 @@
         <v>4.5</v>
       </c>
       <c r="H14">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="I14">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K14">
         <v>4.5</v>
@@ -4039,7 +4039,7 @@
         <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4257,13 +4257,13 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K15">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4272,7 +4272,7 @@
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="O15">
         <v>1.26</v>
@@ -4302,112 +4302,112 @@
         <v>1.67</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4735,7 +4735,7 @@
         <v>2.72</v>
       </c>
       <c r="G17">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H17">
         <v>2.54</v>
@@ -4744,7 +4744,7 @@
         <v>2.58</v>
       </c>
       <c r="J17">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K17">
         <v>4.2</v>
@@ -4762,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.64</v>
+        <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5222,7 +5222,7 @@
         <v>2.56</v>
       </c>
       <c r="H19">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="I19">
         <v>4</v>
@@ -5231,7 +5231,7 @@
         <v>3.65</v>
       </c>
       <c r="K19">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5458,13 +5458,13 @@
         <v>156</v>
       </c>
       <c r="F20">
-        <v>3.55</v>
+        <v>1.89</v>
       </c>
       <c r="G20">
         <v>4.6</v>
       </c>
       <c r="H20">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I20">
         <v>2.12</v>
@@ -5473,7 +5473,7 @@
         <v>3.2</v>
       </c>
       <c r="K20">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5700,7 +5700,7 @@
         <v>157</v>
       </c>
       <c r="F21">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="G21">
         <v>1.86</v>
@@ -5715,7 +5715,7 @@
         <v>3.25</v>
       </c>
       <c r="K21">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -6426,22 +6426,22 @@
         <v>160</v>
       </c>
       <c r="F24">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="G24">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H24">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I24">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="J24">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6456,10 +6456,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="Q24">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6668,22 +6668,22 @@
         <v>161</v>
       </c>
       <c r="F25">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="G25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H25">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="I25">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="J25">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K25">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6698,10 +6698,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q25">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>1.89</v>
       </c>
       <c r="G27">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="H27">
         <v>4.6</v>
@@ -7164,7 +7164,7 @@
         <v>5.2</v>
       </c>
       <c r="J27">
-        <v>1.26</v>
+        <v>3.45</v>
       </c>
       <c r="K27">
         <v>3.85</v>
@@ -7185,7 +7185,7 @@
         <v>1.68</v>
       </c>
       <c r="Q27">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R27">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -508,7 +508,7 @@
     <t>CD Nacional Funchal</t>
   </si>
   <si>
-    <t>2026-08-08 06:24:27</t>
+    <t>2026-08-08 08:48:13</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1114,7 @@
         <v>110</v>
       </c>
       <c r="J2">
-        <v>1.06</v>
+        <v>2.08</v>
       </c>
       <c r="K2">
         <v>110</v>
@@ -1368,7 +1368,7 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.68</v>
+        <v>1.53</v>
       </c>
       <c r="O3">
         <v>1.02</v>
@@ -1586,22 +1586,22 @@
         <v>140</v>
       </c>
       <c r="F4">
-        <v>1.98</v>
+        <v>2.64</v>
       </c>
       <c r="G4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>1.43</v>
+        <v>2.68</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1610,13 +1610,13 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="O4">
         <v>1.51</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
         <v>2.56</v>
@@ -1634,10 +1634,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -1828,7 +1828,7 @@
         <v>141</v>
       </c>
       <c r="F5">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G5">
         <v>2.62</v>
@@ -1837,19 +1837,19 @@
         <v>3.1</v>
       </c>
       <c r="I5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J5">
         <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
         <v>3.15</v>
@@ -1858,10 +1858,10 @@
         <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
         <v>1.13</v>
@@ -1870,16 +1870,16 @@
         <v>3.4</v>
       </c>
       <c r="T5">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X5">
         <v>12</v>
@@ -2318,7 +2318,7 @@
         <v>2.52</v>
       </c>
       <c r="H7">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="I7">
         <v>3.85</v>
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q7">
         <v>1.7</v>
@@ -3280,13 +3280,13 @@
         <v>147</v>
       </c>
       <c r="F11">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G11">
         <v>2.2</v>
       </c>
       <c r="H11">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I11">
         <v>4.8</v>
@@ -3295,7 +3295,7 @@
         <v>3.45</v>
       </c>
       <c r="K11">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="Q11">
         <v>2.06</v>
@@ -3794,10 +3794,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q13">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4006,7 +4006,7 @@
         <v>150</v>
       </c>
       <c r="F14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G14">
         <v>4.5</v>
@@ -4039,7 +4039,7 @@
         <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4248,7 +4248,7 @@
         <v>151</v>
       </c>
       <c r="F15">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G15">
         <v>2.5</v>
@@ -4263,7 +4263,7 @@
         <v>3.3</v>
       </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4732,10 +4732,10 @@
         <v>153</v>
       </c>
       <c r="F17">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="G17">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H17">
         <v>2.54</v>
@@ -4747,7 +4747,7 @@
         <v>3.9</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -5222,7 +5222,7 @@
         <v>2.56</v>
       </c>
       <c r="H19">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="I19">
         <v>4</v>
@@ -5231,7 +5231,7 @@
         <v>3.65</v>
       </c>
       <c r="K19">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5458,19 +5458,19 @@
         <v>156</v>
       </c>
       <c r="F20">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="G20">
         <v>4.6</v>
       </c>
       <c r="H20">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I20">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="J20">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K20">
         <v>5.2</v>
@@ -5700,22 +5700,22 @@
         <v>157</v>
       </c>
       <c r="F21">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="G21">
         <v>1.86</v>
       </c>
       <c r="H21">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="J21">
         <v>3.25</v>
       </c>
       <c r="K21">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5724,7 +5724,7 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>1.87</v>
+        <v>3.9</v>
       </c>
       <c r="O21">
         <v>1.26</v>
@@ -5748,7 +5748,7 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="W21">
         <v>2.14</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -508,7 +508,7 @@
     <t>CD Nacional Funchal</t>
   </si>
   <si>
-    <t>2026-08-08 08:48:13</t>
+    <t>2026-08-08 11:10:43</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1105,7 @@
         <v>1.04</v>
       </c>
       <c r="G2">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H2">
         <v>2.06</v>
@@ -1114,7 +1114,7 @@
         <v>110</v>
       </c>
       <c r="J2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="K2">
         <v>110</v>
@@ -1132,7 +1132,7 @@
         <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q2">
         <v>1.3</v>
@@ -1153,7 +1153,7 @@
         <v>1.01</v>
       </c>
       <c r="W2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1356,7 +1356,7 @@
         <v>3.8</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="K3">
         <v>3.75</v>
@@ -1383,7 +1383,7 @@
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1586,10 +1586,10 @@
         <v>140</v>
       </c>
       <c r="F4">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G4">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="H4">
         <v>2.52</v>
@@ -1598,25 +1598,25 @@
         <v>3</v>
       </c>
       <c r="J4">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M4">
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="O4">
         <v>1.51</v>
       </c>
       <c r="P4">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
         <v>2.56</v>
@@ -1625,7 +1625,7 @@
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>2.56</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1640,7 +1640,7 @@
         <v>1.42</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
         <v>1000</v>
@@ -1697,55 +1697,55 @@
         <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="AR4">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="AS4">
-        <v>1.1</v>
+        <v>26</v>
       </c>
       <c r="AT4">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="AV4">
-        <v>1.1</v>
+        <v>9.6</v>
       </c>
       <c r="AW4">
-        <v>1.1</v>
+        <v>26</v>
       </c>
       <c r="AX4">
-        <v>1.1</v>
+        <v>14</v>
       </c>
       <c r="AY4">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>1.1</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>1.1</v>
+        <v>40</v>
       </c>
       <c r="BB4">
-        <v>1.1</v>
+        <v>36</v>
       </c>
       <c r="BC4">
-        <v>1.1</v>
+        <v>29</v>
       </c>
       <c r="BD4">
-        <v>1.1</v>
+        <v>40</v>
       </c>
       <c r="BE4">
-        <v>1.1</v>
+        <v>40</v>
       </c>
       <c r="BF4">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1828,7 +1828,7 @@
         <v>141</v>
       </c>
       <c r="F5">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G5">
         <v>2.62</v>
@@ -1843,7 +1843,7 @@
         <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1876,7 +1876,7 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W5">
         <v>1.61</v>
@@ -2070,226 +2070,226 @@
         <v>142</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H6">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>330</v>
+        <v>3.55</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>164</v>
@@ -2312,22 +2312,22 @@
         <v>143</v>
       </c>
       <c r="F7">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="G7">
+        <v>2.76</v>
+      </c>
+      <c r="H7">
+        <v>2.64</v>
+      </c>
+      <c r="I7">
+        <v>4.1</v>
+      </c>
+      <c r="J7">
         <v>2.52</v>
       </c>
-      <c r="H7">
-        <v>2.78</v>
-      </c>
-      <c r="I7">
-        <v>3.85</v>
-      </c>
-      <c r="J7">
-        <v>3.5</v>
-      </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2342,10 +2342,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -3280,13 +3280,13 @@
         <v>147</v>
       </c>
       <c r="F11">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G11">
         <v>2.2</v>
       </c>
       <c r="H11">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I11">
         <v>4.8</v>
@@ -3295,7 +3295,7 @@
         <v>3.45</v>
       </c>
       <c r="K11">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Q11">
         <v>2.06</v>
@@ -3767,10 +3767,10 @@
         <v>1.33</v>
       </c>
       <c r="G13">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H13">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I13">
         <v>11</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4248,19 +4248,19 @@
         <v>151</v>
       </c>
       <c r="F15">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G15">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I15">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K15">
         <v>4.4</v>
@@ -4296,118 +4296,118 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -5458,13 +5458,13 @@
         <v>156</v>
       </c>
       <c r="F20">
-        <v>3.5</v>
+        <v>1.86</v>
       </c>
       <c r="G20">
         <v>4.6</v>
       </c>
       <c r="H20">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="I20">
         <v>2.16</v>
@@ -5473,7 +5473,7 @@
         <v>3.3</v>
       </c>
       <c r="K20">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5700,7 +5700,7 @@
         <v>157</v>
       </c>
       <c r="F21">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G21">
         <v>1.86</v>
@@ -5709,13 +5709,13 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="J21">
         <v>3.25</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5727,7 +5727,7 @@
         <v>3.9</v>
       </c>
       <c r="O21">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P21">
         <v>1.87</v>
@@ -5748,7 +5748,7 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="W21">
         <v>2.14</v>
@@ -5808,10 +5808,10 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR21">
         <v>34</v>
@@ -5820,13 +5820,13 @@
         <v>40</v>
       </c>
       <c r="AT21">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU21">
         <v>7.8</v>
       </c>
       <c r="AV21">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW21">
         <v>40</v>
@@ -5844,13 +5844,13 @@
         <v>40</v>
       </c>
       <c r="BB21">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD21">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE21">
         <v>40</v>
@@ -5942,22 +5942,22 @@
         <v>158</v>
       </c>
       <c r="F22">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G22">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H22">
         <v>1.93</v>
       </c>
       <c r="I22">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="J22">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K22">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -5966,22 +5966,22 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O22">
         <v>1.3</v>
       </c>
       <c r="P22">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="Q22">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="R22">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S22">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -5990,7 +5990,7 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W22">
         <v>1.26</v>
@@ -6184,7 +6184,7 @@
         <v>159</v>
       </c>
       <c r="F23">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="G23">
         <v>2.42</v>
@@ -6193,13 +6193,13 @@
         <v>3.25</v>
       </c>
       <c r="I23">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J23">
         <v>3.35</v>
       </c>
       <c r="K23">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6429,7 +6429,7 @@
         <v>2.8</v>
       </c>
       <c r="G24">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H24">
         <v>2.64</v>
@@ -6456,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="Q24">
         <v>2.18</v>
@@ -7152,7 +7152,7 @@
         <v>163</v>
       </c>
       <c r="F27">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="G27">
         <v>2.02</v>
@@ -7161,13 +7161,13 @@
         <v>4.6</v>
       </c>
       <c r="I27">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="J27">
         <v>3.45</v>
       </c>
       <c r="K27">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L27">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -508,7 +508,7 @@
     <t>CD Nacional Funchal</t>
   </si>
   <si>
-    <t>2026-08-08 11:10:43</t>
+    <t>2026-08-08 13:31:52</t>
   </si>
 </sst>
 </file>
@@ -1102,166 +1102,166 @@
         <v>138</v>
       </c>
       <c r="F2">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="G2">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H2">
-        <v>2.06</v>
+        <v>4.6</v>
       </c>
       <c r="I2">
-        <v>110</v>
+        <v>5.2</v>
       </c>
       <c r="J2">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
-        <v>110</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
-        <v>1.3</v>
+        <v>1.89</v>
       </c>
       <c r="R2">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S2">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W2">
         <v>2.06</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
+        <v>7.4</v>
+      </c>
+      <c r="AV2">
+        <v>14.5</v>
+      </c>
+      <c r="AW2">
         <v>6.8</v>
       </c>
-      <c r="AV2">
-        <v>1.01</v>
-      </c>
-      <c r="AW2">
-        <v>1.01</v>
-      </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ2">
+        <v>16</v>
+      </c>
+      <c r="BA2">
+        <v>6.8</v>
+      </c>
+      <c r="BB2">
         <v>15.5</v>
       </c>
-      <c r="BA2">
-        <v>1.01</v>
-      </c>
-      <c r="BB2">
-        <v>1.01</v>
-      </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1344,7 +1344,7 @@
         <v>139</v>
       </c>
       <c r="F3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G3">
         <v>2.94</v>
@@ -1356,34 +1356,34 @@
         <v>3.8</v>
       </c>
       <c r="J3">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O3">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1586,28 +1586,28 @@
         <v>140</v>
       </c>
       <c r="F4">
+        <v>1.92</v>
+      </c>
+      <c r="G4">
+        <v>3.25</v>
+      </c>
+      <c r="H4">
         <v>2.68</v>
       </c>
-      <c r="G4">
-        <v>3.8</v>
-      </c>
-      <c r="H4">
-        <v>2.52</v>
-      </c>
       <c r="I4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J4">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>110</v>
       </c>
       <c r="L4">
         <v>1.53</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
         <v>1.25</v>
@@ -1634,10 +1634,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1831,55 +1831,55 @@
         <v>2.46</v>
       </c>
       <c r="G5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I5">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J5">
         <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V5">
         <v>1.41</v>
       </c>
       <c r="W5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X5">
         <v>12</v>
@@ -1894,10 +1894,10 @@
         <v>65</v>
       </c>
       <c r="AB5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5">
         <v>14</v>
@@ -1918,7 +1918,7 @@
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK5">
         <v>30</v>
@@ -1945,7 +1945,7 @@
         <v>19</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT5">
         <v>8.199999999999999</v>
@@ -1957,7 +1957,7 @@
         <v>12</v>
       </c>
       <c r="AW5">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="AX5">
         <v>13.5</v>
@@ -1975,19 +1975,19 @@
         <v>26</v>
       </c>
       <c r="BC5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF5">
         <v>20</v>
       </c>
       <c r="BG5">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2076,10 +2076,10 @@
         <v>2.24</v>
       </c>
       <c r="H6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -2094,13 +2094,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.74</v>
+        <v>1.19</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="Q6">
         <v>2.24</v>
@@ -2118,7 +2118,7 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W6">
         <v>1.8</v>
@@ -2312,7 +2312,7 @@
         <v>143</v>
       </c>
       <c r="F7">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="G7">
         <v>2.76</v>
@@ -2324,214 +2324,214 @@
         <v>4.1</v>
       </c>
       <c r="J7">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="K7">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
         <v>2</v>
       </c>
       <c r="Q7">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>164</v>
@@ -2554,226 +2554,226 @@
         <v>144</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="K8">
-        <v>330</v>
+        <v>3.2</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P8">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
         <v>164</v>
@@ -2796,13 +2796,13 @@
         <v>145</v>
       </c>
       <c r="F9">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G9">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H9">
-        <v>2.98</v>
+        <v>1.08</v>
       </c>
       <c r="I9">
         <v>4.3</v>
@@ -2811,19 +2811,19 @@
         <v>3.2</v>
       </c>
       <c r="K9">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P9">
         <v>1.7</v>
@@ -2832,190 +2832,190 @@
         <v>1.87</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
         <v>164</v>
@@ -3038,220 +3038,220 @@
         <v>146</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J10">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K10">
-        <v>330</v>
+        <v>9.6</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3295,211 +3295,211 @@
         <v>3.45</v>
       </c>
       <c r="K11">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P11">
         <v>1.7</v>
       </c>
       <c r="Q11">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>164</v>
@@ -3767,7 +3767,7 @@
         <v>1.33</v>
       </c>
       <c r="G13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H13">
         <v>9.800000000000001</v>
@@ -3797,7 +3797,7 @@
         <v>3.15</v>
       </c>
       <c r="Q13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4248,166 +4248,166 @@
         <v>151</v>
       </c>
       <c r="F15">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G15">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H15">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J15">
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N15">
-        <v>2.36</v>
+        <v>3.95</v>
       </c>
       <c r="O15">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P15">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q15">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R15">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S15">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V15">
         <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4490,22 +4490,22 @@
         <v>152</v>
       </c>
       <c r="F16">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="G16">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="H16">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="I16">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="J16">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4520,10 +4520,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="Q16">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4762,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.25</v>
+        <v>2.64</v>
       </c>
       <c r="Q17">
         <v>1.52</v>
@@ -5222,7 +5222,7 @@
         <v>2.56</v>
       </c>
       <c r="H19">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="I19">
         <v>4</v>
@@ -5231,7 +5231,7 @@
         <v>3.65</v>
       </c>
       <c r="K19">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5464,7 +5464,7 @@
         <v>4.6</v>
       </c>
       <c r="H20">
-        <v>1.94</v>
+        <v>1.27</v>
       </c>
       <c r="I20">
         <v>2.16</v>
@@ -5700,7 +5700,7 @@
         <v>157</v>
       </c>
       <c r="F21">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G21">
         <v>1.86</v>
@@ -5715,7 +5715,7 @@
         <v>3.25</v>
       </c>
       <c r="K21">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5730,10 +5730,10 @@
         <v>1.25</v>
       </c>
       <c r="P21">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q21">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R21">
         <v>1.35</v>
@@ -5942,166 +5942,166 @@
         <v>158</v>
       </c>
       <c r="F22">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G22">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H22">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="I22">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J22">
         <v>3.45</v>
       </c>
       <c r="K22">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N22">
         <v>3.5</v>
       </c>
       <c r="O22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P22">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q22">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="R22">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S22">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T22">
         <v>1.01</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V22">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W22">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6184,22 +6184,22 @@
         <v>159</v>
       </c>
       <c r="F23">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="H23">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="I23">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="J23">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K23">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6214,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q23">
         <v>1.8</v>
@@ -6429,16 +6429,16 @@
         <v>2.8</v>
       </c>
       <c r="G24">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="H24">
         <v>2.64</v>
       </c>
       <c r="I24">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="J24">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K24">
         <v>3.8</v>
@@ -6668,22 +6668,22 @@
         <v>161</v>
       </c>
       <c r="F25">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="G25">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="H25">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="I25">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="J25">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K25">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6698,10 +6698,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q25">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7152,22 +7152,22 @@
         <v>163</v>
       </c>
       <c r="F27">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="G27">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I27">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J27">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K27">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L27">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="168">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Slovakian 2 Liga</t>
   </si>
   <si>
+    <t>Slovenian Premier League</t>
+  </si>
+  <si>
     <t>Romanian Liga I</t>
   </si>
   <si>
@@ -370,6 +373,9 @@
     <t>MSK Povazska Bystrica</t>
   </si>
   <si>
+    <t>Mura</t>
+  </si>
+  <si>
     <t>Karpaty</t>
   </si>
   <si>
@@ -448,6 +454,9 @@
     <t>Zlate Moravce</t>
   </si>
   <si>
+    <t>NK Radomlje</t>
+  </si>
+  <si>
     <t>LNZ-Lebedyn</t>
   </si>
   <si>
@@ -508,7 +517,7 @@
     <t>CD Nacional Funchal</t>
   </si>
   <si>
-    <t>2026-08-08 13:31:52</t>
+    <t>2026-08-08 15:51:59</t>
   </si>
 </sst>
 </file>
@@ -840,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB27"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1090,34 +1099,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F2">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="H2">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1141,7 +1150,7 @@
         <v>1.37</v>
       </c>
       <c r="S2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
         <v>1.8</v>
@@ -1150,34 +1159,34 @@
         <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB2">
         <v>9.6</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF2">
         <v>12.5</v>
@@ -1186,7 +1195,7 @@
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI2">
         <v>70</v>
@@ -1198,16 +1207,16 @@
         <v>21</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN2">
         <v>13</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP2">
         <v>11.5</v>
@@ -1216,10 +1225,10 @@
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS2">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
@@ -1231,19 +1240,19 @@
         <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
         <v>9</v>
       </c>
       <c r="AY2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ2">
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
         <v>15.5</v>
@@ -1252,16 +1261,16 @@
         <v>15</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE2">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2">
         <v>9.4</v>
       </c>
       <c r="BG2">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1324,7 +1333,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1332,28 +1341,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F3">
         <v>2.5</v>
       </c>
       <c r="G3">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J3">
         <v>2.9</v>
@@ -1365,25 +1374,25 @@
         <v>1.42</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="O3">
         <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1392,10 +1401,10 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1566,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1574,178 +1583,178 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F4">
-        <v>1.92</v>
+        <v>2.82</v>
       </c>
       <c r="G4">
         <v>3.25</v>
       </c>
       <c r="H4">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="I4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J4">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="K4">
-        <v>110</v>
+        <v>3.3</v>
       </c>
       <c r="L4">
         <v>1.53</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="O4">
+        <v>1.53</v>
+      </c>
+      <c r="P4">
         <v>1.51</v>
       </c>
-      <c r="P4">
-        <v>1.25</v>
-      </c>
       <c r="Q4">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>2.56</v>
+        <v>5.3</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V4">
         <v>1.48</v>
       </c>
       <c r="W4">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4">
+        <v>7.2</v>
+      </c>
+      <c r="AR4">
+        <v>15</v>
+      </c>
+      <c r="AS4">
+        <v>5.8</v>
+      </c>
+      <c r="AT4">
+        <v>7.4</v>
+      </c>
+      <c r="AU4">
         <v>6.2</v>
       </c>
-      <c r="AR4">
-        <v>10</v>
-      </c>
-      <c r="AS4">
-        <v>26</v>
-      </c>
-      <c r="AT4">
-        <v>7.2</v>
-      </c>
-      <c r="AU4">
+      <c r="AV4">
+        <v>11.5</v>
+      </c>
+      <c r="AW4">
+        <v>5.7</v>
+      </c>
+      <c r="AX4">
+        <v>15.5</v>
+      </c>
+      <c r="AY4">
+        <v>12</v>
+      </c>
+      <c r="AZ4">
+        <v>19.5</v>
+      </c>
+      <c r="BA4">
+        <v>5.9</v>
+      </c>
+      <c r="BB4">
         <v>5.8</v>
       </c>
-      <c r="AV4">
-        <v>9.6</v>
-      </c>
-      <c r="AW4">
-        <v>26</v>
-      </c>
-      <c r="AX4">
-        <v>14</v>
-      </c>
-      <c r="AY4">
-        <v>11</v>
-      </c>
-      <c r="AZ4">
-        <v>18</v>
-      </c>
-      <c r="BA4">
-        <v>40</v>
-      </c>
-      <c r="BB4">
-        <v>36</v>
-      </c>
       <c r="BC4">
-        <v>29</v>
+        <v>5.7</v>
       </c>
       <c r="BD4">
-        <v>40</v>
+        <v>5.9</v>
       </c>
       <c r="BE4">
-        <v>40</v>
+        <v>6.2</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1808,7 +1817,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1816,16 +1825,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F5">
         <v>2.46</v>
@@ -1834,7 +1843,7 @@
         <v>2.6</v>
       </c>
       <c r="H5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
         <v>3.4</v>
@@ -1885,7 +1894,7 @@
         <v>12</v>
       </c>
       <c r="Y5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z5">
         <v>22</v>
@@ -1945,7 +1954,7 @@
         <v>19</v>
       </c>
       <c r="AS5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT5">
         <v>8.199999999999999</v>
@@ -1975,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="BC5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF5">
         <v>20</v>
@@ -2050,7 +2059,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2058,58 +2067,58 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F6">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G6">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="H6">
         <v>3.7</v>
       </c>
       <c r="I6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="K6">
         <v>3.55</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="O6">
         <v>1.02</v>
       </c>
       <c r="P6">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Q6">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2121,7 +2130,7 @@
         <v>1.21</v>
       </c>
       <c r="W6">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2292,7 +2301,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2300,16 +2309,16 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F7">
         <v>2.16</v>
@@ -2336,22 +2345,22 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O7">
         <v>1.01</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="R7">
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2534,186 +2543,186 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F8">
-        <v>2.9</v>
+        <v>1.83</v>
       </c>
       <c r="G8">
-        <v>3.4</v>
+        <v>2.18</v>
       </c>
       <c r="H8">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="I8">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="J8">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="K8">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>2.28</v>
+        <v>3.55</v>
       </c>
       <c r="O8">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="P8">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="Q8">
-        <v>2.62</v>
+        <v>1.46</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S8">
-        <v>5.5</v>
+        <v>2.48</v>
       </c>
       <c r="T8">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="X8">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>150</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2770,192 +2779,192 @@
         <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
         <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F9">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="G9">
+        <v>3.5</v>
+      </c>
+      <c r="H9">
         <v>2.64</v>
       </c>
-      <c r="H9">
-        <v>1.08</v>
-      </c>
       <c r="I9">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L9">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="P9">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="Q9">
-        <v>1.87</v>
+        <v>2.76</v>
       </c>
       <c r="R9">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP9">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AR9">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AS9">
         <v>38</v>
       </c>
       <c r="AT9">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU9">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AV9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AX9">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BA9">
+        <v>55</v>
+      </c>
+      <c r="BB9">
+        <v>44</v>
+      </c>
+      <c r="BC9">
         <v>36</v>
       </c>
-      <c r="BB9">
-        <v>23</v>
-      </c>
-      <c r="BC9">
-        <v>19</v>
-      </c>
       <c r="BD9">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BE9">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3018,7 +3027,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3026,172 +3035,172 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
         <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F10">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="H10">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="J10">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="K10">
+        <v>4.7</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.06</v>
+      </c>
+      <c r="N10">
+        <v>1.7</v>
+      </c>
+      <c r="O10">
+        <v>1.34</v>
+      </c>
+      <c r="P10">
+        <v>1.7</v>
+      </c>
+      <c r="Q10">
+        <v>1.87</v>
+      </c>
+      <c r="R10">
+        <v>1.24</v>
+      </c>
+      <c r="S10">
+        <v>3.2</v>
+      </c>
+      <c r="T10">
+        <v>1.01</v>
+      </c>
+      <c r="U10">
+        <v>1.01</v>
+      </c>
+      <c r="V10">
+        <v>1.32</v>
+      </c>
+      <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
         <v>9.6</v>
       </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>1.87</v>
-      </c>
-      <c r="O10">
-        <v>1.22</v>
-      </c>
-      <c r="P10">
-        <v>1.87</v>
-      </c>
-      <c r="Q10">
-        <v>1.62</v>
-      </c>
-      <c r="R10">
-        <v>1.33</v>
-      </c>
-      <c r="S10">
-        <v>2.5</v>
-      </c>
-      <c r="T10">
-        <v>1.01</v>
-      </c>
-      <c r="U10">
-        <v>1.01</v>
-      </c>
-      <c r="V10">
-        <v>1.1</v>
-      </c>
-      <c r="W10">
-        <v>2</v>
-      </c>
-      <c r="X10">
-        <v>1000</v>
-      </c>
-      <c r="Y10">
-        <v>1000</v>
-      </c>
-      <c r="Z10">
-        <v>1000</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>1000</v>
-      </c>
-      <c r="AC10">
-        <v>1000</v>
-      </c>
-      <c r="AD10">
-        <v>1000</v>
-      </c>
-      <c r="AE10">
-        <v>1000</v>
-      </c>
-      <c r="AF10">
-        <v>1000</v>
-      </c>
-      <c r="AG10">
-        <v>1000</v>
-      </c>
-      <c r="AH10">
-        <v>1000</v>
-      </c>
-      <c r="AI10">
-        <v>1000</v>
-      </c>
-      <c r="AJ10">
-        <v>1000</v>
-      </c>
-      <c r="AK10">
-        <v>1000</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>1000</v>
-      </c>
-      <c r="AO10">
-        <v>1000</v>
-      </c>
-      <c r="AP10">
-        <v>1.01</v>
-      </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3200,10 +3209,10 @@
         <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
@@ -3254,13 +3263,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3268,58 +3277,58 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
         <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F11">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="G11">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I11">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="J11">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="L11">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="P11">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Q11">
-        <v>2.14</v>
+        <v>1.62</v>
       </c>
       <c r="R11">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="S11">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3328,10 +3337,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="W11">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3388,52 +3397,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3496,13 +3505,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3510,241 +3519,241 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
         <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F12">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="G12">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="H12">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="I12">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K12">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Q12">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3752,483 +3761,483 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F13">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="G13">
+        <v>2.48</v>
+      </c>
+      <c r="H13">
+        <v>3.1</v>
+      </c>
+      <c r="I13">
+        <v>3.5</v>
+      </c>
+      <c r="J13">
+        <v>3.5</v>
+      </c>
+      <c r="K13">
+        <v>3.9</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.06</v>
+      </c>
+      <c r="N13">
+        <v>3.95</v>
+      </c>
+      <c r="O13">
+        <v>1.27</v>
+      </c>
+      <c r="P13">
+        <v>2</v>
+      </c>
+      <c r="Q13">
+        <v>1.81</v>
+      </c>
+      <c r="R13">
         <v>1.39</v>
       </c>
-      <c r="H13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I13">
-        <v>11</v>
-      </c>
-      <c r="J13">
-        <v>5.5</v>
-      </c>
-      <c r="K13">
-        <v>6.4</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>3.15</v>
-      </c>
-      <c r="Q13">
-        <v>1.41</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CB13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F14">
-        <v>4.2</v>
+        <v>1.34</v>
       </c>
       <c r="G14">
-        <v>4.5</v>
+        <v>1.37</v>
       </c>
       <c r="H14">
-        <v>1.81</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I14">
-        <v>1.92</v>
+        <v>11</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="K14">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P14">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q14">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4236,31 +4245,31 @@
         <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F15">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="G15">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="I15">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <v>4.5</v>
@@ -4269,145 +4278,145 @@
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="O15">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P15">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q15">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="R15">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="S15">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="T15">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="U15">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="W15">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="X15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Y15">
+        <v>14</v>
+      </c>
+      <c r="Z15">
         <v>15</v>
       </c>
-      <c r="Z15">
+      <c r="AA15">
+        <v>23</v>
+      </c>
+      <c r="AB15">
+        <v>24</v>
+      </c>
+      <c r="AC15">
+        <v>11</v>
+      </c>
+      <c r="AD15">
+        <v>11.5</v>
+      </c>
+      <c r="AE15">
+        <v>18.5</v>
+      </c>
+      <c r="AF15">
+        <v>38</v>
+      </c>
+      <c r="AG15">
+        <v>19</v>
+      </c>
+      <c r="AH15">
+        <v>16.5</v>
+      </c>
+      <c r="AI15">
+        <v>27</v>
+      </c>
+      <c r="AJ15">
+        <v>85</v>
+      </c>
+      <c r="AK15">
+        <v>46</v>
+      </c>
+      <c r="AL15">
+        <v>46</v>
+      </c>
+      <c r="AM15">
+        <v>65</v>
+      </c>
+      <c r="AN15">
+        <v>34</v>
+      </c>
+      <c r="AO15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP15">
+        <v>20</v>
+      </c>
+      <c r="AQ15">
+        <v>11</v>
+      </c>
+      <c r="AR15">
+        <v>12</v>
+      </c>
+      <c r="AS15">
+        <v>18.5</v>
+      </c>
+      <c r="AT15">
+        <v>19</v>
+      </c>
+      <c r="AU15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW15">
+        <v>14.5</v>
+      </c>
+      <c r="AX15">
+        <v>25</v>
+      </c>
+      <c r="AY15">
+        <v>15</v>
+      </c>
+      <c r="AZ15">
+        <v>13</v>
+      </c>
+      <c r="BA15">
+        <v>6.6</v>
+      </c>
+      <c r="BB15">
+        <v>7.8</v>
+      </c>
+      <c r="BC15">
         <v>29</v>
       </c>
-      <c r="AA15">
-        <v>70</v>
-      </c>
-      <c r="AB15">
-        <v>14</v>
-      </c>
-      <c r="AC15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD15">
-        <v>15</v>
-      </c>
-      <c r="AE15">
-        <v>44</v>
-      </c>
-      <c r="AF15">
-        <v>17.5</v>
-      </c>
-      <c r="AG15">
-        <v>14</v>
-      </c>
-      <c r="AH15">
-        <v>19.5</v>
-      </c>
-      <c r="AI15">
-        <v>55</v>
-      </c>
-      <c r="AJ15">
-        <v>40</v>
-      </c>
-      <c r="AK15">
-        <v>30</v>
-      </c>
-      <c r="AL15">
-        <v>44</v>
-      </c>
-      <c r="AM15">
-        <v>100</v>
-      </c>
-      <c r="AN15">
-        <v>18</v>
-      </c>
-      <c r="AO15">
-        <v>40</v>
-      </c>
-      <c r="AP15">
-        <v>12</v>
-      </c>
-      <c r="AQ15">
-        <v>10.5</v>
-      </c>
-      <c r="AR15">
-        <v>20</v>
-      </c>
-      <c r="AS15">
-        <v>38</v>
-      </c>
-      <c r="AT15">
-        <v>9.6</v>
-      </c>
-      <c r="AU15">
-        <v>6.2</v>
-      </c>
-      <c r="AV15">
-        <v>11.5</v>
-      </c>
-      <c r="AW15">
-        <v>25</v>
-      </c>
-      <c r="AX15">
-        <v>12</v>
-      </c>
-      <c r="AY15">
-        <v>9.6</v>
-      </c>
-      <c r="AZ15">
-        <v>11.5</v>
-      </c>
-      <c r="BA15">
-        <v>32</v>
-      </c>
-      <c r="BB15">
-        <v>22</v>
-      </c>
-      <c r="BC15">
-        <v>20</v>
-      </c>
       <c r="BD15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BE15">
-        <v>55</v>
+        <v>7.6</v>
       </c>
       <c r="BF15">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BG15">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4464,13 +4473,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4478,232 +4487,232 @@
         <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F16">
-        <v>2.98</v>
+        <v>2.24</v>
       </c>
       <c r="G16">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="H16">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="J16">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P16">
-        <v>3.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q16">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4712,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4720,716 +4729,716 @@
         <v>93</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F17">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="G17">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="H17">
-        <v>2.54</v>
+        <v>2.08</v>
       </c>
       <c r="I17">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P17">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E18" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P18">
-        <v>1.24</v>
+        <v>2.64</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
         <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F19">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="G19">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="H19">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="I19">
+        <v>3.9</v>
+      </c>
+      <c r="J19">
+        <v>2.88</v>
+      </c>
+      <c r="K19">
+        <v>4.5</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.06</v>
+      </c>
+      <c r="N19">
+        <v>3.4</v>
+      </c>
+      <c r="O19">
+        <v>1.34</v>
+      </c>
+      <c r="P19">
+        <v>1.69</v>
+      </c>
+      <c r="Q19">
+        <v>1.86</v>
+      </c>
+      <c r="R19">
+        <v>1.25</v>
+      </c>
+      <c r="S19">
+        <v>3.15</v>
+      </c>
+      <c r="T19">
+        <v>1.01</v>
+      </c>
+      <c r="U19">
+        <v>1.01</v>
+      </c>
+      <c r="V19">
+        <v>1.34</v>
+      </c>
+      <c r="W19">
+        <v>1.46</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>1000</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.01</v>
+      </c>
+      <c r="AQ19">
+        <v>1.01</v>
+      </c>
+      <c r="AR19">
+        <v>1.01</v>
+      </c>
+      <c r="AS19">
+        <v>1.01</v>
+      </c>
+      <c r="AT19">
+        <v>1.01</v>
+      </c>
+      <c r="AU19">
+        <v>1.01</v>
+      </c>
+      <c r="AV19">
+        <v>1.01</v>
+      </c>
+      <c r="AW19">
+        <v>1.01</v>
+      </c>
+      <c r="AX19">
+        <v>1.01</v>
+      </c>
+      <c r="AY19">
+        <v>1.01</v>
+      </c>
+      <c r="AZ19">
+        <v>1.01</v>
+      </c>
+      <c r="BA19">
+        <v>1.01</v>
+      </c>
+      <c r="BB19">
+        <v>1.01</v>
+      </c>
+      <c r="BC19">
+        <v>1.01</v>
+      </c>
+      <c r="BD19">
+        <v>1.01</v>
+      </c>
+      <c r="BE19">
+        <v>1.01</v>
+      </c>
+      <c r="BF19">
+        <v>1.01</v>
+      </c>
+      <c r="BG19">
+        <v>1.01</v>
+      </c>
+      <c r="BH19">
         <v>4</v>
       </c>
-      <c r="J19">
-        <v>3.65</v>
-      </c>
-      <c r="K19">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>2.42</v>
-      </c>
-      <c r="Q19">
-        <v>1.37</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AI19">
-        <v>0</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>0</v>
-      </c>
-      <c r="AO19">
-        <v>0</v>
-      </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19">
-        <v>0</v>
-      </c>
-      <c r="AV19">
-        <v>0</v>
-      </c>
-      <c r="AW19">
-        <v>0</v>
-      </c>
-      <c r="AX19">
-        <v>0</v>
-      </c>
-      <c r="AY19">
-        <v>0</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>0</v>
-      </c>
-      <c r="BC19">
-        <v>0</v>
-      </c>
-      <c r="BD19">
-        <v>0</v>
-      </c>
-      <c r="BE19">
-        <v>0</v>
-      </c>
-      <c r="BF19">
-        <v>0</v>
-      </c>
-      <c r="BG19">
-        <v>0</v>
-      </c>
-      <c r="BH19">
-        <v>0</v>
-      </c>
       <c r="BI19">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5438,284 +5447,284 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F20">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="G20">
-        <v>4.6</v>
+        <v>2.56</v>
       </c>
       <c r="H20">
-        <v>1.27</v>
+        <v>2.7</v>
       </c>
       <c r="I20">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P20">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q20">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
         <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F21">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="G21">
-        <v>1.86</v>
+        <v>4.6</v>
       </c>
       <c r="H21">
-        <v>6</v>
+        <v>1.27</v>
       </c>
       <c r="I21">
-        <v>11.5</v>
+        <v>2.16</v>
       </c>
       <c r="J21">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5724,22 +5733,22 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>3.9</v>
+        <v>2.46</v>
       </c>
       <c r="O21">
+        <v>1.16</v>
+      </c>
+      <c r="P21">
+        <v>2.46</v>
+      </c>
+      <c r="Q21">
+        <v>1.5</v>
+      </c>
+      <c r="R21">
         <v>1.25</v>
       </c>
-      <c r="P21">
-        <v>1.88</v>
-      </c>
-      <c r="Q21">
-        <v>1.64</v>
-      </c>
-      <c r="R21">
-        <v>1.35</v>
-      </c>
       <c r="S21">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5748,10 +5757,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.09</v>
+        <v>1.86</v>
       </c>
       <c r="W21">
-        <v>2.14</v>
+        <v>1.27</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5808,53 +5817,53 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="AQ21">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR21">
+        <v>11</v>
+      </c>
+      <c r="AS21">
+        <v>18.5</v>
+      </c>
+      <c r="AT21">
+        <v>16</v>
+      </c>
+      <c r="AU21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW21">
+        <v>13</v>
+      </c>
+      <c r="AX21">
+        <v>22</v>
+      </c>
+      <c r="AY21">
+        <v>11.5</v>
+      </c>
+      <c r="AZ21">
+        <v>11</v>
+      </c>
+      <c r="BA21">
+        <v>18</v>
+      </c>
+      <c r="BB21">
+        <v>40</v>
+      </c>
+      <c r="BC21">
+        <v>25</v>
+      </c>
+      <c r="BD21">
+        <v>26</v>
+      </c>
+      <c r="BE21">
         <v>34</v>
       </c>
-      <c r="AS21">
-        <v>40</v>
-      </c>
-      <c r="AT21">
-        <v>7.2</v>
-      </c>
-      <c r="AU21">
-        <v>7.8</v>
-      </c>
-      <c r="AV21">
-        <v>18</v>
-      </c>
-      <c r="AW21">
-        <v>40</v>
-      </c>
-      <c r="AX21">
-        <v>7.6</v>
-      </c>
-      <c r="AY21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ21">
-        <v>17</v>
-      </c>
-      <c r="BA21">
-        <v>40</v>
-      </c>
-      <c r="BB21">
-        <v>11.5</v>
-      </c>
-      <c r="BC21">
-        <v>12.5</v>
-      </c>
-      <c r="BD21">
-        <v>24</v>
-      </c>
-      <c r="BE21">
-        <v>40</v>
-      </c>
       <c r="BF21">
         <v>1.01</v>
       </c>
@@ -5922,186 +5931,186 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
         <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F22">
-        <v>3.75</v>
+        <v>1.5</v>
       </c>
       <c r="G22">
-        <v>4.5</v>
+        <v>1.86</v>
       </c>
       <c r="H22">
-        <v>1.98</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>2.18</v>
+        <v>11.5</v>
       </c>
       <c r="J22">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K22">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N22">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O22">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="P22">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q22">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="R22">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S22">
-        <v>3.45</v>
+        <v>2.56</v>
       </c>
       <c r="T22">
         <v>1.01</v>
       </c>
       <c r="U22">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.84</v>
+        <v>1.1</v>
       </c>
       <c r="W22">
-        <v>1.29</v>
+        <v>2.16</v>
       </c>
       <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>1000</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>14</v>
+      </c>
+      <c r="AQ22">
         <v>17</v>
       </c>
-      <c r="Y22">
-        <v>9.6</v>
-      </c>
-      <c r="Z22">
-        <v>13.5</v>
-      </c>
-      <c r="AA22">
-        <v>27</v>
-      </c>
-      <c r="AB22">
-        <v>15</v>
-      </c>
-      <c r="AC22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD22">
-        <v>13</v>
-      </c>
-      <c r="AE22">
-        <v>28</v>
-      </c>
-      <c r="AF22">
-        <v>32</v>
-      </c>
-      <c r="AG22">
-        <v>17.5</v>
-      </c>
-      <c r="AH22">
-        <v>23</v>
-      </c>
-      <c r="AI22">
-        <v>48</v>
-      </c>
-      <c r="AJ22">
-        <v>110</v>
-      </c>
-      <c r="AK22">
-        <v>65</v>
-      </c>
-      <c r="AL22">
-        <v>65</v>
-      </c>
-      <c r="AM22">
-        <v>130</v>
-      </c>
-      <c r="AN22">
-        <v>70</v>
-      </c>
-      <c r="AO22">
-        <v>17.5</v>
-      </c>
-      <c r="AP22">
-        <v>10</v>
-      </c>
-      <c r="AQ22">
-        <v>6.8</v>
-      </c>
       <c r="AR22">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="AS22">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="AT22">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AU22">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV22">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AW22">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="AX22">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="AY22">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ22">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA22">
-        <v>5.1</v>
+        <v>40</v>
       </c>
       <c r="BB22">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC22">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="BD22">
-        <v>5.3</v>
+        <v>24</v>
       </c>
       <c r="BE22">
-        <v>5.5</v>
+        <v>40</v>
       </c>
       <c r="BF22">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6164,523 +6173,523 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="G23">
-        <v>2.22</v>
+        <v>4.5</v>
       </c>
       <c r="H23">
-        <v>3.65</v>
+        <v>1.98</v>
       </c>
       <c r="I23">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="J23">
         <v>3.4</v>
       </c>
       <c r="K23">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P23">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="Q23">
+        <v>1.96</v>
+      </c>
+      <c r="R23">
+        <v>1.32</v>
+      </c>
+      <c r="S23">
+        <v>3.45</v>
+      </c>
+      <c r="T23">
         <v>1.8</v>
       </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
         <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F24">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>3.3</v>
+        <v>2.22</v>
       </c>
       <c r="H24">
-        <v>2.64</v>
+        <v>3.65</v>
       </c>
       <c r="I24">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="J24">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K24">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P24">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q24">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E25" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F25">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="G25">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="H25">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="I25">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="J25">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K25">
         <v>3.8</v>
@@ -6698,10 +6707,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q25">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6890,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6898,34 +6907,34 @@
         <v>96</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
         <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -6940,10 +6949,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q26">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7132,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7140,241 +7149,483 @@
         <v>97</v>
       </c>
       <c r="B27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>1.24</v>
+      </c>
+      <c r="Q27">
+        <v>1.01</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <v>0</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+      <c r="BG27">
+        <v>0</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <v>0</v>
+      </c>
+      <c r="BK27">
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <v>0</v>
+      </c>
+      <c r="BN27">
+        <v>0</v>
+      </c>
+      <c r="BO27">
+        <v>0</v>
+      </c>
+      <c r="BP27">
+        <v>0</v>
+      </c>
+      <c r="BQ27">
+        <v>0</v>
+      </c>
+      <c r="BR27">
+        <v>0</v>
+      </c>
+      <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
+        <v>0</v>
+      </c>
+      <c r="BU27">
+        <v>0</v>
+      </c>
+      <c r="BV27">
+        <v>0</v>
+      </c>
+      <c r="BW27">
+        <v>0</v>
+      </c>
+      <c r="BX27">
+        <v>0</v>
+      </c>
+      <c r="BY27">
+        <v>0</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
         <v>98</v>
       </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" t="s">
-        <v>163</v>
-      </c>
-      <c r="F27">
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F28">
         <v>1.89</v>
       </c>
-      <c r="G27">
+      <c r="G28">
         <v>2</v>
       </c>
-      <c r="H27">
+      <c r="H28">
         <v>4.7</v>
       </c>
-      <c r="I27">
+      <c r="I28">
         <v>5.2</v>
       </c>
-      <c r="J27">
+      <c r="J28">
         <v>3.4</v>
       </c>
-      <c r="K27">
-        <v>3.7</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>1.68</v>
-      </c>
-      <c r="Q27">
-        <v>2.14</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27">
-        <v>0</v>
-      </c>
-      <c r="AI27">
-        <v>0</v>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>0</v>
-      </c>
-      <c r="AO27">
-        <v>0</v>
-      </c>
-      <c r="AP27">
-        <v>0</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27">
-        <v>0</v>
-      </c>
-      <c r="AV27">
-        <v>0</v>
-      </c>
-      <c r="AW27">
-        <v>0</v>
-      </c>
-      <c r="AX27">
-        <v>0</v>
-      </c>
-      <c r="AY27">
-        <v>0</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>0</v>
-      </c>
-      <c r="BC27">
-        <v>0</v>
-      </c>
-      <c r="BD27">
-        <v>0</v>
-      </c>
-      <c r="BE27">
-        <v>0</v>
-      </c>
-      <c r="BF27">
-        <v>0</v>
-      </c>
-      <c r="BG27">
-        <v>0</v>
-      </c>
-      <c r="BH27">
-        <v>0</v>
-      </c>
-      <c r="BI27">
-        <v>0</v>
-      </c>
-      <c r="BJ27">
-        <v>0</v>
-      </c>
-      <c r="BK27">
-        <v>0</v>
-      </c>
-      <c r="BL27">
-        <v>0</v>
-      </c>
-      <c r="BM27">
-        <v>0</v>
-      </c>
-      <c r="BN27">
-        <v>0</v>
-      </c>
-      <c r="BO27">
-        <v>0</v>
-      </c>
-      <c r="BP27">
-        <v>0</v>
-      </c>
-      <c r="BQ27">
-        <v>0</v>
-      </c>
-      <c r="BR27">
-        <v>0</v>
-      </c>
-      <c r="BS27">
-        <v>0</v>
-      </c>
-      <c r="BT27">
-        <v>0</v>
-      </c>
-      <c r="BU27">
-        <v>0</v>
-      </c>
-      <c r="BV27">
-        <v>0</v>
-      </c>
-      <c r="BW27">
-        <v>0</v>
-      </c>
-      <c r="BX27">
-        <v>0</v>
-      </c>
-      <c r="BY27">
-        <v>0</v>
-      </c>
-      <c r="BZ27">
-        <v>0</v>
-      </c>
-      <c r="CA27">
-        <v>0</v>
-      </c>
-      <c r="CB27" t="s">
-        <v>164</v>
+      <c r="K28">
+        <v>3.75</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>1.69</v>
+      </c>
+      <c r="Q28">
+        <v>2.16</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+      <c r="BQ28">
+        <v>0</v>
+      </c>
+      <c r="BR28">
+        <v>0</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
+        <v>0</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -517,7 +517,7 @@
     <t>CD Nacional Funchal</t>
   </si>
   <si>
-    <t>2026-08-08 15:51:59</t>
+    <t>2026-08-08 18:10:34</t>
   </si>
 </sst>
 </file>
@@ -1114,163 +1114,163 @@
         <v>1.85</v>
       </c>
       <c r="G2">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="I2">
-        <v>4.9</v>
+        <v>110</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>1.06</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>110</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="O2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q2">
-        <v>1.89</v>
+        <v>1.3</v>
       </c>
       <c r="R2">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1353,46 +1353,46 @@
         <v>141</v>
       </c>
       <c r="F3">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="G3">
-        <v>2.82</v>
+        <v>1000</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="I3">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L3">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>1.25</v>
+      </c>
+      <c r="O3">
         <v>1.02</v>
       </c>
-      <c r="N3">
-        <v>1.48</v>
-      </c>
-      <c r="O3">
-        <v>1.47</v>
-      </c>
       <c r="P3">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="Q3">
-        <v>2.46</v>
+        <v>1.02</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>2.46</v>
+        <v>1.05</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1401,10 +1401,10 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1595,166 +1595,166 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>2.82</v>
+        <v>1.06</v>
       </c>
       <c r="G4">
-        <v>3.25</v>
+        <v>110</v>
       </c>
       <c r="H4">
-        <v>2.74</v>
+        <v>1.32</v>
       </c>
       <c r="I4">
-        <v>3.1</v>
+        <v>110</v>
       </c>
       <c r="J4">
-        <v>2.9</v>
+        <v>1.31</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>110</v>
       </c>
       <c r="L4">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="O4">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P4">
+        <v>1.24</v>
+      </c>
+      <c r="Q4">
         <v>1.51</v>
-      </c>
-      <c r="Q4">
-        <v>2.58</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>5.3</v>
+        <v>1.51</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR4">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="AS4">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT4">
         <v>7.4</v>
       </c>
       <c r="AU4">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX4">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AY4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>5.9</v>
+        <v>40</v>
       </c>
       <c r="BB4">
-        <v>5.8</v>
+        <v>36</v>
       </c>
       <c r="BC4">
-        <v>5.7</v>
+        <v>29</v>
       </c>
       <c r="BD4">
-        <v>5.9</v>
+        <v>40</v>
       </c>
       <c r="BE4">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BF4">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1837,166 +1837,166 @@
         <v>143</v>
       </c>
       <c r="F5">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="G5">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I5">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J5">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="O5">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>1.38</v>
       </c>
       <c r="R5">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>1.38</v>
       </c>
       <c r="T5">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR5">
+        <v>15</v>
+      </c>
+      <c r="AS5">
+        <v>36</v>
+      </c>
+      <c r="AT5">
         <v>7.6</v>
       </c>
-      <c r="AD5">
-        <v>14</v>
-      </c>
-      <c r="AE5">
-        <v>48</v>
-      </c>
-      <c r="AF5">
-        <v>16</v>
-      </c>
-      <c r="AG5">
-        <v>12</v>
-      </c>
-      <c r="AH5">
-        <v>19</v>
-      </c>
-      <c r="AI5">
-        <v>65</v>
-      </c>
-      <c r="AJ5">
-        <v>38</v>
-      </c>
-      <c r="AK5">
-        <v>30</v>
-      </c>
-      <c r="AL5">
-        <v>55</v>
-      </c>
-      <c r="AM5">
-        <v>130</v>
-      </c>
-      <c r="AN5">
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW5">
         <v>27</v>
       </c>
-      <c r="AO5">
-        <v>50</v>
-      </c>
-      <c r="AP5">
+      <c r="AX5">
         <v>10.5</v>
       </c>
-      <c r="AQ5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR5">
-        <v>19</v>
-      </c>
-      <c r="AS5">
-        <v>11</v>
-      </c>
-      <c r="AT5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU5">
-        <v>6.6</v>
-      </c>
-      <c r="AV5">
-        <v>12</v>
-      </c>
-      <c r="AW5">
-        <v>34</v>
-      </c>
-      <c r="AX5">
-        <v>13.5</v>
-      </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
         <v>38</v>
       </c>
       <c r="BB5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC5">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BD5">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BE5">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="BF5">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2079,25 +2079,25 @@
         <v>144</v>
       </c>
       <c r="F6">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="G6">
-        <v>2.44</v>
+        <v>110</v>
       </c>
       <c r="H6">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="I6">
-        <v>5.8</v>
+        <v>190</v>
       </c>
       <c r="J6">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>330</v>
       </c>
       <c r="L6">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
         <v>1.01</v>
@@ -2106,19 +2106,19 @@
         <v>1.2</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
         <v>1.19</v>
       </c>
       <c r="Q6">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2127,10 +2127,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2321,172 +2321,172 @@
         <v>145</v>
       </c>
       <c r="F7">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
+        <v>110</v>
+      </c>
+      <c r="H7">
+        <v>1.04</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.04</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>1.17</v>
+      </c>
+      <c r="O7">
+        <v>1.01</v>
+      </c>
+      <c r="P7">
+        <v>1.05</v>
+      </c>
+      <c r="Q7">
+        <v>1.02</v>
+      </c>
+      <c r="R7">
+        <v>1.05</v>
+      </c>
+      <c r="S7">
+        <v>1.28</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7">
+        <v>1.01</v>
+      </c>
+      <c r="AR7">
+        <v>1.01</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>1.01</v>
+      </c>
+      <c r="AU7">
+        <v>1.01</v>
+      </c>
+      <c r="AV7">
+        <v>1.01</v>
+      </c>
+      <c r="AW7">
+        <v>1.01</v>
+      </c>
+      <c r="AX7">
+        <v>1.01</v>
+      </c>
+      <c r="AY7">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7">
+        <v>1.01</v>
+      </c>
+      <c r="BA7">
+        <v>1.01</v>
+      </c>
+      <c r="BB7">
+        <v>1.01</v>
+      </c>
+      <c r="BC7">
+        <v>1.01</v>
+      </c>
+      <c r="BD7">
+        <v>1.01</v>
+      </c>
+      <c r="BE7">
+        <v>1.01</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
         <v>2.76</v>
-      </c>
-      <c r="H7">
-        <v>2.64</v>
-      </c>
-      <c r="I7">
-        <v>4.1</v>
-      </c>
-      <c r="J7">
-        <v>3.1</v>
-      </c>
-      <c r="K7">
-        <v>6.4</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.01</v>
-      </c>
-      <c r="N7">
-        <v>1.99</v>
-      </c>
-      <c r="O7">
-        <v>1.01</v>
-      </c>
-      <c r="P7">
-        <v>1.99</v>
-      </c>
-      <c r="Q7">
-        <v>1.69</v>
-      </c>
-      <c r="R7">
-        <v>1.15</v>
-      </c>
-      <c r="S7">
-        <v>1.69</v>
-      </c>
-      <c r="T7">
-        <v>1.01</v>
-      </c>
-      <c r="U7">
-        <v>1.01</v>
-      </c>
-      <c r="V7">
-        <v>1.32</v>
-      </c>
-      <c r="W7">
-        <v>1.56</v>
-      </c>
-      <c r="X7">
-        <v>1000</v>
-      </c>
-      <c r="Y7">
-        <v>1000</v>
-      </c>
-      <c r="Z7">
-        <v>1000</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>1000</v>
-      </c>
-      <c r="AC7">
-        <v>1000</v>
-      </c>
-      <c r="AD7">
-        <v>1000</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>1000</v>
-      </c>
-      <c r="AG7">
-        <v>1000</v>
-      </c>
-      <c r="AH7">
-        <v>1000</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>1000</v>
-      </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>1.01</v>
-      </c>
-      <c r="AQ7">
-        <v>1.01</v>
-      </c>
-      <c r="AR7">
-        <v>1.01</v>
-      </c>
-      <c r="AS7">
-        <v>1.01</v>
-      </c>
-      <c r="AT7">
-        <v>1.01</v>
-      </c>
-      <c r="AU7">
-        <v>1.01</v>
-      </c>
-      <c r="AV7">
-        <v>1.01</v>
-      </c>
-      <c r="AW7">
-        <v>1.01</v>
-      </c>
-      <c r="AX7">
-        <v>1.01</v>
-      </c>
-      <c r="AY7">
-        <v>1.01</v>
-      </c>
-      <c r="AZ7">
-        <v>1.01</v>
-      </c>
-      <c r="BA7">
-        <v>1.01</v>
-      </c>
-      <c r="BB7">
-        <v>1.01</v>
-      </c>
-      <c r="BC7">
-        <v>1.01</v>
-      </c>
-      <c r="BD7">
-        <v>1.01</v>
-      </c>
-      <c r="BE7">
-        <v>1.01</v>
-      </c>
-      <c r="BF7">
-        <v>1.01</v>
-      </c>
-      <c r="BG7">
-        <v>1.01</v>
-      </c>
-      <c r="BH7">
-        <v>4.5</v>
-      </c>
-      <c r="BI7">
-        <v>2.74</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
@@ -2563,46 +2563,46 @@
         <v>146</v>
       </c>
       <c r="F8">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="G8">
-        <v>2.18</v>
+        <v>990</v>
       </c>
       <c r="H8">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="I8">
-        <v>4.6</v>
+        <v>990</v>
       </c>
       <c r="J8">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>500</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="O8">
         <v>1.23</v>
       </c>
       <c r="P8">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="R8">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>2.48</v>
+        <v>1.23</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2611,10 +2611,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2805,166 +2805,166 @@
         <v>147</v>
       </c>
       <c r="F9">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>3.5</v>
+        <v>190</v>
       </c>
       <c r="H9">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>190</v>
       </c>
       <c r="J9">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="K9">
-        <v>3.15</v>
+        <v>330</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="O9">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="Q9">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>150</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3047,22 +3047,22 @@
         <v>148</v>
       </c>
       <c r="F10">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="G10">
         <v>110</v>
       </c>
       <c r="H10">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I10">
-        <v>4.2</v>
+        <v>110</v>
       </c>
       <c r="J10">
-        <v>3.2</v>
+        <v>1.06</v>
       </c>
       <c r="K10">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3071,22 +3071,22 @@
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="O10">
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="Q10">
-        <v>1.87</v>
+        <v>1.34</v>
       </c>
       <c r="R10">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
-        <v>3.2</v>
+        <v>1.34</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3095,7 +3095,7 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
         <v>1.01</v>
@@ -3289,22 +3289,22 @@
         <v>149</v>
       </c>
       <c r="F11">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="H11">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="J11">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="K11">
-        <v>9.6</v>
+        <v>330</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3313,22 +3313,22 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="O11">
         <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="Q11">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="R11">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>2.38</v>
+        <v>1.21</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3337,10 +3337,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3531,166 +3531,166 @@
         <v>150</v>
       </c>
       <c r="F12">
-        <v>1.94</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>110</v>
       </c>
       <c r="H12">
-        <v>3.85</v>
+        <v>1.09</v>
       </c>
       <c r="I12">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>3.45</v>
+        <v>1.08</v>
       </c>
       <c r="K12">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
+        <v>1.07</v>
+      </c>
+      <c r="N12">
+        <v>1.57</v>
+      </c>
+      <c r="O12">
+        <v>1.38</v>
+      </c>
+      <c r="P12">
+        <v>1.57</v>
+      </c>
+      <c r="Q12">
+        <v>1.38</v>
+      </c>
+      <c r="R12">
+        <v>1.18</v>
+      </c>
+      <c r="S12">
+        <v>1.38</v>
+      </c>
+      <c r="T12">
+        <v>1.01</v>
+      </c>
+      <c r="U12">
+        <v>1.01</v>
+      </c>
+      <c r="V12">
+        <v>1.01</v>
+      </c>
+      <c r="W12">
         <v>1.08</v>
       </c>
-      <c r="N12">
-        <v>3.2</v>
-      </c>
-      <c r="O12">
-        <v>1.39</v>
-      </c>
-      <c r="P12">
-        <v>1.75</v>
-      </c>
-      <c r="Q12">
-        <v>2.14</v>
-      </c>
-      <c r="R12">
-        <v>1.23</v>
-      </c>
-      <c r="S12">
-        <v>4.1</v>
-      </c>
-      <c r="T12">
-        <v>1.92</v>
-      </c>
-      <c r="U12">
-        <v>1.88</v>
-      </c>
-      <c r="V12">
-        <v>1.26</v>
-      </c>
-      <c r="W12">
-        <v>1.83</v>
-      </c>
       <c r="X12">
         <v>1000</v>
       </c>
       <c r="Y12">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ12">
+        <v>9.4</v>
+      </c>
+      <c r="AR12">
+        <v>1.49</v>
+      </c>
+      <c r="AS12">
         <v>40</v>
       </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>9.4</v>
-      </c>
-      <c r="AC12">
-        <v>9.4</v>
-      </c>
-      <c r="AD12">
-        <v>22</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>1000</v>
-      </c>
-      <c r="AG12">
-        <v>1000</v>
-      </c>
-      <c r="AH12">
-        <v>1000</v>
-      </c>
-      <c r="AI12">
-        <v>95</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>1.54</v>
-      </c>
-      <c r="AQ12">
-        <v>10</v>
-      </c>
-      <c r="AR12">
-        <v>1.48</v>
-      </c>
-      <c r="AS12">
-        <v>1.54</v>
-      </c>
       <c r="AT12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AU12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AV12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AW12">
-        <v>1.54</v>
+        <v>38</v>
       </c>
       <c r="AX12">
-        <v>1.54</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY12">
-        <v>1.54</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>1.54</v>
+        <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BB12">
-        <v>1.54</v>
+        <v>19.5</v>
       </c>
       <c r="BC12">
-        <v>1.54</v>
+        <v>18</v>
       </c>
       <c r="BD12">
-        <v>1.54</v>
+        <v>30</v>
       </c>
       <c r="BE12">
-        <v>1.54</v>
+        <v>40</v>
       </c>
       <c r="BF12">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3776,163 +3776,163 @@
         <v>2.3</v>
       </c>
       <c r="G13">
-        <v>2.48</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>3.1</v>
+        <v>1.07</v>
       </c>
       <c r="I13">
-        <v>3.5</v>
+        <v>110</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>1.07</v>
       </c>
       <c r="K13">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
-        <v>3.95</v>
+        <v>1.25</v>
       </c>
       <c r="O13">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P13">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>1.81</v>
+        <v>1.26</v>
       </c>
       <c r="R13">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S13">
-        <v>3.05</v>
+        <v>1.26</v>
       </c>
       <c r="T13">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3941,58 +3941,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>167</v>
@@ -4015,22 +4015,22 @@
         <v>152</v>
       </c>
       <c r="F14">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="G14">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H14">
-        <v>9.800000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="I14">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="J14">
-        <v>5.5</v>
+        <v>1.09</v>
       </c>
       <c r="K14">
-        <v>6.4</v>
+        <v>70</v>
       </c>
       <c r="L14">
         <v>1.19</v>
@@ -4039,142 +4039,142 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="P14">
         <v>3.2</v>
       </c>
       <c r="Q14">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="R14">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="S14">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="T14">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="X14">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AO14">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="AR14">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="AS14">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="AT14">
-        <v>12</v>
+        <v>1.3</v>
       </c>
       <c r="AU14">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="AV14">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="AW14">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="AX14">
-        <v>9.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AY14">
-        <v>9.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AZ14">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="BA14">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="BB14">
-        <v>10.5</v>
+        <v>1.3</v>
       </c>
       <c r="BC14">
-        <v>11.5</v>
+        <v>1.3</v>
       </c>
       <c r="BD14">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="BE14">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="BF14">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BG14">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4266,157 +4266,157 @@
         <v>1.83</v>
       </c>
       <c r="I15">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="O15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q15">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R15">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="S15">
-        <v>2.34</v>
+        <v>1.56</v>
       </c>
       <c r="T15">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W15">
         <v>1.29</v>
       </c>
       <c r="X15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ15">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR15">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AS15">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT15">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU15">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV15">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW15">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AX15">
         <v>25</v>
       </c>
       <c r="AY15">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AZ15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BB15">
-        <v>7.8</v>
+        <v>48</v>
       </c>
       <c r="BC15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE15">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BF15">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4499,166 +4499,166 @@
         <v>154</v>
       </c>
       <c r="F16">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="G16">
-        <v>2.5</v>
+        <v>190</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I16">
-        <v>3.25</v>
+        <v>190</v>
       </c>
       <c r="J16">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="K16">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N16">
-        <v>3.95</v>
+        <v>1.25</v>
       </c>
       <c r="O16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P16">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="R16">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>1.26</v>
       </c>
       <c r="T16">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="W16">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4741,22 +4741,22 @@
         <v>155</v>
       </c>
       <c r="F17">
-        <v>2.98</v>
+        <v>1.22</v>
       </c>
       <c r="G17">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="H17">
         <v>2.08</v>
       </c>
       <c r="I17">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="J17">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="K17">
-        <v>5.5</v>
+        <v>950</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4765,142 +4765,142 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>7</v>
+        <v>1.25</v>
       </c>
       <c r="O17">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P17">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="R17">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="S17">
-        <v>1.86</v>
+        <v>1.09</v>
       </c>
       <c r="T17">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4983,22 +4983,22 @@
         <v>156</v>
       </c>
       <c r="F18">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G18">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="H18">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="I18">
         <v>2.58</v>
       </c>
       <c r="J18">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L18">
         <v>1.24</v>
@@ -5007,79 +5007,79 @@
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="O18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P18">
-        <v>2.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q18">
         <v>1.52</v>
       </c>
       <c r="R18">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="S18">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="T18">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
         <v>1.63</v>
       </c>
       <c r="W18">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X18">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y18">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z18">
         <v>21</v>
       </c>
       <c r="AA18">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB18">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AC18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF18">
+        <v>28</v>
+      </c>
+      <c r="AG18">
+        <v>13.5</v>
+      </c>
+      <c r="AH18">
+        <v>14</v>
+      </c>
+      <c r="AI18">
+        <v>30</v>
+      </c>
+      <c r="AJ18">
+        <v>48</v>
+      </c>
+      <c r="AK18">
         <v>29</v>
       </c>
-      <c r="AG18">
-        <v>14</v>
-      </c>
-      <c r="AH18">
-        <v>14.5</v>
-      </c>
-      <c r="AI18">
+      <c r="AL18">
         <v>34</v>
-      </c>
-      <c r="AJ18">
-        <v>50</v>
-      </c>
-      <c r="AK18">
-        <v>32</v>
-      </c>
-      <c r="AL18">
-        <v>36</v>
       </c>
       <c r="AM18">
         <v>50</v>
@@ -5091,58 +5091,58 @@
         <v>12.5</v>
       </c>
       <c r="AP18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ18">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR18">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AS18">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AT18">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU18">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="AV18">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AW18">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AX18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AY18">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="AZ18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA18">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BB18">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BC18">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BD18">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BE18">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5225,22 +5225,22 @@
         <v>157</v>
       </c>
       <c r="F19">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="G19">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H19">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="I19">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="J19">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="K19">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5249,22 +5249,22 @@
         <v>1.06</v>
       </c>
       <c r="N19">
-        <v>3.4</v>
+        <v>1.26</v>
       </c>
       <c r="O19">
         <v>1.34</v>
       </c>
       <c r="P19">
-        <v>1.69</v>
+        <v>1.26</v>
       </c>
       <c r="Q19">
-        <v>1.86</v>
+        <v>1.34</v>
       </c>
       <c r="R19">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="S19">
-        <v>3.15</v>
+        <v>1.34</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5273,10 +5273,10 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W19">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5387,10 +5387,10 @@
         <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
@@ -5467,22 +5467,22 @@
         <v>158</v>
       </c>
       <c r="F20">
-        <v>1.92</v>
+        <v>1.23</v>
       </c>
       <c r="G20">
-        <v>2.56</v>
+        <v>110</v>
       </c>
       <c r="H20">
-        <v>2.7</v>
+        <v>1.27</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="J20">
-        <v>3.65</v>
+        <v>1.14</v>
       </c>
       <c r="K20">
-        <v>7.2</v>
+        <v>110</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5491,22 +5491,22 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="O20">
         <v>1.12</v>
       </c>
       <c r="P20">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="Q20">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="R20">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="S20">
-        <v>1.98</v>
+        <v>1.12</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -5515,10 +5515,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="W20">
-        <v>1.64</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5709,22 +5709,22 @@
         <v>159</v>
       </c>
       <c r="F21">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="G21">
-        <v>4.6</v>
+        <v>110</v>
       </c>
       <c r="H21">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="I21">
-        <v>2.16</v>
+        <v>12.5</v>
       </c>
       <c r="J21">
-        <v>3.1</v>
+        <v>1.08</v>
       </c>
       <c r="K21">
-        <v>110</v>
+        <v>7.6</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5733,22 +5733,22 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>2.46</v>
+        <v>1.61</v>
       </c>
       <c r="O21">
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>2.46</v>
+        <v>1.61</v>
       </c>
       <c r="Q21">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="R21">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S21">
-        <v>2.26</v>
+        <v>1.16</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5757,10 +5757,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="W21">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5951,22 +5951,22 @@
         <v>160</v>
       </c>
       <c r="F22">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="G22">
         <v>1.86</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="I22">
-        <v>11.5</v>
+        <v>110</v>
       </c>
       <c r="J22">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="K22">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -5975,22 +5975,22 @@
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="O22">
         <v>1.25</v>
       </c>
       <c r="P22">
-        <v>1.88</v>
+        <v>1.24</v>
       </c>
       <c r="Q22">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="R22">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="S22">
-        <v>2.56</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -5999,7 +5999,7 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W22">
         <v>2.16</v>
@@ -6193,166 +6193,166 @@
         <v>161</v>
       </c>
       <c r="F23">
-        <v>3.75</v>
+        <v>1.06</v>
       </c>
       <c r="G23">
-        <v>4.5</v>
+        <v>110</v>
       </c>
       <c r="H23">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="I23">
-        <v>2.18</v>
+        <v>970</v>
       </c>
       <c r="J23">
-        <v>3.4</v>
+        <v>1.06</v>
       </c>
       <c r="K23">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N23">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="O23">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P23">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="Q23">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="R23">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S23">
-        <v>3.45</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="W23">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6435,46 +6435,46 @@
         <v>162</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G24">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="H24">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="I24">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J24">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="K24">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N24">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="O24">
+        <v>1.06</v>
+      </c>
+      <c r="P24">
         <v>1.24</v>
       </c>
-      <c r="P24">
-        <v>1.75</v>
-      </c>
       <c r="Q24">
-        <v>1.8</v>
+        <v>1.06</v>
       </c>
       <c r="R24">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S24">
-        <v>3</v>
+        <v>1.06</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6483,10 +6483,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W24">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6597,10 +6597,10 @@
         <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
@@ -6677,226 +6677,226 @@
         <v>163</v>
       </c>
       <c r="F25">
-        <v>2.8</v>
+        <v>1.07</v>
       </c>
       <c r="G25">
-        <v>3.35</v>
+        <v>110</v>
       </c>
       <c r="H25">
-        <v>2.64</v>
+        <v>1.07</v>
       </c>
       <c r="I25">
-        <v>3.15</v>
+        <v>110</v>
       </c>
       <c r="J25">
-        <v>3.1</v>
+        <v>1.13</v>
       </c>
       <c r="K25">
-        <v>3.8</v>
+        <v>110</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P25">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="Q25">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA25">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
         <v>167</v>
@@ -6919,226 +6919,226 @@
         <v>164</v>
       </c>
       <c r="F26">
-        <v>3.6</v>
+        <v>1.21</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="H26">
-        <v>2.2</v>
+        <v>1.21</v>
       </c>
       <c r="I26">
-        <v>2.34</v>
+        <v>110</v>
       </c>
       <c r="J26">
-        <v>3.05</v>
+        <v>1.06</v>
       </c>
       <c r="K26">
-        <v>3.35</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P26">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="Q26">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
         <v>167</v>
@@ -7179,16 +7179,16 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P27">
         <v>1.24</v>
@@ -7197,184 +7197,184 @@
         <v>1.01</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
         <v>0</v>
@@ -7403,226 +7403,226 @@
         <v>166</v>
       </c>
       <c r="F28">
-        <v>1.89</v>
+        <v>1.08</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="H28">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I28">
-        <v>5.2</v>
+        <v>110</v>
       </c>
       <c r="J28">
-        <v>3.4</v>
+        <v>1.06</v>
       </c>
       <c r="K28">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P28">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="Q28">
-        <v>2.16</v>
+        <v>1.39</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
         <v>167</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -517,7 +517,7 @@
     <t>CD Nacional Funchal</t>
   </si>
   <si>
-    <t>2026-08-08 18:10:34</t>
+    <t>2026-08-08 20:28:56</t>
   </si>
 </sst>
 </file>
@@ -1111,166 +1111,166 @@
         <v>140</v>
       </c>
       <c r="F2">
+        <v>1.78</v>
+      </c>
+      <c r="G2">
         <v>1.85</v>
       </c>
-      <c r="G2">
-        <v>1.93</v>
-      </c>
       <c r="H2">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="I2">
-        <v>110</v>
+        <v>5.4</v>
       </c>
       <c r="J2">
-        <v>1.06</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
-        <v>110</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="O2">
         <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="Q2">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
+        <v>1.38</v>
+      </c>
+      <c r="S2">
+        <v>3.2</v>
+      </c>
+      <c r="T2">
+        <v>1.79</v>
+      </c>
+      <c r="U2">
+        <v>2.06</v>
+      </c>
+      <c r="V2">
         <v>1.22</v>
       </c>
-      <c r="S2">
-        <v>1.94</v>
-      </c>
-      <c r="T2">
-        <v>1.01</v>
-      </c>
-      <c r="U2">
-        <v>1.01</v>
-      </c>
-      <c r="V2">
-        <v>1.01</v>
-      </c>
       <c r="W2">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU2">
+        <v>7.2</v>
+      </c>
+      <c r="AV2">
+        <v>13.5</v>
+      </c>
+      <c r="AW2">
+        <v>6.6</v>
+      </c>
+      <c r="AX2">
+        <v>9.4</v>
+      </c>
+      <c r="AY2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>16</v>
+      </c>
+      <c r="BA2">
+        <v>6.6</v>
+      </c>
+      <c r="BB2">
+        <v>17</v>
+      </c>
+      <c r="BC2">
+        <v>15.5</v>
+      </c>
+      <c r="BD2">
+        <v>6.2</v>
+      </c>
+      <c r="BE2">
         <v>6.8</v>
       </c>
-      <c r="AV2">
-        <v>1.01</v>
-      </c>
-      <c r="AW2">
-        <v>1.01</v>
-      </c>
-      <c r="AX2">
-        <v>1.01</v>
-      </c>
-      <c r="AY2">
-        <v>1.01</v>
-      </c>
-      <c r="AZ2">
-        <v>15.5</v>
-      </c>
-      <c r="BA2">
-        <v>1.01</v>
-      </c>
-      <c r="BB2">
-        <v>1.01</v>
-      </c>
-      <c r="BC2">
-        <v>1.01</v>
-      </c>
-      <c r="BD2">
-        <v>1.01</v>
-      </c>
-      <c r="BE2">
-        <v>40</v>
-      </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1353,145 +1353,145 @@
         <v>141</v>
       </c>
       <c r="F3">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="G3">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="H3">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="O3">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
-        <v>1.02</v>
+        <v>2.48</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS3">
         <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW3">
         <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA3">
         <v>1.01</v>
@@ -1595,226 +1595,226 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>1.06</v>
+        <v>2.98</v>
       </c>
       <c r="G4">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="H4">
-        <v>1.32</v>
+        <v>2.58</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>2.92</v>
       </c>
       <c r="J4">
-        <v>1.31</v>
+        <v>2.9</v>
       </c>
       <c r="K4">
-        <v>110</v>
+        <v>3.25</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
-        <v>1.24</v>
+        <v>2.76</v>
       </c>
       <c r="O4">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P4">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q4">
-        <v>1.51</v>
+        <v>2.56</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S4">
-        <v>1.51</v>
+        <v>5.3</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AR4">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="AS4">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AT4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW4">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AX4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY4">
         <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>4.1</v>
       </c>
       <c r="BB4">
+        <v>4.1</v>
+      </c>
+      <c r="BC4">
+        <v>4</v>
+      </c>
+      <c r="BD4">
+        <v>4.1</v>
+      </c>
+      <c r="BE4">
+        <v>4.2</v>
+      </c>
+      <c r="BF4">
+        <v>4.1</v>
+      </c>
+      <c r="BG4">
+        <v>4</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.33</v>
+      </c>
+      <c r="BJ4">
+        <v>16</v>
+      </c>
+      <c r="BK4">
+        <v>1.23</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.33</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.33</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.33</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.31</v>
+      </c>
+      <c r="BT4">
+        <v>7.8</v>
+      </c>
+      <c r="BU4">
+        <v>3.7</v>
+      </c>
+      <c r="BV4">
         <v>36</v>
       </c>
-      <c r="BC4">
-        <v>29</v>
-      </c>
-      <c r="BD4">
-        <v>40</v>
-      </c>
-      <c r="BE4">
-        <v>5.2</v>
-      </c>
-      <c r="BF4">
-        <v>1.01</v>
-      </c>
-      <c r="BG4">
-        <v>1.01</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4">
-        <v>1000</v>
-      </c>
-      <c r="BK4">
-        <v>1.01</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.01</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>1.01</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.01</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.01</v>
-      </c>
-      <c r="BT4">
-        <v>1000</v>
-      </c>
-      <c r="BU4">
-        <v>1.01</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="CB4" t="s">
         <v>167</v>
@@ -1837,46 +1837,46 @@
         <v>143</v>
       </c>
       <c r="F5">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="H5">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J5">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="O5">
         <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q5">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="R5">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="S5">
-        <v>1.38</v>
+        <v>3.85</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1885,55 +1885,55 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="X5">
         <v>1000</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM5">
         <v>1000</v>
@@ -1945,58 +1945,58 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>9.199999999999999</v>
+        <v>2.36</v>
       </c>
       <c r="AQ5">
-        <v>8.800000000000001</v>
+        <v>2.04</v>
       </c>
       <c r="AR5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS5">
-        <v>36</v>
+        <v>2.28</v>
       </c>
       <c r="AT5">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>1.91</v>
       </c>
       <c r="AV5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW5">
-        <v>27</v>
+        <v>2.26</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>2.06</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>2.16</v>
       </c>
       <c r="BA5">
-        <v>38</v>
+        <v>2.28</v>
       </c>
       <c r="BB5">
-        <v>25</v>
+        <v>2.24</v>
       </c>
       <c r="BC5">
-        <v>21</v>
+        <v>2.24</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>2.28</v>
       </c>
       <c r="BE5">
-        <v>40</v>
+        <v>2.36</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2079,22 +2079,22 @@
         <v>144</v>
       </c>
       <c r="F6">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G6">
-        <v>110</v>
+        <v>2.44</v>
       </c>
       <c r="H6">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I6">
-        <v>190</v>
+        <v>5.5</v>
       </c>
       <c r="J6">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>330</v>
+        <v>5.2</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2103,22 +2103,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="Q6">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>3.15</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2127,10 +2127,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2321,22 +2321,22 @@
         <v>145</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G7">
-        <v>110</v>
+        <v>2.76</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J7">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2345,22 +2345,22 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.17</v>
+        <v>3.7</v>
       </c>
       <c r="O7">
         <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q7">
-        <v>1.02</v>
+        <v>1.68</v>
       </c>
       <c r="R7">
         <v>1.05</v>
       </c>
       <c r="S7">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2369,10 +2369,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2483,7 +2483,7 @@
         <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI7">
         <v>2.76</v>
@@ -2563,166 +2563,166 @@
         <v>146</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="G8">
-        <v>990</v>
+        <v>2.16</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I8">
-        <v>990</v>
+        <v>4.2</v>
       </c>
       <c r="J8">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
-        <v>500</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>1.25</v>
+        <v>4.1</v>
       </c>
       <c r="O8">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q8">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S8">
-        <v>1.23</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2731,52 +2731,52 @@
         <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2805,58 +2805,58 @@
         <v>147</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>190</v>
+        <v>3.5</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="I9">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="K9">
-        <v>330</v>
+        <v>3.45</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N9">
-        <v>1.18</v>
+        <v>2.26</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="P9">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3047,46 +3047,46 @@
         <v>148</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="G10">
-        <v>110</v>
+        <v>2.48</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="I10">
-        <v>110</v>
+        <v>3.75</v>
       </c>
       <c r="J10">
-        <v>1.06</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="O10">
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="Q10">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="R10">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S10">
-        <v>1.34</v>
+        <v>3.3</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3095,55 +3095,55 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="X10">
         <v>1000</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM10">
         <v>1000</v>
@@ -3155,58 +3155,58 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>9.6</v>
+        <v>2.16</v>
       </c>
       <c r="AQ10">
         <v>9</v>
       </c>
       <c r="AR10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS10">
-        <v>38</v>
+        <v>2.12</v>
       </c>
       <c r="AT10">
-        <v>7.8</v>
+        <v>1.87</v>
       </c>
       <c r="AU10">
-        <v>6</v>
+        <v>1.81</v>
       </c>
       <c r="AV10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>26</v>
+        <v>2.1</v>
       </c>
       <c r="AX10">
-        <v>10.5</v>
+        <v>1.97</v>
       </c>
       <c r="AY10">
-        <v>9</v>
+        <v>1.93</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>2.02</v>
       </c>
       <c r="BA10">
-        <v>36</v>
+        <v>2.12</v>
       </c>
       <c r="BB10">
-        <v>23</v>
+        <v>2.08</v>
       </c>
       <c r="BC10">
         <v>19</v>
       </c>
       <c r="BD10">
-        <v>29</v>
+        <v>2.1</v>
       </c>
       <c r="BE10">
-        <v>40</v>
+        <v>2.16</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3289,22 +3289,22 @@
         <v>149</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G11">
         <v>1.73</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="K11">
-        <v>330</v>
+        <v>5.2</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3313,22 +3313,22 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="O11">
         <v>1.21</v>
       </c>
       <c r="P11">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="Q11">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S11">
-        <v>1.21</v>
+        <v>2.4</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3337,7 +3337,7 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W11">
         <v>2.36</v>
@@ -3457,52 +3457,52 @@
         <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3531,46 +3531,46 @@
         <v>150</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="G12">
-        <v>110</v>
+        <v>2.14</v>
       </c>
       <c r="H12">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J12">
-        <v>1.08</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>1.57</v>
+        <v>3.05</v>
       </c>
       <c r="O12">
         <v>1.38</v>
       </c>
       <c r="P12">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Q12">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>3.75</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3579,10 +3579,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.88</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3597,7 +3597,7 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>1000</v>
@@ -3627,7 +3627,7 @@
         <v>1000</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM12">
         <v>1000</v>
@@ -3639,58 +3639,58 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>9.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AQ12">
-        <v>9.4</v>
+        <v>1.14</v>
       </c>
       <c r="AR12">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="AS12">
-        <v>40</v>
+        <v>1.14</v>
       </c>
       <c r="AT12">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AV12">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="AW12">
-        <v>38</v>
+        <v>1.14</v>
       </c>
       <c r="AX12">
-        <v>9.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AY12">
-        <v>8.800000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="AZ12">
-        <v>15.5</v>
+        <v>1.14</v>
       </c>
       <c r="BA12">
-        <v>1.52</v>
+        <v>1.14</v>
       </c>
       <c r="BB12">
-        <v>19.5</v>
+        <v>1.14</v>
       </c>
       <c r="BC12">
-        <v>18</v>
+        <v>1.14</v>
       </c>
       <c r="BD12">
-        <v>30</v>
+        <v>1.12</v>
       </c>
       <c r="BE12">
-        <v>40</v>
+        <v>1.14</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3776,223 +3776,223 @@
         <v>2.3</v>
       </c>
       <c r="G13">
-        <v>110</v>
+        <v>2.48</v>
       </c>
       <c r="H13">
-        <v>1.07</v>
+        <v>3.05</v>
       </c>
       <c r="I13">
-        <v>110</v>
+        <v>3.5</v>
       </c>
       <c r="J13">
-        <v>1.07</v>
+        <v>3.5</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
-        <v>1.25</v>
+        <v>3.95</v>
       </c>
       <c r="O13">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="Q13">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="R13">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S13">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH13">
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="CB13" t="s">
         <v>167</v>
@@ -4015,22 +4015,22 @@
         <v>152</v>
       </c>
       <c r="F14">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="G14">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H14">
-        <v>1.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I14">
-        <v>110</v>
+        <v>11.5</v>
       </c>
       <c r="J14">
-        <v>1.09</v>
+        <v>5.6</v>
       </c>
       <c r="K14">
-        <v>70</v>
+        <v>6.4</v>
       </c>
       <c r="L14">
         <v>1.19</v>
@@ -4039,142 +4039,142 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="O14">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="P14">
         <v>3.2</v>
       </c>
       <c r="Q14">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="R14">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="S14">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V14">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="W14">
         <v>3.65</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN14">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP14">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="AQ14">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="AR14">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="AS14">
-        <v>1.3</v>
+        <v>9</v>
       </c>
       <c r="AT14">
-        <v>1.3</v>
+        <v>12</v>
       </c>
       <c r="AU14">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="AV14">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="AW14">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="AX14">
-        <v>1.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY14">
-        <v>1.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="BA14">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="BB14">
-        <v>1.3</v>
+        <v>10.5</v>
       </c>
       <c r="BC14">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="BD14">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="BE14">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="BF14">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BG14">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4263,16 +4263,16 @@
         <v>4.5</v>
       </c>
       <c r="H15">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="I15">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4281,22 +4281,22 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="O15">
         <v>1.17</v>
       </c>
       <c r="P15">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q15">
         <v>1.52</v>
       </c>
       <c r="R15">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S15">
-        <v>1.56</v>
+        <v>2.36</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4305,79 +4305,79 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W15">
         <v>1.29</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN15">
         <v>1000</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP15">
-        <v>19.5</v>
+        <v>2.7</v>
       </c>
       <c r="AQ15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS15">
-        <v>18</v>
+        <v>2.68</v>
       </c>
       <c r="AT15">
-        <v>17</v>
+        <v>2.68</v>
       </c>
       <c r="AU15">
         <v>8.6</v>
@@ -4386,37 +4386,37 @@
         <v>9</v>
       </c>
       <c r="AW15">
-        <v>13</v>
+        <v>2.58</v>
       </c>
       <c r="AX15">
-        <v>25</v>
+        <v>2.78</v>
       </c>
       <c r="AY15">
         <v>12.5</v>
       </c>
       <c r="AZ15">
-        <v>12.5</v>
+        <v>2.58</v>
       </c>
       <c r="BA15">
-        <v>19.5</v>
+        <v>2.72</v>
       </c>
       <c r="BB15">
-        <v>48</v>
+        <v>2.86</v>
       </c>
       <c r="BC15">
-        <v>28</v>
+        <v>2.8</v>
       </c>
       <c r="BD15">
-        <v>28</v>
+        <v>2.8</v>
       </c>
       <c r="BE15">
-        <v>40</v>
+        <v>2.84</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BG15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4499,166 +4499,166 @@
         <v>154</v>
       </c>
       <c r="F16">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="G16">
-        <v>190</v>
+        <v>2.5</v>
       </c>
       <c r="H16">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>190</v>
+        <v>3.55</v>
       </c>
       <c r="J16">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M16">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16">
-        <v>1.25</v>
+        <v>3.95</v>
       </c>
       <c r="O16">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q16">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="R16">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="S16">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4667,52 +4667,52 @@
         <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4741,22 +4741,22 @@
         <v>155</v>
       </c>
       <c r="F17">
-        <v>1.22</v>
+        <v>2.98</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H17">
         <v>2.08</v>
       </c>
       <c r="I17">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="J17">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4765,142 +4765,142 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O17">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P17">
-        <v>1.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q17">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="R17">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="S17">
-        <v>1.09</v>
+        <v>1.87</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="V17">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="W17">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4986,10 +4986,10 @@
         <v>2.8</v>
       </c>
       <c r="G18">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="H18">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I18">
         <v>2.58</v>
@@ -4998,10 +4998,10 @@
         <v>3.95</v>
       </c>
       <c r="K18">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M18">
         <v>1.03</v>
@@ -5013,28 +5013,28 @@
         <v>1.15</v>
       </c>
       <c r="P18">
-        <v>1.56</v>
+        <v>2.26</v>
       </c>
       <c r="Q18">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R18">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S18">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
         <v>1.63</v>
       </c>
       <c r="W18">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X18">
         <v>29</v>
@@ -5049,7 +5049,7 @@
         <v>38</v>
       </c>
       <c r="AB18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC18">
         <v>10</v>
@@ -5061,7 +5061,7 @@
         <v>22</v>
       </c>
       <c r="AF18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG18">
         <v>13.5</v>
@@ -5079,7 +5079,7 @@
         <v>29</v>
       </c>
       <c r="AL18">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM18">
         <v>50</v>
@@ -5106,7 +5106,7 @@
         <v>16.5</v>
       </c>
       <c r="AU18">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AV18">
         <v>11</v>
@@ -5118,7 +5118,7 @@
         <v>21</v>
       </c>
       <c r="AY18">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ18">
         <v>13</v>
@@ -5136,13 +5136,13 @@
         <v>26</v>
       </c>
       <c r="BE18">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF18">
         <v>13</v>
       </c>
       <c r="BG18">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5225,22 +5225,22 @@
         <v>157</v>
       </c>
       <c r="F19">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="H19">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J19">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="K19">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5249,34 +5249,34 @@
         <v>1.06</v>
       </c>
       <c r="N19">
-        <v>1.26</v>
+        <v>3.4</v>
       </c>
       <c r="O19">
         <v>1.34</v>
       </c>
       <c r="P19">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="Q19">
-        <v>1.34</v>
+        <v>1.86</v>
       </c>
       <c r="R19">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="S19">
-        <v>1.34</v>
+        <v>3.35</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V19">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5387,10 +5387,10 @@
         <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI19">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
@@ -5467,22 +5467,22 @@
         <v>158</v>
       </c>
       <c r="F20">
-        <v>1.23</v>
+        <v>2.12</v>
       </c>
       <c r="G20">
-        <v>110</v>
+        <v>2.34</v>
       </c>
       <c r="H20">
-        <v>1.27</v>
+        <v>2.96</v>
       </c>
       <c r="I20">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="J20">
-        <v>1.14</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>110</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5491,202 +5491,202 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P20">
-        <v>1.3</v>
+        <v>2.74</v>
       </c>
       <c r="Q20">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="R20">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="S20">
-        <v>1.12</v>
+        <v>2.12</v>
       </c>
       <c r="T20">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V20">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.74</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO20">
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>24</v>
+        <v>2.4</v>
       </c>
       <c r="AQ20">
-        <v>17.5</v>
+        <v>2.34</v>
       </c>
       <c r="AR20">
         <v>19.5</v>
       </c>
       <c r="AS20">
-        <v>36</v>
+        <v>2.46</v>
       </c>
       <c r="AT20">
-        <v>13</v>
+        <v>2.3</v>
       </c>
       <c r="AU20">
-        <v>8.6</v>
+        <v>2.2</v>
       </c>
       <c r="AV20">
         <v>10</v>
       </c>
       <c r="AW20">
-        <v>21</v>
+        <v>2.4</v>
       </c>
       <c r="AX20">
-        <v>13.5</v>
+        <v>2.32</v>
       </c>
       <c r="AY20">
-        <v>8.800000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="AZ20">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BA20">
-        <v>22</v>
+        <v>2.4</v>
       </c>
       <c r="BB20">
-        <v>23</v>
+        <v>2.4</v>
       </c>
       <c r="BC20">
-        <v>15</v>
+        <v>2.34</v>
       </c>
       <c r="BD20">
         <v>17.5</v>
       </c>
       <c r="BE20">
-        <v>28</v>
+        <v>2.46</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="CB20" t="s">
         <v>167</v>
@@ -5709,46 +5709,46 @@
         <v>159</v>
       </c>
       <c r="F21">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="G21">
-        <v>110</v>
+        <v>4.3</v>
       </c>
       <c r="H21">
-        <v>1.16</v>
+        <v>1.95</v>
       </c>
       <c r="I21">
-        <v>12.5</v>
+        <v>2.1</v>
       </c>
       <c r="J21">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M21">
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>1.61</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>1.61</v>
+        <v>2.46</v>
       </c>
       <c r="Q21">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="R21">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="S21">
-        <v>1.16</v>
+        <v>1.84</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5757,19 +5757,19 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X21">
         <v>1000</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA21">
         <v>1000</v>
@@ -5787,19 +5787,19 @@
         <v>1000</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK21">
         <v>1000</v>
@@ -5814,121 +5814,121 @@
         <v>1000</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP21">
-        <v>19.5</v>
+        <v>1.58</v>
       </c>
       <c r="AQ21">
+        <v>10</v>
+      </c>
+      <c r="AR21">
+        <v>1.46</v>
+      </c>
+      <c r="AS21">
+        <v>1.58</v>
+      </c>
+      <c r="AT21">
+        <v>1.58</v>
+      </c>
+      <c r="AU21">
+        <v>1.58</v>
+      </c>
+      <c r="AV21">
+        <v>1.58</v>
+      </c>
+      <c r="AW21">
+        <v>1.58</v>
+      </c>
+      <c r="AX21">
+        <v>1.52</v>
+      </c>
+      <c r="AY21">
+        <v>1.46</v>
+      </c>
+      <c r="AZ21">
+        <v>1.46</v>
+      </c>
+      <c r="BA21">
+        <v>19</v>
+      </c>
+      <c r="BB21">
+        <v>1.55</v>
+      </c>
+      <c r="BC21">
+        <v>1.58</v>
+      </c>
+      <c r="BD21">
+        <v>1.58</v>
+      </c>
+      <c r="BE21">
+        <v>1.58</v>
+      </c>
+      <c r="BF21">
+        <v>1.58</v>
+      </c>
+      <c r="BG21">
+        <v>1.39</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>2.2</v>
+      </c>
+      <c r="BJ21">
+        <v>12</v>
+      </c>
+      <c r="BK21">
+        <v>1.86</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>2.16</v>
+      </c>
+      <c r="BN21">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR21">
-        <v>11</v>
-      </c>
-      <c r="AS21">
-        <v>18.5</v>
-      </c>
-      <c r="AT21">
-        <v>16</v>
-      </c>
-      <c r="AU21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV21">
+      <c r="BO21">
+        <v>5.1</v>
+      </c>
+      <c r="BP21">
+        <v>34</v>
+      </c>
+      <c r="BQ21">
+        <v>2.06</v>
+      </c>
+      <c r="BR21">
+        <v>40</v>
+      </c>
+      <c r="BS21">
+        <v>2.08</v>
+      </c>
+      <c r="BT21">
+        <v>6.6</v>
+      </c>
+      <c r="BU21">
+        <v>3.65</v>
+      </c>
+      <c r="BV21">
+        <v>15.5</v>
+      </c>
+      <c r="BW21">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW21">
-        <v>13</v>
-      </c>
-      <c r="AX21">
-        <v>22</v>
-      </c>
-      <c r="AY21">
-        <v>11.5</v>
-      </c>
-      <c r="AZ21">
-        <v>11</v>
-      </c>
-      <c r="BA21">
-        <v>18</v>
-      </c>
-      <c r="BB21">
-        <v>40</v>
-      </c>
-      <c r="BC21">
-        <v>25</v>
-      </c>
-      <c r="BD21">
-        <v>26</v>
-      </c>
-      <c r="BE21">
-        <v>34</v>
-      </c>
-      <c r="BF21">
-        <v>1.01</v>
-      </c>
-      <c r="BG21">
-        <v>1.01</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.01</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
-        <v>1.01</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>1.01</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>1.01</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>1.01</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>1.01</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
-      <c r="BU21">
-        <v>1.01</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
-        <v>1.01</v>
-      </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="CB21" t="s">
         <v>167</v>
@@ -5951,46 +5951,46 @@
         <v>160</v>
       </c>
       <c r="F22">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="G22">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="H22">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="I22">
-        <v>110</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M22">
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="O22">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P22">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q22">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="R22">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -5999,10 +5999,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W22">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6059,52 +6059,52 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -6193,22 +6193,22 @@
         <v>161</v>
       </c>
       <c r="F23">
-        <v>1.06</v>
+        <v>3.8</v>
       </c>
       <c r="G23">
-        <v>110</v>
+        <v>4.5</v>
       </c>
       <c r="H23">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="I23">
-        <v>970</v>
+        <v>2.18</v>
       </c>
       <c r="J23">
-        <v>1.06</v>
+        <v>3.4</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6217,142 +6217,142 @@
         <v>1.06</v>
       </c>
       <c r="N23">
+        <v>3.4</v>
+      </c>
+      <c r="O23">
+        <v>1.31</v>
+      </c>
+      <c r="P23">
+        <v>1.85</v>
+      </c>
+      <c r="Q23">
+        <v>1.98</v>
+      </c>
+      <c r="R23">
+        <v>1.31</v>
+      </c>
+      <c r="S23">
+        <v>3.35</v>
+      </c>
+      <c r="T23">
+        <v>1.76</v>
+      </c>
+      <c r="U23">
+        <v>1.01</v>
+      </c>
+      <c r="V23">
+        <v>1.84</v>
+      </c>
+      <c r="W23">
+        <v>1.29</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>11.5</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>34</v>
+      </c>
+      <c r="AB23">
+        <v>18.5</v>
+      </c>
+      <c r="AC23">
+        <v>1000</v>
+      </c>
+      <c r="AD23">
+        <v>1000</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>38</v>
+      </c>
+      <c r="AG23">
+        <v>21</v>
+      </c>
+      <c r="AH23">
+        <v>1000</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>1000</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>1.33</v>
+      </c>
+      <c r="AQ23">
+        <v>1.19</v>
+      </c>
+      <c r="AR23">
+        <v>1.33</v>
+      </c>
+      <c r="AS23">
+        <v>17.5</v>
+      </c>
+      <c r="AT23">
+        <v>10</v>
+      </c>
+      <c r="AU23">
+        <v>1.33</v>
+      </c>
+      <c r="AV23">
+        <v>1.33</v>
+      </c>
+      <c r="AW23">
+        <v>1.33</v>
+      </c>
+      <c r="AX23">
+        <v>1.28</v>
+      </c>
+      <c r="AY23">
         <v>1.25</v>
       </c>
-      <c r="O23">
-        <v>1.3</v>
-      </c>
-      <c r="P23">
-        <v>1.25</v>
-      </c>
-      <c r="Q23">
-        <v>1.3</v>
-      </c>
-      <c r="R23">
-        <v>1.18</v>
-      </c>
-      <c r="S23">
-        <v>1.3</v>
-      </c>
-      <c r="T23">
-        <v>1.01</v>
-      </c>
-      <c r="U23">
-        <v>1.01</v>
-      </c>
-      <c r="V23">
-        <v>1.01</v>
-      </c>
-      <c r="W23">
-        <v>1.01</v>
-      </c>
-      <c r="X23">
-        <v>1000</v>
-      </c>
-      <c r="Y23">
-        <v>1000</v>
-      </c>
-      <c r="Z23">
-        <v>1000</v>
-      </c>
-      <c r="AA23">
-        <v>1000</v>
-      </c>
-      <c r="AB23">
-        <v>1000</v>
-      </c>
-      <c r="AC23">
-        <v>1000</v>
-      </c>
-      <c r="AD23">
-        <v>1000</v>
-      </c>
-      <c r="AE23">
-        <v>1000</v>
-      </c>
-      <c r="AF23">
-        <v>1000</v>
-      </c>
-      <c r="AG23">
-        <v>1000</v>
-      </c>
-      <c r="AH23">
-        <v>1000</v>
-      </c>
-      <c r="AI23">
-        <v>1000</v>
-      </c>
-      <c r="AJ23">
-        <v>1000</v>
-      </c>
-      <c r="AK23">
-        <v>1000</v>
-      </c>
-      <c r="AL23">
-        <v>1000</v>
-      </c>
-      <c r="AM23">
-        <v>1000</v>
-      </c>
-      <c r="AN23">
-        <v>1000</v>
-      </c>
-      <c r="AO23">
-        <v>1000</v>
-      </c>
-      <c r="AP23">
-        <v>1.01</v>
-      </c>
-      <c r="AQ23">
-        <v>1.01</v>
-      </c>
-      <c r="AR23">
-        <v>1.01</v>
-      </c>
-      <c r="AS23">
-        <v>1.01</v>
-      </c>
-      <c r="AT23">
-        <v>1.01</v>
-      </c>
-      <c r="AU23">
-        <v>1.01</v>
-      </c>
-      <c r="AV23">
-        <v>1.01</v>
-      </c>
-      <c r="AW23">
-        <v>1.01</v>
-      </c>
-      <c r="AX23">
-        <v>1.01</v>
-      </c>
-      <c r="AY23">
-        <v>1.01</v>
-      </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6361,58 +6361,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="CB23" t="s">
         <v>167</v>
@@ -6435,22 +6435,22 @@
         <v>162</v>
       </c>
       <c r="F24">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="H24">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I24">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J24">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6459,22 +6459,22 @@
         <v>1.06</v>
       </c>
       <c r="N24">
+        <v>3.15</v>
+      </c>
+      <c r="O24">
         <v>1.24</v>
       </c>
-      <c r="O24">
-        <v>1.06</v>
-      </c>
       <c r="P24">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q24">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="R24">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S24">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6483,10 +6483,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6677,22 +6677,22 @@
         <v>163</v>
       </c>
       <c r="F25">
-        <v>1.07</v>
+        <v>2.72</v>
       </c>
       <c r="G25">
-        <v>110</v>
+        <v>3.35</v>
       </c>
       <c r="H25">
-        <v>1.07</v>
+        <v>2.62</v>
       </c>
       <c r="I25">
-        <v>110</v>
+        <v>2.96</v>
       </c>
       <c r="J25">
-        <v>1.13</v>
+        <v>2.76</v>
       </c>
       <c r="K25">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6701,22 +6701,22 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.24</v>
+        <v>2.72</v>
       </c>
       <c r="O25">
         <v>1.4</v>
       </c>
       <c r="P25">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="Q25">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="R25">
         <v>1.18</v>
       </c>
       <c r="S25">
-        <v>1.4</v>
+        <v>3.55</v>
       </c>
       <c r="T25">
         <v>1.01</v>
@@ -6725,10 +6725,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6785,52 +6785,52 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
         <v>1.01</v>
@@ -6919,112 +6919,112 @@
         <v>164</v>
       </c>
       <c r="F26">
-        <v>1.21</v>
+        <v>3.6</v>
       </c>
       <c r="G26">
+        <v>4.1</v>
+      </c>
+      <c r="H26">
+        <v>2.18</v>
+      </c>
+      <c r="I26">
+        <v>2.36</v>
+      </c>
+      <c r="J26">
+        <v>3</v>
+      </c>
+      <c r="K26">
+        <v>3.35</v>
+      </c>
+      <c r="L26">
+        <v>1.48</v>
+      </c>
+      <c r="M26">
+        <v>1.01</v>
+      </c>
+      <c r="N26">
+        <v>2.58</v>
+      </c>
+      <c r="O26">
+        <v>1.32</v>
+      </c>
+      <c r="P26">
+        <v>1.56</v>
+      </c>
+      <c r="Q26">
+        <v>2.34</v>
+      </c>
+      <c r="R26">
+        <v>1.2</v>
+      </c>
+      <c r="S26">
+        <v>2.82</v>
+      </c>
+      <c r="T26">
+        <v>1.01</v>
+      </c>
+      <c r="U26">
+        <v>1.01</v>
+      </c>
+      <c r="V26">
+        <v>1.73</v>
+      </c>
+      <c r="W26">
+        <v>1.32</v>
+      </c>
+      <c r="X26">
+        <v>11.5</v>
+      </c>
+      <c r="Y26">
+        <v>7</v>
+      </c>
+      <c r="Z26">
+        <v>15</v>
+      </c>
+      <c r="AA26">
+        <v>40</v>
+      </c>
+      <c r="AB26">
+        <v>10.5</v>
+      </c>
+      <c r="AC26">
+        <v>8.4</v>
+      </c>
+      <c r="AD26">
+        <v>12</v>
+      </c>
+      <c r="AE26">
+        <v>40</v>
+      </c>
+      <c r="AF26">
+        <v>32</v>
+      </c>
+      <c r="AG26">
+        <v>21</v>
+      </c>
+      <c r="AH26">
+        <v>34</v>
+      </c>
+      <c r="AI26">
+        <v>75</v>
+      </c>
+      <c r="AJ26">
+        <v>120</v>
+      </c>
+      <c r="AK26">
+        <v>80</v>
+      </c>
+      <c r="AL26">
         <v>110</v>
       </c>
-      <c r="H26">
-        <v>1.21</v>
-      </c>
-      <c r="I26">
-        <v>110</v>
-      </c>
-      <c r="J26">
-        <v>1.06</v>
-      </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
-      <c r="L26">
-        <v>1.01</v>
-      </c>
-      <c r="M26">
-        <v>1.01</v>
-      </c>
-      <c r="N26">
-        <v>1.24</v>
-      </c>
-      <c r="O26">
-        <v>1.01</v>
-      </c>
-      <c r="P26">
-        <v>1.24</v>
-      </c>
-      <c r="Q26">
-        <v>1.01</v>
-      </c>
-      <c r="R26">
-        <v>1.14</v>
-      </c>
-      <c r="S26">
-        <v>1.01</v>
-      </c>
-      <c r="T26">
-        <v>1.01</v>
-      </c>
-      <c r="U26">
-        <v>1.01</v>
-      </c>
-      <c r="V26">
-        <v>1.01</v>
-      </c>
-      <c r="W26">
-        <v>1.01</v>
-      </c>
-      <c r="X26">
-        <v>1000</v>
-      </c>
-      <c r="Y26">
-        <v>1000</v>
-      </c>
-      <c r="Z26">
-        <v>1000</v>
-      </c>
-      <c r="AA26">
-        <v>1000</v>
-      </c>
-      <c r="AB26">
-        <v>1000</v>
-      </c>
-      <c r="AC26">
-        <v>1000</v>
-      </c>
-      <c r="AD26">
-        <v>1000</v>
-      </c>
-      <c r="AE26">
-        <v>1000</v>
-      </c>
-      <c r="AF26">
-        <v>1000</v>
-      </c>
-      <c r="AG26">
-        <v>1000</v>
-      </c>
-      <c r="AH26">
-        <v>1000</v>
-      </c>
-      <c r="AI26">
-        <v>1000</v>
-      </c>
-      <c r="AJ26">
-        <v>1000</v>
-      </c>
-      <c r="AK26">
-        <v>1000</v>
-      </c>
-      <c r="AL26">
-        <v>1000</v>
-      </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP26">
         <v>1.01</v>
@@ -7060,22 +7060,22 @@
         <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG26">
         <v>1.01</v>
@@ -7403,31 +7403,31 @@
         <v>166</v>
       </c>
       <c r="F28">
-        <v>1.08</v>
+        <v>1.86</v>
       </c>
       <c r="G28">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I28">
-        <v>110</v>
+        <v>5.4</v>
       </c>
       <c r="J28">
-        <v>1.06</v>
+        <v>3.4</v>
       </c>
       <c r="K28">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O28">
         <v>1.39</v>
@@ -7436,13 +7436,13 @@
         <v>1.25</v>
       </c>
       <c r="Q28">
-        <v>1.39</v>
+        <v>2.24</v>
       </c>
       <c r="R28">
         <v>1.18</v>
       </c>
       <c r="S28">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -7451,52 +7451,52 @@
         <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA28">
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI28">
         <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL28">
         <v>1000</v>
@@ -7511,58 +7511,58 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>9.4</v>
+        <v>2.38</v>
       </c>
       <c r="AQ28">
         <v>10</v>
       </c>
       <c r="AR28">
-        <v>24</v>
+        <v>2.78</v>
       </c>
       <c r="AS28">
-        <v>65</v>
+        <v>2.96</v>
       </c>
       <c r="AT28">
-        <v>6.2</v>
+        <v>2.24</v>
       </c>
       <c r="AU28">
-        <v>6.4</v>
+        <v>2.28</v>
       </c>
       <c r="AV28">
-        <v>15.5</v>
+        <v>2.64</v>
       </c>
       <c r="AW28">
-        <v>42</v>
+        <v>2.86</v>
       </c>
       <c r="AX28">
-        <v>8.800000000000001</v>
+        <v>2.44</v>
       </c>
       <c r="AY28">
-        <v>9</v>
+        <v>2.42</v>
       </c>
       <c r="AZ28">
-        <v>17.5</v>
+        <v>2.66</v>
       </c>
       <c r="BA28">
-        <v>55</v>
+        <v>2.96</v>
       </c>
       <c r="BB28">
-        <v>17.5</v>
+        <v>2.68</v>
       </c>
       <c r="BC28">
-        <v>17.5</v>
+        <v>2.68</v>
       </c>
       <c r="BD28">
-        <v>30</v>
+        <v>2.96</v>
       </c>
       <c r="BE28">
-        <v>90</v>
+        <v>2.96</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7571,58 +7571,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="CB28" t="s">
         <v>167</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -517,7 +517,7 @@
     <t>CD Nacional Funchal</t>
   </si>
   <si>
-    <t>2026-08-08 20:28:56</t>
+    <t>2026-08-08 22:45:38</t>
   </si>
 </sst>
 </file>
@@ -1111,166 +1111,166 @@
         <v>140</v>
       </c>
       <c r="F2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G2">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H2">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
+        <v>4.1</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
         <v>3.95</v>
-      </c>
-      <c r="L2">
-        <v>1.01</v>
-      </c>
-      <c r="M2">
-        <v>1.07</v>
-      </c>
-      <c r="N2">
-        <v>3.9</v>
       </c>
       <c r="O2">
         <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="U2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W2">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
         <v>21</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AK2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL2">
+        <v>38</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>11</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>13.5</v>
+      </c>
+      <c r="AQ2">
+        <v>15.5</v>
+      </c>
+      <c r="AR2">
+        <v>34</v>
+      </c>
+      <c r="AS2">
         <v>40</v>
       </c>
-      <c r="AM2">
-        <v>110</v>
-      </c>
-      <c r="AN2">
-        <v>11.5</v>
-      </c>
-      <c r="AO2">
-        <v>100</v>
-      </c>
-      <c r="AP2">
-        <v>11.5</v>
-      </c>
-      <c r="AQ2">
-        <v>12.5</v>
-      </c>
-      <c r="AR2">
-        <v>6.2</v>
-      </c>
-      <c r="AS2">
-        <v>6.8</v>
-      </c>
       <c r="AT2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV2">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AW2">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="AX2">
         <v>9.4</v>
       </c>
       <c r="AY2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BB2">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BC2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BE2">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="BF2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1353,10 +1353,10 @@
         <v>141</v>
       </c>
       <c r="F3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H3">
         <v>3.05</v>
@@ -1365,13 +1365,13 @@
         <v>3.6</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M3">
         <v>1.11</v>
@@ -1380,7 +1380,7 @@
         <v>2.68</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P3">
         <v>1.56</v>
@@ -1389,13 +1389,13 @@
         <v>2.48</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
         <v>4.9</v>
       </c>
       <c r="T3">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U3">
         <v>1.82</v>
@@ -1413,7 +1413,7 @@
         <v>12</v>
       </c>
       <c r="Z3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA3">
         <v>80</v>
@@ -1422,22 +1422,22 @@
         <v>10</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE3">
         <v>60</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI3">
         <v>85</v>
@@ -1446,7 +1446,7 @@
         <v>55</v>
       </c>
       <c r="AK3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL3">
         <v>75</v>
@@ -1595,43 +1595,43 @@
         <v>142</v>
       </c>
       <c r="F4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="H4">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="I4">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J4">
         <v>2.9</v>
       </c>
       <c r="K4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L4">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="O4">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P4">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="Q4">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
         <v>5.3</v>
@@ -1640,19 +1640,19 @@
         <v>2.12</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="V4">
         <v>1.52</v>
       </c>
       <c r="W4">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X4">
         <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z4">
         <v>20</v>
@@ -1682,7 +1682,7 @@
         <v>28</v>
       </c>
       <c r="AI4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ4">
         <v>75</v>
@@ -1703,7 +1703,7 @@
         <v>60</v>
       </c>
       <c r="AP4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4">
         <v>7</v>
@@ -1712,7 +1712,7 @@
         <v>14</v>
       </c>
       <c r="AS4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT4">
         <v>7.8</v>
@@ -1724,7 +1724,7 @@
         <v>11</v>
       </c>
       <c r="AW4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX4">
         <v>14.5</v>
@@ -1736,85 +1736,85 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
+        <v>4.2</v>
+      </c>
+      <c r="BB4">
+        <v>4.2</v>
+      </c>
+      <c r="BC4">
         <v>4.1</v>
       </c>
-      <c r="BB4">
+      <c r="BD4">
+        <v>4.2</v>
+      </c>
+      <c r="BE4">
+        <v>4.4</v>
+      </c>
+      <c r="BF4">
+        <v>4.2</v>
+      </c>
+      <c r="BG4">
         <v>4.1</v>
       </c>
-      <c r="BC4">
-        <v>4</v>
-      </c>
-      <c r="BD4">
-        <v>4.1</v>
-      </c>
-      <c r="BE4">
+      <c r="BH4">
+        <v>2.72</v>
+      </c>
+      <c r="BI4">
+        <v>2.26</v>
+      </c>
+      <c r="BJ4">
+        <v>11.5</v>
+      </c>
+      <c r="BK4">
+        <v>6</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>12.5</v>
+      </c>
+      <c r="BN4">
+        <v>6.2</v>
+      </c>
+      <c r="BO4">
+        <v>4.6</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>9.4</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>10.5</v>
+      </c>
+      <c r="BT4">
+        <v>5.6</v>
+      </c>
+      <c r="BU4">
         <v>4.2</v>
       </c>
-      <c r="BF4">
-        <v>4.1</v>
-      </c>
-      <c r="BG4">
-        <v>4</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>1.33</v>
-      </c>
-      <c r="BJ4">
-        <v>16</v>
-      </c>
-      <c r="BK4">
-        <v>1.23</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.33</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>1.33</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.33</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.31</v>
-      </c>
-      <c r="BT4">
-        <v>7.8</v>
-      </c>
-      <c r="BU4">
-        <v>3.7</v>
-      </c>
       <c r="BV4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.33</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.31</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>167</v>
@@ -1840,91 +1840,91 @@
         <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H5">
         <v>3.1</v>
       </c>
       <c r="I5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J5">
         <v>3.25</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AA5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB5">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AD5">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AG5">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>50</v>
@@ -1933,70 +1933,70 @@
         <v>44</v>
       </c>
       <c r="AL5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP5">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>2.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AS5">
-        <v>2.28</v>
+        <v>38</v>
       </c>
       <c r="AT5">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>1.91</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>2.26</v>
+        <v>27</v>
       </c>
       <c r="AX5">
+        <v>13.5</v>
+      </c>
+      <c r="AY5">
         <v>10.5</v>
       </c>
-      <c r="AY5">
-        <v>2.06</v>
-      </c>
       <c r="AZ5">
-        <v>2.16</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>2.28</v>
+        <v>38</v>
       </c>
       <c r="BB5">
-        <v>2.24</v>
+        <v>26</v>
       </c>
       <c r="BC5">
-        <v>2.24</v>
+        <v>21</v>
       </c>
       <c r="BD5">
-        <v>2.28</v>
+        <v>8.6</v>
       </c>
       <c r="BE5">
-        <v>2.36</v>
+        <v>9.6</v>
       </c>
       <c r="BF5">
-        <v>2.36</v>
+        <v>20</v>
       </c>
       <c r="BG5">
-        <v>2.36</v>
+        <v>8.6</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2578,10 +2578,10 @@
         <v>3.55</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="M8">
         <v>1.05</v>
@@ -2599,7 +2599,7 @@
         <v>1.69</v>
       </c>
       <c r="R8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S8">
         <v>2.96</v>
@@ -2725,13 +2725,13 @@
         <v>4.6</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BK8">
         <v>6.2</v>
@@ -2743,16 +2743,16 @@
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BO8">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="BP8">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BQ8">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR8">
         <v>34</v>
@@ -2761,13 +2761,13 @@
         <v>17</v>
       </c>
       <c r="BT8">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BU8">
         <v>4.9</v>
       </c>
       <c r="BV8">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BW8">
         <v>18.5</v>
@@ -2805,7 +2805,7 @@
         <v>147</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G9">
         <v>3.5</v>
@@ -2820,22 +2820,22 @@
         <v>2.78</v>
       </c>
       <c r="K9">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P9">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="Q9">
         <v>2.74</v>
@@ -2847,10 +2847,10 @@
         <v>5.1</v>
       </c>
       <c r="T9">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="V9">
         <v>1.5</v>
@@ -2859,91 +2859,91 @@
         <v>1.4</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS9">
         <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW9">
         <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA9">
         <v>1.01</v>
@@ -3050,7 +3050,7 @@
         <v>2.22</v>
       </c>
       <c r="G10">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H10">
         <v>3.3</v>
@@ -3098,7 +3098,7 @@
         <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3313,7 +3313,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="O11">
         <v>1.21</v>
@@ -3454,55 +3454,55 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ11">
         <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>6.6</v>
+        <v>1.78</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.199999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="BN11">
         <v>5.8</v>
       </c>
       <c r="BO11">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="BP11">
         <v>14.5</v>
       </c>
       <c r="BQ11">
-        <v>7.4</v>
+        <v>1.82</v>
       </c>
       <c r="BR11">
         <v>30</v>
       </c>
       <c r="BS11">
-        <v>9.199999999999999</v>
+        <v>1.94</v>
       </c>
       <c r="BT11">
         <v>12</v>
       </c>
       <c r="BU11">
-        <v>6.2</v>
+        <v>1.77</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3561,7 +3561,7 @@
         <v>1.38</v>
       </c>
       <c r="P12">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q12">
         <v>2.1</v>
@@ -3776,16 +3776,16 @@
         <v>2.3</v>
       </c>
       <c r="G13">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H13">
         <v>3.05</v>
       </c>
       <c r="I13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K13">
         <v>3.8</v>
@@ -3797,34 +3797,34 @@
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P13">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="Q13">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R13">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S13">
         <v>3</v>
       </c>
       <c r="T13">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V13">
         <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X13">
         <v>19.5</v>
@@ -3833,31 +3833,31 @@
         <v>17</v>
       </c>
       <c r="Z13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA13">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB13">
         <v>14</v>
       </c>
       <c r="AC13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD13">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF13">
         <v>19.5</v>
       </c>
       <c r="AG13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH13">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI13">
         <v>55</v>
@@ -3866,34 +3866,34 @@
         <v>34</v>
       </c>
       <c r="AK13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM13">
         <v>100</v>
       </c>
       <c r="AN13">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AO13">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AP13">
         <v>13.5</v>
       </c>
       <c r="AQ13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR13">
         <v>19.5</v>
       </c>
       <c r="AS13">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT13">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU13">
         <v>7.2</v>
@@ -3902,7 +3902,7 @@
         <v>10</v>
       </c>
       <c r="AW13">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX13">
         <v>11.5</v>
@@ -3923,16 +3923,16 @@
         <v>20</v>
       </c>
       <c r="BD13">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE13">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF13">
         <v>13</v>
       </c>
       <c r="BG13">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4018,7 +4018,7 @@
         <v>1.34</v>
       </c>
       <c r="G14">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H14">
         <v>9.800000000000001</v>
@@ -4027,7 +4027,7 @@
         <v>11.5</v>
       </c>
       <c r="J14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K14">
         <v>6.4</v>
@@ -4051,7 +4051,7 @@
         <v>1.41</v>
       </c>
       <c r="R14">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S14">
         <v>2</v>
@@ -4066,19 +4066,19 @@
         <v>1.09</v>
       </c>
       <c r="W14">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="X14">
         <v>42</v>
       </c>
       <c r="Y14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z14">
         <v>120</v>
       </c>
       <c r="AA14">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AB14">
         <v>15</v>
@@ -4141,10 +4141,10 @@
         <v>5.7</v>
       </c>
       <c r="AV14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW14">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX14">
         <v>9.800000000000001</v>
@@ -4153,10 +4153,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB14">
         <v>10.5</v>
@@ -4266,7 +4266,7 @@
         <v>1.84</v>
       </c>
       <c r="I15">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4281,16 +4281,16 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>2.56</v>
+        <v>5.3</v>
       </c>
       <c r="O15">
         <v>1.17</v>
       </c>
       <c r="P15">
-        <v>1.56</v>
+        <v>2.48</v>
       </c>
       <c r="Q15">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="R15">
         <v>1.55</v>
@@ -4302,10 +4302,10 @@
         <v>1.01</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V15">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W15">
         <v>1.29</v>
@@ -4499,7 +4499,7 @@
         <v>154</v>
       </c>
       <c r="F16">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G16">
         <v>2.5</v>
@@ -4508,7 +4508,7 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J16">
         <v>3.55</v>
@@ -4562,7 +4562,7 @@
         <v>29</v>
       </c>
       <c r="AA16">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB16">
         <v>14</v>
@@ -4574,7 +4574,7 @@
         <v>17</v>
       </c>
       <c r="AE16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF16">
         <v>20</v>
@@ -4604,7 +4604,7 @@
         <v>18</v>
       </c>
       <c r="AO16">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AP16">
         <v>12</v>
@@ -4756,7 +4756,7 @@
         <v>4.4</v>
       </c>
       <c r="K17">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4849,7 +4849,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP17">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
         <v>16</v>
@@ -4873,7 +4873,7 @@
         <v>16.5</v>
       </c>
       <c r="AX17">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
         <v>11.5</v>
@@ -4885,7 +4885,7 @@
         <v>16</v>
       </c>
       <c r="BB17">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
         <v>20</v>
@@ -4894,7 +4894,7 @@
         <v>19.5</v>
       </c>
       <c r="BE17">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>9.6</v>
@@ -5007,28 +5007,28 @@
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="O18">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P18">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="Q18">
         <v>1.53</v>
       </c>
       <c r="R18">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="S18">
         <v>2.3</v>
       </c>
       <c r="T18">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="V18">
         <v>1.63</v>
@@ -5037,19 +5037,19 @@
         <v>1.53</v>
       </c>
       <c r="X18">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z18">
         <v>21</v>
       </c>
       <c r="AA18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB18">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AC18">
         <v>10</v>
@@ -5058,28 +5058,28 @@
         <v>12.5</v>
       </c>
       <c r="AE18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF18">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG18">
         <v>13.5</v>
       </c>
       <c r="AH18">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AI18">
+        <v>28</v>
+      </c>
+      <c r="AJ18">
+        <v>42</v>
+      </c>
+      <c r="AK18">
+        <v>26</v>
+      </c>
+      <c r="AL18">
         <v>30</v>
-      </c>
-      <c r="AJ18">
-        <v>48</v>
-      </c>
-      <c r="AK18">
-        <v>29</v>
-      </c>
-      <c r="AL18">
-        <v>32</v>
       </c>
       <c r="AM18">
         <v>50</v>
@@ -5106,7 +5106,7 @@
         <v>16.5</v>
       </c>
       <c r="AU18">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AV18">
         <v>11</v>
@@ -5118,7 +5118,7 @@
         <v>21</v>
       </c>
       <c r="AY18">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18">
         <v>13</v>
@@ -5136,13 +5136,13 @@
         <v>26</v>
       </c>
       <c r="BE18">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BF18">
         <v>13</v>
       </c>
       <c r="BG18">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5234,10 +5234,10 @@
         <v>2.96</v>
       </c>
       <c r="I19">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J19">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K19">
         <v>4</v>
@@ -5264,16 +5264,16 @@
         <v>1.25</v>
       </c>
       <c r="S19">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T19">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U19">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
         <v>1.57</v>
@@ -5515,7 +5515,7 @@
         <v>2.46</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
         <v>1.74</v>
@@ -5709,7 +5709,7 @@
         <v>159</v>
       </c>
       <c r="F21">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G21">
         <v>4.3</v>
@@ -5733,7 +5733,7 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="O21">
         <v>1.16</v>
@@ -5745,10 +5745,10 @@
         <v>1.4</v>
       </c>
       <c r="R21">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S21">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5766,10 +5766,10 @@
         <v>1000</v>
       </c>
       <c r="Y21">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z21">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA21">
         <v>1000</v>
@@ -5802,7 +5802,7 @@
         <v>80</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL21">
         <v>1000</v>
@@ -5817,58 +5817,58 @@
         <v>11.5</v>
       </c>
       <c r="AP21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AQ21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR21">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AS21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AT21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AU21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AV21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AW21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AX21">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AY21">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AZ21">
-        <v>1.46</v>
+        <v>11</v>
       </c>
       <c r="BA21">
         <v>19</v>
       </c>
       <c r="BB21">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BC21">
         <v>1.58</v>
       </c>
       <c r="BD21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="BE21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="BF21">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="BG21">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5951,7 +5951,7 @@
         <v>160</v>
       </c>
       <c r="F22">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G22">
         <v>1.69</v>
@@ -5984,7 +5984,7 @@
         <v>1.87</v>
       </c>
       <c r="Q22">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="R22">
         <v>1.35</v>
@@ -6199,7 +6199,7 @@
         <v>4.5</v>
       </c>
       <c r="H23">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I23">
         <v>2.18</v>
@@ -6214,145 +6214,145 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N23">
+        <v>3.55</v>
+      </c>
+      <c r="O23">
+        <v>1.33</v>
+      </c>
+      <c r="P23">
+        <v>1.86</v>
+      </c>
+      <c r="Q23">
+        <v>2</v>
+      </c>
+      <c r="R23">
+        <v>1.32</v>
+      </c>
+      <c r="S23">
         <v>3.4</v>
       </c>
-      <c r="O23">
-        <v>1.31</v>
-      </c>
-      <c r="P23">
-        <v>1.85</v>
-      </c>
-      <c r="Q23">
-        <v>1.98</v>
-      </c>
-      <c r="R23">
-        <v>1.31</v>
-      </c>
-      <c r="S23">
-        <v>3.35</v>
-      </c>
       <c r="T23">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U23">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V23">
         <v>1.84</v>
       </c>
       <c r="W23">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y23">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA23">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AB23">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF23">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AG23">
+        <v>17.5</v>
+      </c>
+      <c r="AH23">
+        <v>23</v>
+      </c>
+      <c r="AI23">
+        <v>48</v>
+      </c>
+      <c r="AJ23">
+        <v>110</v>
+      </c>
+      <c r="AK23">
+        <v>65</v>
+      </c>
+      <c r="AL23">
+        <v>65</v>
+      </c>
+      <c r="AM23">
+        <v>130</v>
+      </c>
+      <c r="AN23">
+        <v>70</v>
+      </c>
+      <c r="AO23">
+        <v>20</v>
+      </c>
+      <c r="AP23">
+        <v>10</v>
+      </c>
+      <c r="AQ23">
+        <v>6.8</v>
+      </c>
+      <c r="AR23">
+        <v>9.6</v>
+      </c>
+      <c r="AS23">
         <v>21</v>
       </c>
-      <c r="AH23">
-        <v>1000</v>
-      </c>
-      <c r="AI23">
-        <v>1000</v>
-      </c>
-      <c r="AJ23">
-        <v>1000</v>
-      </c>
-      <c r="AK23">
-        <v>1000</v>
-      </c>
-      <c r="AL23">
-        <v>1000</v>
-      </c>
-      <c r="AM23">
-        <v>1000</v>
-      </c>
-      <c r="AN23">
-        <v>1000</v>
-      </c>
-      <c r="AO23">
-        <v>1000</v>
-      </c>
-      <c r="AP23">
-        <v>1.33</v>
-      </c>
-      <c r="AQ23">
-        <v>1.19</v>
-      </c>
-      <c r="AR23">
-        <v>1.33</v>
-      </c>
-      <c r="AS23">
-        <v>17.5</v>
-      </c>
       <c r="AT23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU23">
-        <v>1.33</v>
+        <v>7.2</v>
       </c>
       <c r="AV23">
-        <v>1.33</v>
+        <v>8</v>
       </c>
       <c r="AW23">
-        <v>1.33</v>
+        <v>16.5</v>
       </c>
       <c r="AX23">
-        <v>1.28</v>
+        <v>4.5</v>
       </c>
       <c r="AY23">
-        <v>1.25</v>
+        <v>12</v>
       </c>
       <c r="AZ23">
-        <v>1.33</v>
+        <v>15.5</v>
       </c>
       <c r="BA23">
-        <v>1.33</v>
+        <v>4.7</v>
       </c>
       <c r="BB23">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="BC23">
-        <v>1.33</v>
+        <v>4.8</v>
       </c>
       <c r="BD23">
-        <v>1.33</v>
+        <v>4.8</v>
       </c>
       <c r="BE23">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="BF23">
-        <v>1.33</v>
+        <v>4.8</v>
       </c>
       <c r="BG23">
-        <v>1.33</v>
+        <v>12</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6447,40 +6447,40 @@
         <v>4.3</v>
       </c>
       <c r="J24">
+        <v>3.45</v>
+      </c>
+      <c r="K24">
+        <v>3.8</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.07</v>
+      </c>
+      <c r="N24">
+        <v>3.3</v>
+      </c>
+      <c r="O24">
+        <v>1.31</v>
+      </c>
+      <c r="P24">
+        <v>1.89</v>
+      </c>
+      <c r="Q24">
+        <v>1.95</v>
+      </c>
+      <c r="R24">
+        <v>1.33</v>
+      </c>
+      <c r="S24">
         <v>3.35</v>
       </c>
-      <c r="K24">
-        <v>3.85</v>
-      </c>
-      <c r="L24">
-        <v>1.01</v>
-      </c>
-      <c r="M24">
-        <v>1.06</v>
-      </c>
-      <c r="N24">
-        <v>3.15</v>
-      </c>
-      <c r="O24">
-        <v>1.24</v>
-      </c>
-      <c r="P24">
-        <v>1.29</v>
-      </c>
-      <c r="Q24">
-        <v>1.83</v>
-      </c>
-      <c r="R24">
-        <v>1.27</v>
-      </c>
-      <c r="S24">
-        <v>3</v>
-      </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V24">
         <v>1.3</v>
@@ -6489,112 +6489,112 @@
         <v>1.81</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6680,28 +6680,28 @@
         <v>2.72</v>
       </c>
       <c r="G25">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H25">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="I25">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="J25">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="K25">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N25">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="O25">
         <v>1.4</v>
@@ -6713,10 +6713,10 @@
         <v>2.16</v>
       </c>
       <c r="R25">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S25">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="T25">
         <v>1.01</v>
@@ -6725,10 +6725,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W25">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6940,13 +6940,13 @@
         <v>1.48</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N26">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O26">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="P26">
         <v>1.56</v>
@@ -6955,16 +6955,16 @@
         <v>2.34</v>
       </c>
       <c r="R26">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S26">
-        <v>2.82</v>
+        <v>1.02</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V26">
         <v>1.73</v>
@@ -7427,28 +7427,28 @@
         <v>1.09</v>
       </c>
       <c r="N28">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P28">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="Q28">
         <v>2.24</v>
       </c>
       <c r="R28">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S28">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V28">
         <v>1.22</v>
@@ -7457,112 +7457,112 @@
         <v>2</v>
       </c>
       <c r="X28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y28">
+        <v>15</v>
+      </c>
+      <c r="Z28">
+        <v>38</v>
+      </c>
+      <c r="AA28">
+        <v>160</v>
+      </c>
+      <c r="AB28">
+        <v>7.8</v>
+      </c>
+      <c r="AC28">
+        <v>8.4</v>
+      </c>
+      <c r="AD28">
+        <v>21</v>
+      </c>
+      <c r="AE28">
+        <v>95</v>
+      </c>
+      <c r="AF28">
+        <v>11.5</v>
+      </c>
+      <c r="AG28">
+        <v>11</v>
+      </c>
+      <c r="AH28">
+        <v>23</v>
+      </c>
+      <c r="AI28">
+        <v>110</v>
+      </c>
+      <c r="AJ28">
+        <v>24</v>
+      </c>
+      <c r="AK28">
+        <v>25</v>
+      </c>
+      <c r="AL28">
+        <v>55</v>
+      </c>
+      <c r="AM28">
+        <v>190</v>
+      </c>
+      <c r="AN28">
         <v>18.5</v>
       </c>
-      <c r="Z28">
-        <v>46</v>
-      </c>
-      <c r="AA28">
-        <v>1000</v>
-      </c>
-      <c r="AB28">
+      <c r="AO28">
+        <v>130</v>
+      </c>
+      <c r="AP28">
+        <v>9.6</v>
+      </c>
+      <c r="AQ28">
+        <v>12</v>
+      </c>
+      <c r="AR28">
+        <v>7</v>
+      </c>
+      <c r="AS28">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT28">
+        <v>6.4</v>
+      </c>
+      <c r="AU28">
+        <v>6.8</v>
+      </c>
+      <c r="AV28">
+        <v>16.5</v>
+      </c>
+      <c r="AW28">
+        <v>7.8</v>
+      </c>
+      <c r="AX28">
         <v>9.4</v>
       </c>
-      <c r="AC28">
-        <v>10</v>
-      </c>
-      <c r="AD28">
-        <v>25</v>
-      </c>
-      <c r="AE28">
-        <v>100</v>
-      </c>
-      <c r="AF28">
-        <v>14</v>
-      </c>
-      <c r="AG28">
-        <v>13.5</v>
-      </c>
-      <c r="AH28">
-        <v>28</v>
-      </c>
-      <c r="AI28">
-        <v>1000</v>
-      </c>
-      <c r="AJ28">
-        <v>29</v>
-      </c>
-      <c r="AK28">
-        <v>29</v>
-      </c>
-      <c r="AL28">
-        <v>1000</v>
-      </c>
-      <c r="AM28">
-        <v>1000</v>
-      </c>
-      <c r="AN28">
-        <v>1000</v>
-      </c>
-      <c r="AO28">
-        <v>1000</v>
-      </c>
-      <c r="AP28">
-        <v>2.38</v>
-      </c>
-      <c r="AQ28">
-        <v>10</v>
-      </c>
-      <c r="AR28">
-        <v>2.78</v>
-      </c>
-      <c r="AS28">
-        <v>2.96</v>
-      </c>
-      <c r="AT28">
-        <v>2.24</v>
-      </c>
-      <c r="AU28">
-        <v>2.28</v>
-      </c>
-      <c r="AV28">
-        <v>2.64</v>
-      </c>
-      <c r="AW28">
-        <v>2.86</v>
-      </c>
-      <c r="AX28">
-        <v>2.44</v>
-      </c>
       <c r="AY28">
-        <v>2.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28">
-        <v>2.66</v>
+        <v>18.5</v>
       </c>
       <c r="BA28">
-        <v>2.96</v>
+        <v>8</v>
       </c>
       <c r="BB28">
-        <v>2.68</v>
+        <v>19</v>
       </c>
       <c r="BC28">
-        <v>2.68</v>
+        <v>19.5</v>
       </c>
       <c r="BD28">
-        <v>2.96</v>
+        <v>7.4</v>
       </c>
       <c r="BE28">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF28">
-        <v>2.96</v>
+        <v>13</v>
       </c>
       <c r="BG28">
-        <v>2.96</v>
+        <v>8</v>
       </c>
       <c r="BH28">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="191">
   <si>
     <t>League</t>
   </si>
@@ -313,6 +313,18 @@
     <t>Portuguese Primeira Liga</t>
   </si>
   <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
     <t>2026-08-10</t>
   </si>
   <si>
@@ -355,6 +367,21 @@
     <t>19:15:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Universidad de Chile</t>
   </si>
   <si>
@@ -391,24 +418,24 @@
     <t>Norrby IF</t>
   </si>
   <si>
+    <t>Vasteras SK</t>
+  </si>
+  <si>
+    <t>Lusitania Futebol Clube</t>
+  </si>
+  <si>
     <t>Sirius</t>
   </si>
   <si>
-    <t>Vasteras SK</t>
+    <t>Moss</t>
   </si>
   <si>
     <t>Benfica B</t>
   </si>
   <si>
-    <t>Moss</t>
-  </si>
-  <si>
     <t>Silkeborg</t>
   </si>
   <si>
-    <t>Lusitania Futebol Clube</t>
-  </si>
-  <si>
     <t>Jong AZ Alkmaar</t>
   </si>
   <si>
@@ -424,18 +451,39 @@
     <t>CFR Cluj</t>
   </si>
   <si>
+    <t>CA Rentistas</t>
+  </si>
+  <si>
     <t>Tecnico Universitario</t>
   </si>
   <si>
-    <t>CA Rentistas</t>
-  </si>
-  <si>
     <t>Fram</t>
   </si>
   <si>
     <t>Santa Clara</t>
   </si>
   <si>
+    <t>Aguilas Doradas</t>
+  </si>
+  <si>
+    <t>Libertad FC</t>
+  </si>
+  <si>
+    <t>Libertad</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Deportivo Maldonado</t>
+  </si>
+  <si>
+    <t>Goias</t>
+  </si>
+  <si>
+    <t>Ind Medellin</t>
+  </si>
+  <si>
     <t>Palestino</t>
   </si>
   <si>
@@ -472,24 +520,24 @@
     <t>Orebro</t>
   </si>
   <si>
+    <t>Djurgardens</t>
+  </si>
+  <si>
+    <t>Porto B</t>
+  </si>
+  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
-    <t>Djurgardens</t>
+    <t>Odds BK</t>
   </si>
   <si>
     <t>Leixoes</t>
   </si>
   <si>
-    <t>Odds BK</t>
-  </si>
-  <si>
     <t>OB</t>
   </si>
   <si>
-    <t>Porto B</t>
-  </si>
-  <si>
     <t>FC Eindhoven</t>
   </si>
   <si>
@@ -505,19 +553,40 @@
     <t>Universitatea Cluj</t>
   </si>
   <si>
+    <t>Plaza Colonia</t>
+  </si>
+  <si>
     <t>Mushuc Runa</t>
   </si>
   <si>
-    <t>Plaza Colonia</t>
-  </si>
-  <si>
     <t>KR Reykjavik</t>
   </si>
   <si>
     <t>CD Nacional Funchal</t>
   </si>
   <si>
-    <t>2026-08-08 22:45:38</t>
+    <t>Llaneros FC</t>
+  </si>
+  <si>
+    <t>Univ Catolica (Ecu)</t>
+  </si>
+  <si>
+    <t>Sportivo Trinidense</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Racing Club (Uru)</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>Millonarios</t>
+  </si>
+  <si>
+    <t>2026-08-09 01:02:42</t>
   </si>
 </sst>
 </file>
@@ -849,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB28"/>
+  <dimension ref="A1:CB35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1099,28 +1168,28 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="F2">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G2">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H2">
         <v>5.2</v>
       </c>
       <c r="I2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J2">
         <v>3.85</v>
@@ -1129,7 +1198,7 @@
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M2">
         <v>1.06</v>
@@ -1156,13 +1225,13 @@
         <v>1.85</v>
       </c>
       <c r="U2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X2">
         <v>16.5</v>
@@ -1219,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
         <v>15.5</v>
@@ -1276,64 +1345,64 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1341,25 +1410,25 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="F3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G3">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I3">
         <v>3.6</v>
@@ -1368,19 +1437,19 @@
         <v>2.98</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
         <v>1.56</v>
@@ -1404,10 +1473,10 @@
         <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y3">
         <v>12</v>
@@ -1470,7 +1539,7 @@
         <v>15.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT3">
         <v>6.2</v>
@@ -1482,7 +1551,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX3">
         <v>11.5</v>
@@ -1494,79 +1563,79 @@
         <v>15.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1575,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1583,16 +1652,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1604,7 +1673,7 @@
         <v>2.68</v>
       </c>
       <c r="I4">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J4">
         <v>2.9</v>
@@ -1619,13 +1688,13 @@
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O4">
         <v>1.54</v>
       </c>
       <c r="P4">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q4">
         <v>2.6</v>
@@ -1673,7 +1742,7 @@
         <v>50</v>
       </c>
       <c r="AF4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG4">
         <v>18</v>
@@ -1724,7 +1793,7 @@
         <v>11</v>
       </c>
       <c r="AW4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX4">
         <v>14.5</v>
@@ -1748,7 +1817,7 @@
         <v>4.2</v>
       </c>
       <c r="BE4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF4">
         <v>4.2</v>
@@ -1757,7 +1826,7 @@
         <v>4.1</v>
       </c>
       <c r="BH4">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BI4">
         <v>2.26</v>
@@ -1772,19 +1841,19 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN4">
         <v>6.2</v>
       </c>
       <c r="BO4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1802,13 +1871,13 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
@@ -1817,7 +1886,7 @@
         <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1825,22 +1894,22 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F5">
         <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H5">
         <v>3.1</v>
@@ -1852,7 +1921,7 @@
         <v>3.25</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1867,28 +1936,28 @@
         <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
         <v>4</v>
       </c>
       <c r="T5">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X5">
         <v>13.5</v>
@@ -1909,10 +1978,10 @@
         <v>7.6</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF5">
         <v>16</v>
@@ -1927,7 +1996,7 @@
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AK5">
         <v>44</v>
@@ -1936,13 +2005,13 @@
         <v>55</v>
       </c>
       <c r="AM5">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN5">
         <v>27</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -1957,7 +2026,7 @@
         <v>38</v>
       </c>
       <c r="AT5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
@@ -1987,79 +2056,79 @@
         <v>21</v>
       </c>
       <c r="BD5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BE5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5">
         <v>20</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2067,43 +2136,43 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="F6">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="H6">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="I6">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K6">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
         <v>1.02</v>
@@ -2115,10 +2184,10 @@
         <v>2.12</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S6">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2127,10 +2196,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W6">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2187,52 +2256,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2301,7 +2370,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2309,241 +2378,241 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="F7">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G7">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="H7">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="I7">
+        <v>3.6</v>
+      </c>
+      <c r="J7">
+        <v>3.5</v>
+      </c>
+      <c r="K7">
+        <v>3.9</v>
+      </c>
+      <c r="L7">
+        <v>1.31</v>
+      </c>
+      <c r="M7">
+        <v>1.06</v>
+      </c>
+      <c r="N7">
+        <v>3.95</v>
+      </c>
+      <c r="O7">
+        <v>1.28</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7">
+        <v>1.81</v>
+      </c>
+      <c r="R7">
+        <v>1.38</v>
+      </c>
+      <c r="S7">
+        <v>3.05</v>
+      </c>
+      <c r="T7">
+        <v>1.69</v>
+      </c>
+      <c r="U7">
+        <v>2.22</v>
+      </c>
+      <c r="V7">
+        <v>1.38</v>
+      </c>
+      <c r="W7">
+        <v>1.66</v>
+      </c>
+      <c r="X7">
+        <v>19.5</v>
+      </c>
+      <c r="Y7">
+        <v>17</v>
+      </c>
+      <c r="Z7">
+        <v>29</v>
+      </c>
+      <c r="AA7">
+        <v>70</v>
+      </c>
+      <c r="AB7">
+        <v>13.5</v>
+      </c>
+      <c r="AC7">
+        <v>10</v>
+      </c>
+      <c r="AD7">
+        <v>17</v>
+      </c>
+      <c r="AE7">
+        <v>44</v>
+      </c>
+      <c r="AF7">
+        <v>19.5</v>
+      </c>
+      <c r="AG7">
+        <v>14</v>
+      </c>
+      <c r="AH7">
+        <v>20</v>
+      </c>
+      <c r="AI7">
+        <v>55</v>
+      </c>
+      <c r="AJ7">
+        <v>38</v>
+      </c>
+      <c r="AK7">
+        <v>30</v>
+      </c>
+      <c r="AL7">
+        <v>44</v>
+      </c>
+      <c r="AM7">
+        <v>100</v>
+      </c>
+      <c r="AN7">
+        <v>21</v>
+      </c>
+      <c r="AO7">
+        <v>40</v>
+      </c>
+      <c r="AP7">
+        <v>11.5</v>
+      </c>
+      <c r="AQ7">
+        <v>10</v>
+      </c>
+      <c r="AR7">
+        <v>17</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU7">
+        <v>6.2</v>
+      </c>
+      <c r="AV7">
+        <v>10</v>
+      </c>
+      <c r="AW7">
+        <v>1.03</v>
+      </c>
+      <c r="AX7">
+        <v>11.5</v>
+      </c>
+      <c r="AY7">
+        <v>8.4</v>
+      </c>
+      <c r="AZ7">
+        <v>12</v>
+      </c>
+      <c r="BA7">
+        <v>1.01</v>
+      </c>
+      <c r="BB7">
+        <v>1.03</v>
+      </c>
+      <c r="BC7">
+        <v>17.5</v>
+      </c>
+      <c r="BD7">
+        <v>1.03</v>
+      </c>
+      <c r="BE7">
+        <v>1.01</v>
+      </c>
+      <c r="BF7">
+        <v>12.5</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>3.75</v>
+      </c>
+      <c r="BI7">
+        <v>2.86</v>
+      </c>
+      <c r="BJ7">
+        <v>9.6</v>
+      </c>
+      <c r="BK7">
+        <v>5</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>9.6</v>
+      </c>
+      <c r="BN7">
+        <v>5.5</v>
+      </c>
+      <c r="BO7">
         <v>4.1</v>
       </c>
-      <c r="J7">
-        <v>3.15</v>
-      </c>
-      <c r="K7">
+      <c r="BP7">
+        <v>17.5</v>
+      </c>
+      <c r="BQ7">
         <v>6.4</v>
       </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.01</v>
-      </c>
-      <c r="N7">
-        <v>3.7</v>
-      </c>
-      <c r="O7">
-        <v>1.01</v>
-      </c>
-      <c r="P7">
-        <v>1.85</v>
-      </c>
-      <c r="Q7">
-        <v>1.68</v>
-      </c>
-      <c r="R7">
-        <v>1.05</v>
-      </c>
-      <c r="S7">
-        <v>1.68</v>
-      </c>
-      <c r="T7">
-        <v>1.01</v>
-      </c>
-      <c r="U7">
-        <v>1.01</v>
-      </c>
-      <c r="V7">
-        <v>1.32</v>
-      </c>
-      <c r="W7">
-        <v>1.56</v>
-      </c>
-      <c r="X7">
-        <v>1000</v>
-      </c>
-      <c r="Y7">
-        <v>1000</v>
-      </c>
-      <c r="Z7">
-        <v>1000</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>1000</v>
-      </c>
-      <c r="AC7">
-        <v>1000</v>
-      </c>
-      <c r="AD7">
-        <v>1000</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>1000</v>
-      </c>
-      <c r="AG7">
-        <v>1000</v>
-      </c>
-      <c r="AH7">
-        <v>1000</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>1000</v>
-      </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>1.01</v>
-      </c>
-      <c r="AQ7">
-        <v>1.01</v>
-      </c>
-      <c r="AR7">
-        <v>1.01</v>
-      </c>
-      <c r="AS7">
-        <v>1.01</v>
-      </c>
-      <c r="AT7">
-        <v>1.01</v>
-      </c>
-      <c r="AU7">
-        <v>1.01</v>
-      </c>
-      <c r="AV7">
-        <v>1.01</v>
-      </c>
-      <c r="AW7">
-        <v>1.01</v>
-      </c>
-      <c r="AX7">
-        <v>1.01</v>
-      </c>
-      <c r="AY7">
-        <v>1.01</v>
-      </c>
-      <c r="AZ7">
-        <v>1.01</v>
-      </c>
-      <c r="BA7">
-        <v>1.01</v>
-      </c>
-      <c r="BB7">
-        <v>1.01</v>
-      </c>
-      <c r="BC7">
-        <v>1.01</v>
-      </c>
-      <c r="BD7">
-        <v>1.01</v>
-      </c>
-      <c r="BE7">
-        <v>1.01</v>
-      </c>
-      <c r="BF7">
-        <v>1.01</v>
-      </c>
-      <c r="BG7">
-        <v>1.01</v>
-      </c>
-      <c r="BH7">
-        <v>4.5</v>
-      </c>
-      <c r="BI7">
-        <v>2.76</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>1.01</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.01</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
-      <c r="BO7">
-        <v>1.01</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>1.01</v>
-      </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2551,19 +2620,19 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="F8">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G8">
         <v>2.16</v>
@@ -2575,7 +2644,7 @@
         <v>4.2</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
         <v>4.1</v>
@@ -2596,7 +2665,7 @@
         <v>2.04</v>
       </c>
       <c r="Q8">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="R8">
         <v>1.42</v>
@@ -2644,7 +2713,7 @@
         <v>16</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH8">
         <v>20</v>
@@ -2677,22 +2746,22 @@
         <v>12</v>
       </c>
       <c r="AR8">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS8">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT8">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU8">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV8">
         <v>12</v>
       </c>
       <c r="AW8">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="AX8">
         <v>10.5</v>
@@ -2704,7 +2773,7 @@
         <v>13</v>
       </c>
       <c r="BA8">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB8">
         <v>19</v>
@@ -2713,16 +2782,16 @@
         <v>16</v>
       </c>
       <c r="BD8">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE8">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF8">
         <v>10</v>
       </c>
       <c r="BG8">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH8">
         <v>3.85</v>
@@ -2785,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2793,16 +2862,16 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="F9">
         <v>3.05</v>
@@ -2823,7 +2892,7 @@
         <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M9">
         <v>1.14</v>
@@ -2844,7 +2913,7 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="T9">
         <v>2.14</v>
@@ -2889,7 +2958,7 @@
         <v>16</v>
       </c>
       <c r="AH9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI9">
         <v>90</v>
@@ -2904,10 +2973,10 @@
         <v>100</v>
       </c>
       <c r="AM9">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO9">
         <v>65</v>
@@ -2922,7 +2991,7 @@
         <v>12.5</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT9">
         <v>6.8</v>
@@ -2934,7 +3003,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX9">
         <v>15.5</v>
@@ -2946,88 +3015,88 @@
         <v>18.5</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB9" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3035,16 +3104,16 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="F10">
         <v>2.22</v>
@@ -3071,7 +3140,7 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>1.67</v>
+        <v>2.82</v>
       </c>
       <c r="O10">
         <v>1.34</v>
@@ -3269,7 +3338,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3277,16 +3346,16 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="F11">
         <v>1.64</v>
@@ -3295,34 +3364,34 @@
         <v>1.73</v>
       </c>
       <c r="H11">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I11">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J11">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K11">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O11">
         <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q11">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
         <v>1.39</v>
@@ -3331,70 +3400,70 @@
         <v>2.4</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V11">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W11">
         <v>2.36</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP11">
         <v>1.01</v>
@@ -3406,7 +3475,7 @@
         <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
         <v>1.01</v>
@@ -3418,7 +3487,7 @@
         <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
         <v>1.01</v>
@@ -3430,7 +3499,7 @@
         <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
         <v>1.01</v>
@@ -3442,7 +3511,7 @@
         <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3511,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3519,22 +3588,22 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="F12">
         <v>1.94</v>
       </c>
       <c r="G12">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H12">
         <v>4.1</v>
@@ -3546,151 +3615,151 @@
         <v>3.5</v>
       </c>
       <c r="K12">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P12">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Q12">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R12">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W12">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB12">
+        <v>8</v>
+      </c>
+      <c r="AC12">
         <v>9</v>
       </c>
-      <c r="AC12">
-        <v>1000</v>
-      </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL12">
         <v>55</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP12">
-        <v>1.14</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12">
-        <v>1.14</v>
+        <v>11</v>
       </c>
       <c r="AR12">
-        <v>1.14</v>
+        <v>4.8</v>
       </c>
       <c r="AS12">
-        <v>1.14</v>
+        <v>5.3</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU12">
-        <v>1.14</v>
+        <v>6.8</v>
       </c>
       <c r="AV12">
-        <v>1.14</v>
+        <v>15.5</v>
       </c>
       <c r="AW12">
-        <v>1.14</v>
+        <v>5.1</v>
       </c>
       <c r="AX12">
-        <v>1.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY12">
-        <v>1.14</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
-        <v>1.14</v>
+        <v>18</v>
       </c>
       <c r="BA12">
-        <v>1.14</v>
+        <v>5.2</v>
       </c>
       <c r="BB12">
-        <v>1.14</v>
+        <v>4.6</v>
       </c>
       <c r="BC12">
-        <v>1.14</v>
+        <v>20</v>
       </c>
       <c r="BD12">
-        <v>1.12</v>
+        <v>5</v>
       </c>
       <c r="BE12">
-        <v>1.14</v>
+        <v>5.3</v>
       </c>
       <c r="BF12">
-        <v>1.14</v>
+        <v>15</v>
       </c>
       <c r="BG12">
-        <v>1.14</v>
+        <v>5.2</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3753,7 +3822,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3761,16 +3830,16 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="F13">
         <v>2.3</v>
@@ -3809,7 +3878,7 @@
         <v>1.82</v>
       </c>
       <c r="R13">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S13">
         <v>3</v>
@@ -3995,7 +4064,7 @@
         <v>1.75</v>
       </c>
       <c r="CB13" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4003,179 +4072,179 @@
         <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F14">
-        <v>1.34</v>
+        <v>4.2</v>
       </c>
       <c r="G14">
-        <v>1.37</v>
+        <v>4.5</v>
       </c>
       <c r="H14">
-        <v>9.800000000000001</v>
+        <v>1.85</v>
       </c>
       <c r="I14">
+        <v>1.93</v>
+      </c>
+      <c r="J14">
+        <v>4</v>
+      </c>
+      <c r="K14">
+        <v>4.4</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.03</v>
+      </c>
+      <c r="N14">
+        <v>5.5</v>
+      </c>
+      <c r="O14">
+        <v>1.18</v>
+      </c>
+      <c r="P14">
+        <v>2.48</v>
+      </c>
+      <c r="Q14">
+        <v>1.58</v>
+      </c>
+      <c r="R14">
+        <v>1.61</v>
+      </c>
+      <c r="S14">
+        <v>2.42</v>
+      </c>
+      <c r="T14">
+        <v>1.59</v>
+      </c>
+      <c r="U14">
+        <v>2.52</v>
+      </c>
+      <c r="V14">
+        <v>2.08</v>
+      </c>
+      <c r="W14">
+        <v>1.29</v>
+      </c>
+      <c r="X14">
+        <v>26</v>
+      </c>
+      <c r="Y14">
+        <v>14</v>
+      </c>
+      <c r="Z14">
+        <v>15</v>
+      </c>
+      <c r="AA14">
+        <v>23</v>
+      </c>
+      <c r="AB14">
+        <v>24</v>
+      </c>
+      <c r="AC14">
+        <v>11</v>
+      </c>
+      <c r="AD14">
         <v>11.5</v>
       </c>
-      <c r="J14">
-        <v>5.7</v>
-      </c>
-      <c r="K14">
-        <v>6.4</v>
-      </c>
-      <c r="L14">
-        <v>1.19</v>
-      </c>
-      <c r="M14">
-        <v>1.02</v>
-      </c>
-      <c r="N14">
-        <v>7.4</v>
-      </c>
-      <c r="O14">
-        <v>1.13</v>
-      </c>
-      <c r="P14">
-        <v>3.2</v>
-      </c>
-      <c r="Q14">
-        <v>1.41</v>
-      </c>
-      <c r="R14">
-        <v>1.9</v>
-      </c>
-      <c r="S14">
-        <v>2</v>
-      </c>
-      <c r="T14">
-        <v>1.72</v>
-      </c>
-      <c r="U14">
-        <v>2.24</v>
-      </c>
-      <c r="V14">
-        <v>1.09</v>
-      </c>
-      <c r="W14">
-        <v>3.75</v>
-      </c>
-      <c r="X14">
-        <v>42</v>
-      </c>
-      <c r="Y14">
-        <v>55</v>
-      </c>
-      <c r="Z14">
-        <v>120</v>
-      </c>
-      <c r="AA14">
-        <v>320</v>
-      </c>
-      <c r="AB14">
+      <c r="AE14">
+        <v>18.5</v>
+      </c>
+      <c r="AF14">
+        <v>38</v>
+      </c>
+      <c r="AG14">
+        <v>19</v>
+      </c>
+      <c r="AH14">
+        <v>16.5</v>
+      </c>
+      <c r="AI14">
+        <v>28</v>
+      </c>
+      <c r="AJ14">
+        <v>85</v>
+      </c>
+      <c r="AK14">
+        <v>46</v>
+      </c>
+      <c r="AL14">
+        <v>46</v>
+      </c>
+      <c r="AM14">
+        <v>65</v>
+      </c>
+      <c r="AN14">
+        <v>34</v>
+      </c>
+      <c r="AO14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP14">
+        <v>20</v>
+      </c>
+      <c r="AQ14">
+        <v>11</v>
+      </c>
+      <c r="AR14">
+        <v>12</v>
+      </c>
+      <c r="AS14">
+        <v>18.5</v>
+      </c>
+      <c r="AT14">
+        <v>19</v>
+      </c>
+      <c r="AU14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW14">
+        <v>14.5</v>
+      </c>
+      <c r="AX14">
+        <v>25</v>
+      </c>
+      <c r="AY14">
         <v>15</v>
       </c>
-      <c r="AC14">
-        <v>15</v>
-      </c>
-      <c r="AD14">
-        <v>42</v>
-      </c>
-      <c r="AE14">
-        <v>140</v>
-      </c>
-      <c r="AF14">
-        <v>12</v>
-      </c>
-      <c r="AG14">
-        <v>12</v>
-      </c>
-      <c r="AH14">
-        <v>25</v>
-      </c>
-      <c r="AI14">
-        <v>110</v>
-      </c>
-      <c r="AJ14">
+      <c r="AZ14">
         <v>13</v>
       </c>
-      <c r="AK14">
-        <v>14.5</v>
-      </c>
-      <c r="AL14">
+      <c r="BA14">
+        <v>6.6</v>
+      </c>
+      <c r="BB14">
+        <v>7.8</v>
+      </c>
+      <c r="BC14">
+        <v>32</v>
+      </c>
+      <c r="BD14">
         <v>29</v>
       </c>
-      <c r="AM14">
-        <v>90</v>
-      </c>
-      <c r="AN14">
-        <v>3.85</v>
-      </c>
-      <c r="AO14">
-        <v>120</v>
-      </c>
-      <c r="AP14">
+      <c r="BE14">
         <v>7.6</v>
       </c>
-      <c r="AQ14">
-        <v>8</v>
-      </c>
-      <c r="AR14">
-        <v>8.6</v>
-      </c>
-      <c r="AS14">
-        <v>9</v>
-      </c>
-      <c r="AT14">
-        <v>12</v>
-      </c>
-      <c r="AU14">
-        <v>5.7</v>
-      </c>
-      <c r="AV14">
-        <v>7.6</v>
-      </c>
-      <c r="AW14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ14">
+      <c r="BF14">
         <v>6.8</v>
       </c>
-      <c r="BA14">
-        <v>8.6</v>
-      </c>
-      <c r="BB14">
-        <v>10.5</v>
-      </c>
-      <c r="BC14">
-        <v>11.5</v>
-      </c>
-      <c r="BD14">
+      <c r="BG14">
         <v>7</v>
       </c>
-      <c r="BE14">
-        <v>8.4</v>
-      </c>
-      <c r="BF14">
-        <v>3.55</v>
-      </c>
-      <c r="BG14">
-        <v>8.6</v>
-      </c>
       <c r="BH14">
         <v>1000</v>
       </c>
@@ -4237,428 +4306,428 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="F15">
-        <v>4.2</v>
+        <v>2.44</v>
       </c>
       <c r="G15">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="H15">
-        <v>1.84</v>
+        <v>2.96</v>
       </c>
       <c r="I15">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="J15">
+        <v>3.25</v>
+      </c>
+      <c r="K15">
         <v>4</v>
       </c>
-      <c r="K15">
-        <v>4.4</v>
-      </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="P15">
-        <v>2.48</v>
+        <v>1.78</v>
       </c>
       <c r="Q15">
+        <v>2.04</v>
+      </c>
+      <c r="R15">
+        <v>1.3</v>
+      </c>
+      <c r="S15">
+        <v>3.7</v>
+      </c>
+      <c r="T15">
+        <v>1.79</v>
+      </c>
+      <c r="U15">
+        <v>2.02</v>
+      </c>
+      <c r="V15">
+        <v>1.42</v>
+      </c>
+      <c r="W15">
         <v>1.57</v>
       </c>
-      <c r="R15">
-        <v>1.55</v>
-      </c>
-      <c r="S15">
-        <v>2.36</v>
-      </c>
-      <c r="T15">
-        <v>1.01</v>
-      </c>
-      <c r="U15">
-        <v>2.36</v>
-      </c>
-      <c r="V15">
-        <v>2.06</v>
-      </c>
-      <c r="W15">
-        <v>1.29</v>
-      </c>
       <c r="X15">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="Y15">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Z15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA15">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AB15">
+        <v>10.5</v>
+      </c>
+      <c r="AC15">
+        <v>8</v>
+      </c>
+      <c r="AD15">
+        <v>14.5</v>
+      </c>
+      <c r="AE15">
+        <v>40</v>
+      </c>
+      <c r="AF15">
+        <v>17</v>
+      </c>
+      <c r="AG15">
+        <v>12.5</v>
+      </c>
+      <c r="AH15">
+        <v>18.5</v>
+      </c>
+      <c r="AI15">
+        <v>55</v>
+      </c>
+      <c r="AJ15">
+        <v>40</v>
+      </c>
+      <c r="AK15">
         <v>32</v>
       </c>
-      <c r="AC15">
-        <v>14.5</v>
-      </c>
-      <c r="AD15">
+      <c r="AL15">
+        <v>46</v>
+      </c>
+      <c r="AM15">
+        <v>130</v>
+      </c>
+      <c r="AN15">
+        <v>27</v>
+      </c>
+      <c r="AO15">
+        <v>40</v>
+      </c>
+      <c r="AP15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ15">
+        <v>8.4</v>
+      </c>
+      <c r="AR15">
+        <v>15.5</v>
+      </c>
+      <c r="AS15">
+        <v>1.01</v>
+      </c>
+      <c r="AT15">
+        <v>7.4</v>
+      </c>
+      <c r="AU15">
+        <v>5.8</v>
+      </c>
+      <c r="AV15">
+        <v>10</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>12</v>
+      </c>
+      <c r="AY15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ15">
         <v>13</v>
       </c>
-      <c r="AE15">
-        <v>22</v>
-      </c>
-      <c r="AF15">
-        <v>50</v>
-      </c>
-      <c r="AG15">
-        <v>25</v>
-      </c>
-      <c r="AH15">
-        <v>22</v>
-      </c>
-      <c r="AI15">
-        <v>38</v>
-      </c>
-      <c r="AJ15">
-        <v>100</v>
-      </c>
-      <c r="AK15">
-        <v>60</v>
-      </c>
-      <c r="AL15">
-        <v>65</v>
-      </c>
-      <c r="AM15">
-        <v>85</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>11.5</v>
-      </c>
-      <c r="AP15">
-        <v>2.7</v>
-      </c>
-      <c r="AQ15">
-        <v>10</v>
-      </c>
-      <c r="AR15">
-        <v>11</v>
-      </c>
-      <c r="AS15">
-        <v>2.68</v>
-      </c>
-      <c r="AT15">
-        <v>2.68</v>
-      </c>
-      <c r="AU15">
-        <v>8.6</v>
-      </c>
-      <c r="AV15">
-        <v>9</v>
-      </c>
-      <c r="AW15">
-        <v>2.58</v>
-      </c>
-      <c r="AX15">
-        <v>2.78</v>
-      </c>
-      <c r="AY15">
-        <v>12.5</v>
-      </c>
-      <c r="AZ15">
-        <v>2.58</v>
-      </c>
       <c r="BA15">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>2.8</v>
+        <v>21</v>
       </c>
       <c r="BD15">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>2.94</v>
+        <v>18.5</v>
       </c>
       <c r="BG15">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="F16">
-        <v>2.24</v>
+        <v>1.34</v>
       </c>
       <c r="G16">
-        <v>2.5</v>
+        <v>1.37</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="J16">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="K16">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="L16">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="M16">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N16">
-        <v>3.95</v>
+        <v>7.8</v>
       </c>
       <c r="O16">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="P16">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="Q16">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="R16">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>1.98</v>
       </c>
       <c r="T16">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="U16">
         <v>2.24</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="W16">
-        <v>1.66</v>
+        <v>3.6</v>
       </c>
       <c r="X16">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="Y16">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="Z16">
+        <v>120</v>
+      </c>
+      <c r="AA16">
+        <v>320</v>
+      </c>
+      <c r="AB16">
+        <v>15</v>
+      </c>
+      <c r="AC16">
+        <v>15</v>
+      </c>
+      <c r="AD16">
+        <v>42</v>
+      </c>
+      <c r="AE16">
+        <v>140</v>
+      </c>
+      <c r="AF16">
+        <v>12</v>
+      </c>
+      <c r="AG16">
+        <v>12</v>
+      </c>
+      <c r="AH16">
+        <v>22</v>
+      </c>
+      <c r="AI16">
+        <v>110</v>
+      </c>
+      <c r="AJ16">
+        <v>13</v>
+      </c>
+      <c r="AK16">
+        <v>14.5</v>
+      </c>
+      <c r="AL16">
         <v>29</v>
       </c>
-      <c r="AA16">
-        <v>65</v>
-      </c>
-      <c r="AB16">
-        <v>14</v>
-      </c>
-      <c r="AC16">
+      <c r="AM16">
+        <v>90</v>
+      </c>
+      <c r="AN16">
+        <v>3.85</v>
+      </c>
+      <c r="AO16">
+        <v>120</v>
+      </c>
+      <c r="AP16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ16">
+        <v>8.6</v>
+      </c>
+      <c r="AR16">
+        <v>9.4</v>
+      </c>
+      <c r="AS16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT16">
+        <v>12</v>
+      </c>
+      <c r="AU16">
+        <v>6</v>
+      </c>
+      <c r="AV16">
+        <v>8</v>
+      </c>
+      <c r="AW16">
+        <v>9.4</v>
+      </c>
+      <c r="AX16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16">
+        <v>7</v>
+      </c>
+      <c r="BA16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB16">
         <v>10.5</v>
       </c>
-      <c r="AD16">
-        <v>17</v>
-      </c>
-      <c r="AE16">
-        <v>42</v>
-      </c>
-      <c r="AF16">
-        <v>20</v>
-      </c>
-      <c r="AG16">
-        <v>14</v>
-      </c>
-      <c r="AH16">
-        <v>19.5</v>
-      </c>
-      <c r="AI16">
-        <v>55</v>
-      </c>
-      <c r="AJ16">
-        <v>40</v>
-      </c>
-      <c r="AK16">
-        <v>30</v>
-      </c>
-      <c r="AL16">
-        <v>42</v>
-      </c>
-      <c r="AM16">
-        <v>95</v>
-      </c>
-      <c r="AN16">
-        <v>18</v>
-      </c>
-      <c r="AO16">
-        <v>30</v>
-      </c>
-      <c r="AP16">
-        <v>12</v>
-      </c>
-      <c r="AQ16">
-        <v>10.5</v>
-      </c>
-      <c r="AR16">
-        <v>17</v>
-      </c>
-      <c r="AS16">
-        <v>38</v>
-      </c>
-      <c r="AT16">
-        <v>8.4</v>
-      </c>
-      <c r="AU16">
-        <v>6.2</v>
-      </c>
-      <c r="AV16">
-        <v>10</v>
-      </c>
-      <c r="AW16">
-        <v>25</v>
-      </c>
-      <c r="AX16">
-        <v>12</v>
-      </c>
-      <c r="AY16">
-        <v>8.4</v>
-      </c>
-      <c r="AZ16">
+      <c r="BC16">
         <v>11.5</v>
       </c>
-      <c r="BA16">
-        <v>30</v>
-      </c>
-      <c r="BB16">
-        <v>22</v>
-      </c>
-      <c r="BC16">
-        <v>17.5</v>
-      </c>
       <c r="BD16">
-        <v>24</v>
+        <v>7.4</v>
       </c>
       <c r="BE16">
-        <v>55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="BG16">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4667,61 +4736,61 @@
         <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4729,16 +4798,16 @@
         <v>93</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="F17">
         <v>2.98</v>
@@ -4963,434 +5032,434 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="F18">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="G18">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="H18">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="J18">
+        <v>3.55</v>
+      </c>
+      <c r="K18">
+        <v>3.9</v>
+      </c>
+      <c r="L18">
+        <v>1.28</v>
+      </c>
+      <c r="M18">
+        <v>1.06</v>
+      </c>
+      <c r="N18">
         <v>3.95</v>
       </c>
-      <c r="K18">
-        <v>4.1</v>
-      </c>
-      <c r="L18">
-        <v>1.25</v>
-      </c>
-      <c r="M18">
-        <v>1.03</v>
-      </c>
-      <c r="N18">
-        <v>5.9</v>
-      </c>
       <c r="O18">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="P18">
-        <v>2.64</v>
+        <v>2.02</v>
       </c>
       <c r="Q18">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="R18">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="T18">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="U18">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="V18">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="X18">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Y18">
+        <v>17</v>
+      </c>
+      <c r="Z18">
+        <v>29</v>
+      </c>
+      <c r="AA18">
+        <v>65</v>
+      </c>
+      <c r="AB18">
+        <v>14</v>
+      </c>
+      <c r="AC18">
+        <v>10.5</v>
+      </c>
+      <c r="AD18">
+        <v>17</v>
+      </c>
+      <c r="AE18">
+        <v>42</v>
+      </c>
+      <c r="AF18">
+        <v>20</v>
+      </c>
+      <c r="AG18">
+        <v>14</v>
+      </c>
+      <c r="AH18">
+        <v>19.5</v>
+      </c>
+      <c r="AI18">
+        <v>55</v>
+      </c>
+      <c r="AJ18">
+        <v>40</v>
+      </c>
+      <c r="AK18">
+        <v>30</v>
+      </c>
+      <c r="AL18">
+        <v>42</v>
+      </c>
+      <c r="AM18">
+        <v>95</v>
+      </c>
+      <c r="AN18">
+        <v>18</v>
+      </c>
+      <c r="AO18">
+        <v>30</v>
+      </c>
+      <c r="AP18">
+        <v>12</v>
+      </c>
+      <c r="AQ18">
+        <v>10.5</v>
+      </c>
+      <c r="AR18">
+        <v>17</v>
+      </c>
+      <c r="AS18">
+        <v>1.01</v>
+      </c>
+      <c r="AT18">
+        <v>8.4</v>
+      </c>
+      <c r="AU18">
+        <v>6.2</v>
+      </c>
+      <c r="AV18">
+        <v>10</v>
+      </c>
+      <c r="AW18">
+        <v>1.01</v>
+      </c>
+      <c r="AX18">
+        <v>12</v>
+      </c>
+      <c r="AY18">
+        <v>8.4</v>
+      </c>
+      <c r="AZ18">
+        <v>11.5</v>
+      </c>
+      <c r="BA18">
+        <v>1.01</v>
+      </c>
+      <c r="BB18">
+        <v>1.01</v>
+      </c>
+      <c r="BC18">
         <v>17.5</v>
       </c>
-      <c r="Z18">
+      <c r="BD18">
+        <v>1.01</v>
+      </c>
+      <c r="BE18">
+        <v>1.01</v>
+      </c>
+      <c r="BF18">
+        <v>12</v>
+      </c>
+      <c r="BG18">
         <v>21</v>
       </c>
-      <c r="AA18">
-        <v>36</v>
-      </c>
-      <c r="AB18">
-        <v>18.5</v>
-      </c>
-      <c r="AC18">
-        <v>10</v>
-      </c>
-      <c r="AD18">
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.93</v>
+      </c>
+      <c r="BJ18">
         <v>12.5</v>
       </c>
-      <c r="AE18">
+      <c r="BK18">
+        <v>1.68</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.93</v>
+      </c>
+      <c r="BN18">
+        <v>7.2</v>
+      </c>
+      <c r="BO18">
+        <v>3.65</v>
+      </c>
+      <c r="BP18">
         <v>23</v>
       </c>
-      <c r="AF18">
-        <v>29</v>
-      </c>
-      <c r="AG18">
-        <v>13.5</v>
-      </c>
-      <c r="AH18">
-        <v>14.5</v>
-      </c>
-      <c r="AI18">
-        <v>28</v>
-      </c>
-      <c r="AJ18">
-        <v>42</v>
-      </c>
-      <c r="AK18">
-        <v>26</v>
-      </c>
-      <c r="AL18">
-        <v>30</v>
-      </c>
-      <c r="AM18">
-        <v>50</v>
-      </c>
-      <c r="AN18">
-        <v>15</v>
-      </c>
-      <c r="AO18">
-        <v>12.5</v>
-      </c>
-      <c r="AP18">
-        <v>20</v>
-      </c>
-      <c r="AQ18">
-        <v>15.5</v>
-      </c>
-      <c r="AR18">
-        <v>18.5</v>
-      </c>
-      <c r="AS18">
-        <v>32</v>
-      </c>
-      <c r="AT18">
-        <v>16.5</v>
-      </c>
-      <c r="AU18">
+      <c r="BQ18">
+        <v>1.79</v>
+      </c>
+      <c r="BR18">
+        <v>38</v>
+      </c>
+      <c r="BS18">
+        <v>1.84</v>
+      </c>
+      <c r="BT18">
         <v>9</v>
       </c>
-      <c r="AV18">
-        <v>11</v>
-      </c>
-      <c r="AW18">
-        <v>20</v>
-      </c>
-      <c r="AX18">
-        <v>21</v>
-      </c>
-      <c r="AY18">
-        <v>11.5</v>
-      </c>
-      <c r="AZ18">
-        <v>13</v>
-      </c>
-      <c r="BA18">
-        <v>24</v>
-      </c>
-      <c r="BB18">
-        <v>36</v>
-      </c>
-      <c r="BC18">
-        <v>23</v>
-      </c>
-      <c r="BD18">
-        <v>26</v>
-      </c>
-      <c r="BE18">
-        <v>42</v>
-      </c>
-      <c r="BF18">
-        <v>13</v>
-      </c>
-      <c r="BG18">
-        <v>11</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.01</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.01</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.01</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>1.01</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>1.01</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>1.01</v>
-      </c>
-      <c r="BT18">
-        <v>1000</v>
-      </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E19" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="F19">
+        <v>2.8</v>
+      </c>
+      <c r="G19">
+        <v>2.9</v>
+      </c>
+      <c r="H19">
         <v>2.44</v>
       </c>
-      <c r="G19">
-        <v>2.74</v>
-      </c>
-      <c r="H19">
-        <v>2.96</v>
-      </c>
       <c r="I19">
-        <v>3.65</v>
+        <v>2.56</v>
       </c>
       <c r="J19">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M19">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N19">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="O19">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="P19">
-        <v>1.7</v>
+        <v>2.64</v>
       </c>
       <c r="Q19">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="R19">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="S19">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="T19">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U19">
-        <v>1.76</v>
+        <v>2.72</v>
       </c>
       <c r="V19">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="W19">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH19">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
@@ -5441,13 +5510,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5455,16 +5524,16 @@
         <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="F20">
         <v>2.12</v>
@@ -5485,7 +5554,7 @@
         <v>4.6</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M20">
         <v>1.02</v>
@@ -5500,7 +5569,7 @@
         <v>2.74</v>
       </c>
       <c r="Q20">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R20">
         <v>1.71</v>
@@ -5518,178 +5587,178 @@
         <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X20">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="Y20">
+        <v>22</v>
+      </c>
+      <c r="Z20">
         <v>30</v>
       </c>
-      <c r="Z20">
-        <v>40</v>
-      </c>
       <c r="AA20">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AB20">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AC20">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AD20">
+        <v>15.5</v>
+      </c>
+      <c r="AE20">
+        <v>32</v>
+      </c>
+      <c r="AF20">
+        <v>20</v>
+      </c>
+      <c r="AG20">
+        <v>12.5</v>
+      </c>
+      <c r="AH20">
+        <v>15.5</v>
+      </c>
+      <c r="AI20">
+        <v>34</v>
+      </c>
+      <c r="AJ20">
+        <v>30</v>
+      </c>
+      <c r="AK20">
         <v>21</v>
       </c>
-      <c r="AE20">
-        <v>42</v>
-      </c>
-      <c r="AF20">
+      <c r="AL20">
         <v>27</v>
-      </c>
-      <c r="AG20">
-        <v>17</v>
-      </c>
-      <c r="AH20">
-        <v>21</v>
-      </c>
-      <c r="AI20">
-        <v>44</v>
-      </c>
-      <c r="AJ20">
-        <v>42</v>
-      </c>
-      <c r="AK20">
-        <v>28</v>
-      </c>
-      <c r="AL20">
-        <v>38</v>
       </c>
       <c r="AM20">
         <v>70</v>
       </c>
       <c r="AN20">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP20">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ20">
-        <v>2.34</v>
+        <v>16</v>
       </c>
       <c r="AR20">
         <v>19.5</v>
       </c>
       <c r="AS20">
-        <v>2.46</v>
+        <v>7.2</v>
       </c>
       <c r="AT20">
-        <v>2.3</v>
+        <v>13</v>
       </c>
       <c r="AU20">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV20">
+        <v>10.5</v>
+      </c>
+      <c r="AW20">
+        <v>22</v>
+      </c>
+      <c r="AX20">
+        <v>13.5</v>
+      </c>
+      <c r="AY20">
         <v>10</v>
       </c>
-      <c r="AW20">
-        <v>2.4</v>
-      </c>
-      <c r="AX20">
-        <v>2.32</v>
-      </c>
-      <c r="AY20">
-        <v>2.22</v>
-      </c>
       <c r="AZ20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA20">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB20">
-        <v>2.4</v>
+        <v>20</v>
       </c>
       <c r="BC20">
-        <v>2.34</v>
+        <v>15</v>
       </c>
       <c r="BD20">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BE20">
-        <v>2.46</v>
+        <v>7</v>
       </c>
       <c r="BF20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG20">
-        <v>2.54</v>
+        <v>12</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI20">
-        <v>2.06</v>
+        <v>3.75</v>
       </c>
       <c r="BJ20">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK20">
         <v>5.3</v>
       </c>
       <c r="BL20">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM20">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN20">
+        <v>6</v>
+      </c>
+      <c r="BO20">
+        <v>4.9</v>
+      </c>
+      <c r="BP20">
+        <v>15</v>
+      </c>
+      <c r="BQ20">
+        <v>8.4</v>
+      </c>
+      <c r="BR20">
+        <v>22</v>
+      </c>
+      <c r="BS20">
+        <v>6.6</v>
+      </c>
+      <c r="BT20">
+        <v>7.4</v>
+      </c>
+      <c r="BU20">
+        <v>6</v>
+      </c>
+      <c r="BV20">
+        <v>22</v>
+      </c>
+      <c r="BW20">
+        <v>6.6</v>
+      </c>
+      <c r="BX20">
+        <v>26</v>
+      </c>
+      <c r="BY20">
+        <v>6.8</v>
+      </c>
+      <c r="BZ20">
+        <v>14</v>
+      </c>
+      <c r="CA20">
         <v>8</v>
       </c>
-      <c r="BO20">
-        <v>3.8</v>
-      </c>
-      <c r="BP20">
-        <v>20</v>
-      </c>
-      <c r="BQ20">
-        <v>1.87</v>
-      </c>
-      <c r="BR20">
-        <v>30</v>
-      </c>
-      <c r="BS20">
-        <v>1.93</v>
-      </c>
-      <c r="BT20">
-        <v>10</v>
-      </c>
-      <c r="BU20">
-        <v>4.5</v>
-      </c>
-      <c r="BV20">
-        <v>30</v>
-      </c>
-      <c r="BW20">
-        <v>1.93</v>
-      </c>
-      <c r="BX20">
-        <v>38</v>
-      </c>
-      <c r="BY20">
-        <v>1.95</v>
-      </c>
-      <c r="BZ20">
-        <v>19</v>
-      </c>
-      <c r="CA20">
-        <v>1.86</v>
-      </c>
       <c r="CB20" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5697,16 +5766,16 @@
         <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F21">
         <v>3.5</v>
@@ -5733,7 +5802,7 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O21">
         <v>1.16</v>
@@ -5745,10 +5814,10 @@
         <v>1.4</v>
       </c>
       <c r="R21">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="S21">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5931,7 +6000,7 @@
         <v>2</v>
       </c>
       <c r="CB21" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5939,22 +6008,22 @@
         <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="F22">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G22">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H22">
         <v>6.2</v>
@@ -5984,7 +6053,7 @@
         <v>1.87</v>
       </c>
       <c r="Q22">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="R22">
         <v>1.35</v>
@@ -6002,7 +6071,7 @@
         <v>1.15</v>
       </c>
       <c r="W22">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6173,7 +6242,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6181,16 +6250,16 @@
         <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="F23">
         <v>3.8</v>
@@ -6199,7 +6268,7 @@
         <v>4.5</v>
       </c>
       <c r="H23">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I23">
         <v>2.18</v>
@@ -6241,10 +6310,10 @@
         <v>2.02</v>
       </c>
       <c r="V23">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W23">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X23">
         <v>16.5</v>
@@ -6358,19 +6427,19 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BJ23">
         <v>14.5</v>
       </c>
       <c r="BK23">
-        <v>6.2</v>
+        <v>1.62</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>21</v>
+        <v>1.82</v>
       </c>
       <c r="BN23">
         <v>10</v>
@@ -6382,13 +6451,13 @@
         <v>50</v>
       </c>
       <c r="BQ23">
-        <v>20</v>
+        <v>1.76</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>21</v>
+        <v>1.77</v>
       </c>
       <c r="BT23">
         <v>6.6</v>
@@ -6400,22 +6469,22 @@
         <v>22</v>
       </c>
       <c r="BW23">
-        <v>9.199999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="BX23">
         <v>44</v>
       </c>
       <c r="BY23">
-        <v>17.5</v>
+        <v>1.75</v>
       </c>
       <c r="BZ23">
         <v>38</v>
       </c>
       <c r="CA23">
-        <v>16</v>
+        <v>1.74</v>
       </c>
       <c r="CB23" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6423,19 +6492,19 @@
         <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E24" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G24">
         <v>2.22</v>
@@ -6450,7 +6519,7 @@
         <v>3.45</v>
       </c>
       <c r="K24">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6459,16 +6528,16 @@
         <v>1.07</v>
       </c>
       <c r="N24">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O24">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P24">
         <v>1.89</v>
       </c>
       <c r="Q24">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R24">
         <v>1.33</v>
@@ -6477,10 +6546,10 @@
         <v>3.35</v>
       </c>
       <c r="T24">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U24">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
         <v>1.3</v>
@@ -6525,7 +6594,7 @@
         <v>65</v>
       </c>
       <c r="AJ24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK24">
         <v>27</v>
@@ -6552,7 +6621,7 @@
         <v>21</v>
       </c>
       <c r="AS24">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
         <v>7.4</v>
@@ -6564,7 +6633,7 @@
         <v>12</v>
       </c>
       <c r="AW24">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
         <v>10</v>
@@ -6576,25 +6645,25 @@
         <v>13.5</v>
       </c>
       <c r="BA24">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC24">
         <v>17.5</v>
       </c>
       <c r="BD24">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
         <v>12.5</v>
       </c>
       <c r="BG24">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6657,132 +6726,132 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="F25">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="G25">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="H25">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="I25">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="J25">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="K25">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M25">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N25">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="O25">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="P25">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q25">
+        <v>2.34</v>
+      </c>
+      <c r="R25">
+        <v>1.21</v>
+      </c>
+      <c r="S25">
+        <v>1.02</v>
+      </c>
+      <c r="T25">
         <v>2.16</v>
       </c>
-      <c r="R25">
-        <v>1.23</v>
-      </c>
-      <c r="S25">
-        <v>2.92</v>
-      </c>
-      <c r="T25">
-        <v>1.01</v>
-      </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V25">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="W25">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP25">
         <v>1.01</v>
@@ -6818,37 +6887,37 @@
         <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG25">
         <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL25">
         <v>1000</v>
@@ -6857,291 +6926,291 @@
         <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ25">
         <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BS25">
         <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY25">
         <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA25">
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="F26">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="G26">
+        <v>3.3</v>
+      </c>
+      <c r="H26">
+        <v>2.64</v>
+      </c>
+      <c r="I26">
+        <v>3.15</v>
+      </c>
+      <c r="J26">
+        <v>2.78</v>
+      </c>
+      <c r="K26">
+        <v>3.8</v>
+      </c>
+      <c r="L26">
+        <v>1.4</v>
+      </c>
+      <c r="M26">
+        <v>1.09</v>
+      </c>
+      <c r="N26">
+        <v>2.92</v>
+      </c>
+      <c r="O26">
+        <v>1.4</v>
+      </c>
+      <c r="P26">
+        <v>1.63</v>
+      </c>
+      <c r="Q26">
+        <v>2.18</v>
+      </c>
+      <c r="R26">
+        <v>1.26</v>
+      </c>
+      <c r="S26">
         <v>4.1</v>
       </c>
-      <c r="H26">
-        <v>2.18</v>
-      </c>
-      <c r="I26">
-        <v>2.36</v>
-      </c>
-      <c r="J26">
-        <v>3</v>
-      </c>
-      <c r="K26">
-        <v>3.35</v>
-      </c>
-      <c r="L26">
-        <v>1.48</v>
-      </c>
-      <c r="M26">
-        <v>1.11</v>
-      </c>
-      <c r="N26">
-        <v>2.6</v>
-      </c>
-      <c r="O26">
-        <v>1.54</v>
-      </c>
-      <c r="P26">
-        <v>1.56</v>
-      </c>
-      <c r="Q26">
-        <v>2.34</v>
-      </c>
-      <c r="R26">
-        <v>1.21</v>
-      </c>
-      <c r="S26">
-        <v>1.02</v>
-      </c>
       <c r="T26">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="W26">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="X26">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
+        <v>1000</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>1000</v>
+      </c>
+      <c r="AC26">
+        <v>9.4</v>
+      </c>
+      <c r="AD26">
+        <v>1000</v>
+      </c>
+      <c r="AE26">
+        <v>44</v>
+      </c>
+      <c r="AF26">
+        <v>1000</v>
+      </c>
+      <c r="AG26">
+        <v>17</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>1.23</v>
+      </c>
+      <c r="AQ26">
+        <v>1.23</v>
+      </c>
+      <c r="AR26">
+        <v>1.23</v>
+      </c>
+      <c r="AS26">
+        <v>1.23</v>
+      </c>
+      <c r="AT26">
+        <v>1.23</v>
+      </c>
+      <c r="AU26">
+        <v>1.08</v>
+      </c>
+      <c r="AV26">
+        <v>1.23</v>
+      </c>
+      <c r="AW26">
+        <v>1.19</v>
+      </c>
+      <c r="AX26">
+        <v>1.23</v>
+      </c>
+      <c r="AY26">
+        <v>1.14</v>
+      </c>
+      <c r="AZ26">
+        <v>1.23</v>
+      </c>
+      <c r="BA26">
+        <v>1.23</v>
+      </c>
+      <c r="BB26">
+        <v>1.23</v>
+      </c>
+      <c r="BC26">
+        <v>1.23</v>
+      </c>
+      <c r="BD26">
+        <v>1.23</v>
+      </c>
+      <c r="BE26">
+        <v>1.23</v>
+      </c>
+      <c r="BF26">
+        <v>1.23</v>
+      </c>
+      <c r="BG26">
+        <v>1.23</v>
+      </c>
+      <c r="BH26">
+        <v>3.5</v>
+      </c>
+      <c r="BI26">
+        <v>2.46</v>
+      </c>
+      <c r="BJ26">
+        <v>12</v>
+      </c>
+      <c r="BK26">
+        <v>3.5</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>4.8</v>
+      </c>
+      <c r="BN26">
         <v>7</v>
       </c>
-      <c r="Z26">
-        <v>15</v>
-      </c>
-      <c r="AA26">
-        <v>40</v>
-      </c>
-      <c r="AB26">
-        <v>10.5</v>
-      </c>
-      <c r="AC26">
-        <v>8.4</v>
-      </c>
-      <c r="AD26">
-        <v>12</v>
-      </c>
-      <c r="AE26">
-        <v>40</v>
-      </c>
-      <c r="AF26">
-        <v>32</v>
-      </c>
-      <c r="AG26">
-        <v>21</v>
-      </c>
-      <c r="AH26">
-        <v>34</v>
-      </c>
-      <c r="AI26">
-        <v>75</v>
-      </c>
-      <c r="AJ26">
-        <v>120</v>
-      </c>
-      <c r="AK26">
-        <v>80</v>
-      </c>
-      <c r="AL26">
-        <v>110</v>
-      </c>
-      <c r="AM26">
-        <v>280</v>
-      </c>
-      <c r="AN26">
-        <v>120</v>
-      </c>
-      <c r="AO26">
-        <v>42</v>
-      </c>
-      <c r="AP26">
-        <v>1.01</v>
-      </c>
-      <c r="AQ26">
-        <v>1.01</v>
-      </c>
-      <c r="AR26">
-        <v>1.01</v>
-      </c>
-      <c r="AS26">
-        <v>1.01</v>
-      </c>
-      <c r="AT26">
-        <v>1.01</v>
-      </c>
-      <c r="AU26">
-        <v>1.01</v>
-      </c>
-      <c r="AV26">
-        <v>1.01</v>
-      </c>
-      <c r="AW26">
-        <v>1.01</v>
-      </c>
-      <c r="AX26">
-        <v>1.01</v>
-      </c>
-      <c r="AY26">
-        <v>1.01</v>
-      </c>
-      <c r="AZ26">
-        <v>1.01</v>
-      </c>
-      <c r="BA26">
-        <v>9</v>
-      </c>
-      <c r="BB26">
-        <v>9</v>
-      </c>
-      <c r="BC26">
-        <v>9</v>
-      </c>
-      <c r="BD26">
-        <v>9</v>
-      </c>
-      <c r="BE26">
-        <v>9</v>
-      </c>
-      <c r="BF26">
-        <v>9</v>
-      </c>
-      <c r="BG26">
-        <v>1.01</v>
-      </c>
-      <c r="BH26">
-        <v>1000</v>
-      </c>
-      <c r="BI26">
-        <v>1.01</v>
-      </c>
-      <c r="BJ26">
-        <v>1000</v>
-      </c>
-      <c r="BK26">
-        <v>1.01</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>1.01</v>
-      </c>
-      <c r="BN26">
-        <v>1000</v>
-      </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="CB26" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7149,16 +7218,16 @@
         <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -7383,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7391,19 +7460,19 @@
         <v>98</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="F28">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -7418,7 +7487,7 @@
         <v>3.4</v>
       </c>
       <c r="K28">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7430,7 +7499,7 @@
         <v>3</v>
       </c>
       <c r="O28">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P28">
         <v>1.68</v>
@@ -7448,7 +7517,7 @@
         <v>1.82</v>
       </c>
       <c r="U28">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="V28">
         <v>1.22</v>
@@ -7568,19 +7637,19 @@
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BJ28">
         <v>15</v>
       </c>
       <c r="BK28">
-        <v>7</v>
+        <v>1.62</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>22</v>
+        <v>1.81</v>
       </c>
       <c r="BN28">
         <v>5.9</v>
@@ -7592,13 +7661,13 @@
         <v>20</v>
       </c>
       <c r="BQ28">
-        <v>9.199999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="BR28">
         <v>46</v>
       </c>
       <c r="BS28">
-        <v>20</v>
+        <v>1.75</v>
       </c>
       <c r="BT28">
         <v>11</v>
@@ -7610,22 +7679,1716 @@
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>22</v>
+        <v>1.77</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>22</v>
+        <v>1.78</v>
       </c>
       <c r="BZ28">
         <v>44</v>
       </c>
       <c r="CA28">
+        <v>1.75</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" t="s">
+        <v>183</v>
+      </c>
+      <c r="F29">
+        <v>1.99</v>
+      </c>
+      <c r="G29">
+        <v>2.18</v>
+      </c>
+      <c r="H29">
+        <v>4.1</v>
+      </c>
+      <c r="I29">
+        <v>5.3</v>
+      </c>
+      <c r="J29">
+        <v>3.1</v>
+      </c>
+      <c r="K29">
+        <v>3.6</v>
+      </c>
+      <c r="L29">
+        <v>1.44</v>
+      </c>
+      <c r="M29">
+        <v>1.1</v>
+      </c>
+      <c r="N29">
+        <v>2.84</v>
+      </c>
+      <c r="O29">
+        <v>1.44</v>
+      </c>
+      <c r="P29">
+        <v>1.6</v>
+      </c>
+      <c r="Q29">
+        <v>2.28</v>
+      </c>
+      <c r="R29">
+        <v>1.23</v>
+      </c>
+      <c r="S29">
+        <v>4.5</v>
+      </c>
+      <c r="T29">
+        <v>1.88</v>
+      </c>
+      <c r="U29">
+        <v>1.74</v>
+      </c>
+      <c r="V29">
+        <v>1.23</v>
+      </c>
+      <c r="W29">
+        <v>1.84</v>
+      </c>
+      <c r="X29">
+        <v>12</v>
+      </c>
+      <c r="Y29">
+        <v>15</v>
+      </c>
+      <c r="Z29">
+        <v>38</v>
+      </c>
+      <c r="AA29">
+        <v>130</v>
+      </c>
+      <c r="AB29">
+        <v>8.6</v>
+      </c>
+      <c r="AC29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD29">
+        <v>22</v>
+      </c>
+      <c r="AE29">
+        <v>80</v>
+      </c>
+      <c r="AF29">
+        <v>14</v>
+      </c>
+      <c r="AG29">
+        <v>13</v>
+      </c>
+      <c r="AH29">
+        <v>26</v>
+      </c>
+      <c r="AI29">
+        <v>100</v>
+      </c>
+      <c r="AJ29">
+        <v>32</v>
+      </c>
+      <c r="AK29">
+        <v>32</v>
+      </c>
+      <c r="AL29">
+        <v>60</v>
+      </c>
+      <c r="AM29">
+        <v>180</v>
+      </c>
+      <c r="AN29">
+        <v>26</v>
+      </c>
+      <c r="AO29">
+        <v>120</v>
+      </c>
+      <c r="AP29">
+        <v>8</v>
+      </c>
+      <c r="AQ29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR29">
+        <v>4.4</v>
+      </c>
+      <c r="AS29">
+        <v>4.8</v>
+      </c>
+      <c r="AT29">
+        <v>5.9</v>
+      </c>
+      <c r="AU29">
+        <v>6</v>
+      </c>
+      <c r="AV29">
+        <v>14</v>
+      </c>
+      <c r="AW29">
+        <v>4.7</v>
+      </c>
+      <c r="AX29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY29">
+        <v>8.4</v>
+      </c>
+      <c r="AZ29">
+        <v>18.5</v>
+      </c>
+      <c r="BA29">
+        <v>4.7</v>
+      </c>
+      <c r="BB29">
+        <v>20</v>
+      </c>
+      <c r="BC29">
+        <v>20</v>
+      </c>
+      <c r="BD29">
+        <v>4.6</v>
+      </c>
+      <c r="BE29">
+        <v>4.8</v>
+      </c>
+      <c r="BF29">
+        <v>17</v>
+      </c>
+      <c r="BG29">
+        <v>4.8</v>
+      </c>
+      <c r="BH29">
+        <v>3.25</v>
+      </c>
+      <c r="BI29">
+        <v>2.46</v>
+      </c>
+      <c r="BJ29">
+        <v>12.5</v>
+      </c>
+      <c r="BK29">
+        <v>4.1</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>5.9</v>
+      </c>
+      <c r="BN29">
+        <v>5.2</v>
+      </c>
+      <c r="BO29">
+        <v>3.7</v>
+      </c>
+      <c r="BP29">
         <v>19</v>
       </c>
-      <c r="CB28" t="s">
-        <v>167</v>
+      <c r="BQ29">
+        <v>4.6</v>
+      </c>
+      <c r="BR29">
+        <v>42</v>
+      </c>
+      <c r="BS29">
+        <v>5.3</v>
+      </c>
+      <c r="BT29">
+        <v>8.6</v>
+      </c>
+      <c r="BU29">
+        <v>3.55</v>
+      </c>
+      <c r="BV29">
+        <v>48</v>
+      </c>
+      <c r="BW29">
+        <v>5.4</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>5.6</v>
+      </c>
+      <c r="BZ29">
+        <v>42</v>
+      </c>
+      <c r="CA29">
+        <v>5.3</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" t="s">
+        <v>184</v>
+      </c>
+      <c r="F30">
+        <v>4.2</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30">
+        <v>1.92</v>
+      </c>
+      <c r="I30">
+        <v>2.1</v>
+      </c>
+      <c r="J30">
+        <v>3.05</v>
+      </c>
+      <c r="K30">
+        <v>3.8</v>
+      </c>
+      <c r="L30">
+        <v>1.4</v>
+      </c>
+      <c r="M30">
+        <v>1.07</v>
+      </c>
+      <c r="N30">
+        <v>3.3</v>
+      </c>
+      <c r="O30">
+        <v>1.34</v>
+      </c>
+      <c r="P30">
+        <v>1.78</v>
+      </c>
+      <c r="Q30">
+        <v>2</v>
+      </c>
+      <c r="R30">
+        <v>1.3</v>
+      </c>
+      <c r="S30">
+        <v>3.6</v>
+      </c>
+      <c r="T30">
+        <v>1.84</v>
+      </c>
+      <c r="U30">
+        <v>1.95</v>
+      </c>
+      <c r="V30">
+        <v>1.91</v>
+      </c>
+      <c r="W30">
+        <v>1.25</v>
+      </c>
+      <c r="X30">
+        <v>13.5</v>
+      </c>
+      <c r="Y30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z30">
+        <v>12.5</v>
+      </c>
+      <c r="AA30">
+        <v>25</v>
+      </c>
+      <c r="AB30">
+        <v>15.5</v>
+      </c>
+      <c r="AC30">
+        <v>8.6</v>
+      </c>
+      <c r="AD30">
+        <v>11</v>
+      </c>
+      <c r="AE30">
+        <v>23</v>
+      </c>
+      <c r="AF30">
+        <v>36</v>
+      </c>
+      <c r="AG30">
+        <v>19</v>
+      </c>
+      <c r="AH30">
+        <v>21</v>
+      </c>
+      <c r="AI30">
+        <v>50</v>
+      </c>
+      <c r="AJ30">
+        <v>130</v>
+      </c>
+      <c r="AK30">
+        <v>75</v>
+      </c>
+      <c r="AL30">
+        <v>85</v>
+      </c>
+      <c r="AM30">
+        <v>150</v>
+      </c>
+      <c r="AN30">
+        <v>90</v>
+      </c>
+      <c r="AO30">
+        <v>19.5</v>
+      </c>
+      <c r="AP30">
+        <v>11</v>
+      </c>
+      <c r="AQ30">
+        <v>7.2</v>
+      </c>
+      <c r="AR30">
+        <v>10</v>
+      </c>
+      <c r="AS30">
+        <v>19.5</v>
+      </c>
+      <c r="AT30">
+        <v>12.5</v>
+      </c>
+      <c r="AU30">
+        <v>7</v>
+      </c>
+      <c r="AV30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW30">
+        <v>18.5</v>
+      </c>
+      <c r="AX30">
+        <v>6.4</v>
+      </c>
+      <c r="AY30">
+        <v>15</v>
+      </c>
+      <c r="AZ30">
+        <v>16.5</v>
+      </c>
+      <c r="BA30">
+        <v>6.6</v>
+      </c>
+      <c r="BB30">
+        <v>7.4</v>
+      </c>
+      <c r="BC30">
+        <v>7</v>
+      </c>
+      <c r="BD30">
+        <v>7</v>
+      </c>
+      <c r="BE30">
+        <v>7.4</v>
+      </c>
+      <c r="BF30">
+        <v>7.2</v>
+      </c>
+      <c r="BG30">
+        <v>11.5</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
+        <v>1.86</v>
+      </c>
+      <c r="BJ30">
+        <v>14.5</v>
+      </c>
+      <c r="BK30">
+        <v>1.65</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.86</v>
+      </c>
+      <c r="BN30">
+        <v>10.5</v>
+      </c>
+      <c r="BO30">
+        <v>5.1</v>
+      </c>
+      <c r="BP30">
+        <v>1000</v>
+      </c>
+      <c r="BQ30">
+        <v>1.8</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>1.82</v>
+      </c>
+      <c r="BT30">
+        <v>6</v>
+      </c>
+      <c r="BU30">
+        <v>3.2</v>
+      </c>
+      <c r="BV30">
+        <v>20</v>
+      </c>
+      <c r="BW30">
+        <v>1.71</v>
+      </c>
+      <c r="BX30">
+        <v>42</v>
+      </c>
+      <c r="BY30">
+        <v>1.79</v>
+      </c>
+      <c r="BZ30">
+        <v>38</v>
+      </c>
+      <c r="CA30">
+        <v>1.78</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" t="s">
+        <v>151</v>
+      </c>
+      <c r="E31" t="s">
+        <v>185</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>1.01</v>
+      </c>
+      <c r="M31">
+        <v>1.01</v>
+      </c>
+      <c r="N31">
+        <v>1.25</v>
+      </c>
+      <c r="O31">
+        <v>1.45</v>
+      </c>
+      <c r="P31">
+        <v>1.25</v>
+      </c>
+      <c r="Q31">
+        <v>1.45</v>
+      </c>
+      <c r="R31">
+        <v>1.18</v>
+      </c>
+      <c r="S31">
+        <v>1.45</v>
+      </c>
+      <c r="T31">
+        <v>1.01</v>
+      </c>
+      <c r="U31">
+        <v>1.01</v>
+      </c>
+      <c r="V31">
+        <v>1.01</v>
+      </c>
+      <c r="W31">
+        <v>1.01</v>
+      </c>
+      <c r="X31">
+        <v>1000</v>
+      </c>
+      <c r="Y31">
+        <v>1000</v>
+      </c>
+      <c r="Z31">
+        <v>1000</v>
+      </c>
+      <c r="AA31">
+        <v>1000</v>
+      </c>
+      <c r="AB31">
+        <v>1000</v>
+      </c>
+      <c r="AC31">
+        <v>1000</v>
+      </c>
+      <c r="AD31">
+        <v>1000</v>
+      </c>
+      <c r="AE31">
+        <v>1000</v>
+      </c>
+      <c r="AF31">
+        <v>1000</v>
+      </c>
+      <c r="AG31">
+        <v>1000</v>
+      </c>
+      <c r="AH31">
+        <v>1000</v>
+      </c>
+      <c r="AI31">
+        <v>1000</v>
+      </c>
+      <c r="AJ31">
+        <v>1000</v>
+      </c>
+      <c r="AK31">
+        <v>1000</v>
+      </c>
+      <c r="AL31">
+        <v>1000</v>
+      </c>
+      <c r="AM31">
+        <v>1000</v>
+      </c>
+      <c r="AN31">
+        <v>1000</v>
+      </c>
+      <c r="AO31">
+        <v>1000</v>
+      </c>
+      <c r="AP31">
+        <v>1.01</v>
+      </c>
+      <c r="AQ31">
+        <v>1.01</v>
+      </c>
+      <c r="AR31">
+        <v>1.01</v>
+      </c>
+      <c r="AS31">
+        <v>1.01</v>
+      </c>
+      <c r="AT31">
+        <v>1.01</v>
+      </c>
+      <c r="AU31">
+        <v>1.01</v>
+      </c>
+      <c r="AV31">
+        <v>1.01</v>
+      </c>
+      <c r="AW31">
+        <v>1.01</v>
+      </c>
+      <c r="AX31">
+        <v>1.01</v>
+      </c>
+      <c r="AY31">
+        <v>1.01</v>
+      </c>
+      <c r="AZ31">
+        <v>1.01</v>
+      </c>
+      <c r="BA31">
+        <v>1.01</v>
+      </c>
+      <c r="BB31">
+        <v>1.01</v>
+      </c>
+      <c r="BC31">
+        <v>1.01</v>
+      </c>
+      <c r="BD31">
+        <v>1.01</v>
+      </c>
+      <c r="BE31">
+        <v>1.01</v>
+      </c>
+      <c r="BF31">
+        <v>1.01</v>
+      </c>
+      <c r="BG31">
+        <v>1.01</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>1.01</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.01</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.01</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.01</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.01</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.01</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.01</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.01</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.01</v>
+      </c>
+      <c r="BZ31">
+        <v>0</v>
+      </c>
+      <c r="CA31">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" t="s">
+        <v>152</v>
+      </c>
+      <c r="E32" t="s">
+        <v>186</v>
+      </c>
+      <c r="F32">
+        <v>3.35</v>
+      </c>
+      <c r="G32">
+        <v>3.75</v>
+      </c>
+      <c r="H32">
+        <v>2.52</v>
+      </c>
+      <c r="I32">
+        <v>2.74</v>
+      </c>
+      <c r="J32">
+        <v>2.92</v>
+      </c>
+      <c r="K32">
+        <v>3</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.14</v>
+      </c>
+      <c r="N32">
+        <v>2.4</v>
+      </c>
+      <c r="O32">
+        <v>1.59</v>
+      </c>
+      <c r="P32">
+        <v>1.44</v>
+      </c>
+      <c r="Q32">
+        <v>2.88</v>
+      </c>
+      <c r="R32">
+        <v>1.16</v>
+      </c>
+      <c r="S32">
+        <v>6</v>
+      </c>
+      <c r="T32">
+        <v>2.04</v>
+      </c>
+      <c r="U32">
+        <v>1.71</v>
+      </c>
+      <c r="V32">
+        <v>1.58</v>
+      </c>
+      <c r="W32">
+        <v>1.36</v>
+      </c>
+      <c r="X32">
+        <v>8</v>
+      </c>
+      <c r="Y32">
+        <v>7.6</v>
+      </c>
+      <c r="Z32">
+        <v>15.5</v>
+      </c>
+      <c r="AA32">
+        <v>48</v>
+      </c>
+      <c r="AB32">
+        <v>9.6</v>
+      </c>
+      <c r="AC32">
+        <v>7.4</v>
+      </c>
+      <c r="AD32">
+        <v>14</v>
+      </c>
+      <c r="AE32">
+        <v>48</v>
+      </c>
+      <c r="AF32">
+        <v>25</v>
+      </c>
+      <c r="AG32">
+        <v>17</v>
+      </c>
+      <c r="AH32">
+        <v>26</v>
+      </c>
+      <c r="AI32">
+        <v>95</v>
+      </c>
+      <c r="AJ32">
+        <v>100</v>
+      </c>
+      <c r="AK32">
+        <v>80</v>
+      </c>
+      <c r="AL32">
+        <v>110</v>
+      </c>
+      <c r="AM32">
+        <v>240</v>
+      </c>
+      <c r="AN32">
+        <v>100</v>
+      </c>
+      <c r="AO32">
+        <v>55</v>
+      </c>
+      <c r="AP32">
+        <v>6.8</v>
+      </c>
+      <c r="AQ32">
+        <v>6.2</v>
+      </c>
+      <c r="AR32">
+        <v>12.5</v>
+      </c>
+      <c r="AS32">
+        <v>7.6</v>
+      </c>
+      <c r="AT32">
+        <v>7.8</v>
+      </c>
+      <c r="AU32">
+        <v>6</v>
+      </c>
+      <c r="AV32">
+        <v>11</v>
+      </c>
+      <c r="AW32">
+        <v>7.6</v>
+      </c>
+      <c r="AX32">
+        <v>19.5</v>
+      </c>
+      <c r="AY32">
+        <v>14</v>
+      </c>
+      <c r="AZ32">
+        <v>6.6</v>
+      </c>
+      <c r="BA32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC32">
+        <v>8</v>
+      </c>
+      <c r="BD32">
+        <v>8.4</v>
+      </c>
+      <c r="BE32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF32">
+        <v>8.4</v>
+      </c>
+      <c r="BG32">
+        <v>7.8</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.68</v>
+      </c>
+      <c r="BJ32">
+        <v>16</v>
+      </c>
+      <c r="BK32">
+        <v>1.52</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.68</v>
+      </c>
+      <c r="BN32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO32">
+        <v>4.4</v>
+      </c>
+      <c r="BP32">
+        <v>50</v>
+      </c>
+      <c r="BQ32">
+        <v>1.63</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.65</v>
+      </c>
+      <c r="BT32">
+        <v>7</v>
+      </c>
+      <c r="BU32">
+        <v>3.55</v>
+      </c>
+      <c r="BV32">
+        <v>34</v>
+      </c>
+      <c r="BW32">
+        <v>1.6</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.64</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.65</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" t="s">
+        <v>153</v>
+      </c>
+      <c r="E33" t="s">
+        <v>187</v>
+      </c>
+      <c r="F33">
+        <v>2.7</v>
+      </c>
+      <c r="G33">
+        <v>3.1</v>
+      </c>
+      <c r="H33">
+        <v>2.88</v>
+      </c>
+      <c r="I33">
+        <v>3.25</v>
+      </c>
+      <c r="J33">
+        <v>2.88</v>
+      </c>
+      <c r="K33">
+        <v>3.3</v>
+      </c>
+      <c r="L33">
+        <v>1.01</v>
+      </c>
+      <c r="M33">
+        <v>1.12</v>
+      </c>
+      <c r="N33">
+        <v>1.01</v>
+      </c>
+      <c r="O33">
+        <v>1.01</v>
+      </c>
+      <c r="P33">
+        <v>1.54</v>
+      </c>
+      <c r="Q33">
+        <v>2.48</v>
+      </c>
+      <c r="R33">
+        <v>1.14</v>
+      </c>
+      <c r="S33">
+        <v>1.02</v>
+      </c>
+      <c r="T33">
+        <v>2</v>
+      </c>
+      <c r="U33">
+        <v>1.8</v>
+      </c>
+      <c r="V33">
+        <v>1.01</v>
+      </c>
+      <c r="W33">
+        <v>1.01</v>
+      </c>
+      <c r="X33">
+        <v>1000</v>
+      </c>
+      <c r="Y33">
+        <v>1000</v>
+      </c>
+      <c r="Z33">
+        <v>1000</v>
+      </c>
+      <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>1000</v>
+      </c>
+      <c r="AC33">
+        <v>1000</v>
+      </c>
+      <c r="AD33">
+        <v>1000</v>
+      </c>
+      <c r="AE33">
+        <v>1000</v>
+      </c>
+      <c r="AF33">
+        <v>1000</v>
+      </c>
+      <c r="AG33">
+        <v>1000</v>
+      </c>
+      <c r="AH33">
+        <v>1000</v>
+      </c>
+      <c r="AI33">
+        <v>1000</v>
+      </c>
+      <c r="AJ33">
+        <v>1000</v>
+      </c>
+      <c r="AK33">
+        <v>1000</v>
+      </c>
+      <c r="AL33">
+        <v>1000</v>
+      </c>
+      <c r="AM33">
+        <v>1000</v>
+      </c>
+      <c r="AN33">
+        <v>1000</v>
+      </c>
+      <c r="AO33">
+        <v>1000</v>
+      </c>
+      <c r="AP33">
+        <v>1.01</v>
+      </c>
+      <c r="AQ33">
+        <v>1.01</v>
+      </c>
+      <c r="AR33">
+        <v>1.01</v>
+      </c>
+      <c r="AS33">
+        <v>1.01</v>
+      </c>
+      <c r="AT33">
+        <v>1.01</v>
+      </c>
+      <c r="AU33">
+        <v>1.01</v>
+      </c>
+      <c r="AV33">
+        <v>1.01</v>
+      </c>
+      <c r="AW33">
+        <v>1.01</v>
+      </c>
+      <c r="AX33">
+        <v>1.01</v>
+      </c>
+      <c r="AY33">
+        <v>1.01</v>
+      </c>
+      <c r="AZ33">
+        <v>1.01</v>
+      </c>
+      <c r="BA33">
+        <v>1.01</v>
+      </c>
+      <c r="BB33">
+        <v>1.01</v>
+      </c>
+      <c r="BC33">
+        <v>1.01</v>
+      </c>
+      <c r="BD33">
+        <v>1.01</v>
+      </c>
+      <c r="BE33">
+        <v>1.01</v>
+      </c>
+      <c r="BF33">
+        <v>1.01</v>
+      </c>
+      <c r="BG33">
+        <v>1.01</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.01</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.01</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.01</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.01</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.01</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.01</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.01</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.01</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.01</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" t="s">
+        <v>154</v>
+      </c>
+      <c r="E34" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34">
+        <v>1.68</v>
+      </c>
+      <c r="G34">
+        <v>1.86</v>
+      </c>
+      <c r="H34">
+        <v>5.2</v>
+      </c>
+      <c r="I34">
+        <v>6.8</v>
+      </c>
+      <c r="J34">
+        <v>3.5</v>
+      </c>
+      <c r="K34">
+        <v>4.7</v>
+      </c>
+      <c r="L34">
+        <v>1.01</v>
+      </c>
+      <c r="M34">
+        <v>1.01</v>
+      </c>
+      <c r="N34">
+        <v>2.96</v>
+      </c>
+      <c r="O34">
+        <v>1.38</v>
+      </c>
+      <c r="P34">
+        <v>1.68</v>
+      </c>
+      <c r="Q34">
+        <v>2.18</v>
+      </c>
+      <c r="R34">
+        <v>1.17</v>
+      </c>
+      <c r="S34">
+        <v>3.9</v>
+      </c>
+      <c r="T34">
+        <v>1.01</v>
+      </c>
+      <c r="U34">
+        <v>1.01</v>
+      </c>
+      <c r="V34">
+        <v>1.17</v>
+      </c>
+      <c r="W34">
+        <v>2.16</v>
+      </c>
+      <c r="X34">
+        <v>13.5</v>
+      </c>
+      <c r="Y34">
+        <v>1000</v>
+      </c>
+      <c r="Z34">
+        <v>1000</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>1000</v>
+      </c>
+      <c r="AC34">
+        <v>10</v>
+      </c>
+      <c r="AD34">
+        <v>28</v>
+      </c>
+      <c r="AE34">
+        <v>1000</v>
+      </c>
+      <c r="AF34">
+        <v>12</v>
+      </c>
+      <c r="AG34">
+        <v>12.5</v>
+      </c>
+      <c r="AH34">
+        <v>29</v>
+      </c>
+      <c r="AI34">
+        <v>1000</v>
+      </c>
+      <c r="AJ34">
+        <v>23</v>
+      </c>
+      <c r="AK34">
+        <v>26</v>
+      </c>
+      <c r="AL34">
+        <v>1000</v>
+      </c>
+      <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>1000</v>
+      </c>
+      <c r="AO34">
+        <v>1000</v>
+      </c>
+      <c r="AP34">
+        <v>1.71</v>
+      </c>
+      <c r="AQ34">
+        <v>1.95</v>
+      </c>
+      <c r="AR34">
+        <v>1.95</v>
+      </c>
+      <c r="AS34">
+        <v>1.95</v>
+      </c>
+      <c r="AT34">
+        <v>1.95</v>
+      </c>
+      <c r="AU34">
+        <v>1.63</v>
+      </c>
+      <c r="AV34">
+        <v>1.83</v>
+      </c>
+      <c r="AW34">
+        <v>1.95</v>
+      </c>
+      <c r="AX34">
+        <v>1.68</v>
+      </c>
+      <c r="AY34">
+        <v>1.69</v>
+      </c>
+      <c r="AZ34">
+        <v>1.83</v>
+      </c>
+      <c r="BA34">
+        <v>1.95</v>
+      </c>
+      <c r="BB34">
+        <v>1.8</v>
+      </c>
+      <c r="BC34">
+        <v>1.82</v>
+      </c>
+      <c r="BD34">
+        <v>1.95</v>
+      </c>
+      <c r="BE34">
+        <v>1.95</v>
+      </c>
+      <c r="BF34">
+        <v>1.95</v>
+      </c>
+      <c r="BG34">
+        <v>1.95</v>
+      </c>
+      <c r="BH34">
+        <v>3.65</v>
+      </c>
+      <c r="BI34">
+        <v>2.46</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.39</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.39</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>1.39</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.39</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.39</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.39</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.39</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.39</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.39</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35">
+        <v>2.54</v>
+      </c>
+      <c r="G35">
+        <v>3.15</v>
+      </c>
+      <c r="H35">
+        <v>2.72</v>
+      </c>
+      <c r="I35">
+        <v>3.45</v>
+      </c>
+      <c r="J35">
+        <v>3.1</v>
+      </c>
+      <c r="K35">
+        <v>4.2</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.01</v>
+      </c>
+      <c r="N35">
+        <v>2.92</v>
+      </c>
+      <c r="O35">
+        <v>1.36</v>
+      </c>
+      <c r="P35">
+        <v>1.64</v>
+      </c>
+      <c r="Q35">
+        <v>2.02</v>
+      </c>
+      <c r="R35">
+        <v>1.25</v>
+      </c>
+      <c r="S35">
+        <v>3.15</v>
+      </c>
+      <c r="T35">
+        <v>1.01</v>
+      </c>
+      <c r="U35">
+        <v>1.01</v>
+      </c>
+      <c r="V35">
+        <v>1.42</v>
+      </c>
+      <c r="W35">
+        <v>1.47</v>
+      </c>
+      <c r="X35">
+        <v>1000</v>
+      </c>
+      <c r="Y35">
+        <v>1000</v>
+      </c>
+      <c r="Z35">
+        <v>1000</v>
+      </c>
+      <c r="AA35">
+        <v>1000</v>
+      </c>
+      <c r="AB35">
+        <v>1000</v>
+      </c>
+      <c r="AC35">
+        <v>1000</v>
+      </c>
+      <c r="AD35">
+        <v>1000</v>
+      </c>
+      <c r="AE35">
+        <v>1000</v>
+      </c>
+      <c r="AF35">
+        <v>1000</v>
+      </c>
+      <c r="AG35">
+        <v>1000</v>
+      </c>
+      <c r="AH35">
+        <v>1000</v>
+      </c>
+      <c r="AI35">
+        <v>1000</v>
+      </c>
+      <c r="AJ35">
+        <v>1000</v>
+      </c>
+      <c r="AK35">
+        <v>1000</v>
+      </c>
+      <c r="AL35">
+        <v>1000</v>
+      </c>
+      <c r="AM35">
+        <v>1000</v>
+      </c>
+      <c r="AN35">
+        <v>1000</v>
+      </c>
+      <c r="AO35">
+        <v>1000</v>
+      </c>
+      <c r="AP35">
+        <v>1.01</v>
+      </c>
+      <c r="AQ35">
+        <v>1.01</v>
+      </c>
+      <c r="AR35">
+        <v>1.01</v>
+      </c>
+      <c r="AS35">
+        <v>1.01</v>
+      </c>
+      <c r="AT35">
+        <v>1.01</v>
+      </c>
+      <c r="AU35">
+        <v>1.01</v>
+      </c>
+      <c r="AV35">
+        <v>1.01</v>
+      </c>
+      <c r="AW35">
+        <v>1.01</v>
+      </c>
+      <c r="AX35">
+        <v>1.01</v>
+      </c>
+      <c r="AY35">
+        <v>1.01</v>
+      </c>
+      <c r="AZ35">
+        <v>1.01</v>
+      </c>
+      <c r="BA35">
+        <v>1.01</v>
+      </c>
+      <c r="BB35">
+        <v>1.01</v>
+      </c>
+      <c r="BC35">
+        <v>1.01</v>
+      </c>
+      <c r="BD35">
+        <v>1.01</v>
+      </c>
+      <c r="BE35">
+        <v>1.01</v>
+      </c>
+      <c r="BF35">
+        <v>1.01</v>
+      </c>
+      <c r="BG35">
+        <v>1.01</v>
+      </c>
+      <c r="BH35">
+        <v>4</v>
+      </c>
+      <c r="BI35">
+        <v>2.42</v>
+      </c>
+      <c r="BJ35">
+        <v>13</v>
+      </c>
+      <c r="BK35">
+        <v>2.88</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>3.7</v>
+      </c>
+      <c r="BN35">
+        <v>7.2</v>
+      </c>
+      <c r="BO35">
+        <v>4</v>
+      </c>
+      <c r="BP35">
+        <v>29</v>
+      </c>
+      <c r="BQ35">
+        <v>3.25</v>
+      </c>
+      <c r="BR35">
+        <v>48</v>
+      </c>
+      <c r="BS35">
+        <v>3.4</v>
+      </c>
+      <c r="BT35">
+        <v>7.6</v>
+      </c>
+      <c r="BU35">
+        <v>4.2</v>
+      </c>
+      <c r="BV35">
+        <v>30</v>
+      </c>
+      <c r="BW35">
+        <v>3.3</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>3.45</v>
+      </c>
+      <c r="BZ35">
+        <v>42</v>
+      </c>
+      <c r="CA35">
+        <v>3.4</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -586,7 +586,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-09 01:02:42</t>
+    <t>2026-08-09 03:18:47</t>
   </si>
 </sst>
 </file>
@@ -1183,43 +1183,43 @@
         <v>1.74</v>
       </c>
       <c r="G2">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H2">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="I2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J2">
         <v>3.85</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
         <v>1.3</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
         <v>1.85</v>
@@ -1228,28 +1228,28 @@
         <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="Y2">
         <v>18.5</v>
       </c>
       <c r="Z2">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD2">
         <v>20</v>
@@ -1258,43 +1258,43 @@
         <v>90</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AK2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AS2">
         <v>40</v>
@@ -1303,31 +1303,31 @@
         <v>8</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
         <v>32</v>
       </c>
       <c r="AX2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BA2">
         <v>32</v>
       </c>
       <c r="BB2">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC2">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BD2">
         <v>23</v>
@@ -1422,220 +1422,220 @@
         <v>157</v>
       </c>
       <c r="F3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G3">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="M3">
         <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P3">
         <v>1.56</v>
       </c>
       <c r="Q3">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="R3">
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1664,226 +1664,226 @@
         <v>158</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="G4">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H4">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I4">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J4">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K4">
         <v>3.3</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="M4">
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P4">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q4">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S4">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>190</v>
@@ -1909,13 +1909,13 @@
         <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J5">
         <v>3.25</v>
@@ -1924,148 +1924,148 @@
         <v>3.5</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
         <v>1.76</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
         <v>1.29</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2148,59 +2148,59 @@
         <v>160</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
-        <v>2.22</v>
+        <v>110</v>
       </c>
       <c r="H6">
-        <v>4.1</v>
+        <v>1.24</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>170</v>
       </c>
       <c r="J6">
-        <v>3.15</v>
+        <v>1.24</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L6">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.62</v>
+        <v>1.17</v>
       </c>
       <c r="O6">
+        <v>1.41</v>
+      </c>
+      <c r="P6">
+        <v>1.17</v>
+      </c>
+      <c r="Q6">
+        <v>1.41</v>
+      </c>
+      <c r="R6">
+        <v>1.18</v>
+      </c>
+      <c r="S6">
         <v>1.02</v>
       </c>
-      <c r="P6">
-        <v>1.47</v>
-      </c>
-      <c r="Q6">
-        <v>2.12</v>
-      </c>
-      <c r="R6">
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.75</v>
+      </c>
+      <c r="V6">
+        <v>1.01</v>
+      </c>
+      <c r="W6">
         <v>1.23</v>
       </c>
-      <c r="S6">
-        <v>4.4</v>
-      </c>
-      <c r="T6">
-        <v>1.01</v>
-      </c>
-      <c r="U6">
-        <v>1.01</v>
-      </c>
-      <c r="V6">
-        <v>1.23</v>
-      </c>
-      <c r="W6">
-        <v>1.81</v>
-      </c>
       <c r="X6">
         <v>1000</v>
       </c>
@@ -2256,52 +2256,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2390,226 +2390,226 @@
         <v>161</v>
       </c>
       <c r="F7">
-        <v>2.2</v>
+        <v>1.02</v>
       </c>
       <c r="G7">
-        <v>2.52</v>
+        <v>190</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="I7">
-        <v>3.6</v>
+        <v>190</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L7">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>3.95</v>
+        <v>1.09</v>
       </c>
       <c r="O7">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="Q7">
-        <v>1.81</v>
+        <v>1.03</v>
       </c>
       <c r="R7">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="S7">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="T7">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
         <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
         <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
         <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
         <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>190</v>
@@ -2632,220 +2632,220 @@
         <v>162</v>
       </c>
       <c r="F8">
-        <v>1.97</v>
+        <v>1.05</v>
       </c>
       <c r="G8">
-        <v>2.16</v>
+        <v>95</v>
       </c>
       <c r="H8">
-        <v>3.65</v>
+        <v>1.09</v>
       </c>
       <c r="I8">
-        <v>4.2</v>
+        <v>990</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>1.11</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L8">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>1.25</v>
       </c>
       <c r="O8">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P8">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.78</v>
+        <v>1.23</v>
       </c>
       <c r="R8">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>1.23</v>
       </c>
       <c r="T8">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2874,226 +2874,226 @@
         <v>163</v>
       </c>
       <c r="F9">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>3.5</v>
+        <v>110</v>
       </c>
       <c r="H9">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>950</v>
       </c>
       <c r="L9">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="O9">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="Q9">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
         <v>190</v>
@@ -3116,22 +3116,22 @@
         <v>164</v>
       </c>
       <c r="F10">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="G10">
-        <v>2.46</v>
+        <v>110</v>
       </c>
       <c r="H10">
-        <v>3.3</v>
+        <v>1.08</v>
       </c>
       <c r="I10">
-        <v>3.75</v>
+        <v>110</v>
       </c>
       <c r="J10">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="K10">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3140,22 +3140,22 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>2.82</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.87</v>
+        <v>1.34</v>
       </c>
       <c r="R10">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
-        <v>3.3</v>
+        <v>1.34</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3164,55 +3164,55 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.68</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1000</v>
       </c>
       <c r="Y10">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
         <v>1000</v>
@@ -3224,58 +3224,58 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3358,112 +3358,112 @@
         <v>165</v>
       </c>
       <c r="F11">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="G11">
         <v>1.73</v>
       </c>
       <c r="H11">
-        <v>4.8</v>
+        <v>2.42</v>
       </c>
       <c r="I11">
-        <v>5.9</v>
+        <v>130</v>
       </c>
       <c r="J11">
-        <v>3.95</v>
+        <v>2.42</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>3.4</v>
+        <v>1.18</v>
       </c>
       <c r="O11">
         <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2.06</v>
+        <v>1.18</v>
       </c>
       <c r="Q11">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="R11">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="T11">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
         <v>2.36</v>
       </c>
       <c r="X11">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
         <v>1.01</v>
@@ -3475,7 +3475,7 @@
         <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
         <v>1.01</v>
@@ -3487,7 +3487,7 @@
         <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
         <v>1.01</v>
@@ -3499,7 +3499,7 @@
         <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
         <v>1.01</v>
@@ -3511,7 +3511,7 @@
         <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3523,55 +3523,55 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3600,166 +3600,166 @@
         <v>166</v>
       </c>
       <c r="F12">
-        <v>1.94</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
-        <v>2.1</v>
+        <v>90</v>
       </c>
       <c r="H12">
-        <v>4.1</v>
+        <v>1.09</v>
       </c>
       <c r="I12">
-        <v>4.9</v>
+        <v>110</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>1.06</v>
       </c>
       <c r="K12">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="O12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P12">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="Q12">
-        <v>2.18</v>
+        <v>1.38</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
-        <v>4.1</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.9</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3845,16 +3845,16 @@
         <v>2.3</v>
       </c>
       <c r="G13">
-        <v>2.52</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>3.05</v>
+        <v>1.08</v>
       </c>
       <c r="I13">
-        <v>3.45</v>
+        <v>110</v>
       </c>
       <c r="J13">
-        <v>3.55</v>
+        <v>1.27</v>
       </c>
       <c r="K13">
         <v>3.8</v>
@@ -3863,205 +3863,205 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="O13">
         <v>1.26</v>
       </c>
       <c r="P13">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="R13">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>1.26</v>
       </c>
       <c r="T13">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="X13">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>190</v>
@@ -4087,163 +4087,163 @@
         <v>4.2</v>
       </c>
       <c r="G14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H14">
         <v>1.85</v>
       </c>
       <c r="I14">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="O14">
         <v>1.18</v>
       </c>
       <c r="P14">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R14">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="S14">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T14">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="U14">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="W14">
         <v>1.29</v>
       </c>
       <c r="X14">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z14">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AA14">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD14">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE14">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AP14">
-        <v>20</v>
+        <v>1.34</v>
       </c>
       <c r="AQ14">
-        <v>11</v>
+        <v>1.28</v>
       </c>
       <c r="AR14">
-        <v>12</v>
+        <v>1.29</v>
       </c>
       <c r="AS14">
-        <v>18.5</v>
+        <v>1.34</v>
       </c>
       <c r="AT14">
-        <v>19</v>
+        <v>1.34</v>
       </c>
       <c r="AU14">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AV14">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AW14">
-        <v>14.5</v>
+        <v>1.33</v>
       </c>
       <c r="AX14">
-        <v>25</v>
+        <v>1.34</v>
       </c>
       <c r="AY14">
-        <v>15</v>
+        <v>1.33</v>
       </c>
       <c r="AZ14">
-        <v>13</v>
+        <v>1.33</v>
       </c>
       <c r="BA14">
-        <v>6.6</v>
+        <v>1.34</v>
       </c>
       <c r="BB14">
-        <v>7.8</v>
+        <v>1.34</v>
       </c>
       <c r="BC14">
-        <v>32</v>
+        <v>1.34</v>
       </c>
       <c r="BD14">
-        <v>29</v>
+        <v>1.34</v>
       </c>
       <c r="BE14">
-        <v>7.6</v>
+        <v>1.34</v>
       </c>
       <c r="BF14">
-        <v>6.8</v>
+        <v>1.34</v>
       </c>
       <c r="BG14">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4326,145 +4326,145 @@
         <v>169</v>
       </c>
       <c r="F15">
-        <v>2.44</v>
+        <v>1.43</v>
       </c>
       <c r="G15">
-        <v>2.74</v>
+        <v>110</v>
       </c>
       <c r="H15">
-        <v>2.96</v>
+        <v>1.58</v>
       </c>
       <c r="I15">
-        <v>3.4</v>
+        <v>110</v>
       </c>
       <c r="J15">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="O15">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="Q15">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="R15">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="S15">
-        <v>3.7</v>
+        <v>1.34</v>
       </c>
       <c r="T15">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X15">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
         <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
         <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
         <v>1.01</v>
@@ -4473,7 +4473,7 @@
         <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
         <v>1.01</v>
@@ -4482,64 +4482,64 @@
         <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
         <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4568,22 +4568,22 @@
         <v>170</v>
       </c>
       <c r="F16">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="G16">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="H16">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="I16">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="J16">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="K16">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L16">
         <v>1.19</v>
@@ -4592,142 +4592,142 @@
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>7.8</v>
+        <v>3.25</v>
       </c>
       <c r="O16">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P16">
         <v>3.2</v>
       </c>
       <c r="Q16">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="R16">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="S16">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="T16">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="U16">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V16">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="W16">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="X16">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>3.85</v>
+        <v>970</v>
       </c>
       <c r="AO16">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>8.199999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="AQ16">
-        <v>8.6</v>
+        <v>1.32</v>
       </c>
       <c r="AR16">
-        <v>9.4</v>
+        <v>1.32</v>
       </c>
       <c r="AS16">
-        <v>9.800000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="AT16">
-        <v>12</v>
+        <v>1.32</v>
       </c>
       <c r="AU16">
-        <v>6</v>
+        <v>1.32</v>
       </c>
       <c r="AV16">
-        <v>8</v>
+        <v>1.32</v>
       </c>
       <c r="AW16">
-        <v>9.4</v>
+        <v>1.32</v>
       </c>
       <c r="AX16">
-        <v>9.800000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="AY16">
-        <v>9.800000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="AZ16">
-        <v>7</v>
+        <v>1.32</v>
       </c>
       <c r="BA16">
-        <v>9.199999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="BB16">
-        <v>10.5</v>
+        <v>1.32</v>
       </c>
       <c r="BC16">
-        <v>11.5</v>
+        <v>1.32</v>
       </c>
       <c r="BD16">
-        <v>7.4</v>
+        <v>1.32</v>
       </c>
       <c r="BE16">
-        <v>9.199999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="BF16">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>9.4</v>
+        <v>1.32</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4810,166 +4810,166 @@
         <v>171</v>
       </c>
       <c r="F17">
-        <v>2.98</v>
+        <v>1.09</v>
       </c>
       <c r="G17">
-        <v>3.35</v>
+        <v>110</v>
       </c>
       <c r="H17">
         <v>2.08</v>
       </c>
       <c r="I17">
-        <v>2.24</v>
+        <v>85</v>
       </c>
       <c r="J17">
-        <v>4.4</v>
+        <v>1.09</v>
       </c>
       <c r="K17">
-        <v>5.5</v>
+        <v>950</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17">
-        <v>8.199999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="O17">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P17">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="R17">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="S17">
-        <v>1.87</v>
+        <v>1.09</v>
       </c>
       <c r="T17">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
-        <v>1.43</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
         <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
         <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
         <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5052,145 +5052,145 @@
         <v>172</v>
       </c>
       <c r="F18">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="G18">
-        <v>2.5</v>
+        <v>110</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I18">
-        <v>3.5</v>
+        <v>110</v>
       </c>
       <c r="J18">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="K18">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L18">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
         <v>1.06</v>
       </c>
       <c r="N18">
-        <v>3.95</v>
+        <v>1.25</v>
       </c>
       <c r="O18">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P18">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="R18">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="S18">
-        <v>3</v>
+        <v>1.26</v>
       </c>
       <c r="T18">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W18">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
         <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
         <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
         <v>1.01</v>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
         <v>1.01</v>
@@ -5208,64 +5208,64 @@
         <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -5294,16 +5294,16 @@
         <v>173</v>
       </c>
       <c r="F19">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G19">
-        <v>2.9</v>
+        <v>110</v>
       </c>
       <c r="H19">
-        <v>2.44</v>
+        <v>1.37</v>
       </c>
       <c r="I19">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -5318,40 +5318,40 @@
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="O19">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P19">
-        <v>2.64</v>
+        <v>1.3</v>
       </c>
       <c r="Q19">
         <v>1.53</v>
       </c>
       <c r="R19">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="S19">
         <v>2.3</v>
       </c>
       <c r="T19">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W19">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
         <v>27</v>
       </c>
       <c r="Y19">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z19">
         <v>21</v>
@@ -5360,82 +5360,82 @@
         <v>36</v>
       </c>
       <c r="AB19">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AD19">
         <v>12.5</v>
       </c>
       <c r="AE19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF19">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="AG19">
-        <v>13.5</v>
+        <v>50</v>
       </c>
       <c r="AH19">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="AI19">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AJ19">
-        <v>42</v>
+        <v>580</v>
       </c>
       <c r="AK19">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="AL19">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="AM19">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="AN19">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="AO19">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AP19">
         <v>20</v>
       </c>
       <c r="AQ19">
-        <v>15.5</v>
+        <v>8.6</v>
       </c>
       <c r="AR19">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS19">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="AT19">
         <v>16.5</v>
       </c>
       <c r="AU19">
+        <v>2</v>
+      </c>
+      <c r="AV19">
         <v>9</v>
       </c>
-      <c r="AV19">
-        <v>11</v>
-      </c>
       <c r="AW19">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AX19">
         <v>21</v>
       </c>
       <c r="AY19">
-        <v>11.5</v>
+        <v>2.16</v>
       </c>
       <c r="AZ19">
         <v>13</v>
       </c>
       <c r="BA19">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BB19">
         <v>36</v>
@@ -5447,13 +5447,13 @@
         <v>26</v>
       </c>
       <c r="BE19">
-        <v>42</v>
+        <v>2.24</v>
       </c>
       <c r="BF19">
         <v>13</v>
       </c>
       <c r="BG19">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5536,226 +5536,226 @@
         <v>174</v>
       </c>
       <c r="F20">
-        <v>2.12</v>
+        <v>1.23</v>
       </c>
       <c r="G20">
-        <v>2.34</v>
+        <v>110</v>
       </c>
       <c r="H20">
-        <v>2.96</v>
+        <v>1.27</v>
       </c>
       <c r="I20">
-        <v>3.45</v>
+        <v>110</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>1.14</v>
       </c>
       <c r="K20">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L20">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>1.31</v>
       </c>
       <c r="O20">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P20">
-        <v>2.74</v>
+        <v>1.31</v>
       </c>
       <c r="Q20">
-        <v>1.46</v>
+        <v>1.12</v>
       </c>
       <c r="R20">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="S20">
-        <v>2.12</v>
+        <v>1.12</v>
       </c>
       <c r="T20">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="W20">
-        <v>1.75</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
         <v>190</v>
@@ -5778,25 +5778,25 @@
         <v>175</v>
       </c>
       <c r="F21">
-        <v>3.5</v>
+        <v>1.26</v>
       </c>
       <c r="G21">
-        <v>4.3</v>
+        <v>110</v>
       </c>
       <c r="H21">
-        <v>1.95</v>
+        <v>1.16</v>
       </c>
       <c r="I21">
-        <v>2.1</v>
+        <v>110</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>1.09</v>
       </c>
       <c r="K21">
-        <v>4.5</v>
+        <v>100</v>
       </c>
       <c r="L21">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
         <v>1.03</v>
@@ -5808,16 +5808,16 @@
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="Q21">
         <v>1.4</v>
       </c>
       <c r="R21">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="S21">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -5826,19 +5826,19 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.9</v>
+        <v>1.08</v>
       </c>
       <c r="W21">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
         <v>1000</v>
       </c>
       <c r="Y21">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
         <v>1000</v>
@@ -5856,22 +5856,22 @@
         <v>1000</v>
       </c>
       <c r="AF21">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
         <v>1000</v>
@@ -5883,121 +5883,121 @@
         <v>1000</v>
       </c>
       <c r="AO21">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
         <v>190</v>
@@ -6020,46 +6020,46 @@
         <v>176</v>
       </c>
       <c r="F22">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G22">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H22">
-        <v>6.2</v>
+        <v>1.08</v>
       </c>
       <c r="I22">
-        <v>7.4</v>
+        <v>110</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>2.52</v>
       </c>
       <c r="K22">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M22">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N22">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O22">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P22">
+        <v>1.98</v>
+      </c>
+      <c r="Q22">
         <v>1.87</v>
       </c>
-      <c r="Q22">
-        <v>1.65</v>
-      </c>
       <c r="R22">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S22">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6068,10 +6068,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W22">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6262,19 +6262,19 @@
         <v>177</v>
       </c>
       <c r="F23">
-        <v>3.8</v>
+        <v>1.52</v>
       </c>
       <c r="G23">
-        <v>4.5</v>
+        <v>110</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="I23">
-        <v>2.18</v>
+        <v>970</v>
       </c>
       <c r="J23">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="K23">
         <v>3.75</v>
@@ -6283,205 +6283,205 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N23">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="O23">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P23">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="Q23">
         <v>2</v>
       </c>
       <c r="R23">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S23">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="T23">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.85</v>
+        <v>1.08</v>
       </c>
       <c r="W23">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
         <v>190</v>
@@ -6504,154 +6504,154 @@
         <v>178</v>
       </c>
       <c r="F24">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G24">
-        <v>2.22</v>
+        <v>110</v>
       </c>
       <c r="H24">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="I24">
-        <v>4.3</v>
+        <v>170</v>
       </c>
       <c r="J24">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="K24">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N24">
-        <v>3.5</v>
+        <v>1.24</v>
       </c>
       <c r="O24">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="P24">
-        <v>1.89</v>
+        <v>1.24</v>
       </c>
       <c r="Q24">
-        <v>1.93</v>
+        <v>1.06</v>
       </c>
       <c r="R24">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S24">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="T24">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W24">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
         <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
         <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
         <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
         <v>1.01</v>
@@ -6660,7 +6660,7 @@
         <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
         <v>1.01</v>
@@ -6746,112 +6746,112 @@
         <v>179</v>
       </c>
       <c r="F25">
-        <v>3.6</v>
+        <v>1.21</v>
       </c>
       <c r="G25">
-        <v>4.1</v>
+        <v>190</v>
       </c>
       <c r="H25">
-        <v>2.18</v>
+        <v>1.21</v>
       </c>
       <c r="I25">
-        <v>2.36</v>
+        <v>190</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="K25">
-        <v>3.35</v>
+        <v>100</v>
       </c>
       <c r="L25">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>2.6</v>
+        <v>1.25</v>
       </c>
       <c r="O25">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="P25">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="Q25">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="R25">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="S25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T25">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="W25">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="X25">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
         <v>1.01</v>
@@ -6887,37 +6887,37 @@
         <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
         <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
         <v>1000</v>
@@ -6926,43 +6926,43 @@
         <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
         <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
         <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
         <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
         <v>1.01</v>
@@ -6988,46 +6988,46 @@
         <v>180</v>
       </c>
       <c r="F26">
-        <v>2.8</v>
+        <v>1.12</v>
       </c>
       <c r="G26">
-        <v>3.3</v>
+        <v>110</v>
       </c>
       <c r="H26">
-        <v>2.64</v>
+        <v>1.11</v>
       </c>
       <c r="I26">
-        <v>3.15</v>
+        <v>110</v>
       </c>
       <c r="J26">
-        <v>2.78</v>
+        <v>1.12</v>
       </c>
       <c r="K26">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L26">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
-        <v>2.92</v>
+        <v>1.25</v>
       </c>
       <c r="O26">
         <v>1.4</v>
       </c>
       <c r="P26">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="Q26">
-        <v>2.18</v>
+        <v>1.39</v>
       </c>
       <c r="R26">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S26">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -7036,10 +7036,10 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="W26">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7057,19 +7057,19 @@
         <v>1000</v>
       </c>
       <c r="AC26">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
         <v>1000</v>
       </c>
       <c r="AE26">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
         <v>1000</v>
       </c>
       <c r="AG26">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
         <v>1000</v>
@@ -7096,118 +7096,118 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
         <v>190</v>
@@ -7338,52 +7338,52 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF27">
         <v>1.01</v>
@@ -7472,226 +7472,226 @@
         <v>182</v>
       </c>
       <c r="F28">
-        <v>1.88</v>
+        <v>1.08</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="H28">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I28">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J28">
-        <v>3.4</v>
+        <v>1.28</v>
       </c>
       <c r="K28">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="O28">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P28">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="Q28">
         <v>2.24</v>
       </c>
       <c r="R28">
+        <v>1.18</v>
+      </c>
+      <c r="S28">
+        <v>2.24</v>
+      </c>
+      <c r="T28">
+        <v>1.01</v>
+      </c>
+      <c r="U28">
+        <v>1.01</v>
+      </c>
+      <c r="V28">
+        <v>1.01</v>
+      </c>
+      <c r="W28">
         <v>1.26</v>
       </c>
-      <c r="S28">
-        <v>4.1</v>
-      </c>
-      <c r="T28">
-        <v>1.82</v>
-      </c>
-      <c r="U28">
-        <v>1.89</v>
-      </c>
-      <c r="V28">
-        <v>1.22</v>
-      </c>
-      <c r="W28">
-        <v>2</v>
-      </c>
       <c r="X28">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
         <v>190</v>
@@ -7714,226 +7714,226 @@
         <v>183</v>
       </c>
       <c r="F29">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="G29">
-        <v>2.18</v>
+        <v>110</v>
       </c>
       <c r="H29">
-        <v>4.1</v>
+        <v>1.77</v>
       </c>
       <c r="I29">
-        <v>5.3</v>
+        <v>150</v>
       </c>
       <c r="J29">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="K29">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L29">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N29">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="O29">
         <v>1.44</v>
       </c>
       <c r="P29">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="Q29">
-        <v>2.28</v>
+        <v>1.43</v>
       </c>
       <c r="R29">
+        <v>1.13</v>
+      </c>
+      <c r="S29">
+        <v>2.36</v>
+      </c>
+      <c r="T29">
+        <v>1.01</v>
+      </c>
+      <c r="U29">
+        <v>1.01</v>
+      </c>
+      <c r="V29">
+        <v>1.01</v>
+      </c>
+      <c r="W29">
         <v>1.23</v>
       </c>
-      <c r="S29">
-        <v>4.5</v>
-      </c>
-      <c r="T29">
-        <v>1.88</v>
-      </c>
-      <c r="U29">
-        <v>1.74</v>
-      </c>
-      <c r="V29">
-        <v>1.23</v>
-      </c>
-      <c r="W29">
-        <v>1.84</v>
-      </c>
       <c r="X29">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z29">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD29">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE29">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG29">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH29">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI29">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK29">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL29">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM29">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO29">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR29">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS29">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT29">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU29">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV29">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW29">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX29">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY29">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA29">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB29">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC29">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD29">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE29">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF29">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG29">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH29">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
         <v>190</v>
@@ -7956,226 +7956,226 @@
         <v>184</v>
       </c>
       <c r="F30">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="H30">
-        <v>1.92</v>
+        <v>1.05</v>
       </c>
       <c r="I30">
-        <v>2.1</v>
+        <v>110</v>
       </c>
       <c r="J30">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="K30">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L30">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
         <v>1.07</v>
       </c>
       <c r="N30">
-        <v>3.3</v>
+        <v>1.24</v>
       </c>
       <c r="O30">
         <v>1.34</v>
       </c>
       <c r="P30">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="R30">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S30">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U30">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="W30">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="X30">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR30">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU30">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV30">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW30">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY30">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA30">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH30">
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="s">
         <v>190</v>
@@ -8440,19 +8440,19 @@
         <v>186</v>
       </c>
       <c r="F32">
-        <v>3.35</v>
+        <v>1.52</v>
       </c>
       <c r="G32">
-        <v>3.75</v>
+        <v>110</v>
       </c>
       <c r="H32">
-        <v>2.52</v>
+        <v>1.52</v>
       </c>
       <c r="I32">
-        <v>2.74</v>
+        <v>110</v>
       </c>
       <c r="J32">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="K32">
         <v>3</v>
@@ -8461,205 +8461,205 @@
         <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="O32">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="P32">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="R32">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="S32">
-        <v>6</v>
+        <v>2.26</v>
       </c>
       <c r="T32">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U32">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="W32">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD32">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH32">
         <v>1000</v>
       </c>
       <c r="BI32">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU32">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
         <v>190</v>
@@ -8682,28 +8682,28 @@
         <v>187</v>
       </c>
       <c r="F33">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="G33">
-        <v>3.1</v>
+        <v>190</v>
       </c>
       <c r="H33">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="I33">
-        <v>3.25</v>
+        <v>190</v>
       </c>
       <c r="J33">
-        <v>2.88</v>
+        <v>1.02</v>
       </c>
       <c r="K33">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L33">
         <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N33">
         <v>1.01</v>
@@ -8712,10 +8712,10 @@
         <v>1.01</v>
       </c>
       <c r="P33">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q33">
-        <v>2.48</v>
+        <v>1.1</v>
       </c>
       <c r="R33">
         <v>1.14</v>
@@ -8724,10 +8724,10 @@
         <v>1.02</v>
       </c>
       <c r="T33">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U33">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V33">
         <v>1.01</v>
@@ -8924,22 +8924,22 @@
         <v>188</v>
       </c>
       <c r="F34">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="G34">
-        <v>1.86</v>
+        <v>110</v>
       </c>
       <c r="H34">
-        <v>5.2</v>
+        <v>1.09</v>
       </c>
       <c r="I34">
-        <v>6.8</v>
+        <v>110</v>
       </c>
       <c r="J34">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="K34">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -8948,22 +8948,22 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>2.96</v>
+        <v>1.25</v>
       </c>
       <c r="O34">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="P34">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="Q34">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="R34">
         <v>1.17</v>
       </c>
       <c r="S34">
-        <v>3.9</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
         <v>1.01</v>
@@ -8972,13 +8972,13 @@
         <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W34">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y34">
         <v>1000</v>
@@ -8993,31 +8993,31 @@
         <v>1000</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD34">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE34">
         <v>1000</v>
       </c>
       <c r="AF34">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG34">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH34">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI34">
         <v>1000</v>
       </c>
       <c r="AJ34">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK34">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL34">
         <v>1000</v>
@@ -9032,118 +9032,118 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="AR34">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="AS34">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT34">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="AU34">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="AV34">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="AW34">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="AX34">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="AY34">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="BA34">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BB34">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC34">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BD34">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE34">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BF34">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BG34">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH34">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI34">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BN34">
         <v>1000</v>
       </c>
       <c r="BO34">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BP34">
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BT34">
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="CB34" t="s">
         <v>190</v>
@@ -9166,22 +9166,22 @@
         <v>189</v>
       </c>
       <c r="F35">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="G35">
-        <v>3.15</v>
+        <v>190</v>
       </c>
       <c r="H35">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I35">
-        <v>3.45</v>
+        <v>190</v>
       </c>
       <c r="J35">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="K35">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -9190,22 +9190,22 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>2.92</v>
+        <v>1.26</v>
       </c>
       <c r="O35">
         <v>1.36</v>
       </c>
       <c r="P35">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="Q35">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="R35">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="S35">
-        <v>3.15</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
         <v>1.01</v>
@@ -9214,10 +9214,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="W35">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9328,64 +9328,64 @@
         <v>1.01</v>
       </c>
       <c r="BH35">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI35">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BJ35">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK35">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BN35">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO35">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP35">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BR35">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS35">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT35">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU35">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV35">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW35">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA35">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB35" t="s">
         <v>190</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -586,7 +586,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-09 03:18:47</t>
+    <t>2026-08-09 05:34:30</t>
   </si>
 </sst>
 </file>
@@ -1180,25 +1180,25 @@
         <v>156</v>
       </c>
       <c r="F2">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G2">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H2">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
         <v>4.2</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M2">
         <v>1.06</v>
@@ -1213,7 +1213,7 @@
         <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R2">
         <v>1.4</v>
@@ -1228,178 +1228,178 @@
         <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W2">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="X2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y2">
+        <v>19</v>
+      </c>
+      <c r="Z2">
+        <v>46</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>9</v>
+      </c>
+      <c r="AC2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>22</v>
+      </c>
+      <c r="AE2">
+        <v>95</v>
+      </c>
+      <c r="AF2">
+        <v>10.5</v>
+      </c>
+      <c r="AG2">
+        <v>10.5</v>
+      </c>
+      <c r="AH2">
+        <v>21</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
         <v>18.5</v>
       </c>
-      <c r="Z2">
-        <v>80</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>10</v>
-      </c>
-      <c r="AC2">
-        <v>9.6</v>
-      </c>
-      <c r="AD2">
-        <v>20</v>
-      </c>
-      <c r="AE2">
+      <c r="AK2">
+        <v>19</v>
+      </c>
+      <c r="AL2">
+        <v>38</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>10.5</v>
+      </c>
+      <c r="AO2">
         <v>90</v>
       </c>
-      <c r="AF2">
-        <v>12</v>
-      </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
-      <c r="AH2">
-        <v>29</v>
-      </c>
-      <c r="AI2">
-        <v>1000</v>
-      </c>
-      <c r="AJ2">
-        <v>23</v>
-      </c>
-      <c r="AK2">
-        <v>24</v>
-      </c>
-      <c r="AL2">
-        <v>80</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>12</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
       <c r="AP2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AR2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AS2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT2">
         <v>8</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AX2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
+        <v>17.5</v>
+      </c>
+      <c r="BA2">
+        <v>44</v>
+      </c>
+      <c r="BB2">
         <v>15</v>
       </c>
-      <c r="BA2">
-        <v>32</v>
-      </c>
-      <c r="BB2">
-        <v>13.5</v>
-      </c>
       <c r="BC2">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE2">
         <v>40</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>190</v>
@@ -1422,37 +1422,37 @@
         <v>157</v>
       </c>
       <c r="F3">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G3">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="H3">
+        <v>3.35</v>
+      </c>
+      <c r="I3">
+        <v>3.65</v>
+      </c>
+      <c r="J3">
         <v>3.05</v>
       </c>
-      <c r="I3">
-        <v>3.55</v>
-      </c>
-      <c r="J3">
-        <v>2.94</v>
-      </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M3">
         <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
         <v>1.51</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q3">
         <v>2.58</v>
@@ -1461,181 +1461,181 @@
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
         <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1664,19 +1664,19 @@
         <v>158</v>
       </c>
       <c r="F4">
+        <v>2.92</v>
+      </c>
+      <c r="G4">
+        <v>3.05</v>
+      </c>
+      <c r="H4">
+        <v>2.74</v>
+      </c>
+      <c r="I4">
         <v>2.94</v>
       </c>
-      <c r="G4">
-        <v>3.2</v>
-      </c>
-      <c r="H4">
-        <v>2.66</v>
-      </c>
-      <c r="I4">
-        <v>2.9</v>
-      </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K4">
         <v>3.3</v>
@@ -1688,7 +1688,7 @@
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O4">
         <v>1.55</v>
@@ -1697,193 +1697,193 @@
         <v>1.55</v>
       </c>
       <c r="Q4">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
         <v>5.5</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V4">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>190</v>
@@ -1909,22 +1909,22 @@
         <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H5">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I5">
+        <v>3.4</v>
+      </c>
+      <c r="J5">
         <v>3.3</v>
-      </c>
-      <c r="J5">
-        <v>3.25</v>
       </c>
       <c r="K5">
         <v>3.5</v>
       </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M5">
         <v>1.09</v>
@@ -1936,7 +1936,7 @@
         <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
         <v>2.2</v>
@@ -1948,184 +1948,184 @@
         <v>4.1</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="s">
         <v>190</v>
@@ -2148,166 +2148,166 @@
         <v>160</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="G6">
-        <v>110</v>
+        <v>2.18</v>
       </c>
       <c r="H6">
+        <v>4.2</v>
+      </c>
+      <c r="I6">
+        <v>5.2</v>
+      </c>
+      <c r="J6">
+        <v>3.1</v>
+      </c>
+      <c r="K6">
+        <v>3.6</v>
+      </c>
+      <c r="L6">
+        <v>1.42</v>
+      </c>
+      <c r="M6">
+        <v>1.1</v>
+      </c>
+      <c r="N6">
+        <v>2.84</v>
+      </c>
+      <c r="O6">
+        <v>1.4</v>
+      </c>
+      <c r="P6">
+        <v>1.58</v>
+      </c>
+      <c r="Q6">
+        <v>2.32</v>
+      </c>
+      <c r="R6">
+        <v>1.2</v>
+      </c>
+      <c r="S6">
+        <v>4.4</v>
+      </c>
+      <c r="T6">
+        <v>1.89</v>
+      </c>
+      <c r="U6">
+        <v>1.8</v>
+      </c>
+      <c r="V6">
         <v>1.24</v>
       </c>
-      <c r="I6">
-        <v>170</v>
-      </c>
-      <c r="J6">
-        <v>1.24</v>
-      </c>
-      <c r="K6">
-        <v>950</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
-      <c r="N6">
-        <v>1.17</v>
-      </c>
-      <c r="O6">
-        <v>1.41</v>
-      </c>
-      <c r="P6">
-        <v>1.17</v>
-      </c>
-      <c r="Q6">
-        <v>1.41</v>
-      </c>
-      <c r="R6">
-        <v>1.18</v>
-      </c>
-      <c r="S6">
-        <v>1.02</v>
-      </c>
-      <c r="T6">
-        <v>1.01</v>
-      </c>
-      <c r="U6">
-        <v>1.75</v>
-      </c>
-      <c r="V6">
-        <v>1.01</v>
-      </c>
       <c r="W6">
-        <v>1.23</v>
+        <v>1.84</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2316,7 +2316,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
@@ -2328,28 +2328,28 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2364,7 +2364,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2390,169 +2390,169 @@
         <v>161</v>
       </c>
       <c r="F7">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="G7">
-        <v>190</v>
+        <v>2.44</v>
       </c>
       <c r="H7">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="I7">
-        <v>190</v>
+        <v>3.6</v>
       </c>
       <c r="J7">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="O7">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="P7">
-        <v>1.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
+        <v>1.72</v>
+      </c>
+      <c r="R7">
+        <v>1.43</v>
+      </c>
+      <c r="S7">
+        <v>2.84</v>
+      </c>
+      <c r="T7">
+        <v>1.62</v>
+      </c>
+      <c r="U7">
+        <v>2.28</v>
+      </c>
+      <c r="V7">
+        <v>1.39</v>
+      </c>
+      <c r="W7">
+        <v>1.69</v>
+      </c>
+      <c r="X7">
+        <v>22</v>
+      </c>
+      <c r="Y7">
+        <v>16</v>
+      </c>
+      <c r="Z7">
+        <v>26</v>
+      </c>
+      <c r="AA7">
+        <v>60</v>
+      </c>
+      <c r="AB7">
+        <v>12.5</v>
+      </c>
+      <c r="AC7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD7">
+        <v>14.5</v>
+      </c>
+      <c r="AE7">
+        <v>36</v>
+      </c>
+      <c r="AF7">
+        <v>17</v>
+      </c>
+      <c r="AG7">
+        <v>12</v>
+      </c>
+      <c r="AH7">
+        <v>17</v>
+      </c>
+      <c r="AI7">
+        <v>44</v>
+      </c>
+      <c r="AJ7">
+        <v>32</v>
+      </c>
+      <c r="AK7">
+        <v>24</v>
+      </c>
+      <c r="AL7">
+        <v>36</v>
+      </c>
+      <c r="AM7">
+        <v>80</v>
+      </c>
+      <c r="AN7">
+        <v>16</v>
+      </c>
+      <c r="AO7">
+        <v>30</v>
+      </c>
+      <c r="AP7">
+        <v>13</v>
+      </c>
+      <c r="AQ7">
+        <v>11</v>
+      </c>
+      <c r="AR7">
+        <v>18</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU7">
+        <v>6.6</v>
+      </c>
+      <c r="AV7">
+        <v>10</v>
+      </c>
+      <c r="AW7">
         <v>1.03</v>
       </c>
-      <c r="R7">
-        <v>1.09</v>
-      </c>
-      <c r="S7">
-        <v>1.01</v>
-      </c>
-      <c r="T7">
-        <v>1.01</v>
-      </c>
-      <c r="U7">
-        <v>1.01</v>
-      </c>
-      <c r="V7">
-        <v>1.01</v>
-      </c>
-      <c r="W7">
-        <v>1.01</v>
-      </c>
-      <c r="X7">
-        <v>1000</v>
-      </c>
-      <c r="Y7">
-        <v>1000</v>
-      </c>
-      <c r="Z7">
-        <v>1000</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>1000</v>
-      </c>
-      <c r="AC7">
-        <v>1000</v>
-      </c>
-      <c r="AD7">
-        <v>1000</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>1000</v>
-      </c>
-      <c r="AG7">
-        <v>1000</v>
-      </c>
-      <c r="AH7">
-        <v>1000</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>1000</v>
-      </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>1.01</v>
-      </c>
-      <c r="AQ7">
-        <v>1.01</v>
-      </c>
-      <c r="AR7">
-        <v>1.01</v>
-      </c>
-      <c r="AS7">
-        <v>1.01</v>
-      </c>
-      <c r="AT7">
-        <v>1.01</v>
-      </c>
-      <c r="AU7">
-        <v>1.01</v>
-      </c>
-      <c r="AV7">
-        <v>1.01</v>
-      </c>
-      <c r="AW7">
-        <v>1.01</v>
-      </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA7">
         <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
         <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI7">
         <v>1.01</v>
@@ -2561,55 +2561,55 @@
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="CB7" t="s">
         <v>190</v>
@@ -2632,220 +2632,220 @@
         <v>162</v>
       </c>
       <c r="F8">
+        <v>1.97</v>
+      </c>
+      <c r="G8">
+        <v>2.18</v>
+      </c>
+      <c r="H8">
+        <v>3.65</v>
+      </c>
+      <c r="I8">
+        <v>4.3</v>
+      </c>
+      <c r="J8">
+        <v>3.65</v>
+      </c>
+      <c r="K8">
+        <v>4.1</v>
+      </c>
+      <c r="L8">
+        <v>1.31</v>
+      </c>
+      <c r="M8">
         <v>1.05</v>
       </c>
-      <c r="G8">
-        <v>95</v>
-      </c>
-      <c r="H8">
-        <v>1.09</v>
-      </c>
-      <c r="I8">
-        <v>990</v>
-      </c>
-      <c r="J8">
-        <v>1.11</v>
-      </c>
-      <c r="K8">
-        <v>950</v>
-      </c>
-      <c r="L8">
-        <v>1.01</v>
-      </c>
-      <c r="M8">
-        <v>1.01</v>
-      </c>
       <c r="N8">
+        <v>4.2</v>
+      </c>
+      <c r="O8">
         <v>1.25</v>
       </c>
-      <c r="O8">
-        <v>1.23</v>
-      </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q8">
-        <v>1.23</v>
+        <v>1.74</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S8">
-        <v>1.23</v>
+        <v>2.88</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2874,169 +2874,169 @@
         <v>163</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>3.55</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>2.98</v>
       </c>
       <c r="J9">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>1.18</v>
+        <v>2.34</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="P9">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI9">
         <v>1.01</v>
@@ -3045,55 +3045,55 @@
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="CB9" t="s">
         <v>190</v>
@@ -3116,22 +3116,22 @@
         <v>164</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G10">
-        <v>110</v>
+        <v>2.54</v>
       </c>
       <c r="H10">
-        <v>1.08</v>
+        <v>3.05</v>
       </c>
       <c r="I10">
-        <v>110</v>
+        <v>4.2</v>
       </c>
       <c r="J10">
-        <v>1.06</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3140,22 +3140,22 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="O10">
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q10">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="R10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S10">
-        <v>1.34</v>
+        <v>3.25</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3164,10 +3164,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.64</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3358,22 +3358,22 @@
         <v>165</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="G11">
         <v>1.73</v>
       </c>
       <c r="H11">
-        <v>2.42</v>
+        <v>4.3</v>
       </c>
       <c r="I11">
-        <v>130</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3382,22 +3382,22 @@
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>1.18</v>
+        <v>3.2</v>
       </c>
       <c r="O11">
         <v>1.21</v>
       </c>
       <c r="P11">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="Q11">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S11">
-        <v>1.2</v>
+        <v>2.46</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3406,7 +3406,7 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W11">
         <v>2.36</v>
@@ -3415,7 +3415,7 @@
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z11">
         <v>1000</v>
@@ -3424,154 +3424,154 @@
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE11">
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI11">
         <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM11">
         <v>1000</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3600,166 +3600,166 @@
         <v>166</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="G12">
-        <v>90</v>
+        <v>2.08</v>
       </c>
       <c r="H12">
+        <v>4.2</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>3.5</v>
+      </c>
+      <c r="K12">
+        <v>3.8</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
         <v>1.09</v>
       </c>
-      <c r="I12">
+      <c r="N12">
+        <v>3.05</v>
+      </c>
+      <c r="O12">
+        <v>1.4</v>
+      </c>
+      <c r="P12">
+        <v>1.75</v>
+      </c>
+      <c r="Q12">
+        <v>2.18</v>
+      </c>
+      <c r="R12">
+        <v>1.27</v>
+      </c>
+      <c r="S12">
+        <v>4.1</v>
+      </c>
+      <c r="T12">
+        <v>1.85</v>
+      </c>
+      <c r="U12">
+        <v>1.84</v>
+      </c>
+      <c r="V12">
+        <v>1.25</v>
+      </c>
+      <c r="W12">
+        <v>1.93</v>
+      </c>
+      <c r="X12">
+        <v>13</v>
+      </c>
+      <c r="Y12">
+        <v>14.5</v>
+      </c>
+      <c r="Z12">
+        <v>40</v>
+      </c>
+      <c r="AA12">
+        <v>140</v>
+      </c>
+      <c r="AB12">
+        <v>7.8</v>
+      </c>
+      <c r="AC12">
+        <v>8.4</v>
+      </c>
+      <c r="AD12">
+        <v>22</v>
+      </c>
+      <c r="AE12">
+        <v>85</v>
+      </c>
+      <c r="AF12">
+        <v>12</v>
+      </c>
+      <c r="AG12">
+        <v>12.5</v>
+      </c>
+      <c r="AH12">
+        <v>23</v>
+      </c>
+      <c r="AI12">
+        <v>95</v>
+      </c>
+      <c r="AJ12">
+        <v>29</v>
+      </c>
+      <c r="AK12">
+        <v>29</v>
+      </c>
+      <c r="AL12">
+        <v>55</v>
+      </c>
+      <c r="AM12">
+        <v>170</v>
+      </c>
+      <c r="AN12">
+        <v>22</v>
+      </c>
+      <c r="AO12">
         <v>110</v>
       </c>
-      <c r="J12">
-        <v>1.06</v>
-      </c>
-      <c r="K12">
-        <v>950</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.08</v>
-      </c>
-      <c r="N12">
-        <v>1.57</v>
-      </c>
-      <c r="O12">
-        <v>1.38</v>
-      </c>
-      <c r="P12">
-        <v>1.57</v>
-      </c>
-      <c r="Q12">
-        <v>1.38</v>
-      </c>
-      <c r="R12">
-        <v>1.18</v>
-      </c>
-      <c r="S12">
-        <v>1.38</v>
-      </c>
-      <c r="T12">
-        <v>1.01</v>
-      </c>
-      <c r="U12">
-        <v>1.01</v>
-      </c>
-      <c r="V12">
-        <v>1.01</v>
-      </c>
-      <c r="W12">
-        <v>1.08</v>
-      </c>
-      <c r="X12">
-        <v>1000</v>
-      </c>
-      <c r="Y12">
-        <v>1000</v>
-      </c>
-      <c r="Z12">
-        <v>1000</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>1000</v>
-      </c>
-      <c r="AC12">
-        <v>1000</v>
-      </c>
-      <c r="AD12">
-        <v>1000</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>1000</v>
-      </c>
-      <c r="AG12">
-        <v>1000</v>
-      </c>
-      <c r="AH12">
-        <v>1000</v>
-      </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3842,226 +3842,226 @@
         <v>167</v>
       </c>
       <c r="F13">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G13">
-        <v>110</v>
+        <v>2.5</v>
       </c>
       <c r="H13">
-        <v>1.08</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>110</v>
+        <v>3.5</v>
       </c>
       <c r="J13">
-        <v>1.27</v>
+        <v>3.5</v>
       </c>
       <c r="K13">
         <v>3.8</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M13">
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
         <v>1.26</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q13">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="R13">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="S13">
-        <v>1.26</v>
+        <v>2.98</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB13" t="s">
         <v>190</v>
@@ -4090,16 +4090,16 @@
         <v>4.4</v>
       </c>
       <c r="H14">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I14">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="J14">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4108,7 +4108,7 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O14">
         <v>1.18</v>
@@ -4120,130 +4120,130 @@
         <v>1.53</v>
       </c>
       <c r="R14">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="S14">
         <v>2.38</v>
       </c>
       <c r="T14">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="V14">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="W14">
         <v>1.29</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y14">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z14">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC14">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD14">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO14">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AP14">
-        <v>1.34</v>
+        <v>20</v>
       </c>
       <c r="AQ14">
-        <v>1.28</v>
+        <v>11.5</v>
       </c>
       <c r="AR14">
-        <v>1.29</v>
+        <v>12.5</v>
       </c>
       <c r="AS14">
-        <v>1.34</v>
+        <v>18.5</v>
       </c>
       <c r="AT14">
-        <v>1.34</v>
+        <v>19</v>
       </c>
       <c r="AU14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV14">
+        <v>9.4</v>
+      </c>
+      <c r="AW14">
+        <v>15</v>
+      </c>
+      <c r="AX14">
+        <v>25</v>
+      </c>
+      <c r="AY14">
+        <v>15</v>
+      </c>
+      <c r="AZ14">
+        <v>14</v>
+      </c>
+      <c r="BA14">
+        <v>7.6</v>
+      </c>
+      <c r="BB14">
+        <v>9.4</v>
+      </c>
+      <c r="BC14">
+        <v>29</v>
+      </c>
+      <c r="BD14">
+        <v>29</v>
+      </c>
+      <c r="BE14">
+        <v>9</v>
+      </c>
+      <c r="BF14">
+        <v>8</v>
+      </c>
+      <c r="BG14">
         <v>7.4</v>
-      </c>
-      <c r="AW14">
-        <v>1.33</v>
-      </c>
-      <c r="AX14">
-        <v>1.34</v>
-      </c>
-      <c r="AY14">
-        <v>1.33</v>
-      </c>
-      <c r="AZ14">
-        <v>1.33</v>
-      </c>
-      <c r="BA14">
-        <v>1.34</v>
-      </c>
-      <c r="BB14">
-        <v>1.34</v>
-      </c>
-      <c r="BC14">
-        <v>1.34</v>
-      </c>
-      <c r="BD14">
-        <v>1.34</v>
-      </c>
-      <c r="BE14">
-        <v>1.34</v>
-      </c>
-      <c r="BF14">
-        <v>1.34</v>
-      </c>
-      <c r="BG14">
-        <v>6.2</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4326,145 +4326,145 @@
         <v>169</v>
       </c>
       <c r="F15">
+        <v>2.44</v>
+      </c>
+      <c r="G15">
+        <v>2.74</v>
+      </c>
+      <c r="H15">
+        <v>2.92</v>
+      </c>
+      <c r="I15">
+        <v>3.4</v>
+      </c>
+      <c r="J15">
+        <v>3.2</v>
+      </c>
+      <c r="K15">
+        <v>3.65</v>
+      </c>
+      <c r="L15">
         <v>1.43</v>
       </c>
-      <c r="G15">
-        <v>110</v>
-      </c>
-      <c r="H15">
-        <v>1.58</v>
-      </c>
-      <c r="I15">
-        <v>110</v>
-      </c>
-      <c r="J15">
-        <v>1.04</v>
-      </c>
-      <c r="K15">
-        <v>950</v>
-      </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
       <c r="M15">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
-        <v>1.25</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P15">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q15">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="R15">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="S15">
-        <v>1.34</v>
+        <v>3.55</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V15">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
         <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW15">
         <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA15">
         <v>1.01</v>
@@ -4473,7 +4473,7 @@
         <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
         <v>1.01</v>
@@ -4482,64 +4482,64 @@
         <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG15">
         <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4568,22 +4568,22 @@
         <v>170</v>
       </c>
       <c r="F16">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="G16">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="H16">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I16">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J16">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="K16">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L16">
         <v>1.19</v>
@@ -4592,142 +4592,142 @@
         <v>1.02</v>
       </c>
       <c r="N16">
+        <v>8</v>
+      </c>
+      <c r="O16">
+        <v>1.12</v>
+      </c>
+      <c r="P16">
         <v>3.25</v>
       </c>
-      <c r="O16">
-        <v>1.11</v>
-      </c>
-      <c r="P16">
-        <v>3.2</v>
-      </c>
       <c r="Q16">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R16">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="S16">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="T16">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="U16">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W16">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN16">
-        <v>970</v>
+        <v>3.7</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP16">
-        <v>1.32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ16">
-        <v>1.32</v>
+        <v>9.4</v>
       </c>
       <c r="AR16">
-        <v>1.32</v>
+        <v>10</v>
       </c>
       <c r="AS16">
-        <v>1.32</v>
+        <v>10.5</v>
       </c>
       <c r="AT16">
-        <v>1.32</v>
+        <v>13</v>
       </c>
       <c r="AU16">
-        <v>1.32</v>
+        <v>12</v>
       </c>
       <c r="AV16">
-        <v>1.32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16">
-        <v>1.32</v>
+        <v>10</v>
       </c>
       <c r="AX16">
-        <v>1.32</v>
+        <v>10</v>
       </c>
       <c r="AY16">
-        <v>1.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16">
-        <v>1.32</v>
+        <v>7.6</v>
       </c>
       <c r="BA16">
-        <v>1.32</v>
+        <v>10</v>
       </c>
       <c r="BB16">
-        <v>1.32</v>
+        <v>11</v>
       </c>
       <c r="BC16">
-        <v>1.32</v>
+        <v>11.5</v>
       </c>
       <c r="BD16">
-        <v>1.32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE16">
-        <v>1.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG16">
-        <v>1.32</v>
+        <v>10</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4736,7 +4736,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK16">
         <v>1.01</v>
@@ -4748,25 +4748,25 @@
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS16">
         <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BU16">
         <v>1.01</v>
@@ -4784,10 +4784,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="CB16" t="s">
         <v>190</v>
@@ -4810,223 +4810,223 @@
         <v>171</v>
       </c>
       <c r="F17">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>110</v>
+        <v>3.3</v>
       </c>
       <c r="H17">
         <v>2.08</v>
       </c>
       <c r="I17">
-        <v>85</v>
+        <v>2.24</v>
       </c>
       <c r="J17">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M17">
         <v>1.02</v>
       </c>
       <c r="N17">
-        <v>1.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O17">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P17">
-        <v>1.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q17">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="R17">
-        <v>1.24</v>
+        <v>1.99</v>
       </c>
       <c r="S17">
-        <v>1.09</v>
+        <v>1.89</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="V17">
-        <v>1.29</v>
+        <v>1.81</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM17">
         <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ17">
         <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS17">
         <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW17">
         <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY17">
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA17">
         <v>1.01</v>
@@ -5052,22 +5052,22 @@
         <v>172</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G18">
-        <v>110</v>
+        <v>2.5</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>110</v>
+        <v>3.5</v>
       </c>
       <c r="J18">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="K18">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5076,196 +5076,196 @@
         <v>1.06</v>
       </c>
       <c r="N18">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="O18">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q18">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="R18">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V18">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS18">
         <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA18">
         <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18">
         <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH18">
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -5297,10 +5297,10 @@
         <v>2.82</v>
       </c>
       <c r="G19">
-        <v>110</v>
+        <v>2.92</v>
       </c>
       <c r="H19">
-        <v>1.37</v>
+        <v>2.42</v>
       </c>
       <c r="I19">
         <v>2.52</v>
@@ -5318,127 +5318,127 @@
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="O19">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P19">
-        <v>1.3</v>
+        <v>2.66</v>
       </c>
       <c r="Q19">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R19">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="S19">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="V19">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="X19">
         <v>27</v>
       </c>
       <c r="Y19">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z19">
         <v>21</v>
       </c>
       <c r="AA19">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AB19">
-        <v>55</v>
+        <v>18.5</v>
       </c>
       <c r="AC19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AD19">
         <v>12.5</v>
       </c>
       <c r="AE19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF19">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="AG19">
+        <v>13.5</v>
+      </c>
+      <c r="AH19">
+        <v>14.5</v>
+      </c>
+      <c r="AI19">
+        <v>28</v>
+      </c>
+      <c r="AJ19">
+        <v>42</v>
+      </c>
+      <c r="AK19">
+        <v>26</v>
+      </c>
+      <c r="AL19">
+        <v>30</v>
+      </c>
+      <c r="AM19">
         <v>50</v>
       </c>
-      <c r="AH19">
-        <v>34</v>
-      </c>
-      <c r="AI19">
-        <v>36</v>
-      </c>
-      <c r="AJ19">
-        <v>580</v>
-      </c>
-      <c r="AK19">
-        <v>210</v>
-      </c>
-      <c r="AL19">
-        <v>160</v>
-      </c>
-      <c r="AM19">
-        <v>170</v>
-      </c>
       <c r="AN19">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="AO19">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AP19">
         <v>20</v>
       </c>
       <c r="AQ19">
-        <v>8.6</v>
+        <v>15.5</v>
       </c>
       <c r="AR19">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AS19">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="AT19">
         <v>16.5</v>
       </c>
       <c r="AU19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AV19">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW19">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AX19">
         <v>21</v>
       </c>
       <c r="AY19">
-        <v>2.16</v>
+        <v>12</v>
       </c>
       <c r="AZ19">
         <v>13</v>
       </c>
       <c r="BA19">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BB19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC19">
         <v>23</v>
@@ -5447,13 +5447,13 @@
         <v>26</v>
       </c>
       <c r="BE19">
-        <v>2.24</v>
+        <v>42</v>
       </c>
       <c r="BF19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG19">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5536,22 +5536,22 @@
         <v>174</v>
       </c>
       <c r="F20">
-        <v>1.23</v>
+        <v>2.04</v>
       </c>
       <c r="G20">
-        <v>110</v>
+        <v>2.3</v>
       </c>
       <c r="H20">
-        <v>1.27</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="J20">
-        <v>1.14</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5560,202 +5560,202 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>1.31</v>
+        <v>6.2</v>
       </c>
       <c r="O20">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P20">
-        <v>1.31</v>
+        <v>2.76</v>
       </c>
       <c r="Q20">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="R20">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="S20">
-        <v>1.12</v>
+        <v>2.12</v>
       </c>
       <c r="T20">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="V20">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.78</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="CB20" t="s">
         <v>190</v>
@@ -5778,22 +5778,22 @@
         <v>175</v>
       </c>
       <c r="F21">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="G21">
-        <v>110</v>
+        <v>4.3</v>
       </c>
       <c r="H21">
-        <v>1.16</v>
+        <v>1.95</v>
       </c>
       <c r="I21">
-        <v>110</v>
+        <v>2.12</v>
       </c>
       <c r="J21">
-        <v>1.09</v>
+        <v>3.9</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>4.7</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5802,34 +5802,34 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="O21">
         <v>1.16</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q21">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="R21">
         <v>1.25</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>2.26</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U21">
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.08</v>
+        <v>1.89</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6020,22 +6020,22 @@
         <v>176</v>
       </c>
       <c r="F22">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G22">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H22">
-        <v>1.08</v>
+        <v>6.4</v>
       </c>
       <c r="I22">
-        <v>110</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
-        <v>2.52</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L22">
         <v>1.37</v>
@@ -6047,10 +6047,10 @@
         <v>3.9</v>
       </c>
       <c r="O22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P22">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q22">
         <v>1.87</v>
@@ -6059,127 +6059,127 @@
         <v>1.39</v>
       </c>
       <c r="S22">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V22">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W22">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6262,166 +6262,166 @@
         <v>177</v>
       </c>
       <c r="F23">
-        <v>1.52</v>
+        <v>3.85</v>
       </c>
       <c r="G23">
-        <v>110</v>
+        <v>4.4</v>
       </c>
       <c r="H23">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="I23">
-        <v>970</v>
+        <v>2.18</v>
       </c>
       <c r="J23">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K23">
         <v>3.75</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M23">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N23">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="O23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P23">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R23">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S23">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="T23">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U23">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V23">
-        <v>1.08</v>
+        <v>1.85</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6504,154 +6504,154 @@
         <v>178</v>
       </c>
       <c r="F24">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="G24">
-        <v>110</v>
+        <v>2.18</v>
       </c>
       <c r="H24">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I24">
-        <v>170</v>
+        <v>4.4</v>
       </c>
       <c r="J24">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M24">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N24">
-        <v>1.24</v>
+        <v>3.5</v>
       </c>
       <c r="O24">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="P24">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q24">
-        <v>1.06</v>
+        <v>1.94</v>
       </c>
       <c r="R24">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S24">
-        <v>1.06</v>
+        <v>3.4</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
         <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW24">
         <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA24">
         <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD24">
         <v>1.01</v>
@@ -6660,19 +6660,19 @@
         <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG24">
         <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK24">
         <v>1.01</v>
@@ -6684,13 +6684,13 @@
         <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ24">
         <v>1.01</v>
@@ -6702,10 +6702,10 @@
         <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV24">
         <v>1000</v>
@@ -6746,175 +6746,175 @@
         <v>179</v>
       </c>
       <c r="F25">
-        <v>1.21</v>
+        <v>3.6</v>
       </c>
       <c r="G25">
-        <v>190</v>
+        <v>4.1</v>
       </c>
       <c r="H25">
-        <v>1.21</v>
+        <v>2.18</v>
       </c>
       <c r="I25">
-        <v>190</v>
+        <v>2.38</v>
       </c>
       <c r="J25">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>3.7</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N25">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="O25">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="P25">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="R25">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S25">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V25">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK25">
         <v>1.01</v>
@@ -6926,43 +6926,43 @@
         <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO25">
         <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ25">
         <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BS25">
         <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU25">
         <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW25">
         <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY25">
         <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA25">
         <v>1.01</v>
@@ -6988,226 +6988,226 @@
         <v>180</v>
       </c>
       <c r="F26">
-        <v>1.12</v>
+        <v>2.66</v>
       </c>
       <c r="G26">
-        <v>110</v>
+        <v>3.35</v>
       </c>
       <c r="H26">
-        <v>1.11</v>
+        <v>2.56</v>
       </c>
       <c r="I26">
-        <v>110</v>
+        <v>2.98</v>
       </c>
       <c r="J26">
-        <v>1.12</v>
+        <v>2.66</v>
       </c>
       <c r="K26">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M26">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N26">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="O26">
         <v>1.4</v>
       </c>
       <c r="P26">
+        <v>1.63</v>
+      </c>
+      <c r="Q26">
+        <v>2.16</v>
+      </c>
+      <c r="R26">
+        <v>1.19</v>
+      </c>
+      <c r="S26">
+        <v>3.9</v>
+      </c>
+      <c r="T26">
+        <v>1.68</v>
+      </c>
+      <c r="U26">
+        <v>1.76</v>
+      </c>
+      <c r="V26">
+        <v>1.51</v>
+      </c>
+      <c r="W26">
+        <v>1.43</v>
+      </c>
+      <c r="X26">
+        <v>14</v>
+      </c>
+      <c r="Y26">
+        <v>1000</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>1000</v>
+      </c>
+      <c r="AC26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD26">
+        <v>16</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>1000</v>
+      </c>
+      <c r="AG26">
+        <v>16.5</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>1.3</v>
+      </c>
+      <c r="AQ26">
+        <v>1.43</v>
+      </c>
+      <c r="AR26">
+        <v>1.43</v>
+      </c>
+      <c r="AS26">
+        <v>1.43</v>
+      </c>
+      <c r="AT26">
+        <v>1.43</v>
+      </c>
+      <c r="AU26">
         <v>1.24</v>
       </c>
-      <c r="Q26">
-        <v>1.39</v>
-      </c>
-      <c r="R26">
-        <v>1.18</v>
-      </c>
-      <c r="S26">
-        <v>1.4</v>
-      </c>
-      <c r="T26">
-        <v>1.01</v>
-      </c>
-      <c r="U26">
-        <v>1.01</v>
-      </c>
-      <c r="V26">
-        <v>1.06</v>
-      </c>
-      <c r="W26">
-        <v>1.05</v>
-      </c>
-      <c r="X26">
-        <v>1000</v>
-      </c>
-      <c r="Y26">
-        <v>1000</v>
-      </c>
-      <c r="Z26">
-        <v>1000</v>
-      </c>
-      <c r="AA26">
-        <v>1000</v>
-      </c>
-      <c r="AB26">
-        <v>1000</v>
-      </c>
-      <c r="AC26">
-        <v>1000</v>
-      </c>
-      <c r="AD26">
-        <v>1000</v>
-      </c>
-      <c r="AE26">
-        <v>1000</v>
-      </c>
-      <c r="AF26">
-        <v>1000</v>
-      </c>
-      <c r="AG26">
-        <v>1000</v>
-      </c>
-      <c r="AH26">
-        <v>1000</v>
-      </c>
-      <c r="AI26">
-        <v>1000</v>
-      </c>
-      <c r="AJ26">
-        <v>1000</v>
-      </c>
-      <c r="AK26">
-        <v>1000</v>
-      </c>
-      <c r="AL26">
-        <v>1000</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>1000</v>
-      </c>
-      <c r="AO26">
-        <v>1000</v>
-      </c>
-      <c r="AP26">
-        <v>1.01</v>
-      </c>
-      <c r="AQ26">
-        <v>1.01</v>
-      </c>
-      <c r="AR26">
-        <v>1.01</v>
-      </c>
-      <c r="AS26">
-        <v>1.01</v>
-      </c>
-      <c r="AT26">
-        <v>1.01</v>
-      </c>
-      <c r="AU26">
-        <v>1.01</v>
-      </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="AY26">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BH26">
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="CB26" t="s">
         <v>190</v>
@@ -7472,226 +7472,226 @@
         <v>182</v>
       </c>
       <c r="F28">
-        <v>1.08</v>
+        <v>1.87</v>
       </c>
       <c r="G28">
-        <v>110</v>
+        <v>1.99</v>
       </c>
       <c r="H28">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I28">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J28">
-        <v>1.28</v>
+        <v>3.45</v>
       </c>
       <c r="K28">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N28">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P28">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q28">
         <v>2.24</v>
       </c>
       <c r="R28">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S28">
-        <v>2.24</v>
+        <v>4.1</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V28">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W28">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="CB28" t="s">
         <v>190</v>
@@ -7714,226 +7714,226 @@
         <v>183</v>
       </c>
       <c r="F29">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G29">
-        <v>110</v>
+        <v>2.18</v>
       </c>
       <c r="H29">
-        <v>1.77</v>
+        <v>4.2</v>
       </c>
       <c r="I29">
-        <v>150</v>
+        <v>5.2</v>
       </c>
       <c r="J29">
-        <v>1.24</v>
+        <v>3.15</v>
       </c>
       <c r="K29">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M29">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N29">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="O29">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P29">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q29">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="R29">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="S29">
-        <v>2.36</v>
+        <v>4.6</v>
       </c>
       <c r="T29">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U29">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V29">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W29">
-        <v>1.23</v>
+        <v>1.84</v>
       </c>
       <c r="X29">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y29">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA29">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB29">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC29">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF29">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG29">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH29">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN29">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP29">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ29">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR29">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS29">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT29">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU29">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV29">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW29">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX29">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY29">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ29">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA29">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB29">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC29">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD29">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE29">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF29">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI29">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK29">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO29">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU29">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB29" t="s">
         <v>190</v>
@@ -7956,226 +7956,226 @@
         <v>184</v>
       </c>
       <c r="F30">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="G30">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>1.05</v>
+        <v>1.96</v>
       </c>
       <c r="I30">
-        <v>110</v>
+        <v>2.1</v>
       </c>
       <c r="J30">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="K30">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M30">
         <v>1.07</v>
       </c>
       <c r="N30">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="O30">
         <v>1.34</v>
       </c>
       <c r="P30">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q30">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>3.25</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V30">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="W30">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH30">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI30">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU30">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB30" t="s">
         <v>190</v>
@@ -8440,19 +8440,19 @@
         <v>186</v>
       </c>
       <c r="F32">
-        <v>1.52</v>
+        <v>3.3</v>
       </c>
       <c r="G32">
-        <v>110</v>
+        <v>3.8</v>
       </c>
       <c r="H32">
-        <v>1.52</v>
+        <v>2.52</v>
       </c>
       <c r="I32">
-        <v>110</v>
+        <v>2.76</v>
       </c>
       <c r="J32">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="K32">
         <v>3</v>
@@ -8461,145 +8461,145 @@
         <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N32">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="O32">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="P32">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q32">
-        <v>2.26</v>
+        <v>2.82</v>
       </c>
       <c r="R32">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S32">
-        <v>2.26</v>
+        <v>6</v>
       </c>
       <c r="T32">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U32">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V32">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z32">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA32">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB32">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC32">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD32">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE32">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF32">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG32">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH32">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI32">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ32">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK32">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL32">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM32">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN32">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO32">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP32">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ32">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS32">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT32">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU32">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV32">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW32">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX32">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY32">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AZ32">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA32">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB32">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC32">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD32">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE32">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG32">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8682,28 +8682,28 @@
         <v>187</v>
       </c>
       <c r="F33">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="G33">
-        <v>190</v>
+        <v>3.1</v>
       </c>
       <c r="H33">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="I33">
-        <v>190</v>
+        <v>3.25</v>
       </c>
       <c r="J33">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="K33">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L33">
         <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N33">
         <v>1.01</v>
@@ -8712,10 +8712,10 @@
         <v>1.01</v>
       </c>
       <c r="P33">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q33">
-        <v>1.1</v>
+        <v>2.48</v>
       </c>
       <c r="R33">
         <v>1.14</v>
@@ -8724,10 +8724,10 @@
         <v>1.02</v>
       </c>
       <c r="T33">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U33">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V33">
         <v>1.01</v>
@@ -8736,112 +8736,112 @@
         <v>1.01</v>
       </c>
       <c r="X33">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y33">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z33">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB33">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC33">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD33">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE33">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF33">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG33">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH33">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI33">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ33">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK33">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL33">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM33">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN33">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO33">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP33">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ33">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR33">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS33">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT33">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU33">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV33">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW33">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX33">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY33">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ33">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA33">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB33">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC33">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD33">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE33">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF33">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG33">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8924,166 +8924,166 @@
         <v>188</v>
       </c>
       <c r="F34">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="G34">
-        <v>110</v>
+        <v>1.83</v>
       </c>
       <c r="H34">
+        <v>5.7</v>
+      </c>
+      <c r="I34">
+        <v>6.6</v>
+      </c>
+      <c r="J34">
+        <v>3.55</v>
+      </c>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="L34">
+        <v>1.01</v>
+      </c>
+      <c r="M34">
         <v>1.09</v>
       </c>
-      <c r="I34">
-        <v>110</v>
-      </c>
-      <c r="J34">
-        <v>1.1</v>
-      </c>
-      <c r="K34">
-        <v>950</v>
-      </c>
-      <c r="L34">
-        <v>1.01</v>
-      </c>
-      <c r="M34">
-        <v>1.01</v>
-      </c>
       <c r="N34">
+        <v>2.98</v>
+      </c>
+      <c r="O34">
+        <v>1.42</v>
+      </c>
+      <c r="P34">
+        <v>1.65</v>
+      </c>
+      <c r="Q34">
+        <v>2.24</v>
+      </c>
+      <c r="R34">
         <v>1.25</v>
       </c>
-      <c r="O34">
-        <v>1.02</v>
-      </c>
-      <c r="P34">
-        <v>1.25</v>
-      </c>
-      <c r="Q34">
-        <v>1.4</v>
-      </c>
-      <c r="R34">
-        <v>1.17</v>
-      </c>
       <c r="S34">
-        <v>1.39</v>
+        <v>4.1</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V34">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP34">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ34">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR34">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS34">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT34">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU34">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV34">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW34">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX34">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY34">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ34">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA34">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC34">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD34">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE34">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG34">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9166,166 +9166,166 @@
         <v>189</v>
       </c>
       <c r="F35">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="G35">
-        <v>190</v>
+        <v>2.98</v>
       </c>
       <c r="H35">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="I35">
-        <v>190</v>
+        <v>3.2</v>
       </c>
       <c r="J35">
-        <v>1.02</v>
+        <v>2.92</v>
       </c>
       <c r="K35">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L35">
         <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N35">
-        <v>1.26</v>
+        <v>3.25</v>
       </c>
       <c r="O35">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P35">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="Q35">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="R35">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>3.8</v>
       </c>
       <c r="T35">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U35">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V35">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X35">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y35">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z35">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA35">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB35">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC35">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD35">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE35">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF35">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG35">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH35">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI35">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ35">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK35">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL35">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM35">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN35">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO35">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP35">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ35">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR35">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS35">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT35">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU35">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV35">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW35">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AX35">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY35">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ35">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA35">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB35">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BC35">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BD35">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE35">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF35">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG35">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH35">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -694,7 +694,7 @@
     <t>Real Soacha Cundinamarca FC</t>
   </si>
   <si>
-    <t>2026-08-09 12:44:25</t>
+    <t>2026-08-09 14:56:31</t>
   </si>
 </sst>
 </file>
@@ -1288,22 +1288,22 @@
         <v>180</v>
       </c>
       <c r="F2">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="G2">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="H2">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
         <v>1.41</v>
@@ -1321,37 +1321,37 @@
         <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
         <v>1.85</v>
       </c>
       <c r="U2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W2">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y2">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Z2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB2">
         <v>8.800000000000001</v>
@@ -1363,10 +1363,10 @@
         <v>21</v>
       </c>
       <c r="AE2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG2">
         <v>10</v>
@@ -1378,10 +1378,10 @@
         <v>75</v>
       </c>
       <c r="AJ2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL2">
         <v>36</v>
@@ -1390,7 +1390,7 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO2">
         <v>90</v>
@@ -1399,100 +1399,100 @@
         <v>14</v>
       </c>
       <c r="AQ2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT2">
+        <v>8</v>
+      </c>
+      <c r="AU2">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU2">
-        <v>8</v>
-      </c>
       <c r="AV2">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AW2">
         <v>46</v>
       </c>
       <c r="AX2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY2">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB2">
+        <v>15.5</v>
+      </c>
+      <c r="BC2">
         <v>16</v>
       </c>
-      <c r="BC2">
-        <v>16.5</v>
-      </c>
       <c r="BD2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE2">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="BF2">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BH2">
         <v>3.7</v>
       </c>
       <c r="BI2">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM2">
         <v>9.6</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BP2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BW2">
         <v>8.4</v>
@@ -1504,10 +1504,10 @@
         <v>8.6</v>
       </c>
       <c r="BZ2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="s">
         <v>226</v>
@@ -1539,7 +1539,7 @@
         <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J3">
         <v>3.25</v>
@@ -1548,22 +1548,22 @@
         <v>3.5</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R3">
         <v>1.27</v>
@@ -1578,22 +1578,22 @@
         <v>1.98</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
         <v>1.68</v>
       </c>
       <c r="X3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y3">
         <v>12</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB3">
         <v>9.4</v>
@@ -1608,7 +1608,7 @@
         <v>60</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG3">
         <v>14</v>
@@ -1617,7 +1617,7 @@
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
         <v>40</v>
@@ -1629,7 +1629,7 @@
         <v>55</v>
       </c>
       <c r="AM3">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN3">
         <v>30</v>
@@ -1638,16 +1638,16 @@
         <v>65</v>
       </c>
       <c r="AP3">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AS3">
-        <v>5.5</v>
+        <v>46</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
@@ -1659,10 +1659,10 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>5.2</v>
+        <v>32</v>
       </c>
       <c r="AX3">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
         <v>9.199999999999999</v>
@@ -1671,25 +1671,25 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>5.4</v>
+        <v>44</v>
       </c>
       <c r="BB3">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD3">
-        <v>5.3</v>
+        <v>36</v>
       </c>
       <c r="BE3">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF3">
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="BH3">
         <v>3.3</v>
@@ -1701,16 +1701,16 @@
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BN3">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BO3">
         <v>4</v>
@@ -1719,31 +1719,31 @@
         <v>22</v>
       </c>
       <c r="BQ3">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS3">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BT3">
         <v>7.6</v>
       </c>
       <c r="BU3">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV3">
         <v>36</v>
       </c>
       <c r="BW3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BX3">
         <v>55</v>
       </c>
       <c r="BY3">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>182</v>
       </c>
       <c r="F4">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G4">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H4">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="I4">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="J4">
         <v>3.1</v>
@@ -1793,19 +1793,19 @@
         <v>1.59</v>
       </c>
       <c r="M4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N4">
         <v>2.72</v>
       </c>
       <c r="O4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P4">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q4">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R4">
         <v>1.2</v>
@@ -1817,49 +1817,49 @@
         <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W4">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z4">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA4">
         <v>55</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC4">
         <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF4">
         <v>23</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
         <v>28</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
         <v>80</v>
@@ -1868,28 +1868,28 @@
         <v>60</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AM4">
         <v>220</v>
       </c>
       <c r="AN4">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AO4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP4">
         <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="AT4">
         <v>7.6</v>
@@ -1898,13 +1898,13 @@
         <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW4">
-        <v>5.8</v>
+        <v>27</v>
       </c>
       <c r="AX4">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AY4">
         <v>12.5</v>
@@ -1913,85 +1913,85 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="BB4">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="BC4">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BD4">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="BE4">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF4">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="BG4">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BH4">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BI4">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN4">
         <v>6.2</v>
       </c>
       <c r="BO4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
+        <v>10</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>12</v>
+      </c>
+      <c r="BT4">
+        <v>5.4</v>
+      </c>
+      <c r="BU4">
+        <v>4.1</v>
+      </c>
+      <c r="BV4">
+        <v>24</v>
+      </c>
+      <c r="BW4">
         <v>9.4</v>
       </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>10.5</v>
-      </c>
-      <c r="BT4">
-        <v>5.6</v>
-      </c>
-      <c r="BU4">
-        <v>4.2</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>226</v>
@@ -2014,37 +2014,37 @@
         <v>183</v>
       </c>
       <c r="F5">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G5">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="H5">
         <v>3.25</v>
       </c>
       <c r="I5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J5">
+        <v>3.15</v>
+      </c>
+      <c r="K5">
         <v>3.25</v>
-      </c>
-      <c r="K5">
-        <v>3.35</v>
       </c>
       <c r="L5">
         <v>1.48</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
         <v>1.41</v>
       </c>
       <c r="P5">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
         <v>2.26</v>
@@ -2065,19 +2065,19 @@
         <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X5">
+        <v>11</v>
+      </c>
+      <c r="Y5">
         <v>11.5</v>
-      </c>
-      <c r="Y5">
-        <v>11</v>
       </c>
       <c r="Z5">
         <v>22</v>
       </c>
       <c r="AA5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB5">
         <v>9.4</v>
@@ -2086,13 +2086,13 @@
         <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG5">
         <v>12</v>
@@ -2101,37 +2101,37 @@
         <v>18.5</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>38</v>
       </c>
       <c r="AK5">
+        <v>32</v>
+      </c>
+      <c r="AL5">
+        <v>48</v>
+      </c>
+      <c r="AM5">
+        <v>120</v>
+      </c>
+      <c r="AN5">
         <v>30</v>
       </c>
-      <c r="AL5">
+      <c r="AO5">
         <v>55</v>
-      </c>
-      <c r="AM5">
-        <v>130</v>
-      </c>
-      <c r="AN5">
-        <v>28</v>
-      </c>
-      <c r="AO5">
-        <v>50</v>
       </c>
       <c r="AP5">
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR5">
         <v>19</v>
       </c>
       <c r="AS5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -2140,10 +2140,10 @@
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AX5">
         <v>14</v>
@@ -2152,31 +2152,31 @@
         <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
+        <v>48</v>
+      </c>
+      <c r="BB5">
+        <v>32</v>
+      </c>
+      <c r="BC5">
+        <v>27</v>
+      </c>
+      <c r="BD5">
+        <v>42</v>
+      </c>
+      <c r="BE5">
+        <v>85</v>
+      </c>
+      <c r="BF5">
+        <v>25</v>
+      </c>
+      <c r="BG5">
         <v>38</v>
       </c>
-      <c r="BB5">
-        <v>27</v>
-      </c>
-      <c r="BC5">
-        <v>22</v>
-      </c>
-      <c r="BD5">
-        <v>11</v>
-      </c>
-      <c r="BE5">
-        <v>12.5</v>
-      </c>
-      <c r="BF5">
-        <v>21</v>
-      </c>
-      <c r="BG5">
-        <v>32</v>
-      </c>
       <c r="BH5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI5">
         <v>2.58</v>
@@ -2185,34 +2185,34 @@
         <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BN5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP5">
         <v>23</v>
       </c>
       <c r="BQ5">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BR5">
         <v>42</v>
       </c>
       <c r="BS5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BT5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU5">
         <v>5</v>
@@ -2221,19 +2221,19 @@
         <v>32</v>
       </c>
       <c r="BW5">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BX5">
         <v>48</v>
       </c>
       <c r="BY5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BZ5">
         <v>40</v>
       </c>
       <c r="CA5">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="CB5" t="s">
         <v>226</v>
@@ -2256,19 +2256,19 @@
         <v>184</v>
       </c>
       <c r="F6">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="G6">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="H6">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>990</v>
       </c>
       <c r="J6">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2280,22 +2280,22 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O6">
         <v>1.24</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q6">
         <v>1.73</v>
       </c>
       <c r="R6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2307,7 +2307,7 @@
         <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2498,22 +2498,22 @@
         <v>185</v>
       </c>
       <c r="F7">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H7">
         <v>4.2</v>
       </c>
       <c r="I7">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>3.1</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
         <v>1.48</v>
@@ -2522,7 +2522,7 @@
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="O7">
         <v>1.4</v>
@@ -2531,25 +2531,25 @@
         <v>1.59</v>
       </c>
       <c r="Q7">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R7">
         <v>1.22</v>
       </c>
       <c r="S7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T7">
         <v>2.02</v>
       </c>
       <c r="U7">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X7">
         <v>12</v>
@@ -2558,10 +2558,10 @@
         <v>15</v>
       </c>
       <c r="Z7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB7">
         <v>8.4</v>
@@ -2627,7 +2627,7 @@
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX7">
         <v>8.800000000000001</v>
@@ -2648,16 +2648,16 @@
         <v>19.5</v>
       </c>
       <c r="BD7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF7">
         <v>16.5</v>
       </c>
       <c r="BG7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2669,16 +2669,16 @@
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BN7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO7">
         <v>3.65</v>
@@ -2687,37 +2687,37 @@
         <v>18.5</v>
       </c>
       <c r="BQ7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR7">
         <v>42</v>
       </c>
       <c r="BS7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BT7">
         <v>8.800000000000001</v>
       </c>
       <c r="BU7">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="BV7">
         <v>50</v>
       </c>
       <c r="BW7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX7">
         <v>70</v>
       </c>
       <c r="BY7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ7">
         <v>42</v>
       </c>
       <c r="CA7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB7" t="s">
         <v>226</v>
@@ -2929,7 +2929,7 @@
         <v>15</v>
       </c>
       <c r="BQ8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR8">
         <v>27</v>
@@ -2947,7 +2947,7 @@
         <v>32</v>
       </c>
       <c r="BW8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX8">
         <v>1000</v>
@@ -2997,7 +2997,7 @@
         <v>2.78</v>
       </c>
       <c r="K9">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L9">
         <v>1.53</v>
@@ -3009,7 +3009,7 @@
         <v>2.34</v>
       </c>
       <c r="O9">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P9">
         <v>1.47</v>
@@ -3021,7 +3021,7 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T9">
         <v>2.12</v>
@@ -3230,7 +3230,7 @@
         <v>2.54</v>
       </c>
       <c r="H10">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I10">
         <v>3.4</v>
@@ -3386,64 +3386,64 @@
         <v>15</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="s">
         <v>226</v>
@@ -3469,175 +3469,175 @@
         <v>2.22</v>
       </c>
       <c r="G11">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="H11">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="I11">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J11">
         <v>3.35</v>
       </c>
       <c r="K11">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L11">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="M11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N11">
         <v>3.35</v>
       </c>
       <c r="O11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P11">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="Q11">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="R11">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="T11">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3646,46 +3646,46 @@
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB11" t="s">
         <v>226</v>
@@ -3711,10 +3711,10 @@
         <v>1.83</v>
       </c>
       <c r="G12">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I12">
         <v>4.7</v>
@@ -3723,7 +3723,7 @@
         <v>4</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>1.3</v>
@@ -3732,7 +3732,7 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O12">
         <v>1.24</v>
@@ -3747,13 +3747,13 @@
         <v>1.44</v>
       </c>
       <c r="S12">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T12">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U12">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V12">
         <v>1.27</v>
@@ -3828,7 +3828,7 @@
         <v>6.8</v>
       </c>
       <c r="AT12">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU12">
         <v>7.2</v>
@@ -3870,58 +3870,58 @@
         <v>6.4</v>
       </c>
       <c r="BH12">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BI12">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="BJ12">
         <v>11</v>
       </c>
       <c r="BK12">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BL12">
         <v>120</v>
       </c>
       <c r="BM12">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BN12">
         <v>5.4</v>
       </c>
       <c r="BO12">
-        <v>2.78</v>
+        <v>3.8</v>
       </c>
       <c r="BP12">
         <v>14.5</v>
       </c>
       <c r="BQ12">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BR12">
         <v>28</v>
       </c>
       <c r="BS12">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BT12">
         <v>9</v>
       </c>
       <c r="BU12">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BV12">
         <v>38</v>
       </c>
       <c r="BW12">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BX12">
         <v>46</v>
       </c>
       <c r="BY12">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3953,163 +3953,163 @@
         <v>1.31</v>
       </c>
       <c r="G13">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="H13">
-        <v>3.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I13">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="J13">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L13">
         <v>1.29</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O13">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P13">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Q13">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R13">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S13">
+        <v>2.66</v>
+      </c>
+      <c r="T13">
+        <v>2.18</v>
+      </c>
+      <c r="U13">
+        <v>1.67</v>
+      </c>
+      <c r="V13">
+        <v>1.07</v>
+      </c>
+      <c r="W13">
+        <v>3.15</v>
+      </c>
+      <c r="X13">
+        <v>22</v>
+      </c>
+      <c r="Y13">
+        <v>42</v>
+      </c>
+      <c r="Z13">
+        <v>150</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC13">
+        <v>15</v>
+      </c>
+      <c r="AD13">
+        <v>55</v>
+      </c>
+      <c r="AE13">
+        <v>290</v>
+      </c>
+      <c r="AF13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG13">
+        <v>13</v>
+      </c>
+      <c r="AH13">
+        <v>40</v>
+      </c>
+      <c r="AI13">
+        <v>230</v>
+      </c>
+      <c r="AJ13">
+        <v>13</v>
+      </c>
+      <c r="AK13">
+        <v>19</v>
+      </c>
+      <c r="AL13">
+        <v>55</v>
+      </c>
+      <c r="AM13">
+        <v>260</v>
+      </c>
+      <c r="AN13">
+        <v>7.4</v>
+      </c>
+      <c r="AO13">
+        <v>470</v>
+      </c>
+      <c r="AP13">
+        <v>3.7</v>
+      </c>
+      <c r="AQ13">
+        <v>4</v>
+      </c>
+      <c r="AR13">
+        <v>4.3</v>
+      </c>
+      <c r="AS13">
+        <v>4.4</v>
+      </c>
+      <c r="AT13">
+        <v>3</v>
+      </c>
+      <c r="AU13">
+        <v>3.4</v>
+      </c>
+      <c r="AV13">
+        <v>4.1</v>
+      </c>
+      <c r="AW13">
+        <v>4.4</v>
+      </c>
+      <c r="AX13">
+        <v>3</v>
+      </c>
+      <c r="AY13">
+        <v>3.3</v>
+      </c>
+      <c r="AZ13">
+        <v>4</v>
+      </c>
+      <c r="BA13">
+        <v>4.3</v>
+      </c>
+      <c r="BB13">
+        <v>3.3</v>
+      </c>
+      <c r="BC13">
+        <v>3.6</v>
+      </c>
+      <c r="BD13">
+        <v>4.1</v>
+      </c>
+      <c r="BE13">
+        <v>4.4</v>
+      </c>
+      <c r="BF13">
         <v>2.78</v>
       </c>
-      <c r="T13">
-        <v>1.01</v>
-      </c>
-      <c r="U13">
-        <v>1.01</v>
-      </c>
-      <c r="V13">
-        <v>1.01</v>
-      </c>
-      <c r="W13">
-        <v>3.05</v>
-      </c>
-      <c r="X13">
-        <v>1000</v>
-      </c>
-      <c r="Y13">
-        <v>1000</v>
-      </c>
-      <c r="Z13">
-        <v>1000</v>
-      </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
-        <v>1000</v>
-      </c>
-      <c r="AC13">
-        <v>1000</v>
-      </c>
-      <c r="AD13">
-        <v>1000</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>1000</v>
-      </c>
-      <c r="AG13">
-        <v>1000</v>
-      </c>
-      <c r="AH13">
-        <v>1000</v>
-      </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>1000</v>
-      </c>
-      <c r="AK13">
-        <v>1000</v>
-      </c>
-      <c r="AL13">
-        <v>1000</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>1000</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>1.03</v>
-      </c>
-      <c r="AQ13">
-        <v>1.03</v>
-      </c>
-      <c r="AR13">
-        <v>1.03</v>
-      </c>
-      <c r="AS13">
-        <v>1.03</v>
-      </c>
-      <c r="AT13">
-        <v>1.03</v>
-      </c>
-      <c r="AU13">
-        <v>1.03</v>
-      </c>
-      <c r="AV13">
-        <v>1.03</v>
-      </c>
-      <c r="AW13">
-        <v>1.03</v>
-      </c>
-      <c r="AX13">
-        <v>1.03</v>
-      </c>
-      <c r="AY13">
-        <v>1.03</v>
-      </c>
-      <c r="AZ13">
-        <v>1.03</v>
-      </c>
-      <c r="BA13">
-        <v>1.03</v>
-      </c>
-      <c r="BB13">
-        <v>1.03</v>
-      </c>
-      <c r="BC13">
-        <v>1.03</v>
-      </c>
-      <c r="BD13">
-        <v>1.03</v>
-      </c>
-      <c r="BE13">
-        <v>1.03</v>
-      </c>
-      <c r="BF13">
-        <v>1.01</v>
-      </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH13">
         <v>3.95</v>
@@ -4127,7 +4127,7 @@
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.62</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13">
         <v>3.8</v>
@@ -4157,13 +4157,13 @@
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.61</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.61</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13">
         <v>15</v>
@@ -4192,10 +4192,10 @@
         <v>192</v>
       </c>
       <c r="F14">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G14">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H14">
         <v>4.2</v>
@@ -4210,7 +4210,7 @@
         <v>3.85</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M14">
         <v>1.09</v>
@@ -4219,37 +4219,37 @@
         <v>3.05</v>
       </c>
       <c r="O14">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P14">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q14">
         <v>2.18</v>
       </c>
       <c r="R14">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T14">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U14">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V14">
         <v>1.25</v>
       </c>
       <c r="W14">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X14">
         <v>13</v>
       </c>
       <c r="Y14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z14">
         <v>40</v>
@@ -4309,7 +4309,7 @@
         <v>6</v>
       </c>
       <c r="AS14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT14">
         <v>6.4</v>
@@ -4321,7 +4321,7 @@
         <v>14</v>
       </c>
       <c r="AW14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX14">
         <v>9.800000000000001</v>
@@ -4333,7 +4333,7 @@
         <v>18.5</v>
       </c>
       <c r="BA14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB14">
         <v>20</v>
@@ -4345,7 +4345,7 @@
         <v>6.2</v>
       </c>
       <c r="BE14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF14">
         <v>14.5</v>
@@ -4354,64 +4354,64 @@
         <v>6.6</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB14" t="s">
         <v>226</v>
@@ -4434,7 +4434,7 @@
         <v>193</v>
       </c>
       <c r="F15">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="G15">
         <v>3.7</v>
@@ -4473,13 +4473,13 @@
         <v>1.2</v>
       </c>
       <c r="S15">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="T15">
         <v>1.96</v>
       </c>
       <c r="U15">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="V15">
         <v>1.54</v>
@@ -4676,175 +4676,175 @@
         <v>194</v>
       </c>
       <c r="F16">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G16">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="H16">
-        <v>4.5</v>
+        <v>26</v>
       </c>
       <c r="I16">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="J16">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="L16">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="M16">
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>1.91</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="P16">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q16">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="R16">
         <v>1.9</v>
       </c>
       <c r="S16">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16">
+        <v>7.2</v>
+      </c>
+      <c r="X16">
+        <v>46</v>
+      </c>
+      <c r="Y16">
+        <v>100</v>
+      </c>
+      <c r="Z16">
+        <v>360</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>14</v>
+      </c>
+      <c r="AC16">
+        <v>28</v>
+      </c>
+      <c r="AD16">
+        <v>120</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>9.6</v>
+      </c>
+      <c r="AG16">
+        <v>17</v>
+      </c>
+      <c r="AH16">
+        <v>65</v>
+      </c>
+      <c r="AI16">
+        <v>410</v>
+      </c>
+      <c r="AJ16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK16">
+        <v>17.5</v>
+      </c>
+      <c r="AL16">
+        <v>65</v>
+      </c>
+      <c r="AM16">
+        <v>360</v>
+      </c>
+      <c r="AN16">
+        <v>3.25</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>5</v>
+      </c>
+      <c r="AQ16">
+        <v>5.3</v>
+      </c>
+      <c r="AR16">
+        <v>5.5</v>
+      </c>
+      <c r="AS16">
+        <v>5.6</v>
+      </c>
+      <c r="AT16">
+        <v>10</v>
+      </c>
+      <c r="AU16">
+        <v>18</v>
+      </c>
+      <c r="AV16">
+        <v>5.4</v>
+      </c>
+      <c r="AW16">
+        <v>5.6</v>
+      </c>
+      <c r="AX16">
+        <v>7.2</v>
+      </c>
+      <c r="AY16">
+        <v>11</v>
+      </c>
+      <c r="AZ16">
+        <v>5.1</v>
+      </c>
+      <c r="BA16">
+        <v>5.5</v>
+      </c>
+      <c r="BB16">
+        <v>6.2</v>
+      </c>
+      <c r="BC16">
+        <v>11.5</v>
+      </c>
+      <c r="BD16">
+        <v>5.2</v>
+      </c>
+      <c r="BE16">
+        <v>5.5</v>
+      </c>
+      <c r="BF16">
+        <v>2.44</v>
+      </c>
+      <c r="BG16">
+        <v>5.6</v>
+      </c>
+      <c r="BH16">
+        <v>5.5</v>
+      </c>
+      <c r="BI16">
         <v>4.3</v>
       </c>
-      <c r="X16">
-        <v>1000</v>
-      </c>
-      <c r="Y16">
-        <v>1000</v>
-      </c>
-      <c r="Z16">
-        <v>1000</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>1000</v>
-      </c>
-      <c r="AC16">
-        <v>1000</v>
-      </c>
-      <c r="AD16">
-        <v>1000</v>
-      </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>1000</v>
-      </c>
-      <c r="AG16">
-        <v>1000</v>
-      </c>
-      <c r="AH16">
-        <v>1000</v>
-      </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
-        <v>1000</v>
-      </c>
-      <c r="AK16">
-        <v>1000</v>
-      </c>
-      <c r="AL16">
-        <v>1000</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>1000</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>1.03</v>
-      </c>
-      <c r="AQ16">
-        <v>1.03</v>
-      </c>
-      <c r="AR16">
-        <v>1.03</v>
-      </c>
-      <c r="AS16">
-        <v>1.03</v>
-      </c>
-      <c r="AT16">
-        <v>1.03</v>
-      </c>
-      <c r="AU16">
-        <v>1.03</v>
-      </c>
-      <c r="AV16">
-        <v>1.03</v>
-      </c>
-      <c r="AW16">
-        <v>1.03</v>
-      </c>
-      <c r="AX16">
-        <v>1.03</v>
-      </c>
-      <c r="AY16">
-        <v>1.03</v>
-      </c>
-      <c r="AZ16">
-        <v>1.03</v>
-      </c>
-      <c r="BA16">
-        <v>1.03</v>
-      </c>
-      <c r="BB16">
-        <v>1.03</v>
-      </c>
-      <c r="BC16">
-        <v>1.03</v>
-      </c>
-      <c r="BD16">
-        <v>1.03</v>
-      </c>
-      <c r="BE16">
-        <v>1.03</v>
-      </c>
-      <c r="BF16">
-        <v>1.01</v>
-      </c>
-      <c r="BG16">
-        <v>1.01</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.01</v>
-      </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BK16">
         <v>1.01</v>
@@ -4856,16 +4856,16 @@
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR16">
         <v>1000</v>
@@ -4892,10 +4892,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB16" t="s">
         <v>226</v>
@@ -4924,7 +4924,7 @@
         <v>4.4</v>
       </c>
       <c r="H17">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I17">
         <v>1.92</v>
@@ -4936,7 +4936,7 @@
         <v>4.3</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M17">
         <v>1.04</v>
@@ -4951,7 +4951,7 @@
         <v>2.56</v>
       </c>
       <c r="Q17">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R17">
         <v>1.63</v>
@@ -4963,7 +4963,7 @@
         <v>1.6</v>
       </c>
       <c r="U17">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V17">
         <v>2.08</v>
@@ -4975,7 +4975,7 @@
         <v>25</v>
       </c>
       <c r="Y17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z17">
         <v>14.5</v>
@@ -4987,13 +4987,13 @@
         <v>23</v>
       </c>
       <c r="AC17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17">
         <v>11</v>
       </c>
       <c r="AE17">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF17">
         <v>38</v>
@@ -5005,7 +5005,7 @@
         <v>16</v>
       </c>
       <c r="AI17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ17">
         <v>85</v>
@@ -5026,7 +5026,7 @@
         <v>8.4</v>
       </c>
       <c r="AP17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ17">
         <v>12</v>
@@ -5044,7 +5044,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW17">
         <v>15.5</v>
@@ -5074,67 +5074,67 @@
         <v>30</v>
       </c>
       <c r="BF17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BG17">
         <v>7.6</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK17">
         <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM17">
         <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO17">
         <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ17">
         <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS17">
         <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW17">
         <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY17">
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA17">
         <v>1.01</v>
@@ -5160,49 +5160,49 @@
         <v>196</v>
       </c>
       <c r="F18">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G18">
         <v>1.37</v>
       </c>
       <c r="H18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J18">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K18">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L18">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M18">
         <v>1.02</v>
       </c>
       <c r="N18">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O18">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P18">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q18">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R18">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S18">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="T18">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U18">
         <v>2.3</v>
@@ -5214,7 +5214,7 @@
         <v>3.7</v>
       </c>
       <c r="X18">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Y18">
         <v>55</v>
@@ -5241,7 +5241,7 @@
         <v>11.5</v>
       </c>
       <c r="AG18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH18">
         <v>22</v>
@@ -5265,7 +5265,7 @@
         <v>3.7</v>
       </c>
       <c r="AO18">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
         <v>32</v>
@@ -5280,10 +5280,10 @@
         <v>55</v>
       </c>
       <c r="AT18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU18">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV18">
         <v>32</v>
@@ -5316,67 +5316,67 @@
         <v>34</v>
       </c>
       <c r="BF18">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG18">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI18">
-        <v>2.24</v>
+        <v>4.3</v>
       </c>
       <c r="BJ18">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK18">
-        <v>1.95</v>
+        <v>5.2</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>2.24</v>
+        <v>9</v>
       </c>
       <c r="BN18">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO18">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="BP18">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BQ18">
         <v>5</v>
       </c>
       <c r="BR18">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BS18">
-        <v>2.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT18">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="BU18">
-        <v>1.99</v>
+        <v>5.7</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>2.18</v>
+        <v>8.6</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY18">
-        <v>2.18</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="CA18">
         <v>5.4</v>
@@ -5402,13 +5402,13 @@
         <v>197</v>
       </c>
       <c r="F19">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G19">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H19">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I19">
         <v>3.3</v>
@@ -5438,13 +5438,13 @@
         <v>2.02</v>
       </c>
       <c r="R19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S19">
         <v>3.7</v>
       </c>
       <c r="T19">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U19">
         <v>2.06</v>
@@ -5522,7 +5522,7 @@
         <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU19">
         <v>5.8</v>
@@ -5567,19 +5567,19 @@
         <v>3.3</v>
       </c>
       <c r="BI19">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BJ19">
         <v>9.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN19">
         <v>5.6</v>
@@ -5588,19 +5588,19 @@
         <v>4.2</v>
       </c>
       <c r="BP19">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT19">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU19">
         <v>4.6</v>
@@ -5609,13 +5609,13 @@
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5656,7 +5656,7 @@
         <v>3.4</v>
       </c>
       <c r="J20">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K20">
         <v>3.75</v>
@@ -5665,7 +5665,7 @@
         <v>1.32</v>
       </c>
       <c r="M20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N20">
         <v>4.2</v>
@@ -5674,25 +5674,25 @@
         <v>1.26</v>
       </c>
       <c r="P20">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q20">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R20">
         <v>1.4</v>
       </c>
       <c r="S20">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T20">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U20">
         <v>2.3</v>
       </c>
       <c r="V20">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
         <v>1.67</v>
@@ -5707,13 +5707,13 @@
         <v>28</v>
       </c>
       <c r="AA20">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC20">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD20">
         <v>14.5</v>
@@ -5725,7 +5725,7 @@
         <v>16.5</v>
       </c>
       <c r="AG20">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH20">
         <v>17</v>
@@ -5749,7 +5749,7 @@
         <v>21</v>
       </c>
       <c r="AO20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP20">
         <v>12.5</v>
@@ -5785,7 +5785,7 @@
         <v>13.5</v>
       </c>
       <c r="BA20">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB20">
         <v>18.5</v>
@@ -5794,10 +5794,10 @@
         <v>17.5</v>
       </c>
       <c r="BD20">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE20">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF20">
         <v>12.5</v>
@@ -5806,10 +5806,10 @@
         <v>21</v>
       </c>
       <c r="BH20">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI20">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ20">
         <v>9.6</v>
@@ -5827,16 +5827,16 @@
         <v>5.6</v>
       </c>
       <c r="BO20">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP20">
         <v>18</v>
       </c>
       <c r="BQ20">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS20">
         <v>7.6</v>
@@ -5851,16 +5851,16 @@
         <v>26</v>
       </c>
       <c r="BW20">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX20">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY20">
         <v>8</v>
       </c>
       <c r="BZ20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA20">
         <v>7.2</v>
@@ -5886,7 +5886,7 @@
         <v>199</v>
       </c>
       <c r="F21">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G21">
         <v>3.7</v>
@@ -5910,7 +5910,7 @@
         <v>1.06</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O21">
         <v>1.26</v>
@@ -5919,7 +5919,7 @@
         <v>2.04</v>
       </c>
       <c r="Q21">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R21">
         <v>1.41</v>
@@ -5931,7 +5931,7 @@
         <v>1.66</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V21">
         <v>1.71</v>
@@ -5940,7 +5940,7 @@
         <v>1.37</v>
       </c>
       <c r="X21">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y21">
         <v>13</v>
@@ -6030,16 +6030,16 @@
         <v>1.03</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
         <v>1.01</v>
@@ -6128,25 +6128,25 @@
         <v>200</v>
       </c>
       <c r="F22">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="G22">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H22">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I22">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="J22">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K22">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M22">
         <v>1.02</v>
@@ -6155,34 +6155,34 @@
         <v>7.8</v>
       </c>
       <c r="O22">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P22">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q22">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R22">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S22">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="T22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V22">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W22">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="X22">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y22">
         <v>22</v>
@@ -6197,7 +6197,7 @@
         <v>40</v>
       </c>
       <c r="AC22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD22">
         <v>13</v>
@@ -6206,19 +6206,19 @@
         <v>28</v>
       </c>
       <c r="AF22">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AG22">
         <v>22</v>
       </c>
       <c r="AH22">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI22">
         <v>32</v>
       </c>
       <c r="AJ22">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK22">
         <v>40</v>
@@ -6230,13 +6230,13 @@
         <v>48</v>
       </c>
       <c r="AN22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO22">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AP22">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ22">
         <v>15.5</v>
@@ -6248,10 +6248,10 @@
         <v>21</v>
       </c>
       <c r="AT22">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AU22">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV22">
         <v>9.4</v>
@@ -6260,7 +6260,7 @@
         <v>14</v>
       </c>
       <c r="AX22">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AY22">
         <v>11.5</v>
@@ -6272,7 +6272,7 @@
         <v>16</v>
       </c>
       <c r="BB22">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BC22">
         <v>20</v>
@@ -6281,7 +6281,7 @@
         <v>20</v>
       </c>
       <c r="BE22">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF22">
         <v>9.800000000000001</v>
@@ -6290,10 +6290,10 @@
         <v>6.8</v>
       </c>
       <c r="BH22">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BI22">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ22">
         <v>9.800000000000001</v>
@@ -6308,13 +6308,13 @@
         <v>4.2</v>
       </c>
       <c r="BN22">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO22">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ22">
         <v>3.8</v>
@@ -6326,16 +6326,16 @@
         <v>3.9</v>
       </c>
       <c r="BT22">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU22">
         <v>4.6</v>
       </c>
       <c r="BV22">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BW22">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BX22">
         <v>23</v>
@@ -6344,10 +6344,10 @@
         <v>3.8</v>
       </c>
       <c r="BZ22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CA22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="CB22" t="s">
         <v>226</v>
@@ -6370,10 +6370,10 @@
         <v>201</v>
       </c>
       <c r="F23">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G23">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H23">
         <v>2.62</v>
@@ -6382,7 +6382,7 @@
         <v>2.72</v>
       </c>
       <c r="J23">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K23">
         <v>4.1</v>
@@ -6397,19 +6397,19 @@
         <v>6</v>
       </c>
       <c r="O23">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P23">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="Q23">
         <v>1.54</v>
       </c>
       <c r="R23">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S23">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T23">
         <v>1.5</v>
@@ -6421,13 +6421,13 @@
         <v>1.58</v>
       </c>
       <c r="W23">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X23">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z23">
         <v>27</v>
@@ -6439,7 +6439,7 @@
         <v>18</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23">
         <v>13.5</v>
@@ -6454,7 +6454,7 @@
         <v>13.5</v>
       </c>
       <c r="AH23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI23">
         <v>36</v>
@@ -6463,7 +6463,7 @@
         <v>38</v>
       </c>
       <c r="AK23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL23">
         <v>29</v>
@@ -6484,16 +6484,16 @@
         <v>15.5</v>
       </c>
       <c r="AR23">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS23">
         <v>32</v>
       </c>
       <c r="AT23">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU23">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV23">
         <v>11</v>
@@ -6502,13 +6502,13 @@
         <v>20</v>
       </c>
       <c r="AX23">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY23">
         <v>11.5</v>
       </c>
       <c r="AZ23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA23">
         <v>24</v>
@@ -6526,13 +6526,13 @@
         <v>42</v>
       </c>
       <c r="BF23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG23">
         <v>10.5</v>
       </c>
       <c r="BH23">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI23">
         <v>3.6</v>
@@ -6544,10 +6544,10 @@
         <v>5.4</v>
       </c>
       <c r="BL23">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BM23">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN23">
         <v>6.2</v>
@@ -6556,13 +6556,13 @@
         <v>4.7</v>
       </c>
       <c r="BP23">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ23">
         <v>8</v>
       </c>
       <c r="BR23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS23">
         <v>9.199999999999999</v>
@@ -6645,7 +6645,7 @@
         <v>2.02</v>
       </c>
       <c r="Q24">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R24">
         <v>1.4</v>
@@ -6666,7 +6666,7 @@
         <v>1.67</v>
       </c>
       <c r="X24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y24">
         <v>15</v>
@@ -6774,58 +6774,58 @@
         <v>21</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI24">
-        <v>1.93</v>
+        <v>2.92</v>
       </c>
       <c r="BJ24">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK24">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.93</v>
+        <v>9.4</v>
       </c>
       <c r="BN24">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BO24">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BP24">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="BQ24">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR24">
         <v>38</v>
       </c>
       <c r="BS24">
-        <v>1.84</v>
+        <v>7.6</v>
       </c>
       <c r="BT24">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BU24">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV24">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BW24">
-        <v>1.83</v>
+        <v>7.4</v>
       </c>
       <c r="BX24">
         <v>48</v>
       </c>
       <c r="BY24">
-        <v>1.86</v>
+        <v>8</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6857,19 +6857,19 @@
         <v>2.04</v>
       </c>
       <c r="G25">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H25">
         <v>3.05</v>
       </c>
       <c r="I25">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K25">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L25">
         <v>1.21</v>
@@ -6887,7 +6887,7 @@
         <v>2.76</v>
       </c>
       <c r="Q25">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R25">
         <v>1.72</v>
@@ -6899,13 +6899,13 @@
         <v>1.46</v>
       </c>
       <c r="U25">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V25">
         <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X25">
         <v>38</v>
@@ -6914,7 +6914,7 @@
         <v>23</v>
       </c>
       <c r="Z25">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA25">
         <v>65</v>
@@ -6962,7 +6962,7 @@
         <v>22</v>
       </c>
       <c r="AP25">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ25">
         <v>18</v>
@@ -6971,7 +6971,7 @@
         <v>21</v>
       </c>
       <c r="AS25">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT25">
         <v>14</v>
@@ -7096,25 +7096,25 @@
         <v>204</v>
       </c>
       <c r="F26">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G26">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="H26">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="I26">
         <v>2.12</v>
       </c>
       <c r="J26">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M26">
         <v>1.03</v>
@@ -7123,199 +7123,199 @@
         <v>5.6</v>
       </c>
       <c r="O26">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P26">
         <v>2.56</v>
       </c>
       <c r="Q26">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="R26">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S26">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T26">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U26">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="V26">
         <v>1.89</v>
       </c>
       <c r="W26">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y26">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z26">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF26">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG26">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH26">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI26">
+        <v>32</v>
+      </c>
+      <c r="AJ26">
+        <v>75</v>
+      </c>
+      <c r="AK26">
+        <v>42</v>
+      </c>
+      <c r="AL26">
+        <v>44</v>
+      </c>
+      <c r="AM26">
+        <v>65</v>
+      </c>
+      <c r="AN26">
+        <v>29</v>
+      </c>
+      <c r="AO26">
+        <v>10.5</v>
+      </c>
+      <c r="AP26">
+        <v>20</v>
+      </c>
+      <c r="AQ26">
+        <v>11</v>
+      </c>
+      <c r="AR26">
+        <v>12</v>
+      </c>
+      <c r="AS26">
+        <v>18.5</v>
+      </c>
+      <c r="AT26">
+        <v>15.5</v>
+      </c>
+      <c r="AU26">
+        <v>8</v>
+      </c>
+      <c r="AV26">
+        <v>8.6</v>
+      </c>
+      <c r="AW26">
+        <v>14</v>
+      </c>
+      <c r="AX26">
+        <v>4.3</v>
+      </c>
+      <c r="AY26">
+        <v>12</v>
+      </c>
+      <c r="AZ26">
+        <v>11.5</v>
+      </c>
+      <c r="BA26">
+        <v>20</v>
+      </c>
+      <c r="BB26">
+        <v>4.6</v>
+      </c>
+      <c r="BC26">
+        <v>4.4</v>
+      </c>
+      <c r="BD26">
+        <v>4.4</v>
+      </c>
+      <c r="BE26">
+        <v>4.6</v>
+      </c>
+      <c r="BF26">
+        <v>18</v>
+      </c>
+      <c r="BG26">
+        <v>7.2</v>
+      </c>
+      <c r="BH26">
+        <v>5.1</v>
+      </c>
+      <c r="BI26">
+        <v>3.65</v>
+      </c>
+      <c r="BJ26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK26">
+        <v>3.6</v>
+      </c>
+      <c r="BL26">
+        <v>85</v>
+      </c>
+      <c r="BM26">
+        <v>5.3</v>
+      </c>
+      <c r="BN26">
+        <v>8.4</v>
+      </c>
+      <c r="BO26">
+        <v>5.8</v>
+      </c>
+      <c r="BP26">
+        <v>29</v>
+      </c>
+      <c r="BQ26">
+        <v>4.7</v>
+      </c>
+      <c r="BR26">
         <v>34</v>
       </c>
-      <c r="AJ26">
-        <v>80</v>
-      </c>
-      <c r="AK26">
-        <v>44</v>
-      </c>
-      <c r="AL26">
-        <v>1000</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>1000</v>
-      </c>
-      <c r="AO26">
-        <v>11</v>
-      </c>
-      <c r="AP26">
-        <v>1.65</v>
-      </c>
-      <c r="AQ26">
-        <v>10.5</v>
-      </c>
-      <c r="AR26">
-        <v>1.52</v>
-      </c>
-      <c r="AS26">
-        <v>1.65</v>
-      </c>
-      <c r="AT26">
-        <v>1.65</v>
-      </c>
-      <c r="AU26">
-        <v>1.65</v>
-      </c>
-      <c r="AV26">
-        <v>1.65</v>
-      </c>
-      <c r="AW26">
-        <v>1.65</v>
-      </c>
-      <c r="AX26">
-        <v>1.58</v>
-      </c>
-      <c r="AY26">
-        <v>1.52</v>
-      </c>
-      <c r="AZ26">
-        <v>11</v>
-      </c>
-      <c r="BA26">
-        <v>19</v>
-      </c>
-      <c r="BB26">
-        <v>1.61</v>
-      </c>
-      <c r="BC26">
-        <v>1.59</v>
-      </c>
-      <c r="BD26">
-        <v>1.65</v>
-      </c>
-      <c r="BE26">
-        <v>1.65</v>
-      </c>
-      <c r="BF26">
-        <v>1.65</v>
-      </c>
-      <c r="BG26">
-        <v>1.43</v>
-      </c>
-      <c r="BH26">
-        <v>1000</v>
-      </c>
-      <c r="BI26">
-        <v>1.01</v>
-      </c>
-      <c r="BJ26">
-        <v>1000</v>
-      </c>
-      <c r="BK26">
-        <v>1.01</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>1.01</v>
-      </c>
-      <c r="BN26">
-        <v>1000</v>
-      </c>
-      <c r="BO26">
-        <v>1.01</v>
-      </c>
-      <c r="BP26">
-        <v>1000</v>
-      </c>
-      <c r="BQ26">
-        <v>1.01</v>
-      </c>
-      <c r="BR26">
-        <v>1000</v>
-      </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB26" t="s">
         <v>226</v>
@@ -7341,7 +7341,7 @@
         <v>1.59</v>
       </c>
       <c r="G27">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H27">
         <v>6.6</v>
@@ -7353,7 +7353,7 @@
         <v>4</v>
       </c>
       <c r="K27">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L27">
         <v>1.37</v>
@@ -7374,10 +7374,10 @@
         <v>1.87</v>
       </c>
       <c r="R27">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T27">
         <v>1.89</v>
@@ -7389,16 +7389,16 @@
         <v>1.15</v>
       </c>
       <c r="W27">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X27">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z27">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA27">
         <v>230</v>
@@ -7416,13 +7416,13 @@
         <v>120</v>
       </c>
       <c r="AF27">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG27">
         <v>10.5</v>
       </c>
       <c r="AH27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI27">
         <v>110</v>
@@ -7431,7 +7431,7 @@
         <v>16.5</v>
       </c>
       <c r="AK27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL27">
         <v>38</v>
@@ -7440,7 +7440,7 @@
         <v>150</v>
       </c>
       <c r="AN27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO27">
         <v>150</v>
@@ -7452,10 +7452,10 @@
         <v>18</v>
       </c>
       <c r="AR27">
-        <v>4.8</v>
+        <v>38</v>
       </c>
       <c r="AS27">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AT27">
         <v>7.2</v>
@@ -7467,7 +7467,7 @@
         <v>20</v>
       </c>
       <c r="AW27">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AX27">
         <v>8.199999999999999</v>
@@ -7479,7 +7479,7 @@
         <v>18.5</v>
       </c>
       <c r="BA27">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BB27">
         <v>11.5</v>
@@ -7488,76 +7488,76 @@
         <v>12.5</v>
       </c>
       <c r="BD27">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE27">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BF27">
         <v>6.8</v>
       </c>
       <c r="BG27">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB27" t="s">
         <v>226</v>
@@ -7607,7 +7607,7 @@
         <v>3.55</v>
       </c>
       <c r="O28">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P28">
         <v>1.88</v>
@@ -7649,7 +7649,7 @@
         <v>17.5</v>
       </c>
       <c r="AC28">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD28">
         <v>13</v>
@@ -7721,22 +7721,22 @@
         <v>15.5</v>
       </c>
       <c r="BA28">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB28">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC28">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD28">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE28">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF28">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG28">
         <v>12</v>
@@ -7828,7 +7828,7 @@
         <v>2.18</v>
       </c>
       <c r="H29">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I29">
         <v>4.3</v>
@@ -7837,7 +7837,7 @@
         <v>3.5</v>
       </c>
       <c r="K29">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L29">
         <v>1.4</v>
@@ -7846,19 +7846,19 @@
         <v>1.07</v>
       </c>
       <c r="N29">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O29">
         <v>1.31</v>
       </c>
       <c r="P29">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q29">
         <v>1.94</v>
       </c>
       <c r="R29">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S29">
         <v>3.4</v>
@@ -7909,10 +7909,10 @@
         <v>21</v>
       </c>
       <c r="AI29">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ29">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK29">
         <v>26</v>
@@ -7924,7 +7924,7 @@
         <v>120</v>
       </c>
       <c r="AN29">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO29">
         <v>60</v>
@@ -7984,16 +7984,16 @@
         <v>1.01</v>
       </c>
       <c r="BH29">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI29">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK29">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL29">
         <v>1000</v>
@@ -8064,220 +8064,220 @@
         <v>208</v>
       </c>
       <c r="F30">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="G30">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H30">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="I30">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="J30">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K30">
         <v>3.9</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N30">
-        <v>2.72</v>
+        <v>3.8</v>
       </c>
       <c r="O30">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P30">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Q30">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="R30">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="S30">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP30">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ30">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR30">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AS30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU30">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV30">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY30">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ30">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG30">
         <v>1.01</v>
       </c>
       <c r="BH30">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="BI30">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK30">
-        <v>1.31</v>
+        <v>4</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO30">
-        <v>1.31</v>
+        <v>4.2</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ30">
-        <v>1.31</v>
+        <v>4.8</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS30">
-        <v>1.31</v>
+        <v>5.4</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU30">
-        <v>1.31</v>
+        <v>5.1</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW30">
-        <v>1.31</v>
+        <v>5.2</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY30">
-        <v>1.31</v>
+        <v>5.5</v>
       </c>
       <c r="BZ30">
         <v>0</v>
@@ -8306,226 +8306,226 @@
         <v>209</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="G31">
-        <v>170</v>
+        <v>3.75</v>
       </c>
       <c r="H31">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I31">
-        <v>110</v>
+        <v>2.86</v>
       </c>
       <c r="J31">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="K31">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M31">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="N31">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="O31">
+        <v>1.59</v>
+      </c>
+      <c r="P31">
         <v>1.46</v>
       </c>
-      <c r="P31">
-        <v>1.26</v>
-      </c>
       <c r="Q31">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="R31">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S31">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="T31">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U31">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V31">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB31">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC31">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF31">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG31">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK31">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN31">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP31">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ31">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR31">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS31">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AT31">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU31">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV31">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW31">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="AX31">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AY31">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ31">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
         <v>1.03</v>
       </c>
       <c r="BD31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF31">
         <v>1.01</v>
       </c>
       <c r="BG31">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI31">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU31">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA31">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB31" t="s">
         <v>226</v>
@@ -8551,28 +8551,28 @@
         <v>2.82</v>
       </c>
       <c r="G32">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H32">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I32">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J32">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="K32">
         <v>3.5</v>
       </c>
       <c r="L32">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M32">
         <v>1.09</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O32">
         <v>1.41</v>
@@ -8581,7 +8581,7 @@
         <v>1.71</v>
       </c>
       <c r="Q32">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R32">
         <v>1.26</v>
@@ -8590,7 +8590,7 @@
         <v>4.1</v>
       </c>
       <c r="T32">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U32">
         <v>1.98</v>
@@ -8793,10 +8793,10 @@
         <v>3.4</v>
       </c>
       <c r="G33">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H33">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I33">
         <v>2.48</v>
@@ -8808,7 +8808,7 @@
         <v>3.3</v>
       </c>
       <c r="L33">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M33">
         <v>1.11</v>
@@ -9038,7 +9038,7 @@
         <v>1.98</v>
       </c>
       <c r="H34">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I34">
         <v>5.2</v>
@@ -9059,10 +9059,10 @@
         <v>3.05</v>
       </c>
       <c r="O34">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P34">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q34">
         <v>2.26</v>
@@ -9516,112 +9516,112 @@
         <v>214</v>
       </c>
       <c r="F36">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="G36">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H36">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I36">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="J36">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K36">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M36">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N36">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P36">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q36">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="R36">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>3.2</v>
       </c>
       <c r="T36">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U36">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V36">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="W36">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X36">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y36">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z36">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB36">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD36">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE36">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF36">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG36">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH36">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI36">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ36">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK36">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL36">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM36">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN36">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO36">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP36">
         <v>1.01</v>
@@ -9660,16 +9660,16 @@
         <v>1.01</v>
       </c>
       <c r="BB36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC36">
         <v>1.01</v>
       </c>
       <c r="BD36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF36">
         <v>1.01</v>
@@ -9678,13 +9678,13 @@
         <v>1.01</v>
       </c>
       <c r="BH36">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI36">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ36">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK36">
         <v>1.01</v>
@@ -9696,13 +9696,13 @@
         <v>1.01</v>
       </c>
       <c r="BN36">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO36">
         <v>1.01</v>
       </c>
       <c r="BP36">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ36">
         <v>1.01</v>
@@ -9714,25 +9714,25 @@
         <v>1.01</v>
       </c>
       <c r="BT36">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU36">
         <v>1.01</v>
       </c>
       <c r="BV36">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW36">
         <v>1.01</v>
       </c>
       <c r="BX36">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY36">
         <v>1.01</v>
       </c>
       <c r="BZ36">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA36">
         <v>1.01</v>
@@ -9758,22 +9758,22 @@
         <v>215</v>
       </c>
       <c r="F37">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H37">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I37">
         <v>4.9</v>
       </c>
       <c r="J37">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K37">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="L37">
         <v>1.44</v>
@@ -9788,31 +9788,31 @@
         <v>1.47</v>
       </c>
       <c r="P37">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q37">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R37">
         <v>1.23</v>
       </c>
       <c r="S37">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T37">
         <v>2.02</v>
       </c>
       <c r="U37">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W37">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="X37">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y37">
         <v>14.5</v>
@@ -9824,7 +9824,7 @@
         <v>130</v>
       </c>
       <c r="AB37">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC37">
         <v>8.800000000000001</v>
@@ -9836,10 +9836,10 @@
         <v>85</v>
       </c>
       <c r="AF37">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG37">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH37">
         <v>26</v>
@@ -9848,19 +9848,19 @@
         <v>100</v>
       </c>
       <c r="AJ37">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK37">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL37">
         <v>60</v>
       </c>
       <c r="AM37">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN37">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO37">
         <v>120</v>
@@ -9872,10 +9872,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR37">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS37">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT37">
         <v>5.8</v>
@@ -9887,7 +9887,7 @@
         <v>14</v>
       </c>
       <c r="AW37">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX37">
         <v>9.199999999999999</v>
@@ -9896,10 +9896,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ37">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BA37">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB37">
         <v>20</v>
@@ -9908,16 +9908,16 @@
         <v>20</v>
       </c>
       <c r="BD37">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE37">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF37">
         <v>17.5</v>
       </c>
       <c r="BG37">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH37">
         <v>3.25</v>
@@ -9929,7 +9929,7 @@
         <v>12.5</v>
       </c>
       <c r="BK37">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BL37">
         <v>1000</v>
@@ -9944,7 +9944,7 @@
         <v>3.7</v>
       </c>
       <c r="BP37">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ37">
         <v>4.6</v>
@@ -9962,19 +9962,19 @@
         <v>3.55</v>
       </c>
       <c r="BV37">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BW37">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX37">
         <v>1000</v>
       </c>
       <c r="BY37">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ37">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA37">
         <v>5.3</v>
@@ -10057,34 +10057,34 @@
         <v>16</v>
       </c>
       <c r="Y38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z38">
         <v>14.5</v>
       </c>
       <c r="AA38">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB38">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC38">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD38">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE38">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AF38">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AG38">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH38">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI38">
         <v>50</v>
@@ -10132,7 +10132,7 @@
         <v>18.5</v>
       </c>
       <c r="AX38">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="AY38">
         <v>13</v>
@@ -10141,22 +10141,22 @@
         <v>16.5</v>
       </c>
       <c r="BA38">
-        <v>3.95</v>
+        <v>28</v>
       </c>
       <c r="BB38">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BC38">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BD38">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE38">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BF38">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BG38">
         <v>11.5</v>
@@ -10484,22 +10484,22 @@
         <v>218</v>
       </c>
       <c r="F40">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G40">
         <v>3.65</v>
       </c>
       <c r="H40">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I40">
         <v>2.66</v>
       </c>
       <c r="J40">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K40">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L40">
         <v>1.55</v>
@@ -10511,7 +10511,7 @@
         <v>2.46</v>
       </c>
       <c r="O40">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P40">
         <v>1.47</v>
@@ -10520,10 +10520,10 @@
         <v>2.9</v>
       </c>
       <c r="R40">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S40">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T40">
         <v>2.26</v>
@@ -10541,13 +10541,13 @@
         <v>7.8</v>
       </c>
       <c r="Y40">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z40">
         <v>15</v>
       </c>
       <c r="AA40">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB40">
         <v>9.199999999999999</v>
@@ -10559,16 +10559,16 @@
         <v>14</v>
       </c>
       <c r="AE40">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AF40">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG40">
         <v>17.5</v>
       </c>
       <c r="AH40">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI40">
         <v>1000</v>
@@ -10577,7 +10577,7 @@
         <v>1000</v>
       </c>
       <c r="AK40">
-        <v>75</v>
+        <v>730</v>
       </c>
       <c r="AL40">
         <v>1000</v>
@@ -10589,10 +10589,10 @@
         <v>1000</v>
       </c>
       <c r="AO40">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP40">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ40">
         <v>6.6</v>
@@ -10604,22 +10604,22 @@
         <v>23</v>
       </c>
       <c r="AT40">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU40">
         <v>6.4</v>
       </c>
       <c r="AV40">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW40">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX40">
         <v>19.5</v>
       </c>
       <c r="AY40">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ40">
         <v>21</v>
@@ -10631,7 +10631,7 @@
         <v>32</v>
       </c>
       <c r="BC40">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD40">
         <v>38</v>
@@ -10640,7 +10640,7 @@
         <v>48</v>
       </c>
       <c r="BF40">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG40">
         <v>25</v>
@@ -10738,7 +10738,7 @@
         <v>3.25</v>
       </c>
       <c r="J41">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K41">
         <v>3.3</v>
@@ -10771,7 +10771,7 @@
         <v>2.02</v>
       </c>
       <c r="U41">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V41">
         <v>1.01</v>
@@ -10780,22 +10780,22 @@
         <v>1.01</v>
       </c>
       <c r="X41">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y41">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z41">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AA41">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB41">
         <v>9</v>
       </c>
       <c r="AC41">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD41">
         <v>14.5</v>
@@ -10810,7 +10810,7 @@
         <v>14</v>
       </c>
       <c r="AH41">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI41">
         <v>85</v>
@@ -10843,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="AS41">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AT41">
         <v>7.4</v>
@@ -10855,7 +10855,7 @@
         <v>12</v>
       </c>
       <c r="AW41">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="AX41">
         <v>15</v>
@@ -10867,25 +10867,25 @@
         <v>18</v>
       </c>
       <c r="BA41">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB41">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BC41">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BD41">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE41">
+        <v>10</v>
+      </c>
+      <c r="BF41">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF41">
-        <v>7.8</v>
-      </c>
       <c r="BG41">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10980,10 +10980,10 @@
         <v>6.6</v>
       </c>
       <c r="J42">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K42">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L42">
         <v>1.42</v>
@@ -10998,7 +10998,7 @@
         <v>1.42</v>
       </c>
       <c r="P42">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="Q42">
         <v>2.24</v>
@@ -11061,7 +11061,7 @@
         <v>22</v>
       </c>
       <c r="AK42">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL42">
         <v>55</v>
@@ -11070,7 +11070,7 @@
         <v>200</v>
       </c>
       <c r="AN42">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO42">
         <v>180</v>
@@ -11082,10 +11082,10 @@
         <v>12.5</v>
       </c>
       <c r="AR42">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS42">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT42">
         <v>5.5</v>
@@ -11097,7 +11097,7 @@
         <v>18</v>
       </c>
       <c r="AW42">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX42">
         <v>7.6</v>
@@ -11109,7 +11109,7 @@
         <v>20</v>
       </c>
       <c r="BA42">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB42">
         <v>14.5</v>
@@ -11118,16 +11118,16 @@
         <v>16.5</v>
       </c>
       <c r="BD42">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE42">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF42">
         <v>11.5</v>
       </c>
       <c r="BG42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH42">
         <v>3.4</v>
@@ -11210,46 +11210,46 @@
         <v>221</v>
       </c>
       <c r="F43">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="G43">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="H43">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="I43">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="J43">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="K43">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L43">
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N43">
-        <v>1.24</v>
+        <v>2.66</v>
       </c>
       <c r="O43">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P43">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q43">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R43">
         <v>1.18</v>
       </c>
       <c r="S43">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="T43">
         <v>1.01</v>
@@ -11258,10 +11258,10 @@
         <v>1.01</v>
       </c>
       <c r="V43">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W43">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -11318,52 +11318,52 @@
         <v>1000</v>
       </c>
       <c r="AP43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF43">
         <v>1.01</v>
@@ -11470,13 +11470,13 @@
         <v>5.3</v>
       </c>
       <c r="L44">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M44">
         <v>1.06</v>
       </c>
       <c r="N44">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O44">
         <v>1.29</v>
@@ -11488,7 +11488,7 @@
         <v>1.81</v>
       </c>
       <c r="R44">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S44">
         <v>3.1</v>
@@ -11497,13 +11497,13 @@
         <v>1.85</v>
       </c>
       <c r="U44">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="V44">
         <v>1.14</v>
       </c>
       <c r="W44">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X44">
         <v>20</v>
@@ -11614,64 +11614,64 @@
         <v>4.2</v>
       </c>
       <c r="BH44">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI44">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="BJ44">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK44">
-        <v>1.31</v>
+        <v>3.5</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>1.31</v>
+        <v>4.7</v>
       </c>
       <c r="BN44">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO44">
-        <v>1.31</v>
+        <v>3.25</v>
       </c>
       <c r="BP44">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ44">
-        <v>1.31</v>
+        <v>3.5</v>
       </c>
       <c r="BR44">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS44">
-        <v>1.31</v>
+        <v>4.2</v>
       </c>
       <c r="BT44">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU44">
-        <v>1.31</v>
+        <v>3.4</v>
       </c>
       <c r="BV44">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW44">
-        <v>1.31</v>
+        <v>4.5</v>
       </c>
       <c r="BX44">
         <v>1000</v>
       </c>
       <c r="BY44">
-        <v>1.31</v>
+        <v>4.5</v>
       </c>
       <c r="BZ44">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA44">
-        <v>1.31</v>
+        <v>4</v>
       </c>
       <c r="CB44" t="s">
         <v>226</v>
@@ -11700,16 +11700,16 @@
         <v>3.55</v>
       </c>
       <c r="H45">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I45">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="J45">
         <v>3.35</v>
       </c>
       <c r="K45">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -11733,16 +11733,16 @@
         <v>1.37</v>
       </c>
       <c r="S45">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="T45">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="U45">
         <v>2.2</v>
       </c>
       <c r="V45">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W45">
         <v>1.39</v>
@@ -11948,13 +11948,13 @@
         <v>3.2</v>
       </c>
       <c r="J46">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K46">
         <v>3.55</v>
       </c>
       <c r="L46">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M46">
         <v>1.08</v>
@@ -12098,64 +12098,64 @@
         <v>6.8</v>
       </c>
       <c r="BH46">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI46">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ46">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK46">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL46">
         <v>1000</v>
       </c>
       <c r="BM46">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN46">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO46">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP46">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ46">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR46">
         <v>1000</v>
       </c>
       <c r="BS46">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT46">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU46">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV46">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW46">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX46">
         <v>1000</v>
       </c>
       <c r="BY46">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ46">
         <v>1000</v>
       </c>
       <c r="CA46">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB46" t="s">
         <v>226</v>
@@ -12178,37 +12178,37 @@
         <v>225</v>
       </c>
       <c r="F47">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G47">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="I47">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J47">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="K47">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="L47">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M47">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N47">
-        <v>1.26</v>
+        <v>2.24</v>
       </c>
       <c r="O47">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="P47">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="Q47">
         <v>2.52</v>
@@ -12217,187 +12217,187 @@
         <v>1.2</v>
       </c>
       <c r="S47">
+        <v>3.95</v>
+      </c>
+      <c r="T47">
+        <v>2.08</v>
+      </c>
+      <c r="U47">
+        <v>1.63</v>
+      </c>
+      <c r="V47">
+        <v>1.4</v>
+      </c>
+      <c r="W47">
+        <v>1.5</v>
+      </c>
+      <c r="X47">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y47">
+        <v>11</v>
+      </c>
+      <c r="Z47">
+        <v>24</v>
+      </c>
+      <c r="AA47">
+        <v>80</v>
+      </c>
+      <c r="AB47">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC47">
+        <v>8.4</v>
+      </c>
+      <c r="AD47">
+        <v>18</v>
+      </c>
+      <c r="AE47">
+        <v>65</v>
+      </c>
+      <c r="AF47">
+        <v>21</v>
+      </c>
+      <c r="AG47">
+        <v>16.5</v>
+      </c>
+      <c r="AH47">
+        <v>29</v>
+      </c>
+      <c r="AI47">
+        <v>95</v>
+      </c>
+      <c r="AJ47">
+        <v>60</v>
+      </c>
+      <c r="AK47">
+        <v>55</v>
+      </c>
+      <c r="AL47">
+        <v>90</v>
+      </c>
+      <c r="AM47">
+        <v>240</v>
+      </c>
+      <c r="AN47">
+        <v>65</v>
+      </c>
+      <c r="AO47">
+        <v>80</v>
+      </c>
+      <c r="AP47">
         <v>3</v>
       </c>
-      <c r="T47">
-        <v>1.01</v>
-      </c>
-      <c r="U47">
-        <v>1.01</v>
-      </c>
-      <c r="V47">
-        <v>1.41</v>
-      </c>
-      <c r="W47">
-        <v>1.47</v>
-      </c>
-      <c r="X47">
-        <v>1000</v>
-      </c>
-      <c r="Y47">
-        <v>1000</v>
-      </c>
-      <c r="Z47">
-        <v>1000</v>
-      </c>
-      <c r="AA47">
-        <v>1000</v>
-      </c>
-      <c r="AB47">
-        <v>1000</v>
-      </c>
-      <c r="AC47">
-        <v>1000</v>
-      </c>
-      <c r="AD47">
-        <v>1000</v>
-      </c>
-      <c r="AE47">
-        <v>1000</v>
-      </c>
-      <c r="AF47">
-        <v>1000</v>
-      </c>
-      <c r="AG47">
-        <v>1000</v>
-      </c>
-      <c r="AH47">
-        <v>1000</v>
-      </c>
-      <c r="AI47">
-        <v>1000</v>
-      </c>
-      <c r="AJ47">
-        <v>1000</v>
-      </c>
-      <c r="AK47">
-        <v>1000</v>
-      </c>
-      <c r="AL47">
-        <v>1000</v>
-      </c>
-      <c r="AM47">
-        <v>1000</v>
-      </c>
-      <c r="AN47">
-        <v>1000</v>
-      </c>
-      <c r="AO47">
-        <v>1000</v>
-      </c>
-      <c r="AP47">
-        <v>1.03</v>
-      </c>
       <c r="AQ47">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AR47">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AS47">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT47">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AU47">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AV47">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW47">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX47">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY47">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AZ47">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BA47">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB47">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC47">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD47">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE47">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF47">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG47">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH47">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI47">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ47">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK47">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BL47">
         <v>1000</v>
       </c>
       <c r="BM47">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BN47">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO47">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BP47">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ47">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR47">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS47">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BT47">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU47">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BV47">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW47">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX47">
         <v>1000</v>
       </c>
       <c r="BY47">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ47">
         <v>1000</v>
       </c>
       <c r="CA47">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="CB47" t="s">
         <v>226</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -688,7 +688,7 @@
     <t>Real Soacha Cundinamarca FC</t>
   </si>
   <si>
-    <t>2026-08-09 17:07:04</t>
+    <t>2026-08-09 19:17:25</t>
   </si>
 </sst>
 </file>
@@ -1282,13 +1282,13 @@
         <v>179</v>
       </c>
       <c r="F2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>6.2</v>
@@ -1312,19 +1312,19 @@
         <v>1.29</v>
       </c>
       <c r="P2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q2">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U2">
         <v>2.04</v>
@@ -1333,7 +1333,7 @@
         <v>1.19</v>
       </c>
       <c r="W2">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X2">
         <v>16.5</v>
@@ -1345,7 +1345,7 @@
         <v>48</v>
       </c>
       <c r="AA2">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB2">
         <v>8.800000000000001</v>
@@ -1354,28 +1354,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH2">
         <v>21</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
         <v>16.5</v>
       </c>
       <c r="AK2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL2">
         <v>36</v>
@@ -1384,22 +1384,22 @@
         <v>120</v>
       </c>
       <c r="AN2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AT2">
         <v>8</v>
@@ -1426,7 +1426,7 @@
         <v>65</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC2">
         <v>15.5</v>
@@ -1438,70 +1438,70 @@
         <v>85</v>
       </c>
       <c r="BF2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH2">
         <v>3.7</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BL2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
         <v>4.4</v>
       </c>
       <c r="BO2">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BP2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ2">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="BR2">
         <v>26</v>
       </c>
       <c r="BS2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT2">
         <v>9.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BV2">
         <v>55</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="s">
         <v>224</v>
@@ -1524,16 +1524,16 @@
         <v>180</v>
       </c>
       <c r="F3">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G3">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J3">
         <v>3.25</v>
@@ -1545,19 +1545,19 @@
         <v>1.49</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P3">
         <v>1.72</v>
       </c>
       <c r="Q3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R3">
         <v>1.27</v>
@@ -1566,16 +1566,16 @@
         <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="U3">
         <v>1.98</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X3">
         <v>13.5</v>
@@ -1587,7 +1587,7 @@
         <v>27</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB3">
         <v>9.4</v>
@@ -1611,7 +1611,7 @@
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ3">
         <v>40</v>
@@ -1626,10 +1626,10 @@
         <v>160</v>
       </c>
       <c r="AN3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP3">
         <v>9.800000000000001</v>
@@ -1641,7 +1641,7 @@
         <v>20</v>
       </c>
       <c r="AS3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
@@ -1653,7 +1653,7 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
@@ -1665,10 +1665,10 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC3">
         <v>22</v>
@@ -1677,22 +1677,22 @@
         <v>34</v>
       </c>
       <c r="BE3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF3">
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH3">
         <v>3.3</v>
       </c>
       <c r="BI3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
         <v>7.8</v>
@@ -1701,28 +1701,28 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BN3">
         <v>5.2</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
         <v>22</v>
       </c>
       <c r="BQ3">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BT3">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU3">
         <v>5.7</v>
@@ -1731,13 +1731,13 @@
         <v>36</v>
       </c>
       <c r="BW3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BX3">
         <v>55</v>
       </c>
       <c r="BY3">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1766,22 +1766,22 @@
         <v>181</v>
       </c>
       <c r="F4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G4">
         <v>3.3</v>
       </c>
       <c r="H4">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I4">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J4">
         <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L4">
         <v>1.59</v>
@@ -1790,28 +1790,28 @@
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q4">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R4">
         <v>1.2</v>
       </c>
       <c r="S4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U4">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V4">
         <v>1.58</v>
@@ -1820,25 +1820,25 @@
         <v>1.43</v>
       </c>
       <c r="X4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y4">
         <v>9</v>
       </c>
       <c r="Z4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA4">
         <v>50</v>
       </c>
       <c r="AB4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
         <v>48</v>
@@ -1847,28 +1847,28 @@
         <v>23</v>
       </c>
       <c r="AG4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK4">
         <v>65</v>
       </c>
       <c r="AL4">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM4">
         <v>210</v>
       </c>
       <c r="AN4">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AO4">
         <v>55</v>
@@ -1877,7 +1877,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR4">
         <v>13.5</v>
@@ -1886,7 +1886,7 @@
         <v>32</v>
       </c>
       <c r="AT4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU4">
         <v>6.2</v>
@@ -1895,10 +1895,10 @@
         <v>11</v>
       </c>
       <c r="AW4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AX4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY4">
         <v>12.5</v>
@@ -1910,7 +1910,7 @@
         <v>48</v>
       </c>
       <c r="BB4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BC4">
         <v>34</v>
@@ -1919,7 +1919,7 @@
         <v>50</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF4">
         <v>50</v>
@@ -1928,10 +1928,10 @@
         <v>30</v>
       </c>
       <c r="BH4">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BI4">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
@@ -1946,13 +1946,13 @@
         <v>14</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ4">
         <v>10</v>
@@ -1967,19 +1967,19 @@
         <v>5.4</v>
       </c>
       <c r="BU4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
         <v>55</v>
@@ -2008,16 +2008,16 @@
         <v>182</v>
       </c>
       <c r="F5">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G5">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J5">
         <v>3.15</v>
@@ -2035,13 +2035,13 @@
         <v>3.3</v>
       </c>
       <c r="O5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R5">
         <v>1.28</v>
@@ -2050,16 +2050,16 @@
         <v>4.3</v>
       </c>
       <c r="T5">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W5">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X5">
         <v>11</v>
@@ -2086,7 +2086,7 @@
         <v>42</v>
       </c>
       <c r="AF5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG5">
         <v>12</v>
@@ -2122,13 +2122,13 @@
         <v>10</v>
       </c>
       <c r="AR5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS5">
         <v>50</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
@@ -2167,19 +2167,19 @@
         <v>25</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BH5">
         <v>3.4</v>
       </c>
       <c r="BI5">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="BJ5">
         <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2191,7 +2191,7 @@
         <v>5.9</v>
       </c>
       <c r="BO5">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP5">
         <v>23</v>
@@ -2209,7 +2209,7 @@
         <v>7</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
         <v>32</v>
@@ -2253,16 +2253,16 @@
         <v>1.67</v>
       </c>
       <c r="G6">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H6">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="I6">
         <v>25</v>
       </c>
       <c r="J6">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2274,22 +2274,22 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="O6">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="Q6">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="R6">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="S6">
-        <v>2.54</v>
+        <v>1.78</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2301,7 +2301,7 @@
         <v>1.04</v>
       </c>
       <c r="W6">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2492,19 +2492,19 @@
         <v>184</v>
       </c>
       <c r="F7">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H7">
         <v>4.3</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
         <v>3.55</v>
@@ -2516,13 +2516,13 @@
         <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="O7">
         <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q7">
         <v>2.34</v>
@@ -2543,25 +2543,25 @@
         <v>1.25</v>
       </c>
       <c r="W7">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X7">
         <v>12</v>
       </c>
       <c r="Y7">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA7">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB7">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD7">
         <v>22</v>
@@ -2585,13 +2585,13 @@
         <v>30</v>
       </c>
       <c r="AK7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL7">
         <v>60</v>
       </c>
       <c r="AM7">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN7">
         <v>25</v>
@@ -2606,22 +2606,22 @@
         <v>10</v>
       </c>
       <c r="AR7">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AS7">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT7">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX7">
         <v>8.800000000000001</v>
@@ -2630,10 +2630,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ7">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB7">
         <v>19</v>
@@ -2642,16 +2642,16 @@
         <v>19.5</v>
       </c>
       <c r="BD7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE7">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF7">
         <v>16.5</v>
       </c>
       <c r="BG7">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2663,16 +2663,16 @@
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO7">
         <v>3.65</v>
@@ -2681,37 +2681,37 @@
         <v>18.5</v>
       </c>
       <c r="BQ7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR7">
         <v>42</v>
       </c>
       <c r="BS7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT7">
         <v>8.800000000000001</v>
       </c>
       <c r="BU7">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="BV7">
         <v>50</v>
       </c>
       <c r="BW7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX7">
         <v>70</v>
       </c>
       <c r="BY7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ7">
         <v>42</v>
       </c>
       <c r="CA7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB7" t="s">
         <v>224</v>
@@ -2737,7 +2737,7 @@
         <v>1.98</v>
       </c>
       <c r="G8">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H8">
         <v>3.65</v>
@@ -2746,7 +2746,7 @@
         <v>4.2</v>
       </c>
       <c r="J8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K8">
         <v>4.1</v>
@@ -2776,7 +2776,7 @@
         <v>2.88</v>
       </c>
       <c r="T8">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U8">
         <v>2.22</v>
@@ -2785,10 +2785,10 @@
         <v>1.32</v>
       </c>
       <c r="W8">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y8">
         <v>17.5</v>
@@ -2797,7 +2797,7 @@
         <v>34</v>
       </c>
       <c r="AA8">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB8">
         <v>11.5</v>
@@ -2821,7 +2821,7 @@
         <v>18</v>
       </c>
       <c r="AI8">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ8">
         <v>26</v>
@@ -2833,7 +2833,7 @@
         <v>38</v>
       </c>
       <c r="AM8">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN8">
         <v>13</v>
@@ -2851,7 +2851,7 @@
         <v>23</v>
       </c>
       <c r="AS8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT8">
         <v>8.4</v>
@@ -2863,7 +2863,7 @@
         <v>12</v>
       </c>
       <c r="AW8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX8">
         <v>10.5</v>
@@ -2884,16 +2884,16 @@
         <v>15.5</v>
       </c>
       <c r="BD8">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="BE8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF8">
         <v>9.6</v>
       </c>
       <c r="BG8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH8">
         <v>3.9</v>
@@ -2911,7 +2911,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8">
         <v>5.2</v>
@@ -2929,7 +2929,7 @@
         <v>27</v>
       </c>
       <c r="BS8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT8">
         <v>7.6</v>
@@ -2938,7 +2938,7 @@
         <v>4.9</v>
       </c>
       <c r="BV8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
         <v>7.6</v>
@@ -2947,7 +2947,7 @@
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2979,46 +2979,46 @@
         <v>3.05</v>
       </c>
       <c r="G9">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H9">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I9">
         <v>2.98</v>
       </c>
       <c r="J9">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="O9">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="P9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q9">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U9">
         <v>1.72</v>
@@ -3027,13 +3027,13 @@
         <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>17.5</v>
@@ -3042,7 +3042,7 @@
         <v>60</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9">
         <v>7.2</v>
@@ -3054,7 +3054,7 @@
         <v>50</v>
       </c>
       <c r="AF9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG9">
         <v>16</v>
@@ -3066,7 +3066,7 @@
         <v>85</v>
       </c>
       <c r="AJ9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK9">
         <v>65</v>
@@ -3075,7 +3075,7 @@
         <v>95</v>
       </c>
       <c r="AM9">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN9">
         <v>85</v>
@@ -3084,7 +3084,7 @@
         <v>65</v>
       </c>
       <c r="AP9">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9">
         <v>6</v>
@@ -3093,19 +3093,19 @@
         <v>12.5</v>
       </c>
       <c r="AS9">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AT9">
         <v>7.6</v>
       </c>
       <c r="AU9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV9">
         <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AX9">
         <v>15.5</v>
@@ -3117,37 +3117,37 @@
         <v>20</v>
       </c>
       <c r="BA9">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB9">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BC9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD9">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE9">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF9">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH9">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI9">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ9">
         <v>13.5</v>
       </c>
       <c r="BK9">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -3156,13 +3156,13 @@
         <v>7.2</v>
       </c>
       <c r="BN9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ9">
         <v>6.2</v>
@@ -3174,25 +3174,25 @@
         <v>6.6</v>
       </c>
       <c r="BT9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX9">
         <v>60</v>
       </c>
       <c r="BY9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="CA9">
         <v>6.6</v>
@@ -3260,31 +3260,31 @@
         <v>2.92</v>
       </c>
       <c r="T10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U10">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
         <v>1.65</v>
       </c>
       <c r="X10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y10">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z10">
         <v>25</v>
       </c>
       <c r="AA10">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AB10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC10">
         <v>9.199999999999999</v>
@@ -3293,13 +3293,13 @@
         <v>14.5</v>
       </c>
       <c r="AE10">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AF10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10">
         <v>19</v>
@@ -3311,73 +3311,73 @@
         <v>34</v>
       </c>
       <c r="AK10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL10">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AM10">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AN10">
         <v>17</v>
       </c>
       <c r="AO10">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AP10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ10">
+        <v>10.5</v>
+      </c>
+      <c r="AR10">
+        <v>17</v>
+      </c>
+      <c r="AS10">
+        <v>7</v>
+      </c>
+      <c r="AT10">
+        <v>9</v>
+      </c>
+      <c r="AU10">
+        <v>7.4</v>
+      </c>
+      <c r="AV10">
         <v>10</v>
       </c>
-      <c r="AR10">
+      <c r="AW10">
+        <v>16</v>
+      </c>
+      <c r="AX10">
+        <v>12</v>
+      </c>
+      <c r="AY10">
+        <v>8.4</v>
+      </c>
+      <c r="AZ10">
+        <v>11.5</v>
+      </c>
+      <c r="BA10">
+        <v>6.8</v>
+      </c>
+      <c r="BB10">
         <v>14.5</v>
       </c>
-      <c r="AS10">
-        <v>1.01</v>
-      </c>
-      <c r="AT10">
-        <v>10</v>
-      </c>
-      <c r="AU10">
-        <v>6.6</v>
-      </c>
-      <c r="AV10">
-        <v>11.5</v>
-      </c>
-      <c r="AW10">
+      <c r="BC10">
+        <v>17</v>
+      </c>
+      <c r="BD10">
         <v>20</v>
       </c>
-      <c r="AX10">
-        <v>14.5</v>
-      </c>
-      <c r="AY10">
-        <v>9</v>
-      </c>
-      <c r="AZ10">
-        <v>11</v>
-      </c>
-      <c r="BA10">
-        <v>25</v>
-      </c>
-      <c r="BB10">
-        <v>1.01</v>
-      </c>
-      <c r="BC10">
+      <c r="BE10">
+        <v>7.4</v>
+      </c>
+      <c r="BF10">
+        <v>12</v>
+      </c>
+      <c r="BG10">
         <v>19.5</v>
-      </c>
-      <c r="BD10">
-        <v>1.03</v>
-      </c>
-      <c r="BE10">
-        <v>1.01</v>
-      </c>
-      <c r="BF10">
-        <v>14</v>
-      </c>
-      <c r="BG10">
-        <v>15</v>
       </c>
       <c r="BH10">
         <v>3.85</v>
@@ -3460,13 +3460,13 @@
         <v>188</v>
       </c>
       <c r="F11">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H11">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I11">
         <v>3.85</v>
@@ -3484,40 +3484,40 @@
         <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O11">
         <v>1.35</v>
       </c>
       <c r="P11">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q11">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R11">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T11">
         <v>1.81</v>
       </c>
       <c r="U11">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V11">
         <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X11">
         <v>13.5</v>
       </c>
       <c r="Y11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z11">
         <v>26</v>
@@ -3538,10 +3538,10 @@
         <v>55</v>
       </c>
       <c r="AF11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH11">
         <v>19.5</v>
@@ -3550,19 +3550,19 @@
         <v>65</v>
       </c>
       <c r="AJ11">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AK11">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AL11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM11">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO11">
         <v>55</v>
@@ -3577,7 +3577,7 @@
         <v>20</v>
       </c>
       <c r="AS11">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT11">
         <v>8</v>
@@ -3601,67 +3601,67 @@
         <v>15.5</v>
       </c>
       <c r="BA11">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB11">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC11">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BD11">
         <v>34</v>
       </c>
       <c r="BE11">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11">
         <v>15.5</v>
       </c>
       <c r="BG11">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BH11">
         <v>3.8</v>
       </c>
       <c r="BI11">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11">
         <v>12</v>
       </c>
       <c r="BK11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BN11">
         <v>6</v>
       </c>
       <c r="BO11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP11">
         <v>21</v>
       </c>
       <c r="BQ11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BR11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT11">
         <v>8</v>
       </c>
       <c r="BU11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV11">
         <v>36</v>
@@ -3670,10 +3670,10 @@
         <v>4.2</v>
       </c>
       <c r="BX11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BZ11">
         <v>36</v>
@@ -3702,22 +3702,22 @@
         <v>189</v>
       </c>
       <c r="F12">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G12">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H12">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J12">
         <v>4.1</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
         <v>1.29</v>
@@ -3753,7 +3753,7 @@
         <v>1.23</v>
       </c>
       <c r="W12">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X12">
         <v>22</v>
@@ -3816,7 +3816,7 @@
         <v>5.8</v>
       </c>
       <c r="AR12">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS12">
         <v>7.4</v>
@@ -3852,7 +3852,7 @@
         <v>14.5</v>
       </c>
       <c r="BD12">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BE12">
         <v>7.2</v>
@@ -3861,7 +3861,7 @@
         <v>4.5</v>
       </c>
       <c r="BG12">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH12">
         <v>4.1</v>
@@ -3968,7 +3968,7 @@
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O13">
         <v>1.24</v>
@@ -3998,13 +3998,13 @@
         <v>3.7</v>
       </c>
       <c r="X13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y13">
         <v>42</v>
       </c>
       <c r="Z13">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="AA13">
         <v>1000</v>
@@ -4013,10 +4013,10 @@
         <v>8.4</v>
       </c>
       <c r="AC13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD13">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AE13">
         <v>370</v>
@@ -4025,19 +4025,19 @@
         <v>7.8</v>
       </c>
       <c r="AG13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH13">
         <v>40</v>
       </c>
       <c r="AI13">
-        <v>270</v>
+        <v>470</v>
       </c>
       <c r="AJ13">
         <v>10</v>
       </c>
       <c r="AK13">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AL13">
         <v>55</v>
@@ -4052,58 +4052,58 @@
         <v>620</v>
       </c>
       <c r="AP13">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AQ13">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS13">
+        <v>8.6</v>
+      </c>
+      <c r="AT13">
+        <v>4.4</v>
+      </c>
+      <c r="AU13">
+        <v>6.4</v>
+      </c>
+      <c r="AV13">
+        <v>7.6</v>
+      </c>
+      <c r="AW13">
+        <v>8.4</v>
+      </c>
+      <c r="AX13">
+        <v>4.4</v>
+      </c>
+      <c r="AY13">
         <v>7</v>
       </c>
-      <c r="AS13">
-        <v>7.2</v>
-      </c>
-      <c r="AT13">
-        <v>3.9</v>
-      </c>
-      <c r="AU13">
-        <v>4.9</v>
-      </c>
-      <c r="AV13">
-        <v>6.6</v>
-      </c>
-      <c r="AW13">
-        <v>7.2</v>
-      </c>
-      <c r="AX13">
-        <v>3.75</v>
-      </c>
-      <c r="AY13">
-        <v>4.7</v>
-      </c>
       <c r="AZ13">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BA13">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BB13">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BC13">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD13">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE13">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF13">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BG13">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH13">
         <v>4.1</v>
@@ -4186,7 +4186,7 @@
         <v>191</v>
       </c>
       <c r="F14">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G14">
         <v>2.06</v>
@@ -4195,7 +4195,7 @@
         <v>4.3</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J14">
         <v>3.5</v>
@@ -4222,7 +4222,7 @@
         <v>2.2</v>
       </c>
       <c r="R14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S14">
         <v>4.2</v>
@@ -4234,10 +4234,10 @@
         <v>1.86</v>
       </c>
       <c r="V14">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W14">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X14">
         <v>13</v>
@@ -4249,7 +4249,7 @@
         <v>40</v>
       </c>
       <c r="AA14">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AB14">
         <v>7.8</v>
@@ -4261,7 +4261,7 @@
         <v>22</v>
       </c>
       <c r="AE14">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AF14">
         <v>12</v>
@@ -4273,7 +4273,7 @@
         <v>23</v>
       </c>
       <c r="AI14">
-        <v>95</v>
+        <v>370</v>
       </c>
       <c r="AJ14">
         <v>29</v>
@@ -4285,13 +4285,13 @@
         <v>55</v>
       </c>
       <c r="AM14">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN14">
         <v>22</v>
       </c>
       <c r="AO14">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP14">
         <v>9.6</v>
@@ -4300,7 +4300,7 @@
         <v>10.5</v>
       </c>
       <c r="AR14">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AS14">
         <v>6.8</v>
@@ -4440,10 +4440,10 @@
         <v>2.82</v>
       </c>
       <c r="J15">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="K15">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L15">
         <v>1.47</v>
@@ -4461,7 +4461,7 @@
         <v>1.52</v>
       </c>
       <c r="Q15">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R15">
         <v>1.17</v>
@@ -4497,7 +4497,7 @@
         <v>11.5</v>
       </c>
       <c r="AC15">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD15">
         <v>15</v>
@@ -4515,19 +4515,19 @@
         <v>26</v>
       </c>
       <c r="AI15">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ15">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AK15">
         <v>55</v>
       </c>
       <c r="AL15">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM15">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN15">
         <v>85</v>
@@ -4536,58 +4536,58 @@
         <v>46</v>
       </c>
       <c r="AP15">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="AQ15">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="AR15">
+        <v>4.4</v>
+      </c>
+      <c r="AS15">
+        <v>5.1</v>
+      </c>
+      <c r="AT15">
+        <v>5.6</v>
+      </c>
+      <c r="AU15">
+        <v>4.4</v>
+      </c>
+      <c r="AV15">
         <v>4.1</v>
       </c>
-      <c r="AS15">
-        <v>4.7</v>
-      </c>
-      <c r="AT15">
-        <v>3.6</v>
-      </c>
-      <c r="AU15">
-        <v>3.25</v>
-      </c>
-      <c r="AV15">
-        <v>3.85</v>
-      </c>
       <c r="AW15">
+        <v>5</v>
+      </c>
+      <c r="AX15">
         <v>4.6</v>
       </c>
-      <c r="AX15">
-        <v>4.3</v>
-      </c>
       <c r="AY15">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AZ15">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BA15">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB15">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC15">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BD15">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE15">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF15">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BG15">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH15">
         <v>2.86</v>
@@ -4691,7 +4691,7 @@
         <v>1.22</v>
       </c>
       <c r="M16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
         <v>6.8</v>
@@ -4703,7 +4703,7 @@
         <v>2.96</v>
       </c>
       <c r="Q16">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R16">
         <v>1.8</v>
@@ -4712,10 +4712,10 @@
         <v>2.04</v>
       </c>
       <c r="T16">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U16">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V16">
         <v>1.03</v>
@@ -4727,22 +4727,22 @@
         <v>42</v>
       </c>
       <c r="Y16">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Z16">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AA16">
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC16">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AD16">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AE16">
         <v>550</v>
@@ -4754,7 +4754,7 @@
         <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AI16">
         <v>350</v>
@@ -4763,31 +4763,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AK16">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AL16">
-        <v>65</v>
+        <v>330</v>
       </c>
       <c r="AM16">
         <v>300</v>
       </c>
       <c r="AN16">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AQ16">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR16">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS16">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT16">
         <v>10</v>
@@ -4796,10 +4796,10 @@
         <v>18</v>
       </c>
       <c r="AV16">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW16">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16">
         <v>7.2</v>
@@ -4808,10 +4808,10 @@
         <v>11</v>
       </c>
       <c r="AZ16">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BA16">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16">
         <v>7</v>
@@ -4820,16 +4820,16 @@
         <v>11.5</v>
       </c>
       <c r="BD16">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE16">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16">
         <v>2.76</v>
       </c>
       <c r="BG16">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH16">
         <v>5.4</v>
@@ -4841,13 +4841,13 @@
         <v>16</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN16">
         <v>3.8</v>
@@ -4865,25 +4865,25 @@
         <v>24</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ16">
         <v>7</v>
@@ -4921,10 +4921,10 @@
         <v>1.88</v>
       </c>
       <c r="I17">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K17">
         <v>4.3</v>
@@ -4942,10 +4942,10 @@
         <v>1.2</v>
       </c>
       <c r="P17">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q17">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R17">
         <v>1.62</v>
@@ -4954,25 +4954,25 @@
         <v>2.5</v>
       </c>
       <c r="T17">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U17">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V17">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y17">
         <v>13</v>
       </c>
       <c r="Z17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA17">
         <v>22</v>
@@ -4984,13 +4984,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE17">
         <v>17.5</v>
       </c>
       <c r="AF17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG17">
         <v>17.5</v>
@@ -5029,49 +5029,49 @@
         <v>12.5</v>
       </c>
       <c r="AS17">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU17">
         <v>8.800000000000001</v>
       </c>
       <c r="AV17">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW17">
         <v>15.5</v>
       </c>
       <c r="AX17">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AY17">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BB17">
         <v>36</v>
       </c>
       <c r="BC17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE17">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BF17">
         <v>28</v>
       </c>
       <c r="BG17">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH17">
         <v>4.6</v>
@@ -5160,13 +5160,13 @@
         <v>1.38</v>
       </c>
       <c r="H18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J18">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K18">
         <v>6</v>
@@ -5175,7 +5175,7 @@
         <v>1.21</v>
       </c>
       <c r="M18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N18">
         <v>7.4</v>
@@ -5190,7 +5190,7 @@
         <v>1.42</v>
       </c>
       <c r="R18">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S18">
         <v>2.04</v>
@@ -5199,16 +5199,16 @@
         <v>1.71</v>
       </c>
       <c r="U18">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V18">
         <v>1.1</v>
       </c>
       <c r="W18">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="X18">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Y18">
         <v>55</v>
@@ -5220,10 +5220,10 @@
         <v>340</v>
       </c>
       <c r="AB18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD18">
         <v>38</v>
@@ -5241,22 +5241,22 @@
         <v>22</v>
       </c>
       <c r="AI18">
-        <v>90</v>
+        <v>380</v>
       </c>
       <c r="AJ18">
+        <v>12.5</v>
+      </c>
+      <c r="AK18">
         <v>13</v>
       </c>
-      <c r="AK18">
-        <v>13.5</v>
-      </c>
       <c r="AL18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN18">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AO18">
         <v>1000</v>
@@ -5265,25 +5265,25 @@
         <v>30</v>
       </c>
       <c r="AQ18">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AR18">
         <v>38</v>
       </c>
       <c r="AS18">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT18">
         <v>12.5</v>
       </c>
       <c r="AU18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV18">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AW18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX18">
         <v>10</v>
@@ -5295,28 +5295,28 @@
         <v>19</v>
       </c>
       <c r="BA18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC18">
         <v>12</v>
       </c>
       <c r="BD18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE18">
         <v>34</v>
       </c>
       <c r="BF18">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BG18">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH18">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI18">
         <v>4.3</v>
@@ -5331,7 +5331,7 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN18">
         <v>4.6</v>
@@ -5349,10 +5349,10 @@
         <v>18.5</v>
       </c>
       <c r="BS18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BU18">
         <v>9.800000000000001</v>
@@ -5361,13 +5361,13 @@
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX18">
         <v>55</v>
       </c>
       <c r="BY18">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18">
         <v>8.800000000000001</v>
@@ -5414,7 +5414,7 @@
         <v>3.65</v>
       </c>
       <c r="L19">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M19">
         <v>1.08</v>
@@ -5426,13 +5426,13 @@
         <v>1.36</v>
       </c>
       <c r="P19">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q19">
         <v>2.04</v>
       </c>
       <c r="R19">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S19">
         <v>3.7</v>
@@ -5441,7 +5441,7 @@
         <v>1.79</v>
       </c>
       <c r="U19">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V19">
         <v>1.44</v>
@@ -5495,7 +5495,7 @@
         <v>55</v>
       </c>
       <c r="AM19">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN19">
         <v>32</v>
@@ -5504,7 +5504,7 @@
         <v>44</v>
       </c>
       <c r="AP19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19">
         <v>8.4</v>
@@ -5513,7 +5513,7 @@
         <v>15</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT19">
         <v>7.6</v>
@@ -5525,7 +5525,7 @@
         <v>10</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX19">
         <v>12</v>
@@ -5540,7 +5540,7 @@
         <v>34</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC19">
         <v>21</v>
@@ -5549,13 +5549,13 @@
         <v>30</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF19">
         <v>18.5</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH19">
         <v>3.3</v>
@@ -5567,7 +5567,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BL19">
         <v>1000</v>
@@ -5579,7 +5579,7 @@
         <v>5.6</v>
       </c>
       <c r="BO19">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP19">
         <v>1000</v>
@@ -5647,13 +5647,13 @@
         <v>3.1</v>
       </c>
       <c r="I20">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J20">
         <v>3.55</v>
       </c>
       <c r="K20">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L20">
         <v>1.32</v>
@@ -5662,16 +5662,16 @@
         <v>1.06</v>
       </c>
       <c r="N20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P20">
         <v>2.04</v>
       </c>
       <c r="Q20">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R20">
         <v>1.4</v>
@@ -5683,10 +5683,10 @@
         <v>1.67</v>
       </c>
       <c r="U20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W20">
         <v>1.67</v>
@@ -5695,13 +5695,13 @@
         <v>21</v>
       </c>
       <c r="Y20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z20">
         <v>28</v>
       </c>
       <c r="AA20">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB20">
         <v>12.5</v>
@@ -5785,13 +5785,13 @@
         <v>18.5</v>
       </c>
       <c r="BC20">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD20">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BE20">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF20">
         <v>12.5</v>
@@ -5880,16 +5880,16 @@
         <v>198</v>
       </c>
       <c r="F21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G21">
         <v>3.7</v>
       </c>
       <c r="H21">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I21">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="J21">
         <v>3.55</v>
@@ -5898,7 +5898,7 @@
         <v>3.9</v>
       </c>
       <c r="L21">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M21">
         <v>1.06</v>
@@ -5910,25 +5910,25 @@
         <v>1.26</v>
       </c>
       <c r="P21">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q21">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R21">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S21">
         <v>2.96</v>
       </c>
       <c r="T21">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U21">
         <v>2.28</v>
       </c>
       <c r="V21">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W21">
         <v>1.37</v>
@@ -5973,7 +5973,7 @@
         <v>70</v>
       </c>
       <c r="AK21">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL21">
         <v>50</v>
@@ -5985,61 +5985,61 @@
         <v>34</v>
       </c>
       <c r="AO21">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP21">
+        <v>14.5</v>
+      </c>
+      <c r="AQ21">
+        <v>9.6</v>
+      </c>
+      <c r="AR21">
         <v>13</v>
       </c>
-      <c r="AQ21">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR21">
-        <v>12</v>
-      </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AT21">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU21">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV21">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW21">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AX21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY21">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ21">
+        <v>13.5</v>
+      </c>
+      <c r="BA21">
+        <v>16</v>
+      </c>
+      <c r="BB21">
+        <v>6.2</v>
+      </c>
+      <c r="BC21">
+        <v>5.9</v>
+      </c>
+      <c r="BD21">
+        <v>6</v>
+      </c>
+      <c r="BE21">
+        <v>6.4</v>
+      </c>
+      <c r="BF21">
+        <v>5.7</v>
+      </c>
+      <c r="BG21">
         <v>12.5</v>
-      </c>
-      <c r="BA21">
-        <v>1.03</v>
-      </c>
-      <c r="BB21">
-        <v>1.01</v>
-      </c>
-      <c r="BC21">
-        <v>1.01</v>
-      </c>
-      <c r="BD21">
-        <v>1.01</v>
-      </c>
-      <c r="BE21">
-        <v>1.01</v>
-      </c>
-      <c r="BF21">
-        <v>1.01</v>
-      </c>
-      <c r="BG21">
-        <v>12</v>
       </c>
       <c r="BH21">
         <v>4.2</v>
@@ -6057,16 +6057,16 @@
         <v>120</v>
       </c>
       <c r="BM21">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BN21">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO21">
         <v>5.3</v>
       </c>
       <c r="BP21">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BQ21">
         <v>4.7</v>
@@ -6078,16 +6078,16 @@
         <v>4.9</v>
       </c>
       <c r="BT21">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU21">
+        <v>4.5</v>
+      </c>
+      <c r="BV21">
+        <v>18</v>
+      </c>
+      <c r="BW21">
         <v>4.2</v>
-      </c>
-      <c r="BV21">
-        <v>18.5</v>
-      </c>
-      <c r="BW21">
-        <v>4.3</v>
       </c>
       <c r="BX21">
         <v>32</v>
@@ -6137,7 +6137,7 @@
         <v>4.1</v>
       </c>
       <c r="K22">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L22">
         <v>1.22</v>
@@ -6152,25 +6152,25 @@
         <v>1.13</v>
       </c>
       <c r="P22">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q22">
         <v>1.39</v>
       </c>
       <c r="R22">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S22">
         <v>1.96</v>
       </c>
       <c r="T22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U22">
         <v>3.1</v>
       </c>
       <c r="V22">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W22">
         <v>1.47</v>
@@ -6200,7 +6200,7 @@
         <v>28</v>
       </c>
       <c r="AF22">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AG22">
         <v>22</v>
@@ -6224,13 +6224,13 @@
         <v>48</v>
       </c>
       <c r="AN22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO22">
         <v>8.4</v>
       </c>
       <c r="AP22">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AQ22">
         <v>15.5</v>
@@ -6254,7 +6254,7 @@
         <v>14</v>
       </c>
       <c r="AX22">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY22">
         <v>11.5</v>
@@ -6266,7 +6266,7 @@
         <v>16</v>
       </c>
       <c r="BB22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC22">
         <v>20</v>
@@ -6275,10 +6275,10 @@
         <v>20</v>
       </c>
       <c r="BE22">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF22">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG22">
         <v>6.8</v>
@@ -6367,13 +6367,13 @@
         <v>2.68</v>
       </c>
       <c r="G23">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H23">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I23">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J23">
         <v>3.85</v>
@@ -6436,7 +6436,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE23">
         <v>24</v>
@@ -6445,7 +6445,7 @@
         <v>22</v>
       </c>
       <c r="AG23">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH23">
         <v>14</v>
@@ -6457,13 +6457,13 @@
         <v>38</v>
       </c>
       <c r="AK23">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL23">
         <v>29</v>
       </c>
       <c r="AM23">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AN23">
         <v>14</v>
@@ -6472,7 +6472,7 @@
         <v>13.5</v>
       </c>
       <c r="AP23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ23">
         <v>15.5</v>
@@ -6481,10 +6481,10 @@
         <v>19.5</v>
       </c>
       <c r="AS23">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT23">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU23">
         <v>8.6</v>
@@ -6505,7 +6505,7 @@
         <v>12.5</v>
       </c>
       <c r="BA23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB23">
         <v>34</v>
@@ -6514,28 +6514,28 @@
         <v>22</v>
       </c>
       <c r="BD23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE23">
         <v>42</v>
       </c>
       <c r="BF23">
+        <v>12.5</v>
+      </c>
+      <c r="BG23">
         <v>12</v>
-      </c>
-      <c r="BG23">
-        <v>10.5</v>
       </c>
       <c r="BH23">
         <v>4.6</v>
       </c>
       <c r="BI23">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ23">
         <v>8.4</v>
       </c>
       <c r="BK23">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL23">
         <v>70</v>
@@ -6553,13 +6553,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ23">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR23">
         <v>24</v>
       </c>
       <c r="BS23">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT23">
         <v>6.2</v>
@@ -6571,16 +6571,16 @@
         <v>17.5</v>
       </c>
       <c r="BW23">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX23">
         <v>24</v>
       </c>
       <c r="BY23">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ23">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA23">
         <v>7.6</v>
@@ -6669,7 +6669,7 @@
         <v>29</v>
       </c>
       <c r="AA24">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="AB24">
         <v>14</v>
@@ -6681,7 +6681,7 @@
         <v>14.5</v>
       </c>
       <c r="AE24">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AF24">
         <v>17.5</v>
@@ -6705,13 +6705,13 @@
         <v>42</v>
       </c>
       <c r="AM24">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AN24">
         <v>21</v>
       </c>
       <c r="AO24">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AP24">
         <v>12</v>
@@ -6723,7 +6723,7 @@
         <v>17</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT24">
         <v>8.4</v>
@@ -6735,7 +6735,7 @@
         <v>10</v>
       </c>
       <c r="AW24">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AX24">
         <v>12</v>
@@ -6747,19 +6747,19 @@
         <v>11.5</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB24">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC24">
         <v>18</v>
       </c>
       <c r="BD24">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF24">
         <v>12.5</v>
@@ -6777,7 +6777,7 @@
         <v>9.4</v>
       </c>
       <c r="BK24">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BL24">
         <v>1000</v>
@@ -6851,19 +6851,19 @@
         <v>2.08</v>
       </c>
       <c r="G25">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H25">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I25">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J25">
         <v>4</v>
       </c>
       <c r="K25">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L25">
         <v>1.21</v>
@@ -6896,7 +6896,7 @@
         <v>2.76</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W25">
         <v>1.79</v>
@@ -6911,7 +6911,7 @@
         <v>30</v>
       </c>
       <c r="AA25">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB25">
         <v>21</v>
@@ -6920,7 +6920,7 @@
         <v>11.5</v>
       </c>
       <c r="AD25">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE25">
         <v>32</v>
@@ -6935,7 +6935,7 @@
         <v>15.5</v>
       </c>
       <c r="AI25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ25">
         <v>34</v>
@@ -6956,7 +6956,7 @@
         <v>22</v>
       </c>
       <c r="AP25">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25">
         <v>18</v>
@@ -6965,7 +6965,7 @@
         <v>21</v>
       </c>
       <c r="AS25">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT25">
         <v>14</v>
@@ -6992,7 +6992,7 @@
         <v>23</v>
       </c>
       <c r="BB25">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BC25">
         <v>16</v>
@@ -7007,7 +7007,7 @@
         <v>7.6</v>
       </c>
       <c r="BG25">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH25">
         <v>5.1</v>
@@ -7049,7 +7049,7 @@
         <v>7.4</v>
       </c>
       <c r="BU25">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV25">
         <v>23</v>
@@ -7093,7 +7093,7 @@
         <v>3.45</v>
       </c>
       <c r="G26">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H26">
         <v>1.99</v>
@@ -7117,7 +7117,7 @@
         <v>5.6</v>
       </c>
       <c r="O26">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P26">
         <v>2.52</v>
@@ -7132,7 +7132,7 @@
         <v>2.3</v>
       </c>
       <c r="T26">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="U26">
         <v>2.52</v>
@@ -7159,7 +7159,7 @@
         <v>24</v>
       </c>
       <c r="AC26">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD26">
         <v>13</v>
@@ -7222,7 +7222,7 @@
         <v>14</v>
       </c>
       <c r="AX26">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AY26">
         <v>12</v>
@@ -7234,16 +7234,16 @@
         <v>20</v>
       </c>
       <c r="BB26">
+        <v>4.8</v>
+      </c>
+      <c r="BC26">
         <v>4.6</v>
       </c>
-      <c r="BC26">
-        <v>4.4</v>
-      </c>
       <c r="BD26">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE26">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF26">
         <v>18</v>
@@ -7252,22 +7252,22 @@
         <v>7.2</v>
       </c>
       <c r="BH26">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BI26">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ26">
         <v>9.800000000000001</v>
       </c>
       <c r="BK26">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BL26">
         <v>85</v>
       </c>
       <c r="BM26">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BN26">
         <v>8.4</v>
@@ -7279,13 +7279,13 @@
         <v>29</v>
       </c>
       <c r="BQ26">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BR26">
         <v>34</v>
       </c>
       <c r="BS26">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BT26">
         <v>6</v>
@@ -7297,19 +7297,19 @@
         <v>15</v>
       </c>
       <c r="BW26">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BX26">
         <v>25</v>
       </c>
       <c r="BY26">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BZ26">
         <v>17</v>
       </c>
       <c r="CA26">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="CB26" t="s">
         <v>224</v>
@@ -7332,10 +7332,10 @@
         <v>204</v>
       </c>
       <c r="F27">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G27">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H27">
         <v>6.4</v>
@@ -7362,10 +7362,10 @@
         <v>1.29</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q27">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R27">
         <v>1.39</v>
@@ -7389,28 +7389,28 @@
         <v>19.5</v>
       </c>
       <c r="Y27">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z27">
         <v>60</v>
       </c>
       <c r="AA27">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AB27">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27">
         <v>26</v>
       </c>
       <c r="AE27">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AF27">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG27">
         <v>10.5</v>
@@ -7431,7 +7431,7 @@
         <v>38</v>
       </c>
       <c r="AM27">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN27">
         <v>11</v>
@@ -7449,7 +7449,7 @@
         <v>38</v>
       </c>
       <c r="AS27">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT27">
         <v>7.2</v>
@@ -7461,7 +7461,7 @@
         <v>20</v>
       </c>
       <c r="AW27">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AX27">
         <v>8.199999999999999</v>
@@ -7473,7 +7473,7 @@
         <v>18.5</v>
       </c>
       <c r="BA27">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BB27">
         <v>11.5</v>
@@ -7482,16 +7482,16 @@
         <v>12.5</v>
       </c>
       <c r="BD27">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="BE27">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF27">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG27">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BH27">
         <v>3.75</v>
@@ -7503,7 +7503,7 @@
         <v>11</v>
       </c>
       <c r="BK27">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BL27">
         <v>1000</v>
@@ -7515,13 +7515,13 @@
         <v>4.3</v>
       </c>
       <c r="BO27">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BP27">
         <v>11</v>
       </c>
       <c r="BQ27">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BR27">
         <v>27</v>
@@ -7533,7 +7533,7 @@
         <v>10.5</v>
       </c>
       <c r="BU27">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BV27">
         <v>60</v>
@@ -7574,16 +7574,16 @@
         <v>205</v>
       </c>
       <c r="F28">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G28">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H28">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="I28">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="J28">
         <v>3.55</v>
@@ -7607,37 +7607,37 @@
         <v>1.87</v>
       </c>
       <c r="Q28">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R28">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S28">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T28">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U28">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V28">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="W28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X28">
         <v>16.5</v>
       </c>
       <c r="Y28">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z28">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AA28">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB28">
         <v>15</v>
@@ -7646,10 +7646,10 @@
         <v>8.6</v>
       </c>
       <c r="AD28">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE28">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AF28">
         <v>36</v>
@@ -7661,7 +7661,7 @@
         <v>23</v>
       </c>
       <c r="AI28">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ28">
         <v>110</v>
@@ -7673,16 +7673,16 @@
         <v>75</v>
       </c>
       <c r="AM28">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN28">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO28">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AP28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28">
         <v>6.8</v>
@@ -7715,31 +7715,31 @@
         <v>15.5</v>
       </c>
       <c r="BA28">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB28">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BC28">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BD28">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE28">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BG28">
         <v>12</v>
       </c>
       <c r="BH28">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI28">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ28">
         <v>10.5</v>
@@ -7754,46 +7754,46 @@
         <v>9.6</v>
       </c>
       <c r="BN28">
+        <v>7.8</v>
+      </c>
+      <c r="BO28">
+        <v>5.6</v>
+      </c>
+      <c r="BP28">
+        <v>38</v>
+      </c>
+      <c r="BQ28">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR28">
+        <v>48</v>
+      </c>
+      <c r="BS28">
+        <v>8.6</v>
+      </c>
+      <c r="BT28">
+        <v>4.9</v>
+      </c>
+      <c r="BU28">
+        <v>3.65</v>
+      </c>
+      <c r="BV28">
+        <v>15</v>
+      </c>
+      <c r="BW28">
+        <v>6</v>
+      </c>
+      <c r="BX28">
+        <v>30</v>
+      </c>
+      <c r="BY28">
         <v>7.6</v>
       </c>
-      <c r="BO28">
-        <v>5.5</v>
-      </c>
-      <c r="BP28">
-        <v>36</v>
-      </c>
-      <c r="BQ28">
-        <v>8</v>
-      </c>
-      <c r="BR28">
-        <v>46</v>
-      </c>
-      <c r="BS28">
-        <v>8.4</v>
-      </c>
-      <c r="BT28">
-        <v>5</v>
-      </c>
-      <c r="BU28">
-        <v>3.7</v>
-      </c>
-      <c r="BV28">
-        <v>15.5</v>
-      </c>
-      <c r="BW28">
-        <v>6.2</v>
-      </c>
-      <c r="BX28">
-        <v>32</v>
-      </c>
-      <c r="BY28">
-        <v>7.8</v>
-      </c>
       <c r="BZ28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA28">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB28" t="s">
         <v>224</v>
@@ -7819,7 +7819,7 @@
         <v>2.2</v>
       </c>
       <c r="G29">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H29">
         <v>3.25</v>
@@ -7855,7 +7855,7 @@
         <v>1.39</v>
       </c>
       <c r="S29">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T29">
         <v>1.67</v>
@@ -7867,7 +7867,7 @@
         <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X29">
         <v>17</v>
@@ -7876,10 +7876,10 @@
         <v>15</v>
       </c>
       <c r="Z29">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA29">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB29">
         <v>11.5</v>
@@ -7909,19 +7909,19 @@
         <v>32</v>
       </c>
       <c r="AK29">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AL29">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AM29">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="AN29">
         <v>17</v>
       </c>
       <c r="AO29">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AP29">
         <v>14</v>
@@ -7933,7 +7933,7 @@
         <v>21</v>
       </c>
       <c r="AS29">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT29">
         <v>9.6</v>
@@ -7945,7 +7945,7 @@
         <v>12</v>
       </c>
       <c r="AW29">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX29">
         <v>11.5</v>
@@ -7957,64 +7957,64 @@
         <v>14</v>
       </c>
       <c r="BA29">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB29">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC29">
         <v>19.5</v>
       </c>
       <c r="BD29">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BE29">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF29">
         <v>12.5</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH29">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI29">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BJ29">
         <v>11</v>
       </c>
       <c r="BK29">
-        <v>3.75</v>
+        <v>7.4</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BN29">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO29">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP29">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ29">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="BR29">
         <v>34</v>
       </c>
       <c r="BS29">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BT29">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BU29">
         <v>5.2</v>
@@ -8023,13 +8023,13 @@
         <v>30</v>
       </c>
       <c r="BW29">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BX29">
         <v>42</v>
       </c>
       <c r="BY29">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BZ29">
         <v>0</v>
@@ -8064,55 +8064,55 @@
         <v>3.75</v>
       </c>
       <c r="H30">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I30">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J30">
         <v>2.78</v>
       </c>
       <c r="K30">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L30">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="M30">
         <v>1.14</v>
       </c>
       <c r="N30">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O30">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="P30">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Q30">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="R30">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S30">
         <v>6</v>
       </c>
       <c r="T30">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U30">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V30">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W30">
         <v>1.36</v>
       </c>
       <c r="X30">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y30">
         <v>7.6</v>
@@ -8121,7 +8121,7 @@
         <v>16</v>
       </c>
       <c r="AA30">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AB30">
         <v>9.4</v>
@@ -8139,97 +8139,97 @@
         <v>25</v>
       </c>
       <c r="AG30">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AH30">
         <v>34</v>
       </c>
       <c r="AI30">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ30">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK30">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AL30">
-        <v>100</v>
+        <v>540</v>
       </c>
       <c r="AM30">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN30">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AO30">
         <v>60</v>
       </c>
       <c r="AP30">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AQ30">
+        <v>6.4</v>
+      </c>
+      <c r="AR30">
+        <v>13</v>
+      </c>
+      <c r="AS30">
+        <v>11.5</v>
+      </c>
+      <c r="AT30">
         <v>5.8</v>
       </c>
-      <c r="AR30">
-        <v>11.5</v>
-      </c>
-      <c r="AS30">
-        <v>7.2</v>
-      </c>
-      <c r="AT30">
-        <v>4.4</v>
-      </c>
       <c r="AU30">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="AV30">
         <v>10</v>
       </c>
       <c r="AW30">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX30">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY30">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="AZ30">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BA30">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB30">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC30">
         <v>40</v>
       </c>
       <c r="BD30">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE30">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF30">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG30">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH30">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="BI30">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BJ30">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK30">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8244,16 +8244,16 @@
         <v>5</v>
       </c>
       <c r="BP30">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ30">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS30">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT30">
         <v>5.5</v>
@@ -8262,22 +8262,22 @@
         <v>4.2</v>
       </c>
       <c r="BV30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW30">
         <v>5.6</v>
       </c>
       <c r="BX30">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY30">
         <v>6.2</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA30">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB30" t="s">
         <v>224</v>
@@ -8330,19 +8330,19 @@
         <v>1.41</v>
       </c>
       <c r="P31">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
       </c>
       <c r="R31">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S31">
         <v>4.1</v>
       </c>
       <c r="T31">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U31">
         <v>1.99</v>
@@ -8351,7 +8351,7 @@
         <v>1.52</v>
       </c>
       <c r="W31">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X31">
         <v>11.5</v>
@@ -8360,7 +8360,7 @@
         <v>12</v>
       </c>
       <c r="Z31">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AA31">
         <v>55</v>
@@ -8399,10 +8399,10 @@
         <v>65</v>
       </c>
       <c r="AM31">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN31">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO31">
         <v>44</v>
@@ -8414,10 +8414,10 @@
         <v>8.4</v>
       </c>
       <c r="AR31">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS31">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT31">
         <v>9</v>
@@ -8429,7 +8429,7 @@
         <v>11</v>
       </c>
       <c r="AW31">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX31">
         <v>16.5</v>
@@ -8441,25 +8441,25 @@
         <v>16.5</v>
       </c>
       <c r="BA31">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB31">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC31">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD31">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE31">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF31">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BG31">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BH31">
         <v>3.5</v>
@@ -8471,13 +8471,13 @@
         <v>12</v>
       </c>
       <c r="BK31">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN31">
         <v>7</v>
@@ -8495,7 +8495,7 @@
         <v>50</v>
       </c>
       <c r="BS31">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT31">
         <v>6.8</v>
@@ -8504,7 +8504,7 @@
         <v>4.3</v>
       </c>
       <c r="BV31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW31">
         <v>4.2</v>
@@ -8542,25 +8542,25 @@
         <v>209</v>
       </c>
       <c r="F32">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="G32">
         <v>3.65</v>
       </c>
       <c r="H32">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="I32">
         <v>2.44</v>
       </c>
       <c r="J32">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K32">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="L32">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="M32">
         <v>1.11</v>
@@ -8641,7 +8641,7 @@
         <v>100</v>
       </c>
       <c r="AM32">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN32">
         <v>110</v>
@@ -8653,25 +8653,25 @@
         <v>7.2</v>
       </c>
       <c r="AQ32">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AR32">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AS32">
-        <v>5.2</v>
+        <v>26</v>
       </c>
       <c r="AT32">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AU32">
         <v>6.2</v>
       </c>
       <c r="AV32">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW32">
-        <v>5.2</v>
+        <v>25</v>
       </c>
       <c r="AX32">
         <v>4.7</v>
@@ -8680,7 +8680,7 @@
         <v>4.3</v>
       </c>
       <c r="AZ32">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="BA32">
         <v>5.5</v>
@@ -8698,70 +8698,70 @@
         <v>5.9</v>
       </c>
       <c r="BF32">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="BG32">
-        <v>5.2</v>
+        <v>27</v>
       </c>
       <c r="BH32">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="BI32">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="BJ32">
         <v>14</v>
       </c>
       <c r="BK32">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BN32">
         <v>8</v>
       </c>
       <c r="BO32">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="BP32">
         <v>46</v>
       </c>
       <c r="BQ32">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR32">
         <v>75</v>
       </c>
       <c r="BS32">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BT32">
         <v>5.9</v>
       </c>
       <c r="BU32">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="BV32">
         <v>26</v>
       </c>
       <c r="BW32">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BX32">
         <v>55</v>
       </c>
       <c r="BY32">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BZ32">
         <v>65</v>
       </c>
       <c r="CA32">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="CB32" t="s">
         <v>224</v>
@@ -8784,10 +8784,10 @@
         <v>210</v>
       </c>
       <c r="F33">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="G33">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H33">
         <v>4.8</v>
@@ -8802,19 +8802,19 @@
         <v>3.65</v>
       </c>
       <c r="L33">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M33">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N33">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O33">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P33">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q33">
         <v>2.26</v>
@@ -8826,7 +8826,7 @@
         <v>4.4</v>
       </c>
       <c r="T33">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U33">
         <v>1.71</v>
@@ -8835,25 +8835,25 @@
         <v>1.24</v>
       </c>
       <c r="W33">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X33">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y33">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z33">
         <v>44</v>
       </c>
       <c r="AA33">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB33">
         <v>7.8</v>
       </c>
       <c r="AC33">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD33">
         <v>24</v>
@@ -8865,7 +8865,7 @@
         <v>13.5</v>
       </c>
       <c r="AG33">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH33">
         <v>24</v>
@@ -8883,7 +8883,7 @@
         <v>48</v>
       </c>
       <c r="AM33">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN33">
         <v>20</v>
@@ -8898,10 +8898,10 @@
         <v>12</v>
       </c>
       <c r="AR33">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="AS33">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT33">
         <v>6.4</v>
@@ -8913,7 +8913,7 @@
         <v>16.5</v>
       </c>
       <c r="AW33">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX33">
         <v>9.199999999999999</v>
@@ -8925,7 +8925,7 @@
         <v>18.5</v>
       </c>
       <c r="BA33">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB33">
         <v>19</v>
@@ -8937,13 +8937,13 @@
         <v>36</v>
       </c>
       <c r="BE33">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BF33">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG33">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH33">
         <v>3.5</v>
@@ -8976,7 +8976,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BR33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS33">
         <v>6.4</v>
@@ -9026,22 +9026,22 @@
         <v>211</v>
       </c>
       <c r="F34">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G34">
         <v>2.96</v>
       </c>
       <c r="H34">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I34">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="J34">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="K34">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>1.12</v>
@@ -9050,28 +9050,28 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O34">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P34">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q34">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R34">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="S34">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T34">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="U34">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="V34">
         <v>1.01</v>
@@ -9080,7 +9080,7 @@
         <v>1.01</v>
       </c>
       <c r="X34">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="Y34">
         <v>48</v>
@@ -9089,19 +9089,19 @@
         <v>42</v>
       </c>
       <c r="AA34">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AB34">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AC34">
         <v>22</v>
       </c>
       <c r="AD34">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE34">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF34">
         <v>50</v>
@@ -9110,7 +9110,7 @@
         <v>21</v>
       </c>
       <c r="AH34">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI34">
         <v>23</v>
@@ -9119,34 +9119,34 @@
         <v>65</v>
       </c>
       <c r="AK34">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL34">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AM34">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="AN34">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO34">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AP34">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ34">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR34">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS34">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT34">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU34">
         <v>14</v>
@@ -9158,7 +9158,7 @@
         <v>16</v>
       </c>
       <c r="AX34">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY34">
         <v>14</v>
@@ -9170,7 +9170,7 @@
         <v>15</v>
       </c>
       <c r="BB34">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC34">
         <v>19.5</v>
@@ -9185,13 +9185,13 @@
         <v>5.8</v>
       </c>
       <c r="BG34">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH34">
         <v>9.199999999999999</v>
       </c>
       <c r="BI34">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ34">
         <v>9</v>
@@ -9203,43 +9203,43 @@
         <v>38</v>
       </c>
       <c r="BM34">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BN34">
         <v>9.4</v>
       </c>
       <c r="BO34">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP34">
         <v>19.5</v>
       </c>
       <c r="BQ34">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BR34">
         <v>19</v>
       </c>
       <c r="BS34">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BT34">
         <v>8.6</v>
       </c>
       <c r="BU34">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="BV34">
         <v>16.5</v>
       </c>
       <c r="BW34">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BX34">
         <v>17.5</v>
       </c>
       <c r="BY34">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BZ34">
         <v>0</v>
@@ -9268,13 +9268,13 @@
         <v>212</v>
       </c>
       <c r="F35">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="G35">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="H35">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I35">
         <v>2.52</v>
@@ -9283,46 +9283,46 @@
         <v>3.15</v>
       </c>
       <c r="K35">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L35">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M35">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N35">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O35">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P35">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="Q35">
+        <v>1.9</v>
+      </c>
+      <c r="R35">
+        <v>1.33</v>
+      </c>
+      <c r="S35">
+        <v>3.1</v>
+      </c>
+      <c r="T35">
+        <v>1.74</v>
+      </c>
+      <c r="U35">
         <v>2.08</v>
-      </c>
-      <c r="R35">
-        <v>1.26</v>
-      </c>
-      <c r="S35">
-        <v>3.5</v>
-      </c>
-      <c r="T35">
-        <v>1.82</v>
-      </c>
-      <c r="U35">
-        <v>1.96</v>
       </c>
       <c r="V35">
         <v>1.65</v>
       </c>
       <c r="W35">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X35">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="Y35">
         <v>10.5</v>
@@ -9331,163 +9331,163 @@
         <v>17</v>
       </c>
       <c r="AA35">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB35">
         <v>14</v>
       </c>
       <c r="AC35">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE35">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF35">
         <v>28</v>
       </c>
       <c r="AG35">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH35">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI35">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AJ35">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AK35">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AL35">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM35">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN35">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO35">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AP35">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="AQ35">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="AR35">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AS35">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT35">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="AU35">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AV35">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AW35">
+        <v>5.2</v>
+      </c>
+      <c r="AX35">
+        <v>5.2</v>
+      </c>
+      <c r="AY35">
         <v>4.6</v>
       </c>
-      <c r="AX35">
-        <v>4.5</v>
-      </c>
-      <c r="AY35">
-        <v>4</v>
-      </c>
       <c r="AZ35">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BA35">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB35">
+        <v>5.9</v>
+      </c>
+      <c r="BC35">
+        <v>5.6</v>
+      </c>
+      <c r="BD35">
+        <v>5.8</v>
+      </c>
+      <c r="BE35">
+        <v>6</v>
+      </c>
+      <c r="BF35">
+        <v>5.6</v>
+      </c>
+      <c r="BG35">
         <v>5</v>
       </c>
-      <c r="BC35">
-        <v>4.9</v>
-      </c>
-      <c r="BD35">
-        <v>4.9</v>
-      </c>
-      <c r="BE35">
-        <v>5.1</v>
-      </c>
-      <c r="BF35">
-        <v>4.9</v>
-      </c>
-      <c r="BG35">
-        <v>4.4</v>
-      </c>
       <c r="BH35">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BI35">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="BJ35">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK35">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BN35">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO35">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP35">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ35">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR35">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS35">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT35">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU35">
         <v>2.92</v>
       </c>
       <c r="BV35">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW35">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX35">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BY35">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BZ35">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="CA35">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="CB35" t="s">
         <v>224</v>
@@ -9513,7 +9513,7 @@
         <v>2</v>
       </c>
       <c r="G36">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H36">
         <v>4.3</v>
@@ -9522,31 +9522,31 @@
         <v>4.9</v>
       </c>
       <c r="J36">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K36">
         <v>3.6</v>
       </c>
       <c r="L36">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M36">
         <v>1.1</v>
       </c>
       <c r="N36">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
         <v>1.47</v>
       </c>
       <c r="P36">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q36">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R36">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S36">
         <v>4.5</v>
@@ -9555,7 +9555,7 @@
         <v>2.02</v>
       </c>
       <c r="U36">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V36">
         <v>1.26</v>
@@ -9573,7 +9573,7 @@
         <v>38</v>
       </c>
       <c r="AA36">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AB36">
         <v>8.199999999999999</v>
@@ -9585,7 +9585,7 @@
         <v>22</v>
       </c>
       <c r="AE36">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AF36">
         <v>13.5</v>
@@ -9597,7 +9597,7 @@
         <v>26</v>
       </c>
       <c r="AI36">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="AJ36">
         <v>29</v>
@@ -9606,25 +9606,25 @@
         <v>30</v>
       </c>
       <c r="AL36">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM36">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN36">
         <v>25</v>
       </c>
       <c r="AO36">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AP36">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ36">
         <v>9.800000000000001</v>
       </c>
       <c r="AR36">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="AS36">
         <v>5.9</v>
@@ -9645,10 +9645,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY36">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ36">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BA36">
         <v>5.8</v>
@@ -9681,13 +9681,13 @@
         <v>12.5</v>
       </c>
       <c r="BK36">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BN36">
         <v>5.2</v>
@@ -9699,16 +9699,16 @@
         <v>18.5</v>
       </c>
       <c r="BQ36">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR36">
         <v>42</v>
       </c>
       <c r="BS36">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BT36">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU36">
         <v>3.55</v>
@@ -9717,19 +9717,19 @@
         <v>50</v>
       </c>
       <c r="BW36">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ36">
         <v>42</v>
       </c>
       <c r="CA36">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB36" t="s">
         <v>224</v>
@@ -9755,7 +9755,7 @@
         <v>4.1</v>
       </c>
       <c r="G37">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H37">
         <v>1.96</v>
@@ -9770,7 +9770,7 @@
         <v>3.7</v>
       </c>
       <c r="L37">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M37">
         <v>1.08</v>
@@ -9779,7 +9779,7 @@
         <v>3.3</v>
       </c>
       <c r="O37">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P37">
         <v>1.79</v>
@@ -9791,13 +9791,13 @@
         <v>1.3</v>
       </c>
       <c r="S37">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T37">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U37">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V37">
         <v>1.92</v>
@@ -9806,7 +9806,7 @@
         <v>1.26</v>
       </c>
       <c r="X37">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y37">
         <v>10</v>
@@ -9818,10 +9818,10 @@
         <v>25</v>
       </c>
       <c r="AB37">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC37">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD37">
         <v>12.5</v>
@@ -9833,7 +9833,7 @@
         <v>36</v>
       </c>
       <c r="AG37">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH37">
         <v>21</v>
@@ -9884,7 +9884,7 @@
         <v>18.5</v>
       </c>
       <c r="AX37">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="AY37">
         <v>13</v>
@@ -9896,19 +9896,19 @@
         <v>28</v>
       </c>
       <c r="BB37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC37">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BD37">
-        <v>4.9</v>
+        <v>28</v>
       </c>
       <c r="BE37">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF37">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BG37">
         <v>11.5</v>
@@ -9917,7 +9917,7 @@
         <v>3.75</v>
       </c>
       <c r="BI37">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ37">
         <v>12.5</v>
@@ -9935,7 +9935,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BO37">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP37">
         <v>48</v>
@@ -9944,7 +9944,7 @@
         <v>4.4</v>
       </c>
       <c r="BR37">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS37">
         <v>4.5</v>
@@ -9994,175 +9994,175 @@
         <v>215</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L38">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M38">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N38">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="O38">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P38">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Q38">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="R38">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S38">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="T38">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U38">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V38">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="X38">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y38">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z38">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA38">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB38">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC38">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD38">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE38">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF38">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG38">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH38">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI38">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ38">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK38">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL38">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM38">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN38">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO38">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP38">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ38">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR38">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS38">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT38">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU38">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV38">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW38">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX38">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY38">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ38">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA38">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB38">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC38">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BD38">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE38">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF38">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG38">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH38">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI38">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BJ38">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK38">
         <v>1.01</v>
@@ -10174,10 +10174,10 @@
         <v>1.01</v>
       </c>
       <c r="BN38">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO38">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP38">
         <v>1000</v>
@@ -10192,10 +10192,10 @@
         <v>1.01</v>
       </c>
       <c r="BT38">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU38">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV38">
         <v>1000</v>
@@ -10242,16 +10242,16 @@
         <v>3.65</v>
       </c>
       <c r="H39">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I39">
         <v>2.66</v>
       </c>
       <c r="J39">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K39">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L39">
         <v>1.55</v>
@@ -10266,13 +10266,13 @@
         <v>1.63</v>
       </c>
       <c r="P39">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q39">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R39">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S39">
         <v>6.4</v>
@@ -10281,7 +10281,7 @@
         <v>2.26</v>
       </c>
       <c r="U39">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V39">
         <v>1.6</v>
@@ -10290,16 +10290,16 @@
         <v>1.37</v>
       </c>
       <c r="X39">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y39">
         <v>7.4</v>
       </c>
       <c r="Z39">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA39">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AB39">
         <v>9.199999999999999</v>
@@ -10308,10 +10308,10 @@
         <v>7.2</v>
       </c>
       <c r="AD39">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE39">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AF39">
         <v>22</v>
@@ -10320,43 +10320,43 @@
         <v>17.5</v>
       </c>
       <c r="AH39">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI39">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ39">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK39">
-        <v>730</v>
+        <v>65</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN39">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO39">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP39">
         <v>6.8</v>
       </c>
       <c r="AQ39">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR39">
         <v>12.5</v>
       </c>
       <c r="AS39">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AT39">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU39">
         <v>6.4</v>
@@ -10365,7 +10365,7 @@
         <v>12</v>
       </c>
       <c r="AW39">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AX39">
         <v>19.5</v>
@@ -10374,28 +10374,28 @@
         <v>15</v>
       </c>
       <c r="AZ39">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA39">
         <v>36</v>
       </c>
       <c r="BB39">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BC39">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BD39">
         <v>38</v>
       </c>
       <c r="BE39">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF39">
         <v>36</v>
       </c>
       <c r="BG39">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH39">
         <v>2.82</v>
@@ -10478,16 +10478,16 @@
         <v>217</v>
       </c>
       <c r="F40">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G40">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H40">
         <v>2.86</v>
       </c>
       <c r="I40">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J40">
         <v>2.92</v>
@@ -10511,7 +10511,7 @@
         <v>1.55</v>
       </c>
       <c r="Q40">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R40">
         <v>1.14</v>
@@ -10538,10 +10538,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z40">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AA40">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AB40">
         <v>9</v>
@@ -10553,7 +10553,7 @@
         <v>14.5</v>
       </c>
       <c r="AE40">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AF40">
         <v>18.5</v>
@@ -10562,7 +10562,7 @@
         <v>14</v>
       </c>
       <c r="AH40">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AI40">
         <v>85</v>
@@ -10571,19 +10571,19 @@
         <v>55</v>
       </c>
       <c r="AK40">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AL40">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM40">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN40">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AO40">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP40">
         <v>7.8</v>
@@ -10595,7 +10595,7 @@
         <v>16</v>
       </c>
       <c r="AS40">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT40">
         <v>7.4</v>
@@ -10619,10 +10619,10 @@
         <v>18</v>
       </c>
       <c r="BA40">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB40">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC40">
         <v>34</v>
@@ -10631,13 +10631,13 @@
         <v>9.4</v>
       </c>
       <c r="BE40">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF40">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG40">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10720,7 +10720,7 @@
         <v>218</v>
       </c>
       <c r="F41">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G41">
         <v>1.85</v>
@@ -10759,7 +10759,7 @@
         <v>1.25</v>
       </c>
       <c r="S41">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T41">
         <v>2.04</v>
@@ -10783,7 +10783,7 @@
         <v>48</v>
       </c>
       <c r="AA41">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB41">
         <v>7.4</v>
@@ -10795,7 +10795,7 @@
         <v>24</v>
       </c>
       <c r="AE41">
-        <v>110</v>
+        <v>480</v>
       </c>
       <c r="AF41">
         <v>11.5</v>
@@ -10807,7 +10807,7 @@
         <v>24</v>
       </c>
       <c r="AI41">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="AJ41">
         <v>22</v>
@@ -10819,22 +10819,22 @@
         <v>50</v>
       </c>
       <c r="AM41">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN41">
         <v>16</v>
       </c>
       <c r="AO41">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP41">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ41">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR41">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="AS41">
         <v>7.4</v>
@@ -10855,7 +10855,7 @@
         <v>7.6</v>
       </c>
       <c r="AY41">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ41">
         <v>20</v>
@@ -10965,103 +10965,103 @@
         <v>3.1</v>
       </c>
       <c r="G42">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="H42">
         <v>2.44</v>
       </c>
       <c r="I42">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K42">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L42">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M42">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N42">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="O42">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P42">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R42">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S42">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="T42">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U42">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V42">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W42">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X42">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Y42">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z42">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA42">
         <v>46</v>
       </c>
       <c r="AB42">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC42">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD42">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE42">
         <v>38</v>
       </c>
       <c r="AF42">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG42">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH42">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI42">
         <v>65</v>
       </c>
       <c r="AJ42">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK42">
         <v>55</v>
       </c>
       <c r="AL42">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AM42">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN42">
         <v>65</v>
@@ -11070,88 +11070,88 @@
         <v>38</v>
       </c>
       <c r="AP42">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="AQ42">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR42">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS42">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AT42">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="AU42">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AV42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW42">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX42">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AY42">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AZ42">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA42">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BB42">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BC42">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD42">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BE42">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF42">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BG42">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BH42">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="BI42">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BJ42">
         <v>11</v>
       </c>
       <c r="BK42">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BN42">
         <v>6.6</v>
       </c>
       <c r="BO42">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP42">
         <v>32</v>
       </c>
       <c r="BQ42">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BR42">
         <v>1000</v>
@@ -11163,19 +11163,19 @@
         <v>5.5</v>
       </c>
       <c r="BU42">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV42">
         <v>23</v>
       </c>
       <c r="BW42">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BZ42">
         <v>1000</v>
@@ -11219,7 +11219,7 @@
         <v>4</v>
       </c>
       <c r="K43">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L43">
         <v>1.31</v>
@@ -11231,10 +11231,10 @@
         <v>3.8</v>
       </c>
       <c r="O43">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P43">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q43">
         <v>1.81</v>
@@ -11366,22 +11366,22 @@
         <v>4.2</v>
       </c>
       <c r="BH43">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI43">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ43">
         <v>12.5</v>
       </c>
       <c r="BK43">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN43">
         <v>4.9</v>
@@ -11393,37 +11393,37 @@
         <v>13</v>
       </c>
       <c r="BQ43">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BR43">
         <v>32</v>
       </c>
       <c r="BS43">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT43">
         <v>11.5</v>
       </c>
       <c r="BU43">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV43">
         <v>65</v>
       </c>
       <c r="BW43">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BZ43">
         <v>24</v>
       </c>
       <c r="CA43">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB43" t="s">
         <v>224</v>
@@ -11461,10 +11461,10 @@
         <v>3.4</v>
       </c>
       <c r="K44">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L44">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M44">
         <v>1.06</v>
@@ -11491,7 +11491,7 @@
         <v>1.69</v>
       </c>
       <c r="U44">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V44">
         <v>1.64</v>
@@ -11572,7 +11572,7 @@
         <v>6.2</v>
       </c>
       <c r="AV44">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW44">
         <v>18</v>
@@ -11587,7 +11587,7 @@
         <v>12</v>
       </c>
       <c r="BA44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB44">
         <v>1.01</v>
@@ -11688,16 +11688,16 @@
         <v>222</v>
       </c>
       <c r="F45">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G45">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H45">
         <v>2.84</v>
       </c>
       <c r="I45">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J45">
         <v>3.2</v>
@@ -11706,7 +11706,7 @@
         <v>3.55</v>
       </c>
       <c r="L45">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M45">
         <v>1.08</v>
@@ -11718,13 +11718,13 @@
         <v>1.39</v>
       </c>
       <c r="P45">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q45">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R45">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S45">
         <v>3.8</v>
@@ -11736,7 +11736,7 @@
         <v>2.02</v>
       </c>
       <c r="V45">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W45">
         <v>1.54</v>
@@ -11787,7 +11787,7 @@
         <v>65</v>
       </c>
       <c r="AM45">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN45">
         <v>32</v>
@@ -11841,13 +11841,13 @@
         <v>32</v>
       </c>
       <c r="BE45">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF45">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG45">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH45">
         <v>3.3</v>
@@ -11859,13 +11859,13 @@
         <v>10.5</v>
       </c>
       <c r="BK45">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL45">
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN45">
         <v>5.8</v>
@@ -11874,7 +11874,7 @@
         <v>4.8</v>
       </c>
       <c r="BP45">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ45">
         <v>7</v>
@@ -11883,7 +11883,7 @@
         <v>1000</v>
       </c>
       <c r="BS45">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT45">
         <v>6.2</v>
@@ -11895,7 +11895,7 @@
         <v>25</v>
       </c>
       <c r="BW45">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX45">
         <v>1000</v>
@@ -11907,7 +11907,7 @@
         <v>1000</v>
       </c>
       <c r="CA45">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB45" t="s">
         <v>224</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -688,7 +688,7 @@
     <t>Real Soacha Cundinamarca FC</t>
   </si>
   <si>
-    <t>2026-08-09 19:17:25</t>
+    <t>2026-08-09 21:25:51</t>
   </si>
 </sst>
 </file>
@@ -1282,226 +1282,226 @@
         <v>179</v>
       </c>
       <c r="F2">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="G2">
-        <v>1.69</v>
+        <v>1.2</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="I2">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="L2">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O2">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="P2">
-        <v>2.08</v>
+        <v>2.94</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="R2">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="T2">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="U2">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="W2">
-        <v>2.44</v>
+        <v>6</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>10.5</v>
+      </c>
+      <c r="AC2">
+        <v>14</v>
+      </c>
+      <c r="AD2">
         <v>48</v>
       </c>
-      <c r="AA2">
-        <v>170</v>
-      </c>
-      <c r="AB2">
+      <c r="AE2">
+        <v>320</v>
+      </c>
+      <c r="AF2">
+        <v>6.6</v>
+      </c>
+      <c r="AG2">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>23</v>
-      </c>
-      <c r="AE2">
-        <v>85</v>
-      </c>
-      <c r="AF2">
-        <v>10</v>
-      </c>
-      <c r="AG2">
-        <v>10</v>
-      </c>
       <c r="AH2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AJ2">
-        <v>16.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK2">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AL2">
         <v>36</v>
       </c>
       <c r="AM2">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AO2">
-        <v>100</v>
+        <v>410</v>
       </c>
       <c r="AP2">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AR2">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="AS2">
-        <v>110</v>
+        <v>13.5</v>
       </c>
       <c r="AT2">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AU2">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="AX2">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="BC2">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD2">
         <v>30</v>
       </c>
       <c r="BE2">
+        <v>110</v>
+      </c>
+      <c r="BF2">
+        <v>5</v>
+      </c>
+      <c r="BG2">
+        <v>230</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BJ2">
+        <v>10.5</v>
+      </c>
+      <c r="BK2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL2">
+        <v>220</v>
+      </c>
+      <c r="BM2">
         <v>85</v>
       </c>
-      <c r="BF2">
-        <v>8.6</v>
-      </c>
-      <c r="BG2">
-        <v>75</v>
-      </c>
-      <c r="BH2">
-        <v>3.7</v>
-      </c>
-      <c r="BI2">
-        <v>3.25</v>
-      </c>
-      <c r="BJ2">
-        <v>11</v>
-      </c>
-      <c r="BK2">
-        <v>8.6</v>
-      </c>
-      <c r="BL2">
-        <v>130</v>
-      </c>
-      <c r="BM2">
-        <v>10.5</v>
-      </c>
       <c r="BN2">
-        <v>4.4</v>
+        <v>2.22</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>2.06</v>
       </c>
       <c r="BP2">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="BQ2">
-        <v>9.6</v>
+        <v>3.65</v>
       </c>
       <c r="BR2">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="BS2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="BT2">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="BY2">
-        <v>9.6</v>
+        <v>80</v>
       </c>
       <c r="BZ2">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="CA2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="s">
         <v>224</v>
@@ -1524,220 +1524,220 @@
         <v>180</v>
       </c>
       <c r="F3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H3">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="O3">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="P3">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.98</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="T3">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="U3">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X3">
+        <v>7.4</v>
+      </c>
+      <c r="Y3">
+        <v>9.6</v>
+      </c>
+      <c r="Z3">
+        <v>25</v>
+      </c>
+      <c r="AA3">
+        <v>110</v>
+      </c>
+      <c r="AB3">
+        <v>6.8</v>
+      </c>
+      <c r="AC3">
+        <v>7.2</v>
+      </c>
+      <c r="AD3">
+        <v>21</v>
+      </c>
+      <c r="AE3">
+        <v>80</v>
+      </c>
+      <c r="AF3">
+        <v>12.5</v>
+      </c>
+      <c r="AG3">
         <v>13.5</v>
       </c>
-      <c r="Y3">
-        <v>12</v>
-      </c>
-      <c r="Z3">
-        <v>27</v>
-      </c>
-      <c r="AA3">
-        <v>90</v>
-      </c>
-      <c r="AB3">
+      <c r="AH3">
+        <v>32</v>
+      </c>
+      <c r="AI3">
+        <v>130</v>
+      </c>
+      <c r="AJ3">
+        <v>38</v>
+      </c>
+      <c r="AK3">
+        <v>48</v>
+      </c>
+      <c r="AL3">
+        <v>110</v>
+      </c>
+      <c r="AM3">
+        <v>360</v>
+      </c>
+      <c r="AN3">
+        <v>46</v>
+      </c>
+      <c r="AO3">
+        <v>160</v>
+      </c>
+      <c r="AP3">
+        <v>6.8</v>
+      </c>
+      <c r="AQ3">
         <v>9.4</v>
       </c>
-      <c r="AC3">
-        <v>8.6</v>
-      </c>
-      <c r="AD3">
+      <c r="AR3">
+        <v>21</v>
+      </c>
+      <c r="AS3">
+        <v>70</v>
+      </c>
+      <c r="AT3">
+        <v>6.2</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
         <v>16</v>
       </c>
-      <c r="AE3">
-        <v>60</v>
-      </c>
-      <c r="AF3">
-        <v>15.5</v>
-      </c>
-      <c r="AG3">
-        <v>14</v>
-      </c>
-      <c r="AH3">
+      <c r="AW3">
+        <v>55</v>
+      </c>
+      <c r="AX3">
+        <v>11</v>
+      </c>
+      <c r="AY3">
+        <v>11.5</v>
+      </c>
+      <c r="AZ3">
+        <v>24</v>
+      </c>
+      <c r="BA3">
+        <v>95</v>
+      </c>
+      <c r="BB3">
+        <v>29</v>
+      </c>
+      <c r="BC3">
+        <v>32</v>
+      </c>
+      <c r="BD3">
+        <v>70</v>
+      </c>
+      <c r="BE3">
+        <v>230</v>
+      </c>
+      <c r="BF3">
+        <v>38</v>
+      </c>
+      <c r="BG3">
+        <v>85</v>
+      </c>
+      <c r="BH3">
+        <v>1.94</v>
+      </c>
+      <c r="BI3">
+        <v>1.84</v>
+      </c>
+      <c r="BJ3">
         <v>23</v>
       </c>
-      <c r="AI3">
-        <v>90</v>
-      </c>
-      <c r="AJ3">
-        <v>40</v>
-      </c>
-      <c r="AK3">
-        <v>34</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
-        <v>160</v>
-      </c>
-      <c r="AN3">
-        <v>29</v>
-      </c>
-      <c r="AO3">
-        <v>75</v>
-      </c>
-      <c r="AP3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ3">
-        <v>10</v>
-      </c>
-      <c r="AR3">
-        <v>20</v>
-      </c>
-      <c r="AS3">
-        <v>50</v>
-      </c>
-      <c r="AT3">
-        <v>6.6</v>
-      </c>
-      <c r="AU3">
-        <v>6.2</v>
-      </c>
-      <c r="AV3">
-        <v>11</v>
-      </c>
-      <c r="AW3">
-        <v>32</v>
-      </c>
-      <c r="AX3">
-        <v>12.5</v>
-      </c>
-      <c r="AY3">
-        <v>10</v>
-      </c>
-      <c r="AZ3">
-        <v>16.5</v>
-      </c>
-      <c r="BA3">
-        <v>44</v>
-      </c>
-      <c r="BB3">
-        <v>22</v>
-      </c>
-      <c r="BC3">
-        <v>22</v>
-      </c>
-      <c r="BD3">
-        <v>34</v>
-      </c>
-      <c r="BE3">
-        <v>6.2</v>
-      </c>
-      <c r="BF3">
-        <v>21</v>
-      </c>
-      <c r="BG3">
-        <v>38</v>
-      </c>
-      <c r="BH3">
-        <v>3.3</v>
-      </c>
-      <c r="BI3">
-        <v>2.52</v>
-      </c>
-      <c r="BJ3">
-        <v>10.5</v>
-      </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="BN3">
         <v>5.2</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="BQ3">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="BS3">
-        <v>7.2</v>
+        <v>65</v>
       </c>
       <c r="BT3">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BV3">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BW3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1766,226 +1766,226 @@
         <v>181</v>
       </c>
       <c r="F4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H4">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="I4">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="K4">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="L4">
-        <v>1.59</v>
+        <v>2.48</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="N4">
-        <v>2.68</v>
+        <v>1.97</v>
       </c>
       <c r="O4">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="P4">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="Q4">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="S4">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="T4">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="V4">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X4">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="Z4">
         <v>16.5</v>
       </c>
       <c r="AA4">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AC4">
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AE4">
+        <v>85</v>
+      </c>
+      <c r="AF4">
+        <v>19</v>
+      </c>
+      <c r="AG4">
+        <v>19.5</v>
+      </c>
+      <c r="AH4">
         <v>48</v>
       </c>
-      <c r="AF4">
+      <c r="AI4">
+        <v>170</v>
+      </c>
+      <c r="AJ4">
+        <v>80</v>
+      </c>
+      <c r="AK4">
+        <v>80</v>
+      </c>
+      <c r="AL4">
+        <v>200</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>180</v>
+      </c>
+      <c r="AO4">
+        <v>140</v>
+      </c>
+      <c r="AP4">
+        <v>5</v>
+      </c>
+      <c r="AQ4">
+        <v>6</v>
+      </c>
+      <c r="AR4">
+        <v>15</v>
+      </c>
+      <c r="AS4">
+        <v>50</v>
+      </c>
+      <c r="AT4">
+        <v>6.4</v>
+      </c>
+      <c r="AU4">
+        <v>6.6</v>
+      </c>
+      <c r="AV4">
+        <v>16</v>
+      </c>
+      <c r="AW4">
+        <v>60</v>
+      </c>
+      <c r="AX4">
+        <v>16.5</v>
+      </c>
+      <c r="AY4">
+        <v>17.5</v>
+      </c>
+      <c r="AZ4">
+        <v>36</v>
+      </c>
+      <c r="BA4">
+        <v>130</v>
+      </c>
+      <c r="BB4">
+        <v>65</v>
+      </c>
+      <c r="BC4">
+        <v>65</v>
+      </c>
+      <c r="BD4">
+        <v>140</v>
+      </c>
+      <c r="BE4">
+        <v>440</v>
+      </c>
+      <c r="BF4">
+        <v>100</v>
+      </c>
+      <c r="BG4">
+        <v>95</v>
+      </c>
+      <c r="BH4">
+        <v>1.69</v>
+      </c>
+      <c r="BI4">
+        <v>1.62</v>
+      </c>
+      <c r="BJ4">
+        <v>32</v>
+      </c>
+      <c r="BK4">
         <v>23</v>
-      </c>
-      <c r="AG4">
-        <v>14.5</v>
-      </c>
-      <c r="AH4">
-        <v>24</v>
-      </c>
-      <c r="AI4">
-        <v>85</v>
-      </c>
-      <c r="AJ4">
-        <v>75</v>
-      </c>
-      <c r="AK4">
-        <v>65</v>
-      </c>
-      <c r="AL4">
-        <v>100</v>
-      </c>
-      <c r="AM4">
-        <v>210</v>
-      </c>
-      <c r="AN4">
-        <v>100</v>
-      </c>
-      <c r="AO4">
-        <v>55</v>
-      </c>
-      <c r="AP4">
-        <v>7.6</v>
-      </c>
-      <c r="AQ4">
-        <v>7</v>
-      </c>
-      <c r="AR4">
-        <v>13.5</v>
-      </c>
-      <c r="AS4">
-        <v>32</v>
-      </c>
-      <c r="AT4">
-        <v>7.8</v>
-      </c>
-      <c r="AU4">
-        <v>6.2</v>
-      </c>
-      <c r="AV4">
-        <v>11</v>
-      </c>
-      <c r="AW4">
-        <v>32</v>
-      </c>
-      <c r="AX4">
-        <v>17.5</v>
-      </c>
-      <c r="AY4">
-        <v>12.5</v>
-      </c>
-      <c r="AZ4">
-        <v>20</v>
-      </c>
-      <c r="BA4">
-        <v>48</v>
-      </c>
-      <c r="BB4">
-        <v>44</v>
-      </c>
-      <c r="BC4">
-        <v>34</v>
-      </c>
-      <c r="BD4">
-        <v>50</v>
-      </c>
-      <c r="BE4">
-        <v>10</v>
-      </c>
-      <c r="BF4">
-        <v>50</v>
-      </c>
-      <c r="BG4">
-        <v>30</v>
-      </c>
-      <c r="BH4">
-        <v>2.7</v>
-      </c>
-      <c r="BI4">
-        <v>2.46</v>
-      </c>
-      <c r="BJ4">
-        <v>11.5</v>
-      </c>
-      <c r="BK4">
-        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BN4">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BO4">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BP4">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>160</v>
       </c>
       <c r="BT4">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU4">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="BW4">
-        <v>9.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="BZ4">
-        <v>55</v>
+        <v>960</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="CB4" t="s">
         <v>224</v>
@@ -2008,58 +2008,58 @@
         <v>182</v>
       </c>
       <c r="F5">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G5">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H5">
         <v>3.3</v>
       </c>
       <c r="I5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J5">
         <v>3.15</v>
       </c>
       <c r="K5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M5">
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P5">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
         <v>1.28</v>
       </c>
       <c r="S5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T5">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X5">
         <v>11</v>
@@ -2074,10 +2074,10 @@
         <v>60</v>
       </c>
       <c r="AB5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD5">
         <v>14</v>
@@ -2110,19 +2110,19 @@
         <v>120</v>
       </c>
       <c r="AN5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ5">
         <v>10</v>
       </c>
       <c r="AR5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS5">
         <v>50</v>
@@ -2131,25 +2131,25 @@
         <v>8.4</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV5">
         <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX5">
         <v>14</v>
       </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB5">
         <v>32</v>
@@ -2161,16 +2161,16 @@
         <v>42</v>
       </c>
       <c r="BE5">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BF5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BG5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI5">
         <v>2.82</v>
@@ -2185,13 +2185,13 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="BN5">
         <v>5.9</v>
       </c>
       <c r="BO5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP5">
         <v>23</v>
@@ -2250,46 +2250,46 @@
         <v>183</v>
       </c>
       <c r="F6">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="G6">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="H6">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="I6">
-        <v>25</v>
+        <v>4.6</v>
       </c>
       <c r="J6">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="O6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P6">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="R6">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="S6">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2298,10 +2298,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="W6">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2403,7 +2403,7 @@
         <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2427,7 +2427,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>85</v>
       </c>
       <c r="BN6">
         <v>1000</v>
@@ -2492,7 +2492,7 @@
         <v>184</v>
       </c>
       <c r="F7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>2.14</v>
@@ -2510,7 +2510,7 @@
         <v>3.55</v>
       </c>
       <c r="L7">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M7">
         <v>1.1</v>
@@ -2519,10 +2519,10 @@
         <v>2.9</v>
       </c>
       <c r="O7">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="P7">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q7">
         <v>2.34</v>
@@ -2534,16 +2534,16 @@
         <v>4.5</v>
       </c>
       <c r="T7">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U7">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V7">
         <v>1.25</v>
       </c>
       <c r="W7">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X7">
         <v>12</v>
@@ -2576,7 +2576,7 @@
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI7">
         <v>100</v>
@@ -2603,13 +2603,13 @@
         <v>8</v>
       </c>
       <c r="AQ7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
@@ -2621,37 +2621,37 @@
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX7">
         <v>8.800000000000001</v>
       </c>
       <c r="AY7">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7">
         <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC7">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF7">
         <v>16.5</v>
       </c>
       <c r="BG7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH7">
         <v>3.25</v>
@@ -2734,10 +2734,10 @@
         <v>185</v>
       </c>
       <c r="F8">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G8">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H8">
         <v>3.65</v>
@@ -2746,7 +2746,7 @@
         <v>4.2</v>
       </c>
       <c r="J8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K8">
         <v>4.1</v>
@@ -2767,25 +2767,25 @@
         <v>2.1</v>
       </c>
       <c r="Q8">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R8">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S8">
         <v>2.88</v>
       </c>
       <c r="T8">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U8">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V8">
         <v>1.32</v>
       </c>
       <c r="W8">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X8">
         <v>19</v>
@@ -2863,28 +2863,28 @@
         <v>12</v>
       </c>
       <c r="AW8">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AX8">
         <v>10.5</v>
       </c>
       <c r="AY8">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA8">
         <v>38</v>
       </c>
       <c r="BB8">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC8">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BE8">
         <v>8</v>
@@ -2985,13 +2985,13 @@
         <v>2.66</v>
       </c>
       <c r="I9">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L9">
         <v>1.54</v>
@@ -3006,7 +3006,7 @@
         <v>1.58</v>
       </c>
       <c r="P9">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q9">
         <v>2.76</v>
@@ -3018,7 +3018,7 @@
         <v>5.9</v>
       </c>
       <c r="T9">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
         <v>1.72</v>
@@ -3054,7 +3054,7 @@
         <v>50</v>
       </c>
       <c r="AF9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG9">
         <v>16</v>
@@ -3093,7 +3093,7 @@
         <v>12.5</v>
       </c>
       <c r="AS9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT9">
         <v>7.6</v>
@@ -3105,37 +3105,37 @@
         <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX9">
         <v>15.5</v>
       </c>
       <c r="AY9">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ9">
         <v>20</v>
       </c>
       <c r="BA9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB9">
+        <v>6.8</v>
+      </c>
+      <c r="BC9">
         <v>7.2</v>
       </c>
-      <c r="BC9">
+      <c r="BD9">
         <v>7</v>
       </c>
-      <c r="BD9">
+      <c r="BE9">
+        <v>8</v>
+      </c>
+      <c r="BF9">
         <v>6.8</v>
       </c>
-      <c r="BE9">
-        <v>7.6</v>
-      </c>
-      <c r="BF9">
-        <v>6.6</v>
-      </c>
       <c r="BG9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH9">
         <v>2.64</v>
@@ -3251,7 +3251,7 @@
         <v>2.14</v>
       </c>
       <c r="Q10">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R10">
         <v>1.44</v>
@@ -3460,7 +3460,7 @@
         <v>188</v>
       </c>
       <c r="F11">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G11">
         <v>2.34</v>
@@ -3469,7 +3469,7 @@
         <v>3.45</v>
       </c>
       <c r="I11">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J11">
         <v>3.4</v>
@@ -3508,7 +3508,7 @@
         <v>2.06</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
         <v>1.74</v>
@@ -3550,7 +3550,7 @@
         <v>65</v>
       </c>
       <c r="AJ11">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AK11">
         <v>65</v>
@@ -3574,10 +3574,10 @@
         <v>10.5</v>
       </c>
       <c r="AR11">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AS11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT11">
         <v>8</v>
@@ -3601,10 +3601,10 @@
         <v>15.5</v>
       </c>
       <c r="BA11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB11">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BC11">
         <v>13</v>
@@ -3613,7 +3613,7 @@
         <v>34</v>
       </c>
       <c r="BE11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF11">
         <v>15.5</v>
@@ -3625,19 +3625,19 @@
         <v>3.8</v>
       </c>
       <c r="BI11">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11">
         <v>12</v>
       </c>
       <c r="BK11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BN11">
         <v>6</v>
@@ -3655,7 +3655,7 @@
         <v>38</v>
       </c>
       <c r="BS11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BT11">
         <v>8</v>
@@ -3670,7 +3670,7 @@
         <v>4.2</v>
       </c>
       <c r="BX11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY11">
         <v>4.4</v>
@@ -3705,13 +3705,13 @@
         <v>1.74</v>
       </c>
       <c r="G12">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="H12">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J12">
         <v>4.1</v>
@@ -3735,10 +3735,10 @@
         <v>2.22</v>
       </c>
       <c r="Q12">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R12">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S12">
         <v>2.7</v>
@@ -3747,13 +3747,13 @@
         <v>1.7</v>
       </c>
       <c r="U12">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W12">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X12">
         <v>22</v>
@@ -3777,13 +3777,13 @@
         <v>21</v>
       </c>
       <c r="AE12">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH12">
         <v>19</v>
@@ -3792,10 +3792,10 @@
         <v>60</v>
       </c>
       <c r="AJ12">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL12">
         <v>32</v>
@@ -3804,22 +3804,22 @@
         <v>95</v>
       </c>
       <c r="AN12">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO12">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP12">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ12">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR12">
         <v>14.5</v>
       </c>
       <c r="AS12">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT12">
         <v>8.800000000000001</v>
@@ -3831,7 +3831,7 @@
         <v>15</v>
       </c>
       <c r="AW12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX12">
         <v>10</v>
@@ -3843,7 +3843,7 @@
         <v>15</v>
       </c>
       <c r="BA12">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB12">
         <v>15.5</v>
@@ -3855,13 +3855,13 @@
         <v>16</v>
       </c>
       <c r="BE12">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH12">
         <v>4.1</v>
@@ -3879,43 +3879,43 @@
         <v>120</v>
       </c>
       <c r="BM12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BN12">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BO12">
         <v>4</v>
       </c>
       <c r="BP12">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BQ12">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="BR12">
         <v>26</v>
       </c>
       <c r="BS12">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT12">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU12">
         <v>6.6</v>
       </c>
       <c r="BV12">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BW12">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BX12">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BY12">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3944,25 +3944,25 @@
         <v>190</v>
       </c>
       <c r="F13">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G13">
         <v>1.34</v>
       </c>
       <c r="H13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="J13">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="K13">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M13">
         <v>1.05</v>
@@ -3977,7 +3977,7 @@
         <v>2.1</v>
       </c>
       <c r="Q13">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R13">
         <v>1.43</v>
@@ -3986,7 +3986,7 @@
         <v>2.66</v>
       </c>
       <c r="T13">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U13">
         <v>1.63</v>
@@ -3995,7 +3995,7 @@
         <v>1.06</v>
       </c>
       <c r="W13">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="X13">
         <v>21</v>
@@ -4019,7 +4019,7 @@
         <v>130</v>
       </c>
       <c r="AE13">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AF13">
         <v>7.8</v>
@@ -4049,19 +4049,19 @@
         <v>5.7</v>
       </c>
       <c r="AO13">
-        <v>620</v>
+        <v>590</v>
       </c>
       <c r="AP13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT13">
         <v>4.4</v>
@@ -4073,7 +4073,7 @@
         <v>7.6</v>
       </c>
       <c r="AW13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX13">
         <v>4.4</v>
@@ -4082,7 +4082,7 @@
         <v>7</v>
       </c>
       <c r="AZ13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA13">
         <v>8.4</v>
@@ -4091,37 +4091,37 @@
         <v>5.8</v>
       </c>
       <c r="BC13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD13">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF13">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BG13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH13">
         <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BJ13">
         <v>14.5</v>
       </c>
       <c r="BK13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>2.72</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13">
         <v>3.7</v>
@@ -4130,7 +4130,7 @@
         <v>2.84</v>
       </c>
       <c r="BP13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BQ13">
         <v>4.4</v>
@@ -4139,13 +4139,13 @@
         <v>28</v>
       </c>
       <c r="BS13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BU13">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -4160,7 +4160,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CA13">
         <v>5.8</v>
@@ -4186,7 +4186,7 @@
         <v>191</v>
       </c>
       <c r="F14">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G14">
         <v>2.06</v>
@@ -4195,7 +4195,7 @@
         <v>4.3</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>3.5</v>
@@ -4210,13 +4210,13 @@
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O14">
         <v>1.41</v>
       </c>
       <c r="P14">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -4237,7 +4237,7 @@
         <v>1.27</v>
       </c>
       <c r="W14">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X14">
         <v>13</v>
@@ -4255,7 +4255,7 @@
         <v>7.8</v>
       </c>
       <c r="AC14">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14">
         <v>22</v>
@@ -4327,7 +4327,7 @@
         <v>18.5</v>
       </c>
       <c r="BA14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB14">
         <v>20</v>
@@ -4336,16 +4336,16 @@
         <v>18</v>
       </c>
       <c r="BD14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF14">
         <v>14.5</v>
       </c>
       <c r="BG14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH14">
         <v>3.4</v>
@@ -4673,58 +4673,58 @@
         <v>1.15</v>
       </c>
       <c r="G16">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J16">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K16">
         <v>10.5</v>
       </c>
       <c r="L16">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M16">
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="O16">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P16">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="Q16">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R16">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="S16">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="T16">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="U16">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="V16">
         <v>1.03</v>
       </c>
       <c r="W16">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="X16">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="Y16">
         <v>950</v>
@@ -4736,7 +4736,7 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC16">
         <v>22</v>
@@ -4745,7 +4745,7 @@
         <v>950</v>
       </c>
       <c r="AE16">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
         <v>9.6</v>
@@ -4769,7 +4769,7 @@
         <v>330</v>
       </c>
       <c r="AM16">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="AN16">
         <v>3.1</v>
@@ -4781,64 +4781,64 @@
         <v>7</v>
       </c>
       <c r="AQ16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS16">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT16">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU16">
         <v>18</v>
       </c>
       <c r="AV16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW16">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX16">
+        <v>6.8</v>
+      </c>
+      <c r="AY16">
+        <v>12.5</v>
+      </c>
+      <c r="AZ16">
+        <v>7.4</v>
+      </c>
+      <c r="BA16">
+        <v>8.4</v>
+      </c>
+      <c r="BB16">
         <v>7.2</v>
       </c>
-      <c r="AY16">
-        <v>11</v>
-      </c>
-      <c r="AZ16">
-        <v>7.2</v>
-      </c>
-      <c r="BA16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB16">
-        <v>7</v>
-      </c>
       <c r="BC16">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF16">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BG16">
         <v>10.5</v>
       </c>
       <c r="BH16">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI16">
         <v>4.2</v>
       </c>
       <c r="BJ16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BK16">
         <v>7.4</v>
@@ -4847,13 +4847,13 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN16">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BO16">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP16">
         <v>5.8</v>
@@ -4862,10 +4862,10 @@
         <v>4.5</v>
       </c>
       <c r="BR16">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT16">
         <v>1000</v>
@@ -4877,16 +4877,16 @@
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CA16">
         <v>6</v>
@@ -4921,10 +4921,10 @@
         <v>1.88</v>
       </c>
       <c r="I17">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="J17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K17">
         <v>4.3</v>
@@ -4951,7 +4951,7 @@
         <v>1.62</v>
       </c>
       <c r="S17">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T17">
         <v>1.61</v>
@@ -4960,7 +4960,7 @@
         <v>2.54</v>
       </c>
       <c r="V17">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="W17">
         <v>1.3</v>
@@ -5154,22 +5154,22 @@
         <v>195</v>
       </c>
       <c r="F18">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G18">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J18">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L18">
         <v>1.21</v>
@@ -5178,7 +5178,7 @@
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O18">
         <v>1.14</v>
@@ -5187,7 +5187,7 @@
         <v>3.2</v>
       </c>
       <c r="Q18">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R18">
         <v>1.9</v>
@@ -5205,10 +5205,10 @@
         <v>1.1</v>
       </c>
       <c r="W18">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="X18">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Y18">
         <v>55</v>
@@ -5217,19 +5217,19 @@
         <v>110</v>
       </c>
       <c r="AA18">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="AB18">
         <v>14</v>
       </c>
       <c r="AC18">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD18">
         <v>38</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF18">
         <v>11.5</v>
@@ -5241,7 +5241,7 @@
         <v>22</v>
       </c>
       <c r="AI18">
-        <v>380</v>
+        <v>90</v>
       </c>
       <c r="AJ18">
         <v>12.5</v>
@@ -5280,10 +5280,10 @@
         <v>13</v>
       </c>
       <c r="AV18">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AW18">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX18">
         <v>10</v>
@@ -5292,10 +5292,10 @@
         <v>10</v>
       </c>
       <c r="AZ18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA18">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BB18">
         <v>11.5</v>
@@ -5307,10 +5307,10 @@
         <v>23</v>
       </c>
       <c r="BE18">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BF18">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BG18">
         <v>75</v>
@@ -5567,7 +5567,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL19">
         <v>1000</v>
@@ -5579,7 +5579,7 @@
         <v>5.6</v>
       </c>
       <c r="BO19">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP19">
         <v>1000</v>
@@ -5653,7 +5653,7 @@
         <v>3.55</v>
       </c>
       <c r="K20">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L20">
         <v>1.32</v>
@@ -5680,7 +5680,7 @@
         <v>3.05</v>
       </c>
       <c r="T20">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U20">
         <v>2.28</v>
@@ -5764,7 +5764,7 @@
         <v>7.2</v>
       </c>
       <c r="AV20">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW20">
         <v>24</v>
@@ -5922,7 +5922,7 @@
         <v>2.96</v>
       </c>
       <c r="T21">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U21">
         <v>2.28</v>
@@ -6081,13 +6081,13 @@
         <v>5.9</v>
       </c>
       <c r="BU21">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BV21">
         <v>18</v>
       </c>
       <c r="BW21">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="BX21">
         <v>32</v>
@@ -6122,25 +6122,25 @@
         <v>199</v>
       </c>
       <c r="F22">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="G22">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H22">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I22">
         <v>2.32</v>
       </c>
       <c r="J22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K22">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M22">
         <v>1.02</v>
@@ -6155,25 +6155,25 @@
         <v>3.2</v>
       </c>
       <c r="Q22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R22">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S22">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="T22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U22">
         <v>3.1</v>
       </c>
       <c r="V22">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W22">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X22">
         <v>44</v>
@@ -6191,7 +6191,7 @@
         <v>40</v>
       </c>
       <c r="AC22">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD22">
         <v>13</v>
@@ -6230,7 +6230,7 @@
         <v>8.4</v>
       </c>
       <c r="AP22">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ22">
         <v>15.5</v>
@@ -6245,7 +6245,7 @@
         <v>21</v>
       </c>
       <c r="AU22">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV22">
         <v>9.4</v>
@@ -6254,10 +6254,10 @@
         <v>14</v>
       </c>
       <c r="AX22">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AY22">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ22">
         <v>10.5</v>
@@ -6266,7 +6266,7 @@
         <v>16</v>
       </c>
       <c r="BB22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC22">
         <v>20</v>
@@ -6275,7 +6275,7 @@
         <v>20</v>
       </c>
       <c r="BE22">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF22">
         <v>10</v>
@@ -6287,7 +6287,7 @@
         <v>6.4</v>
       </c>
       <c r="BI22">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BJ22">
         <v>9.800000000000001</v>
@@ -6299,7 +6299,7 @@
         <v>65</v>
       </c>
       <c r="BM22">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BN22">
         <v>8.6</v>
@@ -6308,19 +6308,19 @@
         <v>5.4</v>
       </c>
       <c r="BP22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BR22">
         <v>27</v>
       </c>
       <c r="BS22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BT22">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU22">
         <v>4.6</v>
@@ -6335,7 +6335,7 @@
         <v>23</v>
       </c>
       <c r="BY22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BZ22">
         <v>13.5</v>
@@ -6436,16 +6436,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF23">
         <v>22</v>
       </c>
       <c r="AG23">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH23">
         <v>14</v>
@@ -6457,7 +6457,7 @@
         <v>38</v>
       </c>
       <c r="AK23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL23">
         <v>29</v>
@@ -6472,7 +6472,7 @@
         <v>13.5</v>
       </c>
       <c r="AP23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ23">
         <v>15.5</v>
@@ -6529,7 +6529,7 @@
         <v>4.6</v>
       </c>
       <c r="BI23">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BJ23">
         <v>8.4</v>
@@ -6636,25 +6636,25 @@
         <v>1.27</v>
       </c>
       <c r="P24">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q24">
         <v>1.8</v>
       </c>
       <c r="R24">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S24">
         <v>3</v>
       </c>
       <c r="T24">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U24">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W24">
         <v>1.67</v>
@@ -6869,7 +6869,7 @@
         <v>1.21</v>
       </c>
       <c r="M25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25">
         <v>6.2</v>
@@ -6884,10 +6884,10 @@
         <v>1.48</v>
       </c>
       <c r="R25">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S25">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T25">
         <v>1.53</v>
@@ -6956,7 +6956,7 @@
         <v>22</v>
       </c>
       <c r="AP25">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ25">
         <v>18</v>
@@ -7096,7 +7096,7 @@
         <v>3.95</v>
       </c>
       <c r="H26">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I26">
         <v>2.12</v>
@@ -7120,22 +7120,22 @@
         <v>1.17</v>
       </c>
       <c r="P26">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q26">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R26">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S26">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T26">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U26">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V26">
         <v>1.89</v>
@@ -7377,7 +7377,7 @@
         <v>1.89</v>
       </c>
       <c r="U27">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V27">
         <v>1.16</v>
@@ -7431,7 +7431,7 @@
         <v>38</v>
       </c>
       <c r="AM27">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN27">
         <v>11</v>
@@ -7467,7 +7467,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY27">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ27">
         <v>18.5</v>
@@ -7479,7 +7479,7 @@
         <v>11.5</v>
       </c>
       <c r="BC27">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD27">
         <v>18</v>
@@ -7503,7 +7503,7 @@
         <v>11</v>
       </c>
       <c r="BK27">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BL27">
         <v>1000</v>
@@ -7521,7 +7521,7 @@
         <v>11</v>
       </c>
       <c r="BQ27">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BR27">
         <v>27</v>
@@ -7580,10 +7580,10 @@
         <v>4.5</v>
       </c>
       <c r="H28">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I28">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J28">
         <v>3.55</v>
@@ -7598,7 +7598,7 @@
         <v>1.07</v>
       </c>
       <c r="N28">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O28">
         <v>1.33</v>
@@ -7610,22 +7610,22 @@
         <v>2</v>
       </c>
       <c r="R28">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S28">
         <v>3.6</v>
       </c>
       <c r="T28">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U28">
         <v>2.04</v>
       </c>
       <c r="V28">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X28">
         <v>16.5</v>
@@ -7637,7 +7637,7 @@
         <v>13</v>
       </c>
       <c r="AA28">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AB28">
         <v>15</v>
@@ -7661,7 +7661,7 @@
         <v>23</v>
       </c>
       <c r="AI28">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ28">
         <v>110</v>
@@ -7670,7 +7670,7 @@
         <v>65</v>
       </c>
       <c r="AL28">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM28">
         <v>580</v>
@@ -7685,7 +7685,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ28">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR28">
         <v>9.6</v>
@@ -7715,22 +7715,22 @@
         <v>15.5</v>
       </c>
       <c r="BA28">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB28">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC28">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD28">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE28">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF28">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG28">
         <v>12</v>
@@ -7819,22 +7819,22 @@
         <v>2.2</v>
       </c>
       <c r="G29">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H29">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I29">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J29">
         <v>3.5</v>
       </c>
       <c r="K29">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L29">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M29">
         <v>1.06</v>
@@ -7855,19 +7855,19 @@
         <v>1.39</v>
       </c>
       <c r="S29">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T29">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U29">
         <v>2.24</v>
       </c>
       <c r="V29">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X29">
         <v>17</v>
@@ -7879,7 +7879,7 @@
         <v>500</v>
       </c>
       <c r="AA29">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB29">
         <v>11.5</v>
@@ -7888,7 +7888,7 @@
         <v>8.4</v>
       </c>
       <c r="AD29">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE29">
         <v>40</v>
@@ -7918,7 +7918,7 @@
         <v>320</v>
       </c>
       <c r="AN29">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AO29">
         <v>500</v>
@@ -7927,55 +7927,55 @@
         <v>14</v>
       </c>
       <c r="AQ29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR29">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AS29">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT29">
         <v>9.6</v>
       </c>
       <c r="AU29">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV29">
         <v>12</v>
       </c>
       <c r="AW29">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AX29">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY29">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29">
         <v>14</v>
       </c>
       <c r="BA29">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB29">
         <v>14.5</v>
       </c>
       <c r="BC29">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD29">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="BE29">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF29">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BG29">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH29">
         <v>3.95</v>
@@ -7987,13 +7987,13 @@
         <v>11</v>
       </c>
       <c r="BK29">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BN29">
         <v>6</v>
@@ -8005,31 +8005,31 @@
         <v>19.5</v>
       </c>
       <c r="BQ29">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="BR29">
         <v>34</v>
       </c>
       <c r="BS29">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BT29">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BU29">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV29">
         <v>30</v>
       </c>
       <c r="BW29">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BX29">
         <v>42</v>
       </c>
       <c r="BY29">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BZ29">
         <v>0</v>
@@ -8064,25 +8064,25 @@
         <v>3.75</v>
       </c>
       <c r="H30">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I30">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J30">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K30">
         <v>3.15</v>
       </c>
       <c r="L30">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M30">
         <v>1.14</v>
       </c>
       <c r="N30">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O30">
         <v>1.6</v>
@@ -8097,16 +8097,16 @@
         <v>1.16</v>
       </c>
       <c r="S30">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="T30">
         <v>2.14</v>
       </c>
       <c r="U30">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V30">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
         <v>1.36</v>
@@ -8154,7 +8154,7 @@
         <v>160</v>
       </c>
       <c r="AL30">
-        <v>540</v>
+        <v>230</v>
       </c>
       <c r="AM30">
         <v>500</v>
@@ -8187,10 +8187,10 @@
         <v>10</v>
       </c>
       <c r="AW30">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX30">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY30">
         <v>14</v>
@@ -8199,28 +8199,28 @@
         <v>19</v>
       </c>
       <c r="BA30">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="BB30">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="BC30">
         <v>40</v>
       </c>
       <c r="BD30">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE30">
         <v>9.199999999999999</v>
       </c>
       <c r="BF30">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG30">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH30">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI30">
         <v>2.2</v>
@@ -8229,13 +8229,13 @@
         <v>13.5</v>
       </c>
       <c r="BK30">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BN30">
         <v>7.2</v>
@@ -8247,16 +8247,16 @@
         <v>40</v>
       </c>
       <c r="BQ30">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BR30">
         <v>70</v>
       </c>
       <c r="BS30">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BT30">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BU30">
         <v>4.2</v>
@@ -8265,19 +8265,19 @@
         <v>28</v>
       </c>
       <c r="BW30">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BX30">
         <v>60</v>
       </c>
       <c r="BY30">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BZ30">
         <v>70</v>
       </c>
       <c r="CA30">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="CB30" t="s">
         <v>224</v>
@@ -8315,7 +8315,7 @@
         <v>3.15</v>
       </c>
       <c r="K31">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L31">
         <v>1.47</v>
@@ -8357,10 +8357,10 @@
         <v>11.5</v>
       </c>
       <c r="Y31">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z31">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AA31">
         <v>55</v>
@@ -8417,7 +8417,7 @@
         <v>8.4</v>
       </c>
       <c r="AS31">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT31">
         <v>9</v>
@@ -8429,7 +8429,7 @@
         <v>11</v>
       </c>
       <c r="AW31">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX31">
         <v>16.5</v>
@@ -8441,19 +8441,19 @@
         <v>16.5</v>
       </c>
       <c r="BA31">
+        <v>5.9</v>
+      </c>
+      <c r="BB31">
+        <v>5.8</v>
+      </c>
+      <c r="BC31">
         <v>5.6</v>
       </c>
-      <c r="BB31">
-        <v>5.6</v>
-      </c>
-      <c r="BC31">
-        <v>5.4</v>
-      </c>
       <c r="BD31">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE31">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF31">
         <v>6.6</v>
@@ -8471,7 +8471,7 @@
         <v>12</v>
       </c>
       <c r="BK31">
-        <v>3.45</v>
+        <v>7.8</v>
       </c>
       <c r="BL31">
         <v>1000</v>
@@ -8557,7 +8557,7 @@
         <v>3.35</v>
       </c>
       <c r="K32">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L32">
         <v>1.58</v>
@@ -8569,7 +8569,7 @@
         <v>2.58</v>
       </c>
       <c r="O32">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P32">
         <v>1.55</v>
@@ -8599,13 +8599,13 @@
         <v>11</v>
       </c>
       <c r="Y32">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Z32">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA32">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB32">
         <v>9.199999999999999</v>
@@ -8614,10 +8614,10 @@
         <v>10</v>
       </c>
       <c r="AD32">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE32">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF32">
         <v>23</v>
@@ -8674,28 +8674,28 @@
         <v>25</v>
       </c>
       <c r="AX32">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY32">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AZ32">
         <v>19.5</v>
       </c>
       <c r="BA32">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BB32">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BC32">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD32">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BE32">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF32">
         <v>9</v>
@@ -8784,22 +8784,22 @@
         <v>210</v>
       </c>
       <c r="F33">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G33">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="H33">
         <v>4.8</v>
       </c>
       <c r="I33">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J33">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K33">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L33">
         <v>1.4</v>
@@ -8808,10 +8808,10 @@
         <v>1.1</v>
       </c>
       <c r="N33">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O33">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P33">
         <v>1.7</v>
@@ -8829,16 +8829,16 @@
         <v>2.04</v>
       </c>
       <c r="U33">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="V33">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W33">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X33">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y33">
         <v>14.5</v>
@@ -8850,7 +8850,7 @@
         <v>150</v>
       </c>
       <c r="AB33">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC33">
         <v>8.199999999999999</v>
@@ -8862,7 +8862,7 @@
         <v>95</v>
       </c>
       <c r="AF33">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG33">
         <v>10.5</v>
@@ -8895,25 +8895,25 @@
         <v>9.6</v>
       </c>
       <c r="AQ33">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR33">
         <v>16</v>
       </c>
       <c r="AS33">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT33">
         <v>6.4</v>
       </c>
       <c r="AU33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV33">
         <v>16.5</v>
       </c>
       <c r="AW33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX33">
         <v>9.199999999999999</v>
@@ -8925,7 +8925,7 @@
         <v>18.5</v>
       </c>
       <c r="BA33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB33">
         <v>19</v>
@@ -8937,13 +8937,13 @@
         <v>36</v>
       </c>
       <c r="BE33">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF33">
         <v>15</v>
       </c>
       <c r="BG33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH33">
         <v>3.5</v>
@@ -9026,7 +9026,7 @@
         <v>211</v>
       </c>
       <c r="F34">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G34">
         <v>2.96</v>
@@ -9053,10 +9053,10 @@
         <v>13</v>
       </c>
       <c r="O34">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P34">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q34">
         <v>1.18</v>
@@ -9271,16 +9271,16 @@
         <v>3.1</v>
       </c>
       <c r="G35">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H35">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I35">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J35">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K35">
         <v>3.9</v>
@@ -9292,31 +9292,31 @@
         <v>1.07</v>
       </c>
       <c r="N35">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O35">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P35">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q35">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R35">
         <v>1.33</v>
       </c>
       <c r="S35">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T35">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U35">
         <v>2.08</v>
       </c>
       <c r="V35">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W35">
         <v>1.4</v>
@@ -9334,7 +9334,7 @@
         <v>36</v>
       </c>
       <c r="AB35">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC35">
         <v>8.4</v>
@@ -9346,7 +9346,7 @@
         <v>27</v>
       </c>
       <c r="AF35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG35">
         <v>16.5</v>
@@ -9382,52 +9382,52 @@
         <v>5.6</v>
       </c>
       <c r="AR35">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AS35">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT35">
         <v>5.8</v>
       </c>
       <c r="AU35">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV35">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="AW35">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX35">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY35">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ35">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA35">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB35">
+        <v>6</v>
+      </c>
+      <c r="BC35">
+        <v>5.7</v>
+      </c>
+      <c r="BD35">
         <v>5.9</v>
       </c>
-      <c r="BC35">
-        <v>5.6</v>
-      </c>
-      <c r="BD35">
-        <v>5.8</v>
-      </c>
       <c r="BE35">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF35">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG35">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BH35">
         <v>3.8</v>
@@ -9439,55 +9439,55 @@
         <v>11</v>
       </c>
       <c r="BK35">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN35">
         <v>7.4</v>
       </c>
       <c r="BO35">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP35">
         <v>32</v>
       </c>
       <c r="BQ35">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR35">
         <v>44</v>
       </c>
       <c r="BS35">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BT35">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU35">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="BV35">
         <v>20</v>
       </c>
       <c r="BW35">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX35">
         <v>36</v>
       </c>
       <c r="BY35">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ35">
         <v>32</v>
       </c>
       <c r="CA35">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="CB35" t="s">
         <v>224</v>
@@ -9525,7 +9525,7 @@
         <v>3.25</v>
       </c>
       <c r="K36">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L36">
         <v>1.5</v>
@@ -9642,13 +9642,13 @@
         <v>5.7</v>
       </c>
       <c r="AX36">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY36">
         <v>9.6</v>
       </c>
       <c r="AZ36">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BA36">
         <v>5.8</v>
@@ -9758,7 +9758,7 @@
         <v>4.8</v>
       </c>
       <c r="H37">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I37">
         <v>2.08</v>
@@ -9767,16 +9767,16 @@
         <v>3.4</v>
       </c>
       <c r="K37">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L37">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M37">
         <v>1.08</v>
       </c>
       <c r="N37">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O37">
         <v>1.35</v>
@@ -9785,7 +9785,7 @@
         <v>1.79</v>
       </c>
       <c r="Q37">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R37">
         <v>1.3</v>
@@ -9794,10 +9794,10 @@
         <v>3.7</v>
       </c>
       <c r="T37">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U37">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V37">
         <v>1.92</v>
@@ -9830,7 +9830,7 @@
         <v>24</v>
       </c>
       <c r="AF37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG37">
         <v>19</v>
@@ -9839,7 +9839,7 @@
         <v>21</v>
       </c>
       <c r="AI37">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ37">
         <v>130</v>
@@ -9896,16 +9896,16 @@
         <v>28</v>
       </c>
       <c r="BB37">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC37">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD37">
         <v>28</v>
       </c>
       <c r="BE37">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF37">
         <v>10.5</v>
@@ -9994,7 +9994,7 @@
         <v>215</v>
       </c>
       <c r="F38">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G38">
         <v>2.58</v>
@@ -10039,7 +10039,7 @@
         <v>1.99</v>
       </c>
       <c r="U38">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V38">
         <v>1.36</v>
@@ -10078,7 +10078,7 @@
         <v>12.5</v>
       </c>
       <c r="AH38">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI38">
         <v>75</v>
@@ -10165,13 +10165,13 @@
         <v>11</v>
       </c>
       <c r="BK38">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN38">
         <v>5.2</v>
@@ -10183,13 +10183,13 @@
         <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR38">
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT38">
         <v>6.8</v>
@@ -10201,13 +10201,13 @@
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ38">
         <v>0</v>
@@ -10248,10 +10248,10 @@
         <v>2.66</v>
       </c>
       <c r="J39">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K39">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L39">
         <v>1.55</v>
@@ -10266,13 +10266,13 @@
         <v>1.63</v>
       </c>
       <c r="P39">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q39">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="R39">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S39">
         <v>6.4</v>
@@ -10281,7 +10281,7 @@
         <v>2.26</v>
       </c>
       <c r="U39">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V39">
         <v>1.6</v>
@@ -10332,7 +10332,7 @@
         <v>65</v>
       </c>
       <c r="AL39">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AM39">
         <v>230</v>
@@ -10380,7 +10380,7 @@
         <v>36</v>
       </c>
       <c r="BB39">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BC39">
         <v>50</v>
@@ -10490,7 +10490,7 @@
         <v>3.2</v>
       </c>
       <c r="J40">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K40">
         <v>3.3</v>
@@ -10595,7 +10595,7 @@
         <v>16</v>
       </c>
       <c r="AS40">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AT40">
         <v>7.4</v>
@@ -10720,31 +10720,31 @@
         <v>218</v>
       </c>
       <c r="F41">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="G41">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H41">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I41">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J41">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K41">
         <v>3.8</v>
       </c>
       <c r="L41">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M41">
         <v>1.09</v>
       </c>
       <c r="N41">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O41">
         <v>1.42</v>
@@ -10765,19 +10765,19 @@
         <v>2.04</v>
       </c>
       <c r="U41">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V41">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W41">
         <v>2.16</v>
       </c>
       <c r="X41">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y41">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z41">
         <v>48</v>
@@ -10792,13 +10792,13 @@
         <v>8.6</v>
       </c>
       <c r="AD41">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE41">
         <v>480</v>
       </c>
       <c r="AF41">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG41">
         <v>12</v>
@@ -10822,7 +10822,7 @@
         <v>580</v>
       </c>
       <c r="AN41">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO41">
         <v>700</v>
@@ -10831,13 +10831,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ41">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR41">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS41">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT41">
         <v>6.2</v>
@@ -10849,37 +10849,37 @@
         <v>18</v>
       </c>
       <c r="AW41">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX41">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AY41">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ41">
         <v>20</v>
       </c>
       <c r="BA41">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB41">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BC41">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BD41">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE41">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF41">
         <v>11.5</v>
       </c>
       <c r="BG41">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH41">
         <v>3.4</v>
@@ -10888,58 +10888,58 @@
         <v>2.56</v>
       </c>
       <c r="BJ41">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK41">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN41">
         <v>4.8</v>
       </c>
       <c r="BO41">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP41">
         <v>15</v>
       </c>
       <c r="BQ41">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BR41">
         <v>38</v>
       </c>
       <c r="BS41">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BT41">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU41">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BV41">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW41">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BX41">
         <v>1000</v>
       </c>
       <c r="BY41">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ41">
         <v>34</v>
       </c>
       <c r="CA41">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="CB41" t="s">
         <v>224</v>
@@ -10965,7 +10965,7 @@
         <v>3.1</v>
       </c>
       <c r="G42">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H42">
         <v>2.44</v>
@@ -10974,10 +10974,10 @@
         <v>2.78</v>
       </c>
       <c r="J42">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K42">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L42">
         <v>1.52</v>
@@ -10986,7 +10986,7 @@
         <v>1.11</v>
       </c>
       <c r="N42">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O42">
         <v>1.48</v>
@@ -10995,16 +10995,16 @@
         <v>1.58</v>
       </c>
       <c r="Q42">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R42">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S42">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="T42">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U42">
         <v>1.87</v>
@@ -11013,7 +11013,7 @@
         <v>1.56</v>
       </c>
       <c r="W42">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X42">
         <v>10</v>
@@ -11025,7 +11025,7 @@
         <v>16.5</v>
       </c>
       <c r="AA42">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AB42">
         <v>10.5</v>
@@ -11070,22 +11070,22 @@
         <v>38</v>
       </c>
       <c r="AP42">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AQ42">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR42">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS42">
         <v>7.4</v>
       </c>
       <c r="AT42">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AU42">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AV42">
         <v>7</v>
@@ -11094,16 +11094,16 @@
         <v>7.2</v>
       </c>
       <c r="AX42">
-        <v>6.4</v>
+        <v>18.5</v>
       </c>
       <c r="AY42">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ42">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA42">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB42">
         <v>8</v>
@@ -11112,16 +11112,16 @@
         <v>7.8</v>
       </c>
       <c r="BD42">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE42">
         <v>8.6</v>
       </c>
       <c r="BF42">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG42">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BH42">
         <v>2.92</v>
@@ -11139,7 +11139,7 @@
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>2.28</v>
+        <v>10</v>
       </c>
       <c r="BN42">
         <v>6.6</v>
@@ -11151,13 +11151,13 @@
         <v>32</v>
       </c>
       <c r="BQ42">
-        <v>2.14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR42">
         <v>1000</v>
       </c>
       <c r="BS42">
-        <v>2.22</v>
+        <v>9</v>
       </c>
       <c r="BT42">
         <v>5.5</v>
@@ -11169,19 +11169,19 @@
         <v>23</v>
       </c>
       <c r="BW42">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>2.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ42">
         <v>1000</v>
       </c>
       <c r="CA42">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB42" t="s">
         <v>224</v>
@@ -11204,100 +11204,100 @@
         <v>220</v>
       </c>
       <c r="F43">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="G43">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="H43">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I43">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="J43">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K43">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L43">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M43">
         <v>1.06</v>
       </c>
       <c r="N43">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O43">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P43">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q43">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R43">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S43">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T43">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U43">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V43">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W43">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="X43">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y43">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z43">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA43">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AB43">
         <v>10.5</v>
       </c>
       <c r="AC43">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD43">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AE43">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF43">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG43">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH43">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI43">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ43">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AK43">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL43">
         <v>44</v>
@@ -11306,124 +11306,124 @@
         <v>150</v>
       </c>
       <c r="AN43">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO43">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AP43">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AQ43">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS43">
+        <v>6.6</v>
+      </c>
+      <c r="AT43">
+        <v>4.1</v>
+      </c>
+      <c r="AU43">
+        <v>7.8</v>
+      </c>
+      <c r="AV43">
+        <v>18.5</v>
+      </c>
+      <c r="AW43">
+        <v>6.4</v>
+      </c>
+      <c r="AX43">
         <v>4.2</v>
-      </c>
-      <c r="AT43">
-        <v>6.4</v>
-      </c>
-      <c r="AU43">
-        <v>7</v>
-      </c>
-      <c r="AV43">
-        <v>17</v>
-      </c>
-      <c r="AW43">
-        <v>4.1</v>
-      </c>
-      <c r="AX43">
-        <v>7.4</v>
       </c>
       <c r="AY43">
         <v>7.4</v>
       </c>
       <c r="AZ43">
-        <v>15.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA43">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="BB43">
-        <v>11.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC43">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="BD43">
-        <v>3.95</v>
+        <v>5.9</v>
       </c>
       <c r="BE43">
+        <v>6.4</v>
+      </c>
+      <c r="BF43">
         <v>4.2</v>
       </c>
-      <c r="BF43">
-        <v>7</v>
-      </c>
       <c r="BG43">
+        <v>6.4</v>
+      </c>
+      <c r="BH43">
         <v>4.2</v>
       </c>
-      <c r="BH43">
-        <v>4.1</v>
-      </c>
       <c r="BI43">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ43">
         <v>12.5</v>
       </c>
       <c r="BK43">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BN43">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO43">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP43">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ43">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BR43">
         <v>32</v>
       </c>
       <c r="BS43">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BT43">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU43">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BV43">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW43">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BX43">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY43">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BZ43">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA43">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="CB43" t="s">
         <v>224</v>
@@ -11458,10 +11458,10 @@
         <v>2.54</v>
       </c>
       <c r="J44">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K44">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L44">
         <v>1.37</v>
@@ -11479,7 +11479,7 @@
         <v>1.98</v>
       </c>
       <c r="Q44">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R44">
         <v>1.37</v>
@@ -11488,10 +11488,10 @@
         <v>3.15</v>
       </c>
       <c r="T44">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U44">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V44">
         <v>1.64</v>
@@ -11503,7 +11503,7 @@
         <v>19</v>
       </c>
       <c r="Y44">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z44">
         <v>19.5</v>
@@ -11524,7 +11524,7 @@
         <v>32</v>
       </c>
       <c r="AF44">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AG44">
         <v>17</v>
@@ -11557,13 +11557,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ44">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AR44">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS44">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="AT44">
         <v>10</v>
@@ -11587,25 +11587,25 @@
         <v>12</v>
       </c>
       <c r="BA44">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB44">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC44">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BD44">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE44">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF44">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BG44">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BH44">
         <v>4.1</v>
@@ -11688,7 +11688,7 @@
         <v>222</v>
       </c>
       <c r="F45">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G45">
         <v>2.82</v>
@@ -11712,7 +11712,7 @@
         <v>1.08</v>
       </c>
       <c r="N45">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O45">
         <v>1.39</v>
@@ -11730,7 +11730,7 @@
         <v>3.8</v>
       </c>
       <c r="T45">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U45">
         <v>2.02</v>
@@ -11814,7 +11814,7 @@
         <v>6</v>
       </c>
       <c r="AV45">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW45">
         <v>25</v>
@@ -11930,52 +11930,52 @@
         <v>223</v>
       </c>
       <c r="F46">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G46">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I46">
         <v>3.55</v>
       </c>
       <c r="J46">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K46">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L46">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="M46">
         <v>1.13</v>
       </c>
       <c r="N46">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="O46">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P46">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q46">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="R46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S46">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="T46">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U46">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V46">
         <v>1.39</v>
@@ -11984,37 +11984,37 @@
         <v>1.51</v>
       </c>
       <c r="X46">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y46">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z46">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA46">
         <v>80</v>
       </c>
       <c r="AB46">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC46">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD46">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE46">
         <v>65</v>
       </c>
       <c r="AF46">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG46">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AH46">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI46">
         <v>95</v>
@@ -12035,121 +12035,121 @@
         <v>60</v>
       </c>
       <c r="AO46">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP46">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="AQ46">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR46">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AS46">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT46">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="AU46">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="AV46">
-        <v>3.9</v>
+        <v>13</v>
       </c>
       <c r="AW46">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AX46">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AY46">
-        <v>3.85</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ46">
-        <v>4.2</v>
+        <v>17.5</v>
       </c>
       <c r="BA46">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BB46">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BC46">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD46">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BE46">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BF46">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BG46">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BH46">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BI46">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BJ46">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK46">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BL46">
         <v>1000</v>
       </c>
       <c r="BM46">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BN46">
         <v>6.4</v>
       </c>
       <c r="BO46">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="BP46">
         <v>32</v>
       </c>
       <c r="BQ46">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BR46">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BS46">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BT46">
         <v>7.2</v>
       </c>
       <c r="BU46">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="BV46">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW46">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BX46">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY46">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BZ46">
         <v>70</v>
       </c>
       <c r="CA46">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB46" t="s">
         <v>224</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -640,7 +640,7 @@
     <t>Real Soacha Cundinamarca FC</t>
   </si>
   <si>
-    <t>2026-08-10 01:43:53</t>
+    <t>2026-08-10 03:53:36</t>
   </si>
 </sst>
 </file>
@@ -1237,58 +1237,58 @@
         <v>2.02</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
         <v>4.8</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P2">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q2">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T2">
         <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V2">
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y2">
         <v>13.5</v>
@@ -1297,7 +1297,7 @@
         <v>34</v>
       </c>
       <c r="AA2">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AB2">
         <v>7.8</v>
@@ -1306,28 +1306,28 @@
         <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE2">
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AK2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL2">
         <v>65</v>
@@ -1336,49 +1336,49 @@
         <v>580</v>
       </c>
       <c r="AN2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AO2">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AP2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
         <v>14</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>16.5</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
       </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC2">
         <v>21</v>
@@ -1387,49 +1387,49 @@
         <v>19.5</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2">
         <v>19.5</v>
       </c>
       <c r="BG2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
         <v>3.2</v>
       </c>
       <c r="BI2">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
         <v>18</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BT2">
         <v>8.6</v>
@@ -1438,22 +1438,22 @@
         <v>6</v>
       </c>
       <c r="BV2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BX2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY2">
         <v>6</v>
       </c>
       <c r="BZ2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB2" t="s">
         <v>208</v>
@@ -1476,70 +1476,70 @@
         <v>169</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="G3">
         <v>2.54</v>
       </c>
       <c r="H3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
         <v>1.26</v>
       </c>
       <c r="P3">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q3">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R3">
         <v>1.44</v>
       </c>
       <c r="S3">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="T3">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U3">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V3">
         <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y3">
         <v>15</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB3">
         <v>12.5</v>
@@ -1551,7 +1551,7 @@
         <v>14</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF3">
         <v>18</v>
@@ -1563,7 +1563,7 @@
         <v>16.5</v>
       </c>
       <c r="AI3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ3">
         <v>34</v>
@@ -1572,22 +1572,22 @@
         <v>25</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AN3">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AO3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR3">
         <v>20</v>
@@ -1596,52 +1596,52 @@
         <v>36</v>
       </c>
       <c r="AT3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
         <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY3">
         <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BE3">
         <v>55</v>
       </c>
       <c r="BF3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BI3">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3">
         <v>9.4</v>
@@ -1653,37 +1653,37 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN3">
         <v>5.7</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1692,10 +1692,10 @@
         <v>8</v>
       </c>
       <c r="BZ3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CA3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
         <v>208</v>
@@ -1718,13 +1718,13 @@
         <v>170</v>
       </c>
       <c r="F4">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I4">
         <v>4.2</v>
@@ -1742,22 +1742,22 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
         <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S4">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T4">
         <v>1.68</v>
@@ -1766,10 +1766,10 @@
         <v>2.26</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X4">
         <v>18.5</v>
@@ -1805,7 +1805,7 @@
         <v>17.5</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ4">
         <v>25</v>
@@ -1820,7 +1820,7 @@
         <v>200</v>
       </c>
       <c r="AN4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO4">
         <v>42</v>
@@ -1835,10 +1835,10 @@
         <v>25</v>
       </c>
       <c r="AS4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU4">
         <v>7.8</v>
@@ -1853,7 +1853,7 @@
         <v>11.5</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
         <v>14</v>
@@ -1865,7 +1865,7 @@
         <v>20</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD4">
         <v>26</v>
@@ -1910,7 +1910,7 @@
         <v>6.4</v>
       </c>
       <c r="BR4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
         <v>8</v>
@@ -1966,13 +1966,13 @@
         <v>3.35</v>
       </c>
       <c r="H5">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I5">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J5">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K5">
         <v>3</v>
@@ -1984,28 +1984,28 @@
         <v>1.15</v>
       </c>
       <c r="N5">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q5">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="R5">
         <v>1.17</v>
       </c>
       <c r="S5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U5">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V5">
         <v>1.51</v>
@@ -2017,31 +2017,31 @@
         <v>7.8</v>
       </c>
       <c r="Y5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z5">
         <v>17</v>
       </c>
       <c r="AA5">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB5">
         <v>8.6</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE5">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF5">
         <v>20</v>
       </c>
       <c r="AG5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH5">
         <v>32</v>
@@ -2071,7 +2071,7 @@
         <v>6.6</v>
       </c>
       <c r="AQ5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR5">
         <v>14.5</v>
@@ -2080,13 +2080,13 @@
         <v>36</v>
       </c>
       <c r="AT5">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW5">
         <v>32</v>
@@ -2098,37 +2098,37 @@
         <v>13</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA5">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB5">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC5">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BD5">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF5">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH5">
         <v>2.58</v>
       </c>
       <c r="BI5">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
         <v>7.6</v>
@@ -2137,7 +2137,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5">
         <v>6.8</v>
@@ -2149,37 +2149,37 @@
         <v>36</v>
       </c>
       <c r="BQ5">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BS5">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BT5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU5">
         <v>4.4</v>
       </c>
       <c r="BV5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW5">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX5">
         <v>60</v>
       </c>
       <c r="BY5">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5">
         <v>70</v>
       </c>
       <c r="CA5">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="s">
         <v>208</v>
@@ -2202,16 +2202,16 @@
         <v>172</v>
       </c>
       <c r="F6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G6">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H6">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J6">
         <v>3.4</v>
@@ -2253,10 +2253,10 @@
         <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y6">
         <v>13.5</v>
@@ -2286,7 +2286,7 @@
         <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI6">
         <v>65</v>
@@ -2307,7 +2307,7 @@
         <v>21</v>
       </c>
       <c r="AO6">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AP6">
         <v>10.5</v>
@@ -2316,7 +2316,7 @@
         <v>10.5</v>
       </c>
       <c r="AR6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS6">
         <v>48</v>
@@ -2343,7 +2343,7 @@
         <v>16</v>
       </c>
       <c r="BA6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB6">
         <v>25</v>
@@ -2364,7 +2364,7 @@
         <v>30</v>
       </c>
       <c r="BH6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI6">
         <v>2.62</v>
@@ -2373,55 +2373,55 @@
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BN6">
         <v>6</v>
       </c>
       <c r="BO6">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BP6">
         <v>21</v>
       </c>
       <c r="BQ6">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BR6">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BT6">
         <v>8</v>
       </c>
       <c r="BU6">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BW6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BX6">
         <v>55</v>
       </c>
       <c r="BY6">
+        <v>4.7</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
         <v>4.4</v>
-      </c>
-      <c r="BZ6">
-        <v>36</v>
-      </c>
-      <c r="CA6">
-        <v>4.2</v>
       </c>
       <c r="CB6" t="s">
         <v>208</v>
@@ -2444,13 +2444,13 @@
         <v>173</v>
       </c>
       <c r="F7">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G7">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I7">
         <v>5.4</v>
@@ -2459,7 +2459,7 @@
         <v>4.2</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
         <v>1.33</v>
@@ -2495,16 +2495,16 @@
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y7">
         <v>22</v>
       </c>
       <c r="Z7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA7">
         <v>130</v>
@@ -2528,7 +2528,7 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI7">
         <v>60</v>
@@ -2537,10 +2537,10 @@
         <v>18.5</v>
       </c>
       <c r="AK7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM7">
         <v>95</v>
@@ -2549,22 +2549,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS7">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU7">
         <v>8.800000000000001</v>
@@ -2573,34 +2573,34 @@
         <v>17.5</v>
       </c>
       <c r="AW7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AX7">
         <v>10</v>
       </c>
       <c r="AY7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ7">
+        <v>16.5</v>
+      </c>
+      <c r="BA7">
+        <v>42</v>
+      </c>
+      <c r="BB7">
         <v>16</v>
-      </c>
-      <c r="BA7">
-        <v>38</v>
-      </c>
-      <c r="BB7">
-        <v>15.5</v>
       </c>
       <c r="BC7">
         <v>14.5</v>
       </c>
       <c r="BD7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE7">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BF7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG7">
         <v>34</v>
@@ -2627,34 +2627,34 @@
         <v>4.7</v>
       </c>
       <c r="BO7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR7">
         <v>24</v>
       </c>
       <c r="BS7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU7">
         <v>6.6</v>
       </c>
       <c r="BV7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW7">
         <v>6.6</v>
       </c>
       <c r="BX7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY7">
         <v>6.6</v>
@@ -2686,13 +2686,13 @@
         <v>174</v>
       </c>
       <c r="F8">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="G8">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H8">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I8">
         <v>4.7</v>
@@ -2701,7 +2701,7 @@
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
         <v>1.49</v>
@@ -2716,37 +2716,37 @@
         <v>1.41</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R8">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S8">
         <v>4.3</v>
       </c>
       <c r="T8">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="U8">
+        <v>1.91</v>
+      </c>
+      <c r="V8">
+        <v>1.28</v>
+      </c>
+      <c r="W8">
         <v>1.92</v>
       </c>
-      <c r="V8">
-        <v>1.27</v>
-      </c>
-      <c r="W8">
-        <v>1.96</v>
-      </c>
       <c r="X8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y8">
         <v>14</v>
       </c>
       <c r="Z8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA8">
         <v>500</v>
@@ -2755,7 +2755,7 @@
         <v>7.8</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD8">
         <v>22</v>
@@ -2764,7 +2764,7 @@
         <v>85</v>
       </c>
       <c r="AF8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG8">
         <v>10.5</v>
@@ -2776,7 +2776,7 @@
         <v>210</v>
       </c>
       <c r="AJ8">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AK8">
         <v>29</v>
@@ -2788,7 +2788,7 @@
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO8">
         <v>270</v>
@@ -2803,7 +2803,7 @@
         <v>23</v>
       </c>
       <c r="AS8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT8">
         <v>6.8</v>
@@ -2812,7 +2812,7 @@
         <v>6.8</v>
       </c>
       <c r="AV8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW8">
         <v>42</v>
@@ -2839,13 +2839,13 @@
         <v>30</v>
       </c>
       <c r="BE8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF8">
         <v>16.5</v>
       </c>
       <c r="BG8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH8">
         <v>3.4</v>
@@ -2863,49 +2863,49 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BN8">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BO8">
         <v>4</v>
       </c>
       <c r="BP8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BR8">
         <v>40</v>
       </c>
       <c r="BS8">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BT8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU8">
         <v>5.1</v>
       </c>
       <c r="BV8">
+        <v>48</v>
+      </c>
+      <c r="BW8">
+        <v>6.4</v>
+      </c>
+      <c r="BX8">
         <v>1000</v>
       </c>
-      <c r="BW8">
-        <v>5.6</v>
-      </c>
-      <c r="BX8">
-        <v>70</v>
-      </c>
       <c r="BY8">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ8">
         <v>38</v>
       </c>
       <c r="CA8">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="s">
         <v>208</v>
@@ -2928,49 +2928,49 @@
         <v>175</v>
       </c>
       <c r="F9">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H9">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I9">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="J9">
         <v>2.96</v>
       </c>
       <c r="K9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L9">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M9">
         <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O9">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P9">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q9">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R9">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S9">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="T9">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U9">
         <v>1.79</v>
@@ -2979,28 +2979,28 @@
         <v>1.54</v>
       </c>
       <c r="W9">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X9">
         <v>11</v>
       </c>
       <c r="Y9">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AA9">
         <v>50</v>
       </c>
       <c r="AB9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC9">
         <v>7.6</v>
       </c>
       <c r="AD9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE9">
         <v>44</v>
@@ -3009,16 +3009,16 @@
         <v>24</v>
       </c>
       <c r="AG9">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI9">
         <v>160</v>
       </c>
       <c r="AJ9">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AK9">
         <v>55</v>
@@ -3030,124 +3030,124 @@
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AO9">
         <v>46</v>
       </c>
       <c r="AP9">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AQ9">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AR9">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="AS9">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT9">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU9">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV9">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="AX9">
-        <v>5.6</v>
+        <v>17</v>
       </c>
       <c r="AY9">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AZ9">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA9">
         <v>5.6</v>
       </c>
       <c r="BB9">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC9">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD9">
         <v>5.6</v>
       </c>
       <c r="BE9">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG9">
         <v>6.2</v>
       </c>
       <c r="BH9">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="BI9">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="BJ9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK9">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BN9">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO9">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP9">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BQ9">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BR9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BS9">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BT9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU9">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="BV9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW9">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BX9">
         <v>55</v>
       </c>
       <c r="BY9">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BZ9">
         <v>60</v>
       </c>
       <c r="CA9">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB9" t="s">
         <v>208</v>
@@ -3170,64 +3170,64 @@
         <v>176</v>
       </c>
       <c r="F10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G10">
         <v>1.34</v>
       </c>
       <c r="H10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I10">
         <v>16.5</v>
       </c>
       <c r="J10">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="K10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L10">
         <v>1.34</v>
       </c>
       <c r="M10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O10">
         <v>1.24</v>
       </c>
       <c r="P10">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q10">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R10">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S10">
         <v>2.88</v>
       </c>
       <c r="T10">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U10">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y10">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="Z10">
         <v>170</v>
@@ -3236,7 +3236,7 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC10">
         <v>14.5</v>
@@ -3245,124 +3245,124 @@
         <v>950</v>
       </c>
       <c r="AE10">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AF10">
         <v>7.8</v>
       </c>
       <c r="AG10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH10">
         <v>950</v>
       </c>
       <c r="AI10">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AJ10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AK10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL10">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AM10">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AN10">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO10">
-        <v>590</v>
+        <v>490</v>
       </c>
       <c r="AP10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AR10">
+        <v>8</v>
+      </c>
+      <c r="AS10">
         <v>8.199999999999999</v>
       </c>
-      <c r="AS10">
-        <v>8.6</v>
-      </c>
       <c r="AT10">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU10">
         <v>6.4</v>
       </c>
       <c r="AV10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW10">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AX10">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY10">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AZ10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BA10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB10">
         <v>5.8</v>
       </c>
       <c r="BC10">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD10">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE10">
+        <v>8</v>
+      </c>
+      <c r="BF10">
+        <v>4.7</v>
+      </c>
+      <c r="BG10">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BF10">
-        <v>3.45</v>
-      </c>
-      <c r="BG10">
-        <v>8.4</v>
       </c>
       <c r="BH10">
         <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BO10">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BP10">
         <v>7.8</v>
       </c>
       <c r="BQ10">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR10">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
         <v>7.4</v>
@@ -3371,22 +3371,22 @@
         <v>16.5</v>
       </c>
       <c r="BU10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA10">
         <v>5.8</v>
@@ -3418,7 +3418,7 @@
         <v>1.17</v>
       </c>
       <c r="H11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I11">
         <v>32</v>
@@ -3442,19 +3442,19 @@
         <v>1.15</v>
       </c>
       <c r="P11">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R11">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S11">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T11">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
         <v>1.58</v>
@@ -3481,7 +3481,7 @@
         <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AD11">
         <v>950</v>
@@ -3499,7 +3499,7 @@
         <v>200</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AJ11">
         <v>9.199999999999999</v>
@@ -3514,61 +3514,61 @@
         <v>360</v>
       </c>
       <c r="AN11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ11">
+        <v>7.8</v>
+      </c>
+      <c r="AR11">
+        <v>8.4</v>
+      </c>
+      <c r="AS11">
+        <v>8.6</v>
+      </c>
+      <c r="AT11">
+        <v>9.6</v>
+      </c>
+      <c r="AU11">
+        <v>18</v>
+      </c>
+      <c r="AV11">
+        <v>8</v>
+      </c>
+      <c r="AW11">
+        <v>8.6</v>
+      </c>
+      <c r="AX11">
+        <v>6.8</v>
+      </c>
+      <c r="AY11">
+        <v>12.5</v>
+      </c>
+      <c r="AZ11">
+        <v>38</v>
+      </c>
+      <c r="BA11">
+        <v>8.4</v>
+      </c>
+      <c r="BB11">
         <v>7.2</v>
       </c>
-      <c r="AR11">
-        <v>7.6</v>
-      </c>
-      <c r="AS11">
-        <v>7.8</v>
-      </c>
-      <c r="AT11">
-        <v>5.4</v>
-      </c>
-      <c r="AU11">
-        <v>5.8</v>
-      </c>
-      <c r="AV11">
+      <c r="BC11">
+        <v>13.5</v>
+      </c>
+      <c r="BD11">
         <v>7.4</v>
       </c>
-      <c r="AW11">
-        <v>7.8</v>
-      </c>
-      <c r="AX11">
-        <v>4.9</v>
-      </c>
-      <c r="AY11">
-        <v>5.4</v>
-      </c>
-      <c r="AZ11">
-        <v>6.8</v>
-      </c>
-      <c r="BA11">
-        <v>7.8</v>
-      </c>
-      <c r="BB11">
-        <v>4.9</v>
-      </c>
-      <c r="BC11">
-        <v>5.3</v>
-      </c>
-      <c r="BD11">
-        <v>6.8</v>
-      </c>
       <c r="BE11">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF11">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BG11">
         <v>10.5</v>
@@ -3580,16 +3580,16 @@
         <v>4.1</v>
       </c>
       <c r="BJ11">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BK11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN11">
         <v>3.7</v>
@@ -3604,28 +3604,28 @@
         <v>4.5</v>
       </c>
       <c r="BR11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BU11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ11">
         <v>7.2</v>
@@ -3666,7 +3666,7 @@
         <v>10.5</v>
       </c>
       <c r="J12">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K12">
         <v>5.9</v>
@@ -3678,25 +3678,25 @@
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P12">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q12">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R12">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S12">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="T12">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U12">
         <v>2.38</v>
@@ -3705,22 +3705,22 @@
         <v>1.1</v>
       </c>
       <c r="W12">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="X12">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y12">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="Z12">
         <v>110</v>
       </c>
       <c r="AA12">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AB12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC12">
         <v>14.5</v>
@@ -3732,16 +3732,16 @@
         <v>110</v>
       </c>
       <c r="AF12">
+        <v>12</v>
+      </c>
+      <c r="AG12">
         <v>11.5</v>
       </c>
-      <c r="AG12">
-        <v>11</v>
-      </c>
       <c r="AH12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI12">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AJ12">
         <v>13</v>
@@ -3750,22 +3750,22 @@
         <v>13</v>
       </c>
       <c r="AL12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM12">
-        <v>310</v>
+        <v>85</v>
       </c>
       <c r="AN12">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AR12">
         <v>60</v>
@@ -3774,28 +3774,28 @@
         <v>65</v>
       </c>
       <c r="AT12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU12">
         <v>13</v>
       </c>
       <c r="AV12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW12">
         <v>40</v>
       </c>
       <c r="AX12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY12">
         <v>10</v>
       </c>
       <c r="AZ12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA12">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BB12">
         <v>12</v>
@@ -3810,10 +3810,10 @@
         <v>32</v>
       </c>
       <c r="BF12">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BG12">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH12">
         <v>5.6</v>
@@ -3849,7 +3849,7 @@
         <v>18</v>
       </c>
       <c r="BS12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT12">
         <v>13</v>
@@ -3861,16 +3861,16 @@
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CA12">
         <v>5.4</v>
@@ -3896,19 +3896,19 @@
         <v>179</v>
       </c>
       <c r="F13">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G13">
         <v>2.74</v>
       </c>
       <c r="H13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I13">
         <v>2.66</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K13">
         <v>3.95</v>
@@ -3926,13 +3926,13 @@
         <v>1.18</v>
       </c>
       <c r="P13">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q13">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R13">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S13">
         <v>2.38</v>
@@ -3941,7 +3941,7 @@
         <v>1.51</v>
       </c>
       <c r="U13">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="V13">
         <v>1.6</v>
@@ -3950,16 +3950,16 @@
         <v>1.57</v>
       </c>
       <c r="X13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y13">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z13">
         <v>22</v>
       </c>
       <c r="AA13">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB13">
         <v>18</v>
@@ -3968,10 +3968,10 @@
         <v>9.6</v>
       </c>
       <c r="AD13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF13">
         <v>23</v>
@@ -3983,13 +3983,13 @@
         <v>14</v>
       </c>
       <c r="AI13">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AJ13">
         <v>40</v>
       </c>
       <c r="AK13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL13">
         <v>29</v>
@@ -3998,7 +3998,7 @@
         <v>48</v>
       </c>
       <c r="AN13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO13">
         <v>13.5</v>
@@ -4007,19 +4007,19 @@
         <v>23</v>
       </c>
       <c r="AQ13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR13">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS13">
         <v>36</v>
       </c>
       <c r="AT13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV13">
         <v>11</v>
@@ -4028,13 +4028,13 @@
         <v>21</v>
       </c>
       <c r="AX13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY13">
         <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA13">
         <v>25</v>
@@ -4067,7 +4067,7 @@
         <v>8.4</v>
       </c>
       <c r="BK13">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL13">
         <v>65</v>
@@ -4138,7 +4138,7 @@
         <v>180</v>
       </c>
       <c r="F14">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="G14">
         <v>3.25</v>
@@ -4147,19 +4147,19 @@
         <v>2.2</v>
       </c>
       <c r="I14">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J14">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L14">
         <v>1.23</v>
       </c>
       <c r="M14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N14">
         <v>7.6</v>
@@ -4168,58 +4168,58 @@
         <v>1.13</v>
       </c>
       <c r="P14">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q14">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R14">
         <v>1.9</v>
       </c>
       <c r="S14">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T14">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U14">
         <v>3.2</v>
       </c>
       <c r="V14">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W14">
         <v>1.45</v>
       </c>
       <c r="X14">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="Y14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z14">
+        <v>26</v>
+      </c>
+      <c r="AA14">
+        <v>36</v>
+      </c>
+      <c r="AB14">
         <v>32</v>
-      </c>
-      <c r="AA14">
-        <v>44</v>
-      </c>
-      <c r="AB14">
-        <v>40</v>
       </c>
       <c r="AC14">
         <v>11.5</v>
       </c>
       <c r="AD14">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AE14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF14">
         <v>34</v>
       </c>
       <c r="AG14">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH14">
         <v>14</v>
@@ -4243,19 +4243,19 @@
         <v>14.5</v>
       </c>
       <c r="AO14">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AP14">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AQ14">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR14">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AS14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT14">
         <v>21</v>
@@ -4264,46 +4264,46 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV14">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AW14">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AX14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY14">
         <v>13.5</v>
       </c>
       <c r="AZ14">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BB14">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BC14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH14">
         <v>6.2</v>
       </c>
       <c r="BI14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ14">
         <v>9.800000000000001</v>
@@ -4321,7 +4321,7 @@
         <v>8.6</v>
       </c>
       <c r="BO14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP14">
         <v>24</v>
@@ -4383,19 +4383,19 @@
         <v>3.55</v>
       </c>
       <c r="G15">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H15">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I15">
         <v>2.22</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K15">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L15">
         <v>1.36</v>
@@ -4404,67 +4404,67 @@
         <v>1.06</v>
       </c>
       <c r="N15">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O15">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P15">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q15">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R15">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S15">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T15">
         <v>1.68</v>
       </c>
       <c r="U15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W15">
         <v>1.37</v>
       </c>
       <c r="X15">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y15">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA15">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AB15">
         <v>17</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF15">
         <v>29</v>
       </c>
       <c r="AG15">
+        <v>16.5</v>
+      </c>
+      <c r="AH15">
         <v>17</v>
-      </c>
-      <c r="AH15">
-        <v>17.5</v>
       </c>
       <c r="AI15">
         <v>34</v>
@@ -4485,79 +4485,79 @@
         <v>36</v>
       </c>
       <c r="AO15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP15">
         <v>14.5</v>
       </c>
       <c r="AQ15">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS15">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AT15">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU15">
         <v>7.2</v>
       </c>
       <c r="AV15">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ15">
         <v>13.5</v>
       </c>
       <c r="BA15">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BB15">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="BC15">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="BD15">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BE15">
-        <v>6.4</v>
+        <v>55</v>
       </c>
       <c r="BF15">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="BG15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH15">
         <v>4.2</v>
       </c>
       <c r="BI15">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15">
         <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL15">
         <v>120</v>
       </c>
       <c r="BM15">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BN15">
         <v>7.8</v>
@@ -4566,13 +4566,13 @@
         <v>5.4</v>
       </c>
       <c r="BP15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ15">
         <v>4.7</v>
       </c>
       <c r="BR15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS15">
         <v>4.9</v>
@@ -4587,13 +4587,13 @@
         <v>18</v>
       </c>
       <c r="BW15">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="BX15">
         <v>32</v>
       </c>
       <c r="BY15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4622,19 +4622,19 @@
         <v>182</v>
       </c>
       <c r="F16">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G16">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H16">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I16">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K16">
         <v>3.85</v>
@@ -4652,7 +4652,7 @@
         <v>1.28</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
         <v>1.84</v>
@@ -4664,16 +4664,16 @@
         <v>3.15</v>
       </c>
       <c r="T16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U16">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W16">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X16">
         <v>17.5</v>
@@ -4682,13 +4682,13 @@
         <v>14.5</v>
       </c>
       <c r="Z16">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AA16">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB16">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC16">
         <v>8.800000000000001</v>
@@ -4697,13 +4697,13 @@
         <v>14.5</v>
       </c>
       <c r="AE16">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AF16">
         <v>17</v>
       </c>
       <c r="AG16">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH16">
         <v>17</v>
@@ -4712,70 +4712,70 @@
         <v>55</v>
       </c>
       <c r="AJ16">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK16">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AL16">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AM16">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO16">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AP16">
+        <v>14</v>
+      </c>
+      <c r="AQ16">
         <v>12</v>
       </c>
-      <c r="AQ16">
-        <v>10</v>
-      </c>
       <c r="AR16">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS16">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="AT16">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU16">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV16">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AX16">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY16">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA16">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BB16">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BC16">
         <v>18</v>
       </c>
       <c r="BD16">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BE16">
-        <v>7.2</v>
+        <v>60</v>
       </c>
       <c r="BF16">
         <v>12.5</v>
@@ -4784,10 +4784,10 @@
         <v>21</v>
       </c>
       <c r="BH16">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI16">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BJ16">
         <v>9.4</v>
@@ -4808,10 +4808,10 @@
         <v>4.6</v>
       </c>
       <c r="BP16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ16">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR16">
         <v>38</v>
@@ -4826,7 +4826,7 @@
         <v>5.6</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW16">
         <v>7.6</v>
@@ -4864,40 +4864,40 @@
         <v>183</v>
       </c>
       <c r="F17">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J17">
         <v>3.25</v>
       </c>
       <c r="K17">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L17">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M17">
         <v>1.08</v>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O17">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P17">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q17">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R17">
         <v>1.32</v>
@@ -4906,13 +4906,13 @@
         <v>3.85</v>
       </c>
       <c r="T17">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U17">
         <v>2.08</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
         <v>1.6</v>
@@ -4924,25 +4924,25 @@
         <v>13.5</v>
       </c>
       <c r="Z17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA17">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AB17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD17">
         <v>16</v>
       </c>
       <c r="AE17">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AF17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG17">
         <v>14.5</v>
@@ -4954,10 +4954,10 @@
         <v>120</v>
       </c>
       <c r="AJ17">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AK17">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AL17">
         <v>55</v>
@@ -4972,97 +4972,97 @@
         <v>44</v>
       </c>
       <c r="AP17">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ17">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AR17">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AS17">
-        <v>4.9</v>
+        <v>36</v>
       </c>
       <c r="AT17">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17">
         <v>6.8</v>
       </c>
       <c r="AV17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW17">
-        <v>4.7</v>
+        <v>26</v>
       </c>
       <c r="AX17">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AY17">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA17">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BB17">
-        <v>4.7</v>
+        <v>26</v>
       </c>
       <c r="BC17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD17">
         <v>30</v>
       </c>
       <c r="BE17">
-        <v>5.1</v>
+        <v>75</v>
       </c>
       <c r="BF17">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BG17">
-        <v>4.8</v>
+        <v>23</v>
       </c>
       <c r="BH17">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BI17">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BJ17">
         <v>9.800000000000001</v>
       </c>
       <c r="BK17">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN17">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP17">
         <v>20</v>
       </c>
       <c r="BQ17">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT17">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU17">
         <v>4.7</v>
@@ -5071,13 +5071,13 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5106,16 +5106,16 @@
         <v>184</v>
       </c>
       <c r="F18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G18">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H18">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="I18">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J18">
         <v>4.1</v>
@@ -5130,13 +5130,13 @@
         <v>1.04</v>
       </c>
       <c r="N18">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O18">
         <v>1.2</v>
       </c>
       <c r="P18">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q18">
         <v>1.61</v>
@@ -5151,10 +5151,10 @@
         <v>1.61</v>
       </c>
       <c r="U18">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V18">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W18">
         <v>1.3</v>
@@ -5166,10 +5166,10 @@
         <v>13</v>
       </c>
       <c r="Z18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB18">
         <v>23</v>
@@ -5181,7 +5181,7 @@
         <v>10.5</v>
       </c>
       <c r="AE18">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF18">
         <v>36</v>
@@ -5193,7 +5193,7 @@
         <v>15.5</v>
       </c>
       <c r="AI18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ18">
         <v>85</v>
@@ -5232,7 +5232,7 @@
         <v>9</v>
       </c>
       <c r="AV18">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW18">
         <v>15.5</v>
@@ -5250,7 +5250,7 @@
         <v>23</v>
       </c>
       <c r="BB18">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BC18">
         <v>38</v>
@@ -5280,7 +5280,7 @@
         <v>5.1</v>
       </c>
       <c r="BL18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BM18">
         <v>10</v>
@@ -5348,16 +5348,16 @@
         <v>185</v>
       </c>
       <c r="F19">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G19">
         <v>2.44</v>
       </c>
       <c r="H19">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I19">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J19">
         <v>3.55</v>
@@ -5369,31 +5369,31 @@
         <v>1.39</v>
       </c>
       <c r="M19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O19">
         <v>1.3</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q19">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T19">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U19">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V19">
         <v>1.44</v>
@@ -5402,25 +5402,25 @@
         <v>1.69</v>
       </c>
       <c r="X19">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y19">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA19">
         <v>65</v>
       </c>
       <c r="AB19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC19">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE19">
         <v>36</v>
@@ -5429,19 +5429,19 @@
         <v>16.5</v>
       </c>
       <c r="AG19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
         <v>17</v>
       </c>
       <c r="AI19">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ19">
         <v>34</v>
       </c>
       <c r="AK19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL19">
         <v>38</v>
@@ -5450,64 +5450,64 @@
         <v>90</v>
       </c>
       <c r="AN19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP19">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR19">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AS19">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AT19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW19">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX19">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY19">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19">
         <v>14.5</v>
       </c>
       <c r="BA19">
+        <v>36</v>
+      </c>
+      <c r="BB19">
+        <v>26</v>
+      </c>
+      <c r="BC19">
+        <v>21</v>
+      </c>
+      <c r="BD19">
         <v>30</v>
       </c>
-      <c r="BB19">
-        <v>19</v>
-      </c>
-      <c r="BC19">
-        <v>20</v>
-      </c>
-      <c r="BD19">
-        <v>18.5</v>
-      </c>
       <c r="BE19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BF19">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BG19">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BH19">
         <v>3.6</v>
@@ -5537,13 +5537,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ19">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR19">
         <v>32</v>
       </c>
       <c r="BS19">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT19">
         <v>6.6</v>
@@ -5552,22 +5552,22 @@
         <v>5.5</v>
       </c>
       <c r="BV19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY19">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ19">
         <v>26</v>
       </c>
       <c r="CA19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB19" t="s">
         <v>208</v>
@@ -5590,55 +5590,55 @@
         <v>186</v>
       </c>
       <c r="F20">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G20">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H20">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I20">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J20">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
         <v>1.29</v>
       </c>
       <c r="M20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N20">
         <v>5.7</v>
       </c>
       <c r="O20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P20">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q20">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R20">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S20">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T20">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U20">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V20">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="W20">
         <v>1.35</v>
@@ -5653,7 +5653,7 @@
         <v>16.5</v>
       </c>
       <c r="AA20">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB20">
         <v>21</v>
@@ -5665,19 +5665,19 @@
         <v>11.5</v>
       </c>
       <c r="AE20">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AF20">
         <v>34</v>
       </c>
       <c r="AG20">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AH20">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI20">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AJ20">
         <v>75</v>
@@ -5692,10 +5692,10 @@
         <v>65</v>
       </c>
       <c r="AN20">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO20">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AP20">
         <v>19.5</v>
@@ -5704,7 +5704,7 @@
         <v>12.5</v>
       </c>
       <c r="AR20">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS20">
         <v>20</v>
@@ -5722,7 +5722,7 @@
         <v>14</v>
       </c>
       <c r="AX20">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AY20">
         <v>12</v>
@@ -5731,19 +5731,19 @@
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB20">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BC20">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD20">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="BE20">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF20">
         <v>18</v>
@@ -5758,16 +5758,16 @@
         <v>3.6</v>
       </c>
       <c r="BJ20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BK20">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BL20">
         <v>85</v>
       </c>
       <c r="BM20">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BN20">
         <v>8.4</v>
@@ -5776,40 +5776,40 @@
         <v>5.8</v>
       </c>
       <c r="BP20">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BQ20">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BR20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS20">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BT20">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BU20">
         <v>4.2</v>
       </c>
       <c r="BV20">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BW20">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BX20">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BY20">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BZ20">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="CA20">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="CB20" t="s">
         <v>208</v>
@@ -5835,10 +5835,10 @@
         <v>2.14</v>
       </c>
       <c r="G21">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H21">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I21">
         <v>3.35</v>
@@ -5862,28 +5862,28 @@
         <v>1.17</v>
       </c>
       <c r="P21">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q21">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R21">
         <v>1.71</v>
       </c>
       <c r="S21">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T21">
         <v>1.53</v>
       </c>
       <c r="U21">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V21">
         <v>1.42</v>
       </c>
       <c r="W21">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X21">
         <v>30</v>
@@ -5940,13 +5940,13 @@
         <v>18.5</v>
       </c>
       <c r="AP21">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AQ21">
         <v>17.5</v>
       </c>
       <c r="AR21">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AS21">
         <v>24</v>
@@ -5961,7 +5961,7 @@
         <v>12.5</v>
       </c>
       <c r="AW21">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX21">
         <v>15</v>
@@ -5973,10 +5973,10 @@
         <v>12.5</v>
       </c>
       <c r="BA21">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB21">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC21">
         <v>16.5</v>
@@ -5994,64 +5994,64 @@
         <v>15.5</v>
       </c>
       <c r="BH21">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI21">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BJ21">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BK21">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BN21">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO21">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP21">
         <v>14.5</v>
       </c>
       <c r="BQ21">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR21">
         <v>22</v>
       </c>
       <c r="BS21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT21">
         <v>7.2</v>
       </c>
-      <c r="BT21">
-        <v>7.4</v>
-      </c>
       <c r="BU21">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV21">
         <v>22</v>
       </c>
       <c r="BW21">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX21">
         <v>27</v>
       </c>
       <c r="BY21">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ21">
         <v>14</v>
       </c>
       <c r="CA21">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="CB21" t="s">
         <v>208</v>
@@ -6074,10 +6074,10 @@
         <v>188</v>
       </c>
       <c r="F22">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G22">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="H22">
         <v>6.6</v>
@@ -6089,49 +6089,49 @@
         <v>4</v>
       </c>
       <c r="K22">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L22">
         <v>1.38</v>
       </c>
       <c r="M22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N22">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O22">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P22">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q22">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R22">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S22">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T22">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U22">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V22">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W22">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="X22">
         <v>19</v>
       </c>
       <c r="Y22">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z22">
         <v>60</v>
@@ -6143,40 +6143,40 @@
         <v>8.6</v>
       </c>
       <c r="AC22">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD22">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE22">
         <v>240</v>
       </c>
       <c r="AF22">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG22">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI22">
         <v>320</v>
       </c>
       <c r="AJ22">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK22">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL22">
         <v>38</v>
       </c>
       <c r="AM22">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN22">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO22">
         <v>530</v>
@@ -6188,10 +6188,10 @@
         <v>18.5</v>
       </c>
       <c r="AR22">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AS22">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AT22">
         <v>7.4</v>
@@ -6200,34 +6200,34 @@
         <v>8.4</v>
       </c>
       <c r="AV22">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW22">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AX22">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY22">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ22">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA22">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BB22">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC22">
         <v>14.5</v>
       </c>
       <c r="BD22">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="BE22">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BF22">
         <v>7.8</v>
@@ -6236,25 +6236,25 @@
         <v>18</v>
       </c>
       <c r="BH22">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI22">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK22">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BN22">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO22">
         <v>3.6</v>
@@ -6263,13 +6263,13 @@
         <v>11</v>
       </c>
       <c r="BQ22">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR22">
         <v>27</v>
       </c>
       <c r="BS22">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT22">
         <v>10.5</v>
@@ -6281,19 +6281,19 @@
         <v>60</v>
       </c>
       <c r="BW22">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX22">
         <v>65</v>
       </c>
       <c r="BY22">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA22">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="s">
         <v>208</v>
@@ -6319,7 +6319,7 @@
         <v>4.1</v>
       </c>
       <c r="G23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H23">
         <v>2.02</v>
@@ -6328,16 +6328,16 @@
         <v>2.1</v>
       </c>
       <c r="J23">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K23">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L23">
         <v>1.42</v>
       </c>
       <c r="M23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
         <v>3.75</v>
@@ -6346,31 +6346,31 @@
         <v>1.34</v>
       </c>
       <c r="P23">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q23">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R23">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S23">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T23">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U23">
         <v>2.04</v>
       </c>
       <c r="V23">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="W23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X23">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y23">
         <v>9.199999999999999</v>
@@ -6403,13 +6403,13 @@
         <v>20</v>
       </c>
       <c r="AI23">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ23">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="AK23">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL23">
         <v>65</v>
@@ -6418,25 +6418,25 @@
         <v>580</v>
       </c>
       <c r="AN23">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO23">
         <v>16.5</v>
       </c>
       <c r="AP23">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR23">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS23">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT23">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU23">
         <v>7.2</v>
@@ -6445,34 +6445,34 @@
         <v>9</v>
       </c>
       <c r="AW23">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AX23">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY23">
         <v>14</v>
       </c>
       <c r="AZ23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA23">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="BB23">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="BC23">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BD23">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BE23">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BF23">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BG23">
         <v>14</v>
@@ -6499,31 +6499,31 @@
         <v>7.8</v>
       </c>
       <c r="BO23">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BP23">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ23">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR23">
         <v>48</v>
       </c>
       <c r="BS23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT23">
         <v>4.9</v>
       </c>
       <c r="BU23">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BV23">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW23">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX23">
         <v>30</v>
@@ -6564,43 +6564,43 @@
         <v>2.34</v>
       </c>
       <c r="H24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I24">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J24">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K24">
         <v>3.85</v>
       </c>
       <c r="L24">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M24">
         <v>1.06</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O24">
         <v>1.29</v>
       </c>
       <c r="P24">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q24">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R24">
         <v>1.4</v>
       </c>
       <c r="S24">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T24">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U24">
         <v>2.24</v>
@@ -6612,16 +6612,16 @@
         <v>1.74</v>
       </c>
       <c r="X24">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Y24">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z24">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AA24">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AB24">
         <v>11.5</v>
@@ -6633,13 +6633,13 @@
         <v>14.5</v>
       </c>
       <c r="AE24">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AF24">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH24">
         <v>17</v>
@@ -6648,22 +6648,22 @@
         <v>55</v>
       </c>
       <c r="AJ24">
+        <v>36</v>
+      </c>
+      <c r="AK24">
         <v>32</v>
       </c>
-      <c r="AK24">
-        <v>40</v>
-      </c>
       <c r="AL24">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AM24">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="AN24">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO24">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP24">
         <v>14</v>
@@ -6672,10 +6672,10 @@
         <v>12</v>
       </c>
       <c r="AR24">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AS24">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="AT24">
         <v>9.6</v>
@@ -6699,34 +6699,34 @@
         <v>14</v>
       </c>
       <c r="BA24">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BB24">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BC24">
         <v>20</v>
       </c>
       <c r="BD24">
-        <v>8.6</v>
+        <v>26</v>
       </c>
       <c r="BE24">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="BF24">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG24">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BH24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI24">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BJ24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK24">
         <v>3.75</v>
@@ -6735,25 +6735,25 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BN24">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO24">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP24">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ24">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR24">
         <v>34</v>
       </c>
       <c r="BS24">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BT24">
         <v>7.6</v>
@@ -6765,13 +6765,13 @@
         <v>30</v>
       </c>
       <c r="BW24">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY24">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6806,19 +6806,19 @@
         <v>3.75</v>
       </c>
       <c r="H25">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I25">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J25">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K25">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L25">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M25">
         <v>1.14</v>
@@ -6833,7 +6833,7 @@
         <v>1.47</v>
       </c>
       <c r="Q25">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R25">
         <v>1.16</v>
@@ -6842,10 +6842,10 @@
         <v>5.9</v>
       </c>
       <c r="T25">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U25">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V25">
         <v>1.56</v>
@@ -6857,7 +6857,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y25">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>16</v>
@@ -6881,7 +6881,7 @@
         <v>25</v>
       </c>
       <c r="AG25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH25">
         <v>34</v>
@@ -6932,7 +6932,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AX25">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY25">
         <v>14</v>
@@ -6947,25 +6947,25 @@
         <v>25</v>
       </c>
       <c r="BC25">
+        <v>8.4</v>
+      </c>
+      <c r="BD25">
         <v>8.6</v>
       </c>
-      <c r="BD25">
-        <v>9</v>
-      </c>
       <c r="BE25">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF25">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG25">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BH25">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI25">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ25">
         <v>13.5</v>
@@ -6977,7 +6977,7 @@
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BN25">
         <v>6.6</v>
@@ -6989,7 +6989,7 @@
         <v>40</v>
       </c>
       <c r="BQ25">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR25">
         <v>1000</v>
@@ -7007,19 +7007,19 @@
         <v>28</v>
       </c>
       <c r="BW25">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX25">
         <v>60</v>
       </c>
       <c r="BY25">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ25">
         <v>70</v>
       </c>
       <c r="CA25">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB25" t="s">
         <v>208</v>
@@ -7042,16 +7042,16 @@
         <v>192</v>
       </c>
       <c r="F26">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G26">
         <v>3.05</v>
       </c>
       <c r="H26">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I26">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J26">
         <v>3.15</v>
@@ -7072,22 +7072,22 @@
         <v>1.43</v>
       </c>
       <c r="P26">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q26">
         <v>2.28</v>
       </c>
       <c r="R26">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S26">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T26">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U26">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V26">
         <v>1.52</v>
@@ -7102,13 +7102,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA26">
         <v>55</v>
       </c>
       <c r="AB26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC26">
         <v>7.4</v>
@@ -7147,22 +7147,22 @@
         <v>46</v>
       </c>
       <c r="AO26">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP26">
         <v>9.4</v>
       </c>
       <c r="AQ26">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR26">
         <v>8.4</v>
       </c>
       <c r="AS26">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT26">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU26">
         <v>6.6</v>
@@ -7171,7 +7171,7 @@
         <v>11</v>
       </c>
       <c r="AW26">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX26">
         <v>16.5</v>
@@ -7183,19 +7183,19 @@
         <v>16.5</v>
       </c>
       <c r="BA26">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB26">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC26">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="BD26">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE26">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF26">
         <v>6.6</v>
@@ -7204,25 +7204,25 @@
         <v>6.8</v>
       </c>
       <c r="BH26">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI26">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK26">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN26">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO26">
         <v>4.4</v>
@@ -7237,7 +7237,7 @@
         <v>50</v>
       </c>
       <c r="BS26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT26">
         <v>6.8</v>
@@ -7246,19 +7246,19 @@
         <v>4.3</v>
       </c>
       <c r="BV26">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX26">
         <v>50</v>
       </c>
       <c r="BY26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ26">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CA26">
         <v>4.4</v>
@@ -7290,19 +7290,19 @@
         <v>3.7</v>
       </c>
       <c r="H27">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I27">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="J27">
         <v>3.2</v>
       </c>
       <c r="K27">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L27">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M27">
         <v>1.11</v>
@@ -7329,22 +7329,22 @@
         <v>2.18</v>
       </c>
       <c r="U27">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V27">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W27">
         <v>1.37</v>
       </c>
       <c r="X27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="Z27">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AA27">
         <v>38</v>
@@ -7356,13 +7356,13 @@
         <v>7.8</v>
       </c>
       <c r="AD27">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AE27">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AF27">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG27">
         <v>16</v>
@@ -7392,7 +7392,7 @@
         <v>46</v>
       </c>
       <c r="AP27">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ27">
         <v>4.4</v>
@@ -7401,67 +7401,67 @@
         <v>7</v>
       </c>
       <c r="AS27">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT27">
         <v>5.1</v>
       </c>
       <c r="AU27">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV27">
         <v>8.4</v>
       </c>
       <c r="AW27">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX27">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AY27">
+        <v>4.6</v>
+      </c>
+      <c r="AZ27">
+        <v>14.5</v>
+      </c>
+      <c r="BA27">
         <v>5.9</v>
       </c>
-      <c r="AZ27">
-        <v>7</v>
-      </c>
-      <c r="BA27">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BB27">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BC27">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BD27">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BE27">
+        <v>6.2</v>
+      </c>
+      <c r="BF27">
         <v>9</v>
       </c>
-      <c r="BF27">
-        <v>8.6</v>
-      </c>
       <c r="BG27">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH27">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI27">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BJ27">
         <v>14</v>
       </c>
       <c r="BK27">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BN27">
         <v>8</v>
@@ -7470,7 +7470,7 @@
         <v>5.1</v>
       </c>
       <c r="BP27">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BQ27">
         <v>4.6</v>
@@ -7479,7 +7479,7 @@
         <v>75</v>
       </c>
       <c r="BS27">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT27">
         <v>5.9</v>
@@ -7491,19 +7491,19 @@
         <v>26</v>
       </c>
       <c r="BW27">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BX27">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY27">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ27">
         <v>65</v>
       </c>
       <c r="CA27">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB27" t="s">
         <v>208</v>
@@ -7526,22 +7526,22 @@
         <v>194</v>
       </c>
       <c r="F28">
+        <v>1.9</v>
+      </c>
+      <c r="G28">
         <v>1.92</v>
       </c>
-      <c r="G28">
-        <v>1.95</v>
-      </c>
       <c r="H28">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J28">
         <v>3.5</v>
       </c>
       <c r="K28">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L28">
         <v>1.5</v>
@@ -7568,163 +7568,163 @@
         <v>4.5</v>
       </c>
       <c r="T28">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U28">
         <v>1.83</v>
       </c>
       <c r="V28">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W28">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X28">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y28">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z28">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA28">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB28">
         <v>7.6</v>
       </c>
       <c r="AC28">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD28">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE28">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF28">
+        <v>10.5</v>
+      </c>
+      <c r="AG28">
         <v>13</v>
-      </c>
-      <c r="AG28">
-        <v>10.5</v>
       </c>
       <c r="AH28">
         <v>24</v>
       </c>
       <c r="AI28">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ28">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AK28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL28">
         <v>48</v>
       </c>
       <c r="AM28">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AN28">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AO28">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP28">
         <v>9.6</v>
       </c>
       <c r="AQ28">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR28">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AS28">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AT28">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU28">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV28">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AW28">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AX28">
         <v>9.199999999999999</v>
       </c>
       <c r="AY28">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ28">
+        <v>20</v>
+      </c>
+      <c r="BA28">
+        <v>44</v>
+      </c>
+      <c r="BB28">
         <v>18.5</v>
       </c>
-      <c r="BA28">
-        <v>7</v>
-      </c>
-      <c r="BB28">
-        <v>19</v>
-      </c>
       <c r="BC28">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD28">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BE28">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BF28">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG28">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="BH28">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI28">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ28">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK28">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="BN28">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BO28">
         <v>3.85</v>
       </c>
       <c r="BP28">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ28">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BR28">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BS28">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BT28">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU28">
         <v>6.2</v>
@@ -7733,19 +7733,19 @@
         <v>60</v>
       </c>
       <c r="BW28">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BX28">
         <v>75</v>
       </c>
       <c r="BY28">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BZ28">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="CA28">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="CB28" t="s">
         <v>208</v>
@@ -7792,19 +7792,19 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="O29">
         <v>1.05</v>
       </c>
       <c r="P29">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q29">
         <v>1.19</v>
       </c>
       <c r="R29">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="S29">
         <v>1.49</v>
@@ -7813,7 +7813,7 @@
         <v>1.24</v>
       </c>
       <c r="U29">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="V29">
         <v>1.01</v>
@@ -7900,7 +7900,7 @@
         <v>16</v>
       </c>
       <c r="AX29">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AY29">
         <v>14</v>
@@ -7933,55 +7933,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BI29">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="BJ29">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK29">
         <v>6</v>
       </c>
       <c r="BL29">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BN29">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BO29">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP29">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BQ29">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BR29">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BS29">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BT29">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU29">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="BV29">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BW29">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BX29">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BY29">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BZ29">
         <v>0</v>
@@ -8019,7 +8019,7 @@
         <v>2.26</v>
       </c>
       <c r="I30">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J30">
         <v>3.25</v>
@@ -8028,43 +8028,43 @@
         <v>3.9</v>
       </c>
       <c r="L30">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M30">
         <v>1.07</v>
       </c>
       <c r="N30">
+        <v>3.65</v>
+      </c>
+      <c r="O30">
+        <v>1.32</v>
+      </c>
+      <c r="P30">
+        <v>1.9</v>
+      </c>
+      <c r="Q30">
+        <v>1.97</v>
+      </c>
+      <c r="R30">
+        <v>1.34</v>
+      </c>
+      <c r="S30">
         <v>3.5</v>
       </c>
-      <c r="O30">
-        <v>1.31</v>
-      </c>
-      <c r="P30">
-        <v>1.86</v>
-      </c>
-      <c r="Q30">
-        <v>1.92</v>
-      </c>
-      <c r="R30">
-        <v>1.33</v>
-      </c>
-      <c r="S30">
-        <v>3.35</v>
-      </c>
       <c r="T30">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="U30">
         <v>2.08</v>
       </c>
       <c r="V30">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W30">
         <v>1.4</v>
       </c>
       <c r="X30">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y30">
         <v>10.5</v>
@@ -8121,13 +8121,13 @@
         <v>5.8</v>
       </c>
       <c r="AQ30">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR30">
         <v>13</v>
       </c>
       <c r="AS30">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="AT30">
         <v>10.5</v>
@@ -8139,37 +8139,37 @@
         <v>9.6</v>
       </c>
       <c r="AW30">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX30">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY30">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="AZ30">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA30">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB30">
         <v>6</v>
       </c>
       <c r="BC30">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD30">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE30">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF30">
         <v>7.2</v>
       </c>
       <c r="BG30">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH30">
         <v>3.8</v>
@@ -8196,7 +8196,7 @@
         <v>3.2</v>
       </c>
       <c r="BP30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ30">
         <v>4.8</v>
@@ -8214,10 +8214,10 @@
         <v>4.2</v>
       </c>
       <c r="BV30">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW30">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX30">
         <v>36</v>
@@ -8252,16 +8252,16 @@
         <v>197</v>
       </c>
       <c r="F31">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G31">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H31">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I31">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J31">
         <v>3.25</v>
@@ -8276,7 +8276,7 @@
         <v>1.1</v>
       </c>
       <c r="N31">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O31">
         <v>1.47</v>
@@ -8285,7 +8285,7 @@
         <v>1.66</v>
       </c>
       <c r="Q31">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R31">
         <v>1.24</v>
@@ -8303,7 +8303,7 @@
         <v>1.27</v>
       </c>
       <c r="W31">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X31">
         <v>11.5</v>
@@ -8342,7 +8342,7 @@
         <v>370</v>
       </c>
       <c r="AJ31">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK31">
         <v>30</v>
@@ -8369,7 +8369,7 @@
         <v>13</v>
       </c>
       <c r="AS31">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT31">
         <v>5.8</v>
@@ -8381,7 +8381,7 @@
         <v>14</v>
       </c>
       <c r="AW31">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX31">
         <v>10</v>
@@ -8393,7 +8393,7 @@
         <v>14</v>
       </c>
       <c r="BA31">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB31">
         <v>20</v>
@@ -8402,7 +8402,7 @@
         <v>20</v>
       </c>
       <c r="BD31">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE31">
         <v>6</v>
@@ -8411,67 +8411,67 @@
         <v>17.5</v>
       </c>
       <c r="BG31">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH31">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BI31">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BJ31">
         <v>12.5</v>
       </c>
       <c r="BK31">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN31">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO31">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BQ31">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BR31">
         <v>42</v>
       </c>
       <c r="BS31">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BT31">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU31">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="BV31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW31">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BZ31">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CA31">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="CB31" t="s">
         <v>208</v>
@@ -8500,55 +8500,55 @@
         <v>4.7</v>
       </c>
       <c r="H32">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="I32">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J32">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K32">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L32">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N32">
         <v>3.55</v>
       </c>
       <c r="O32">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P32">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q32">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R32">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S32">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="T32">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="U32">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V32">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W32">
         <v>1.27</v>
       </c>
       <c r="X32">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -8557,31 +8557,31 @@
         <v>12.5</v>
       </c>
       <c r="AA32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB32">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AC32">
         <v>8.4</v>
       </c>
       <c r="AD32">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE32">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF32">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG32">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH32">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI32">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ32">
         <v>110</v>
@@ -8593,19 +8593,19 @@
         <v>75</v>
       </c>
       <c r="AM32">
-        <v>390</v>
+        <v>130</v>
       </c>
       <c r="AN32">
         <v>75</v>
       </c>
       <c r="AO32">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AP32">
         <v>11</v>
       </c>
       <c r="AQ32">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR32">
         <v>10</v>
@@ -8614,7 +8614,7 @@
         <v>19.5</v>
       </c>
       <c r="AT32">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU32">
         <v>7</v>
@@ -8623,7 +8623,7 @@
         <v>9</v>
       </c>
       <c r="AW32">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AX32">
         <v>24</v>
@@ -8638,16 +8638,16 @@
         <v>28</v>
       </c>
       <c r="BB32">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BC32">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD32">
         <v>28</v>
       </c>
       <c r="BE32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF32">
         <v>10.5</v>
@@ -8656,64 +8656,64 @@
         <v>11.5</v>
       </c>
       <c r="BH32">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI32">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="BJ32">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK32">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BN32">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BO32">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP32">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="BQ32">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BR32">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BS32">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BT32">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BU32">
         <v>3.6</v>
       </c>
       <c r="BV32">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BW32">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="BX32">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BY32">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BZ32">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="CA32">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="CB32" t="s">
         <v>208</v>
@@ -8760,7 +8760,7 @@
         <v>1.11</v>
       </c>
       <c r="N33">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O33">
         <v>1.46</v>
@@ -8769,7 +8769,7 @@
         <v>1.64</v>
       </c>
       <c r="Q33">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R33">
         <v>1.23</v>
@@ -8820,7 +8820,7 @@
         <v>12.5</v>
       </c>
       <c r="AH33">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AI33">
         <v>70</v>
@@ -8853,7 +8853,7 @@
         <v>20</v>
       </c>
       <c r="AS33">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT33">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>13</v>
       </c>
       <c r="AW33">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX33">
         <v>12.5</v>
@@ -8877,25 +8877,25 @@
         <v>18</v>
       </c>
       <c r="BA33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB33">
+        <v>8</v>
+      </c>
+      <c r="BC33">
+        <v>7.8</v>
+      </c>
+      <c r="BD33">
         <v>8.6</v>
       </c>
-      <c r="BB33">
-        <v>7.8</v>
-      </c>
-      <c r="BC33">
-        <v>7.6</v>
-      </c>
-      <c r="BD33">
-        <v>8.4</v>
-      </c>
       <c r="BE33">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF33">
         <v>7.6</v>
       </c>
       <c r="BG33">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH33">
         <v>2.92</v>
@@ -8978,10 +8978,10 @@
         <v>200</v>
       </c>
       <c r="F34">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G34">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H34">
         <v>2.6</v>
@@ -8990,7 +8990,7 @@
         <v>2.62</v>
       </c>
       <c r="J34">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K34">
         <v>3.05</v>
@@ -9011,7 +9011,7 @@
         <v>1.49</v>
       </c>
       <c r="Q34">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R34">
         <v>1.17</v>
@@ -9020,7 +9020,7 @@
         <v>6.4</v>
       </c>
       <c r="T34">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U34">
         <v>1.74</v>
@@ -9032,7 +9032,7 @@
         <v>1.39</v>
       </c>
       <c r="X34">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>7.4</v>
@@ -9047,7 +9047,7 @@
         <v>9</v>
       </c>
       <c r="AC34">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD34">
         <v>13.5</v>
@@ -9056,7 +9056,7 @@
         <v>42</v>
       </c>
       <c r="AF34">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG34">
         <v>16.5</v>
@@ -9065,7 +9065,7 @@
         <v>26</v>
       </c>
       <c r="AI34">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AJ34">
         <v>80</v>
@@ -9074,10 +9074,10 @@
         <v>65</v>
       </c>
       <c r="AL34">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN34">
         <v>90</v>
@@ -9122,7 +9122,7 @@
         <v>34</v>
       </c>
       <c r="BB34">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BC34">
         <v>50</v>
@@ -9140,7 +9140,7 @@
         <v>40</v>
       </c>
       <c r="BH34">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI34">
         <v>2.2</v>
@@ -9149,55 +9149,55 @@
         <v>13.5</v>
       </c>
       <c r="BK34">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>6.4</v>
+        <v>90</v>
       </c>
       <c r="BN34">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BO34">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BP34">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ34">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BT34">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BU34">
         <v>4.1</v>
       </c>
       <c r="BV34">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BW34">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BX34">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY34">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BZ34">
         <v>65</v>
       </c>
       <c r="CA34">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="CB34" t="s">
         <v>208</v>
@@ -9220,10 +9220,10 @@
         <v>201</v>
       </c>
       <c r="F35">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="G35">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H35">
         <v>2.88</v>
@@ -9241,7 +9241,7 @@
         <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N35">
         <v>1.01</v>
@@ -9280,7 +9280,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z35">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AA35">
         <v>900</v>
@@ -9304,7 +9304,7 @@
         <v>14</v>
       </c>
       <c r="AH35">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AI35">
         <v>85</v>
@@ -9313,7 +9313,7 @@
         <v>120</v>
       </c>
       <c r="AK35">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AL35">
         <v>500</v>
@@ -9337,7 +9337,7 @@
         <v>16</v>
       </c>
       <c r="AS35">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT35">
         <v>7.4</v>
@@ -9373,7 +9373,7 @@
         <v>10.5</v>
       </c>
       <c r="BE35">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF35">
         <v>10</v>
@@ -9462,22 +9462,22 @@
         <v>202</v>
       </c>
       <c r="F36">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="G36">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="H36">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I36">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="J36">
         <v>3.55</v>
       </c>
       <c r="K36">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L36">
         <v>1.49</v>
@@ -9486,7 +9486,7 @@
         <v>1.09</v>
       </c>
       <c r="N36">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O36">
         <v>1.42</v>
@@ -9507,13 +9507,13 @@
         <v>2.02</v>
       </c>
       <c r="U36">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V36">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W36">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X36">
         <v>13</v>
@@ -9528,19 +9528,19 @@
         <v>900</v>
       </c>
       <c r="AB36">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC36">
         <v>8.6</v>
       </c>
       <c r="AD36">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE36">
         <v>480</v>
       </c>
       <c r="AF36">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG36">
         <v>11.5</v>
@@ -9564,7 +9564,7 @@
         <v>580</v>
       </c>
       <c r="AN36">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO36">
         <v>700</v>
@@ -9576,52 +9576,52 @@
         <v>12.5</v>
       </c>
       <c r="AR36">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="AS36">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT36">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU36">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV36">
         <v>16.5</v>
       </c>
       <c r="AW36">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX36">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY36">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ36">
         <v>19.5</v>
       </c>
       <c r="BA36">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC36">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD36">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE36">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF36">
         <v>11.5</v>
       </c>
       <c r="BG36">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH36">
         <v>3.35</v>
@@ -9639,16 +9639,16 @@
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>7.8</v>
+        <v>75</v>
       </c>
       <c r="BN36">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO36">
         <v>3.8</v>
       </c>
       <c r="BP36">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BQ36">
         <v>10.5</v>
@@ -9657,7 +9657,7 @@
         <v>38</v>
       </c>
       <c r="BS36">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT36">
         <v>8.800000000000001</v>
@@ -9669,13 +9669,13 @@
         <v>55</v>
       </c>
       <c r="BW36">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BZ36">
         <v>34</v>
@@ -9704,49 +9704,49 @@
         <v>203</v>
       </c>
       <c r="F37">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G37">
         <v>3.6</v>
       </c>
       <c r="H37">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I37">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J37">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K37">
         <v>3.35</v>
       </c>
       <c r="L37">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M37">
         <v>1.11</v>
       </c>
       <c r="N37">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O37">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P37">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q37">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R37">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S37">
         <v>4.8</v>
       </c>
       <c r="T37">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U37">
         <v>1.87</v>
@@ -9755,7 +9755,7 @@
         <v>1.57</v>
       </c>
       <c r="W37">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -9791,7 +9791,7 @@
         <v>22</v>
       </c>
       <c r="AI37">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AJ37">
         <v>900</v>
@@ -9800,7 +9800,7 @@
         <v>55</v>
       </c>
       <c r="AL37">
-        <v>160</v>
+        <v>380</v>
       </c>
       <c r="AM37">
         <v>580</v>
@@ -9821,7 +9821,7 @@
         <v>7</v>
       </c>
       <c r="AS37">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT37">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7</v>
       </c>
       <c r="AW37">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX37">
         <v>18.5</v>
@@ -9848,28 +9848,28 @@
         <v>8</v>
       </c>
       <c r="BB37">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC37">
         <v>8</v>
-      </c>
-      <c r="BC37">
-        <v>7.8</v>
       </c>
       <c r="BD37">
         <v>8.199999999999999</v>
       </c>
       <c r="BE37">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF37">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG37">
         <v>29</v>
       </c>
       <c r="BH37">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI37">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ37">
         <v>11</v>
@@ -9893,7 +9893,7 @@
         <v>32</v>
       </c>
       <c r="BQ37">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR37">
         <v>1000</v>
@@ -9946,10 +9946,10 @@
         <v>204</v>
       </c>
       <c r="F38">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G38">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H38">
         <v>2.32</v>
@@ -9958,28 +9958,28 @@
         <v>2.46</v>
       </c>
       <c r="J38">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K38">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L38">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M38">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N38">
         <v>3.9</v>
       </c>
       <c r="O38">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P38">
         <v>2</v>
       </c>
       <c r="Q38">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R38">
         <v>1.37</v>
@@ -9988,40 +9988,40 @@
         <v>3.35</v>
       </c>
       <c r="T38">
+        <v>1.74</v>
+      </c>
+      <c r="U38">
+        <v>2.16</v>
+      </c>
+      <c r="V38">
         <v>1.69</v>
       </c>
-      <c r="U38">
-        <v>1.85</v>
-      </c>
-      <c r="V38">
-        <v>1.68</v>
-      </c>
       <c r="W38">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X38">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z38">
         <v>17</v>
       </c>
       <c r="AA38">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AB38">
         <v>14</v>
       </c>
       <c r="AC38">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD38">
         <v>12</v>
       </c>
       <c r="AE38">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AF38">
         <v>25</v>
@@ -10033,115 +10033,115 @@
         <v>17.5</v>
       </c>
       <c r="AI38">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ38">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK38">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL38">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM38">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN38">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO38">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AP38">
-        <v>2.98</v>
+        <v>5.6</v>
       </c>
       <c r="AQ38">
-        <v>2.36</v>
+        <v>9</v>
       </c>
       <c r="AR38">
-        <v>2.54</v>
+        <v>13.5</v>
       </c>
       <c r="AS38">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT38">
-        <v>2.46</v>
+        <v>11</v>
       </c>
       <c r="AU38">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="AV38">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW38">
-        <v>2.78</v>
+        <v>18</v>
       </c>
       <c r="AX38">
-        <v>2.66</v>
+        <v>6.2</v>
       </c>
       <c r="AY38">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="AZ38">
-        <v>2.56</v>
+        <v>14</v>
       </c>
       <c r="BA38">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="BB38">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="BC38">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="BD38">
-        <v>3</v>
+        <v>16.5</v>
       </c>
       <c r="BE38">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="BF38">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="BG38">
-        <v>2.7</v>
+        <v>13.5</v>
       </c>
       <c r="BH38">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI38">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="BJ38">
         <v>11.5</v>
       </c>
       <c r="BK38">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BL38">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BM38">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN38">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO38">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP38">
         <v>32</v>
       </c>
       <c r="BQ38">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR38">
         <v>44</v>
       </c>
       <c r="BS38">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT38">
         <v>6.4</v>
@@ -10150,22 +10150,22 @@
         <v>4.1</v>
       </c>
       <c r="BV38">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW38">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BX38">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY38">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BZ38">
         <v>32</v>
       </c>
       <c r="CA38">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB38" t="s">
         <v>208</v>
@@ -10188,22 +10188,22 @@
         <v>205</v>
       </c>
       <c r="F39">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G39">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H39">
         <v>2.86</v>
       </c>
       <c r="I39">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J39">
         <v>3.2</v>
       </c>
       <c r="K39">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L39">
         <v>1.45</v>
@@ -10215,19 +10215,19 @@
         <v>3.5</v>
       </c>
       <c r="O39">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P39">
         <v>1.83</v>
       </c>
       <c r="Q39">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R39">
         <v>1.31</v>
       </c>
       <c r="S39">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T39">
         <v>1.82</v>
@@ -10236,7 +10236,7 @@
         <v>2.04</v>
       </c>
       <c r="V39">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
         <v>1.54</v>
@@ -10353,7 +10353,7 @@
         <v>3.3</v>
       </c>
       <c r="BI39">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ39">
         <v>10.5</v>
@@ -10380,7 +10380,7 @@
         <v>7</v>
       </c>
       <c r="BR39">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS39">
         <v>8.199999999999999</v>
@@ -10436,7 +10436,7 @@
         <v>1.74</v>
       </c>
       <c r="H40">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I40">
         <v>6.6</v>
@@ -10460,13 +10460,13 @@
         <v>1.31</v>
       </c>
       <c r="P40">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q40">
         <v>1.94</v>
       </c>
       <c r="R40">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S40">
         <v>3.45</v>
@@ -10499,7 +10499,7 @@
         <v>10.5</v>
       </c>
       <c r="AC40">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD40">
         <v>23</v>
@@ -10532,124 +10532,124 @@
         <v>140</v>
       </c>
       <c r="AN40">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AO40">
         <v>120</v>
       </c>
       <c r="AP40">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AQ40">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="AR40">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS40">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT40">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="AU40">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="AV40">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AW40">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX40">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AY40">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="AZ40">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="BA40">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB40">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="BC40">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="BD40">
         <v>20</v>
       </c>
       <c r="BE40">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF40">
         <v>4.4</v>
       </c>
       <c r="BG40">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH40">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI40">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ40">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK40">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN40">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO40">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP40">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ40">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BR40">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS40">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT40">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU40">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BV40">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW40">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX40">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY40">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ40">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA40">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB40" t="s">
         <v>208</v>
@@ -10684,7 +10684,7 @@
         <v>3.5</v>
       </c>
       <c r="J41">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K41">
         <v>3.2</v>
@@ -10705,19 +10705,19 @@
         <v>1.52</v>
       </c>
       <c r="Q41">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R41">
         <v>1.18</v>
       </c>
       <c r="S41">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T41">
         <v>2.1</v>
       </c>
       <c r="U41">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V41">
         <v>1.4</v>
@@ -10738,7 +10738,7 @@
         <v>80</v>
       </c>
       <c r="AB41">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC41">
         <v>7.4</v>
@@ -10783,25 +10783,25 @@
         <v>6.2</v>
       </c>
       <c r="AQ41">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR41">
         <v>17.5</v>
       </c>
       <c r="AS41">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="AT41">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU41">
         <v>6</v>
       </c>
       <c r="AV41">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW41">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX41">
         <v>13.5</v>
@@ -10810,40 +10810,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ41">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA41">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB41">
+        <v>6.8</v>
+      </c>
+      <c r="BC41">
+        <v>6.8</v>
+      </c>
+      <c r="BD41">
+        <v>32</v>
+      </c>
+      <c r="BE41">
+        <v>7.6</v>
+      </c>
+      <c r="BF41">
         <v>7</v>
       </c>
-      <c r="BC41">
-        <v>7</v>
-      </c>
-      <c r="BD41">
-        <v>7.4</v>
-      </c>
-      <c r="BE41">
-        <v>7.8</v>
-      </c>
-      <c r="BF41">
+      <c r="BG41">
         <v>7.2</v>
-      </c>
-      <c r="BG41">
-        <v>7.4</v>
       </c>
       <c r="BH41">
         <v>3</v>
       </c>
       <c r="BI41">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ41">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK41">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BL41">
         <v>1000</v>
@@ -10858,7 +10858,7 @@
         <v>4.1</v>
       </c>
       <c r="BP41">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ41">
         <v>4.4</v>
@@ -10870,10 +10870,10 @@
         <v>4.7</v>
       </c>
       <c r="BT41">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU41">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV41">
         <v>40</v>
@@ -10882,16 +10882,16 @@
         <v>4.5</v>
       </c>
       <c r="BX41">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY41">
         <v>4.8</v>
       </c>
       <c r="BZ41">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="CA41">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB41" t="s">
         <v>208</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-10.xlsx
@@ -649,7 +649,7 @@
     <t>Real Soacha Cundinamarca FC</t>
   </si>
   <si>
-    <t>2026-08-10 08:12:44</t>
+    <t>2026-08-10 10:22:49</t>
   </si>
 </sst>
 </file>
@@ -1243,226 +1243,226 @@
         <v>170</v>
       </c>
       <c r="F2">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="G2">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="L2">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
         <v>1.44</v>
       </c>
       <c r="P2">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="Q2">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="S2">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="U2">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="V2">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="W2">
-        <v>2.12</v>
+        <v>3.85</v>
       </c>
       <c r="X2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AD2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="AG2">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AH2">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AI2">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AK2">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AL2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AO2">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AQ2">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AR2">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AS2">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AT2">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV2">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AW2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AX2">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="BB2">
         <v>12</v>
       </c>
       <c r="BC2">
-        <v>9.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="BD2">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BE2">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="BF2">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="BG2">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>211</v>
@@ -1485,43 +1485,43 @@
         <v>171</v>
       </c>
       <c r="F3">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H3">
         <v>3.5</v>
       </c>
       <c r="I3">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O3">
         <v>1.27</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="R3">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S3">
         <v>3.1</v>
@@ -1533,118 +1533,118 @@
         <v>2.16</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z3">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC3">
-        <v>42</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE3">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AF3">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG3">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AI3">
         <v>100</v>
       </c>
       <c r="AJ3">
-        <v>900</v>
+        <v>26</v>
       </c>
       <c r="AK3">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AL3">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AM3">
         <v>580</v>
       </c>
       <c r="AN3">
-        <v>600</v>
+        <v>12.5</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP3">
-        <v>1.72</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3">
+        <v>14.5</v>
+      </c>
+      <c r="AR3">
+        <v>11</v>
+      </c>
+      <c r="AS3">
+        <v>18</v>
+      </c>
+      <c r="AT3">
+        <v>10</v>
+      </c>
+      <c r="AU3">
+        <v>7.8</v>
+      </c>
+      <c r="AV3">
+        <v>12.5</v>
+      </c>
+      <c r="AW3">
+        <v>14.5</v>
+      </c>
+      <c r="AX3">
+        <v>12.5</v>
+      </c>
+      <c r="AY3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3">
+        <v>13.5</v>
+      </c>
+      <c r="BA3">
+        <v>17.5</v>
+      </c>
+      <c r="BB3">
+        <v>20</v>
+      </c>
+      <c r="BC3">
+        <v>17.5</v>
+      </c>
+      <c r="BD3">
+        <v>20</v>
+      </c>
+      <c r="BE3">
+        <v>7.6</v>
+      </c>
+      <c r="BF3">
+        <v>10</v>
+      </c>
+      <c r="BG3">
         <v>6.8</v>
-      </c>
-      <c r="AR3">
-        <v>1.69</v>
-      </c>
-      <c r="AS3">
-        <v>1.7</v>
-      </c>
-      <c r="AT3">
-        <v>6.4</v>
-      </c>
-      <c r="AU3">
-        <v>4.9</v>
-      </c>
-      <c r="AV3">
-        <v>6.2</v>
-      </c>
-      <c r="AW3">
-        <v>1.68</v>
-      </c>
-      <c r="AX3">
-        <v>7.8</v>
-      </c>
-      <c r="AY3">
-        <v>5.2</v>
-      </c>
-      <c r="AZ3">
-        <v>7</v>
-      </c>
-      <c r="BA3">
-        <v>1.69</v>
-      </c>
-      <c r="BB3">
-        <v>1.69</v>
-      </c>
-      <c r="BC3">
-        <v>2.5</v>
-      </c>
-      <c r="BD3">
-        <v>1.68</v>
-      </c>
-      <c r="BE3">
-        <v>1.7</v>
-      </c>
-      <c r="BF3">
-        <v>4.9</v>
-      </c>
-      <c r="BG3">
-        <v>1.72</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1733,13 +1733,13 @@
         <v>2.14</v>
       </c>
       <c r="H4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I4">
         <v>4.1</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
         <v>3.8</v>
@@ -1751,58 +1751,58 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q4">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S4">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T4">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="U4">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
         <v>1.87</v>
       </c>
       <c r="X4">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Y4">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
         <v>32</v>
       </c>
       <c r="AA4">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB4">
         <v>19</v>
       </c>
       <c r="AC4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE4">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF4">
         <v>16.5</v>
@@ -1817,40 +1817,40 @@
         <v>65</v>
       </c>
       <c r="AJ4">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="AK4">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="AL4">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AM4">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="AO4">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP4">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR4">
         <v>25</v>
       </c>
       <c r="AS4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AT4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU4">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AV4">
         <v>14</v>
@@ -1859,19 +1859,19 @@
         <v>20</v>
       </c>
       <c r="AX4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA4">
         <v>24</v>
       </c>
       <c r="BB4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4">
         <v>17.5</v>
@@ -1880,67 +1880,67 @@
         <v>23</v>
       </c>
       <c r="BE4">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BF4">
         <v>10.5</v>
       </c>
       <c r="BG4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1969,226 +1969,226 @@
         <v>173</v>
       </c>
       <c r="F5">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="G5">
+        <v>2.86</v>
+      </c>
+      <c r="H5">
+        <v>2.94</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>3.15</v>
+      </c>
+      <c r="K5">
         <v>3.3</v>
       </c>
-      <c r="H5">
-        <v>2.82</v>
-      </c>
-      <c r="I5">
-        <v>2.98</v>
-      </c>
-      <c r="J5">
-        <v>2.86</v>
-      </c>
-      <c r="K5">
-        <v>2.98</v>
-      </c>
       <c r="L5">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="M5">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N5">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="O5">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="P5">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="R5">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S5">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="T5">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="U5">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="V5">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="X5">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Z5">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AA5">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AB5">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
+        <v>7.2</v>
+      </c>
+      <c r="AD5">
+        <v>13.5</v>
+      </c>
+      <c r="AE5">
+        <v>46</v>
+      </c>
+      <c r="AF5">
+        <v>16.5</v>
+      </c>
+      <c r="AG5">
+        <v>13</v>
+      </c>
+      <c r="AH5">
+        <v>24</v>
+      </c>
+      <c r="AI5">
+        <v>90</v>
+      </c>
+      <c r="AJ5">
+        <v>55</v>
+      </c>
+      <c r="AK5">
         <v>42</v>
       </c>
-      <c r="AD5">
-        <v>970</v>
-      </c>
-      <c r="AE5">
-        <v>120</v>
-      </c>
-      <c r="AF5">
-        <v>38</v>
-      </c>
-      <c r="AG5">
-        <v>970</v>
-      </c>
-      <c r="AH5">
-        <v>1000</v>
-      </c>
-      <c r="AI5">
-        <v>190</v>
-      </c>
-      <c r="AJ5">
-        <v>900</v>
-      </c>
-      <c r="AK5">
-        <v>150</v>
-      </c>
       <c r="AL5">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="AM5">
         <v>500</v>
       </c>
       <c r="AN5">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AO5">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AP5">
-        <v>3.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ5">
-        <v>3.85</v>
+        <v>8.6</v>
       </c>
       <c r="AR5">
-        <v>1.99</v>
+        <v>14.5</v>
       </c>
       <c r="AS5">
-        <v>1.66</v>
+        <v>48</v>
       </c>
       <c r="AT5">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="AU5">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>1.66</v>
+        <v>34</v>
       </c>
       <c r="AX5">
-        <v>1.74</v>
+        <v>15</v>
       </c>
       <c r="AY5">
-        <v>2.06</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5">
-        <v>1.78</v>
+        <v>21</v>
       </c>
       <c r="BA5">
-        <v>1.67</v>
+        <v>46</v>
       </c>
       <c r="BB5">
-        <v>1.67</v>
+        <v>34</v>
       </c>
       <c r="BC5">
-        <v>1.67</v>
+        <v>29</v>
       </c>
       <c r="BD5">
-        <v>1.67</v>
+        <v>46</v>
       </c>
       <c r="BE5">
-        <v>1.68</v>
+        <v>65</v>
       </c>
       <c r="BF5">
-        <v>1.55</v>
+        <v>38</v>
       </c>
       <c r="BG5">
-        <v>1.55</v>
+        <v>46</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="CB5" t="s">
         <v>211</v>
@@ -2211,22 +2211,22 @@
         <v>174</v>
       </c>
       <c r="F6">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="G6">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="H6">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="I6">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J6">
         <v>3.4</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
         <v>1.44</v>
@@ -2235,7 +2235,7 @@
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O6">
         <v>1.37</v>
@@ -2247,85 +2247,85 @@
         <v>2.12</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="X6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y6">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z6">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AA6">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AB6">
         <v>10.5</v>
       </c>
       <c r="AC6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
+        <v>16.5</v>
+      </c>
+      <c r="AE6">
+        <v>42</v>
+      </c>
+      <c r="AF6">
         <v>17.5</v>
       </c>
-      <c r="AE6">
+      <c r="AG6">
+        <v>12</v>
+      </c>
+      <c r="AH6">
+        <v>23</v>
+      </c>
+      <c r="AI6">
+        <v>60</v>
+      </c>
+      <c r="AJ6">
+        <v>36</v>
+      </c>
+      <c r="AK6">
+        <v>29</v>
+      </c>
+      <c r="AL6">
+        <v>44</v>
+      </c>
+      <c r="AM6">
+        <v>130</v>
+      </c>
+      <c r="AN6">
+        <v>26</v>
+      </c>
+      <c r="AO6">
         <v>46</v>
-      </c>
-      <c r="AF6">
-        <v>14</v>
-      </c>
-      <c r="AG6">
-        <v>12.5</v>
-      </c>
-      <c r="AH6">
-        <v>22</v>
-      </c>
-      <c r="AI6">
-        <v>75</v>
-      </c>
-      <c r="AJ6">
-        <v>34</v>
-      </c>
-      <c r="AK6">
-        <v>34</v>
-      </c>
-      <c r="AL6">
-        <v>55</v>
-      </c>
-      <c r="AM6">
-        <v>120</v>
-      </c>
-      <c r="AN6">
-        <v>24</v>
-      </c>
-      <c r="AO6">
-        <v>55</v>
       </c>
       <c r="AP6">
         <v>10</v>
       </c>
       <c r="AQ6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AS6">
         <v>50</v>
@@ -2337,13 +2337,13 @@
         <v>6.8</v>
       </c>
       <c r="AV6">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AW6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AX6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY6">
         <v>10</v>
@@ -2352,85 +2352,85 @@
         <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB6">
         <v>26</v>
       </c>
       <c r="BC6">
+        <v>24</v>
+      </c>
+      <c r="BD6">
+        <v>32</v>
+      </c>
+      <c r="BE6">
+        <v>80</v>
+      </c>
+      <c r="BF6">
         <v>22</v>
       </c>
-      <c r="BD6">
-        <v>34</v>
-      </c>
-      <c r="BE6">
-        <v>75</v>
-      </c>
-      <c r="BF6">
-        <v>16.5</v>
-      </c>
       <c r="BG6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB6" t="s">
         <v>211</v>
@@ -2456,16 +2456,16 @@
         <v>1.7</v>
       </c>
       <c r="G7">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="H7">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K7">
         <v>4.4</v>
@@ -2477,25 +2477,25 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R7">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S7">
         <v>2.92</v>
       </c>
       <c r="T7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U7">
         <v>2.08</v>
@@ -2504,19 +2504,19 @@
         <v>1.22</v>
       </c>
       <c r="W7">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Y7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z7">
         <v>50</v>
       </c>
       <c r="AA7">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB7">
         <v>11.5</v>
@@ -2531,13 +2531,13 @@
         <v>80</v>
       </c>
       <c r="AF7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG7">
         <v>11</v>
       </c>
       <c r="AH7">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
         <v>75</v>
@@ -2546,25 +2546,25 @@
         <v>19.5</v>
       </c>
       <c r="AK7">
+        <v>16.5</v>
+      </c>
+      <c r="AL7">
+        <v>30</v>
+      </c>
+      <c r="AM7">
+        <v>110</v>
+      </c>
+      <c r="AN7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO7">
+        <v>65</v>
+      </c>
+      <c r="AP7">
+        <v>18</v>
+      </c>
+      <c r="AQ7">
         <v>19.5</v>
-      </c>
-      <c r="AL7">
-        <v>40</v>
-      </c>
-      <c r="AM7">
-        <v>200</v>
-      </c>
-      <c r="AN7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO7">
-        <v>120</v>
-      </c>
-      <c r="AP7">
-        <v>15</v>
-      </c>
-      <c r="AQ7">
-        <v>19</v>
       </c>
       <c r="AR7">
         <v>34</v>
@@ -2576,13 +2576,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX7">
         <v>10</v>
@@ -2594,7 +2594,7 @@
         <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB7">
         <v>16</v>
@@ -2695,7 +2695,7 @@
         <v>176</v>
       </c>
       <c r="F8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G8">
         <v>1.32</v>
@@ -2704,31 +2704,31 @@
         <v>10.5</v>
       </c>
       <c r="I8">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="J8">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O8">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P8">
         <v>2.32</v>
       </c>
       <c r="Q8">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R8">
         <v>1.5</v>
@@ -2737,13 +2737,13 @@
         <v>2.78</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="U8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V8">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W8">
         <v>4</v>
@@ -2776,7 +2776,7 @@
         <v>970</v>
       </c>
       <c r="AG8">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
         <v>950</v>
@@ -2785,7 +2785,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>900</v>
+        <v>16.5</v>
       </c>
       <c r="AK8">
         <v>970</v>
@@ -2803,10 +2803,10 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AQ8">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
         <v>4.2</v>
@@ -2818,10 +2818,10 @@
         <v>4.4</v>
       </c>
       <c r="AU8">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AV8">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AW8">
         <v>2.5</v>
@@ -2830,31 +2830,31 @@
         <v>4.4</v>
       </c>
       <c r="AY8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AZ8">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="BA8">
         <v>4.2</v>
       </c>
       <c r="BB8">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC8">
         <v>6.2</v>
       </c>
       <c r="BD8">
-        <v>2.12</v>
+        <v>12.5</v>
       </c>
       <c r="BE8">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="BF8">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BG8">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2940,73 +2940,73 @@
         <v>2.14</v>
       </c>
       <c r="G9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I9">
         <v>4.2</v>
       </c>
       <c r="J9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N9">
         <v>3.1</v>
       </c>
       <c r="O9">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P9">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T9">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="U9">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y9">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA9">
         <v>110</v>
       </c>
       <c r="AB9">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC9">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9">
         <v>19.5</v>
@@ -3018,25 +3018,25 @@
         <v>12.5</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ9">
         <v>32</v>
       </c>
       <c r="AK9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM9">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN9">
         <v>24</v>
@@ -3045,28 +3045,28 @@
         <v>85</v>
       </c>
       <c r="AP9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ9">
         <v>11</v>
       </c>
       <c r="AR9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS9">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AT9">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV9">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX9">
         <v>10.5</v>
@@ -3078,25 +3078,25 @@
         <v>19</v>
       </c>
       <c r="BA9">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE9">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="BF9">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG9">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3126,7 +3126,7 @@
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR9">
         <v>1000</v>
@@ -3179,58 +3179,58 @@
         <v>178</v>
       </c>
       <c r="F10">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="G10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H10">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I10">
         <v>2.8</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L10">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M10">
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P10">
         <v>1.63</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T10">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U10">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V10">
         <v>1.56</v>
       </c>
       <c r="W10">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X10">
         <v>970</v>
@@ -3254,10 +3254,10 @@
         <v>970</v>
       </c>
       <c r="AE10">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AF10">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AG10">
         <v>970</v>
@@ -3266,16 +3266,16 @@
         <v>950</v>
       </c>
       <c r="AI10">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AJ10">
         <v>500</v>
       </c>
       <c r="AK10">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL10">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AM10">
         <v>580</v>
@@ -3308,7 +3308,7 @@
         <v>5.7</v>
       </c>
       <c r="AW10">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AX10">
         <v>8.4</v>
@@ -3317,7 +3317,7 @@
         <v>6.6</v>
       </c>
       <c r="AZ10">
-        <v>1.88</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA10">
         <v>1.92</v>
@@ -3335,7 +3335,7 @@
         <v>1.94</v>
       </c>
       <c r="BF10">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BG10">
         <v>1.94</v>
@@ -3421,22 +3421,22 @@
         <v>179</v>
       </c>
       <c r="F11">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="G11">
         <v>1.16</v>
       </c>
       <c r="H11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="J11">
         <v>9.4</v>
       </c>
       <c r="K11">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="L11">
         <v>1.25</v>
@@ -3445,139 +3445,139 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>1.15</v>
       </c>
       <c r="P11">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R11">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S11">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T11">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="U11">
-        <v>1.26</v>
+        <v>1.59</v>
       </c>
       <c r="V11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W11">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="X11">
+        <v>40</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>380</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>13</v>
+      </c>
+      <c r="AC11">
+        <v>28</v>
+      </c>
+      <c r="AD11">
         <v>950</v>
       </c>
-      <c r="Y11">
-        <v>1000</v>
-      </c>
-      <c r="Z11">
-        <v>1000</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>1000</v>
-      </c>
-      <c r="AC11">
-        <v>1000</v>
-      </c>
-      <c r="AD11">
-        <v>1000</v>
-      </c>
       <c r="AE11">
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG11">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL11">
         <v>330</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AN11">
-        <v>29</v>
+        <v>3.15</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
+        <v>6.4</v>
+      </c>
+      <c r="AQ11">
+        <v>7.6</v>
+      </c>
+      <c r="AR11">
+        <v>7.6</v>
+      </c>
+      <c r="AS11">
+        <v>7.8</v>
+      </c>
+      <c r="AT11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV11">
+        <v>7.2</v>
+      </c>
+      <c r="AW11">
+        <v>7.8</v>
+      </c>
+      <c r="AX11">
         <v>6.6</v>
       </c>
-      <c r="AQ11">
-        <v>4.2</v>
-      </c>
-      <c r="AR11">
-        <v>15</v>
-      </c>
-      <c r="AS11">
-        <v>4.2</v>
-      </c>
-      <c r="AT11">
-        <v>5.2</v>
-      </c>
-      <c r="AU11">
-        <v>1.15</v>
-      </c>
-      <c r="AV11">
-        <v>4.2</v>
-      </c>
-      <c r="AW11">
-        <v>4.2</v>
-      </c>
-      <c r="AX11">
-        <v>3.85</v>
-      </c>
       <c r="AY11">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AZ11">
-        <v>1.15</v>
+        <v>7</v>
       </c>
       <c r="BA11">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BC11">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>1.14</v>
+        <v>7</v>
       </c>
       <c r="BE11">
-        <v>1.15</v>
+        <v>7.6</v>
       </c>
       <c r="BF11">
-        <v>1.06</v>
+        <v>2.92</v>
       </c>
       <c r="BG11">
         <v>10.5</v>
@@ -3663,16 +3663,16 @@
         <v>180</v>
       </c>
       <c r="F12">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G12">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H12">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I12">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J12">
         <v>3.9</v>
@@ -3693,7 +3693,7 @@
         <v>1.18</v>
       </c>
       <c r="P12">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q12">
         <v>1.58</v>
@@ -3708,31 +3708,31 @@
         <v>1.51</v>
       </c>
       <c r="U12">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="V12">
         <v>1.6</v>
       </c>
       <c r="W12">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X12">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="Y12">
         <v>17</v>
       </c>
       <c r="Z12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB12">
         <v>17.5</v>
       </c>
       <c r="AC12">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD12">
         <v>12</v>
@@ -3741,10 +3741,10 @@
         <v>24</v>
       </c>
       <c r="AF12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH12">
         <v>13.5</v>
@@ -3753,34 +3753,34 @@
         <v>29</v>
       </c>
       <c r="AJ12">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AK12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL12">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM12">
         <v>50</v>
       </c>
       <c r="AN12">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR12">
         <v>19</v>
       </c>
       <c r="AS12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT12">
         <v>15.5</v>
@@ -3789,7 +3789,7 @@
         <v>9</v>
       </c>
       <c r="AV12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW12">
         <v>21</v>
@@ -3798,7 +3798,7 @@
         <v>20</v>
       </c>
       <c r="AY12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ12">
         <v>12.5</v>
@@ -3816,10 +3816,10 @@
         <v>26</v>
       </c>
       <c r="BE12">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BF12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG12">
         <v>12.5</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
@@ -3840,13 +3840,13 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>55</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BP12">
         <v>1000</v>
@@ -3864,7 +3864,7 @@
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BV12">
         <v>1000</v>
@@ -3905,19 +3905,19 @@
         <v>181</v>
       </c>
       <c r="F13">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G13">
         <v>3.4</v>
       </c>
       <c r="H13">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I13">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
         <v>4.5</v>
@@ -3926,145 +3926,145 @@
         <v>1.23</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P13">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q13">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="R13">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="S13">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="T13">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="U13">
         <v>2.78</v>
       </c>
       <c r="V13">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="W13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X13">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Y13">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="Z13">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AA13">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="AB13">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AC13">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD13">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE13">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AF13">
+        <v>36</v>
+      </c>
+      <c r="AG13">
+        <v>16</v>
+      </c>
+      <c r="AH13">
+        <v>15</v>
+      </c>
+      <c r="AI13">
+        <v>25</v>
+      </c>
+      <c r="AJ13">
         <v>65</v>
       </c>
-      <c r="AG13">
-        <v>970</v>
-      </c>
-      <c r="AH13">
-        <v>970</v>
-      </c>
-      <c r="AI13">
+      <c r="AK13">
         <v>40</v>
       </c>
-      <c r="AJ13">
-        <v>220</v>
-      </c>
-      <c r="AK13">
-        <v>220</v>
-      </c>
       <c r="AL13">
-        <v>290</v>
+        <v>38</v>
       </c>
       <c r="AM13">
-        <v>580</v>
+        <v>46</v>
       </c>
       <c r="AN13">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AO13">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AP13">
-        <v>1.58</v>
+        <v>24</v>
       </c>
       <c r="AQ13">
-        <v>1.59</v>
+        <v>17</v>
       </c>
       <c r="AR13">
-        <v>1.61</v>
+        <v>18</v>
       </c>
       <c r="AS13">
-        <v>1.64</v>
+        <v>24</v>
       </c>
       <c r="AT13">
-        <v>1.62</v>
+        <v>24</v>
       </c>
       <c r="AU13">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AV13">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AW13">
-        <v>1.58</v>
+        <v>16</v>
       </c>
       <c r="AX13">
-        <v>1.62</v>
+        <v>29</v>
       </c>
       <c r="AY13">
-        <v>1.55</v>
+        <v>13.5</v>
       </c>
       <c r="AZ13">
+        <v>12.5</v>
+      </c>
+      <c r="BA13">
+        <v>19</v>
+      </c>
+      <c r="BB13">
+        <v>36</v>
+      </c>
+      <c r="BC13">
+        <v>26</v>
+      </c>
+      <c r="BD13">
+        <v>24</v>
+      </c>
+      <c r="BE13">
+        <v>32</v>
+      </c>
+      <c r="BF13">
+        <v>12.5</v>
+      </c>
+      <c r="BG13">
         <v>6.6</v>
-      </c>
-      <c r="BA13">
-        <v>1.59</v>
-      </c>
-      <c r="BB13">
-        <v>1.64</v>
-      </c>
-      <c r="BC13">
-        <v>1.49</v>
-      </c>
-      <c r="BD13">
-        <v>1.65</v>
-      </c>
-      <c r="BE13">
-        <v>1.65</v>
-      </c>
-      <c r="BF13">
-        <v>1.55</v>
-      </c>
-      <c r="BG13">
-        <v>1.61</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4147,19 +4147,19 @@
         <v>182</v>
       </c>
       <c r="F14">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="G14">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="H14">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="I14">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="J14">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K14">
         <v>3.75</v>
@@ -4171,34 +4171,34 @@
         <v>1.06</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O14">
         <v>1.3</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q14">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R14">
         <v>1.39</v>
       </c>
       <c r="S14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T14">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U14">
         <v>2.14</v>
       </c>
       <c r="V14">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="W14">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X14">
         <v>970</v>
@@ -4207,61 +4207,61 @@
         <v>970</v>
       </c>
       <c r="Z14">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AA14">
         <v>900</v>
       </c>
       <c r="AB14">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AC14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD14">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AE14">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AF14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG14">
         <v>15.5</v>
       </c>
       <c r="AH14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI14">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AJ14">
         <v>160</v>
       </c>
       <c r="AK14">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AL14">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AM14">
         <v>200</v>
       </c>
       <c r="AN14">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="AO14">
-        <v>55</v>
+        <v>15.5</v>
       </c>
       <c r="AP14">
         <v>7.8</v>
       </c>
       <c r="AQ14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS14">
         <v>24</v>
@@ -4276,91 +4276,91 @@
         <v>10</v>
       </c>
       <c r="AW14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX14">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AY14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AZ14">
         <v>9</v>
       </c>
       <c r="BA14">
+        <v>16.5</v>
+      </c>
+      <c r="BB14">
+        <v>6.4</v>
+      </c>
+      <c r="BC14">
         <v>16</v>
       </c>
-      <c r="BB14">
+      <c r="BD14">
+        <v>42</v>
+      </c>
+      <c r="BE14">
+        <v>6.4</v>
+      </c>
+      <c r="BF14">
+        <v>10</v>
+      </c>
+      <c r="BG14">
+        <v>13.5</v>
+      </c>
+      <c r="BH14">
+        <v>3.95</v>
+      </c>
+      <c r="BI14">
+        <v>2.92</v>
+      </c>
+      <c r="BJ14">
         <v>11</v>
       </c>
-      <c r="BC14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD14">
-        <v>20</v>
-      </c>
-      <c r="BE14">
+      <c r="BK14">
+        <v>7.2</v>
+      </c>
+      <c r="BL14">
+        <v>130</v>
+      </c>
+      <c r="BM14">
         <v>5.5</v>
       </c>
-      <c r="BF14">
-        <v>29</v>
-      </c>
-      <c r="BG14">
-        <v>15</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.04</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.04</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.04</v>
-      </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4389,25 +4389,25 @@
         <v>183</v>
       </c>
       <c r="F15">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="G15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H15">
         <v>3.25</v>
       </c>
       <c r="I15">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J15">
         <v>3.8</v>
       </c>
       <c r="K15">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L15">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M15">
         <v>1.06</v>
@@ -4425,31 +4425,31 @@
         <v>1.86</v>
       </c>
       <c r="R15">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S15">
         <v>3.2</v>
       </c>
       <c r="T15">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U15">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W15">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X15">
+        <v>18</v>
+      </c>
+      <c r="Y15">
         <v>16.5</v>
       </c>
-      <c r="Y15">
-        <v>17.5</v>
-      </c>
       <c r="Z15">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA15">
         <v>65</v>
@@ -4458,22 +4458,22 @@
         <v>12</v>
       </c>
       <c r="AC15">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD15">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE15">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF15">
         <v>17</v>
       </c>
       <c r="AG15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI15">
         <v>60</v>
@@ -4485,22 +4485,22 @@
         <v>24</v>
       </c>
       <c r="AL15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM15">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN15">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP15">
         <v>13.5</v>
       </c>
       <c r="AQ15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR15">
         <v>21</v>
@@ -4512,25 +4512,25 @@
         <v>10</v>
       </c>
       <c r="AU15">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX15">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ15">
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB15">
         <v>26</v>
@@ -4545,10 +4545,10 @@
         <v>60</v>
       </c>
       <c r="BF15">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BG15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4631,22 +4631,22 @@
         <v>184</v>
       </c>
       <c r="F16">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G16">
         <v>2.68</v>
       </c>
       <c r="H16">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I16">
         <v>3.15</v>
       </c>
       <c r="J16">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K16">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L16">
         <v>1.44</v>
@@ -4661,7 +4661,7 @@
         <v>1.35</v>
       </c>
       <c r="P16">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q16">
         <v>2.06</v>
@@ -4673,10 +4673,10 @@
         <v>3.8</v>
       </c>
       <c r="T16">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V16">
         <v>1.47</v>
@@ -4685,166 +4685,166 @@
         <v>1.6</v>
       </c>
       <c r="X16">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y16">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z16">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AA16">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AB16">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC16">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE16">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AF16">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG16">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AI16">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AJ16">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AK16">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL16">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM16">
         <v>580</v>
       </c>
       <c r="AN16">
-        <v>600</v>
+        <v>26</v>
       </c>
       <c r="AO16">
-        <v>600</v>
+        <v>38</v>
       </c>
       <c r="AP16">
+        <v>10.5</v>
+      </c>
+      <c r="AQ16">
+        <v>10</v>
+      </c>
+      <c r="AR16">
+        <v>16</v>
+      </c>
+      <c r="AS16">
+        <v>36</v>
+      </c>
+      <c r="AT16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU16">
+        <v>6.8</v>
+      </c>
+      <c r="AV16">
+        <v>11.5</v>
+      </c>
+      <c r="AW16">
+        <v>25</v>
+      </c>
+      <c r="AX16">
+        <v>14.5</v>
+      </c>
+      <c r="AY16">
+        <v>10.5</v>
+      </c>
+      <c r="AZ16">
+        <v>15</v>
+      </c>
+      <c r="BA16">
+        <v>34</v>
+      </c>
+      <c r="BB16">
+        <v>27</v>
+      </c>
+      <c r="BC16">
+        <v>23</v>
+      </c>
+      <c r="BD16">
+        <v>30</v>
+      </c>
+      <c r="BE16">
+        <v>60</v>
+      </c>
+      <c r="BF16">
+        <v>16.5</v>
+      </c>
+      <c r="BG16">
+        <v>22</v>
+      </c>
+      <c r="BH16">
+        <v>3.3</v>
+      </c>
+      <c r="BI16">
+        <v>2.72</v>
+      </c>
+      <c r="BJ16">
+        <v>9.6</v>
+      </c>
+      <c r="BK16">
+        <v>5.9</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>14</v>
+      </c>
+      <c r="BN16">
+        <v>5.5</v>
+      </c>
+      <c r="BO16">
+        <v>4.2</v>
+      </c>
+      <c r="BP16">
+        <v>20</v>
+      </c>
+      <c r="BQ16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR16">
+        <v>34</v>
+      </c>
+      <c r="BS16">
+        <v>10.5</v>
+      </c>
+      <c r="BT16">
         <v>6.2</v>
       </c>
-      <c r="AQ16">
-        <v>5.5</v>
-      </c>
-      <c r="AR16">
-        <v>1.94</v>
-      </c>
-      <c r="AS16">
-        <v>1.69</v>
-      </c>
-      <c r="AT16">
-        <v>4.9</v>
-      </c>
-      <c r="AU16">
-        <v>3.85</v>
-      </c>
-      <c r="AV16">
-        <v>1.97</v>
-      </c>
-      <c r="AW16">
-        <v>1.68</v>
-      </c>
-      <c r="AX16">
-        <v>1.98</v>
-      </c>
-      <c r="AY16">
-        <v>6</v>
-      </c>
-      <c r="AZ16">
-        <v>1.87</v>
-      </c>
-      <c r="BA16">
-        <v>1.69</v>
-      </c>
-      <c r="BB16">
-        <v>1.68</v>
-      </c>
-      <c r="BC16">
-        <v>1.66</v>
-      </c>
-      <c r="BD16">
-        <v>1.69</v>
-      </c>
-      <c r="BE16">
-        <v>1.71</v>
-      </c>
-      <c r="BF16">
-        <v>1.71</v>
-      </c>
-      <c r="BG16">
-        <v>1.71</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.04</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.04</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.04</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.04</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.04</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>185</v>
       </c>
       <c r="F17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G17">
         <v>4.9</v>
@@ -4882,7 +4882,7 @@
         <v>1.76</v>
       </c>
       <c r="I17">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="J17">
         <v>4.3</v>
@@ -4891,25 +4891,25 @@
         <v>4.4</v>
       </c>
       <c r="L17">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M17">
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O17">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P17">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q17">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R17">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S17">
         <v>2.56</v>
@@ -4918,13 +4918,13 @@
         <v>1.64</v>
       </c>
       <c r="U17">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V17">
         <v>2.28</v>
       </c>
       <c r="W17">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X17">
         <v>23</v>
@@ -4936,49 +4936,49 @@
         <v>12.5</v>
       </c>
       <c r="AA17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC17">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF17">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AG17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH17">
         <v>16</v>
       </c>
       <c r="AI17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ17">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK17">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL17">
         <v>48</v>
       </c>
       <c r="AM17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO17">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP17">
         <v>21</v>
@@ -4990,109 +4990,109 @@
         <v>11.5</v>
       </c>
       <c r="AS17">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT17">
         <v>22</v>
       </c>
       <c r="AU17">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV17">
         <v>9.4</v>
       </c>
       <c r="AW17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY17">
         <v>17</v>
       </c>
       <c r="AZ17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB17">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="BC17">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BD17">
         <v>42</v>
       </c>
       <c r="BE17">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF17">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BG17">
         <v>7.2</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI17">
-        <v>1.39</v>
+        <v>3.9</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK17">
-        <v>1.92</v>
+        <v>8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.87</v>
+        <v>70</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO17">
-        <v>1.66</v>
+        <v>7.6</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ17">
-        <v>1.92</v>
+        <v>9.4</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS17">
-        <v>1.92</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU17">
-        <v>1.43</v>
+        <v>4.4</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW17">
-        <v>1.92</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY17">
-        <v>1.92</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA17">
-        <v>1.92</v>
+        <v>10.5</v>
       </c>
       <c r="CB17" t="s">
         <v>211</v>
@@ -5115,10 +5115,10 @@
         <v>186</v>
       </c>
       <c r="F18">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G18">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H18">
         <v>9.4</v>
@@ -5127,76 +5127,76 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J18">
+        <v>5.7</v>
+      </c>
+      <c r="K18">
         <v>5.8</v>
       </c>
-      <c r="K18">
-        <v>6</v>
-      </c>
       <c r="L18">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N18">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P18">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="Q18">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R18">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="S18">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="T18">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="U18">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
         <v>1.11</v>
       </c>
       <c r="W18">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X18">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y18">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="Z18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AA18">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD18">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE18">
         <v>130</v>
       </c>
       <c r="AF18">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH18">
         <v>22</v>
@@ -5205,136 +5205,136 @@
         <v>90</v>
       </c>
       <c r="AJ18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AL18">
         <v>28</v>
       </c>
       <c r="AM18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN18">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AO18">
-        <v>760</v>
+        <v>130</v>
       </c>
       <c r="AP18">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AQ18">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AR18">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AS18">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AT18">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AU18">
         <v>12</v>
       </c>
       <c r="AV18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW18">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AX18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA18">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BB18">
         <v>11</v>
       </c>
       <c r="BC18">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD18">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE18">
+        <v>70</v>
+      </c>
+      <c r="BF18">
+        <v>4.3</v>
+      </c>
+      <c r="BG18">
+        <v>80</v>
+      </c>
+      <c r="BH18">
+        <v>5.2</v>
+      </c>
+      <c r="BI18">
+        <v>4.3</v>
+      </c>
+      <c r="BJ18">
+        <v>11</v>
+      </c>
+      <c r="BK18">
+        <v>5.2</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>85</v>
+      </c>
+      <c r="BN18">
+        <v>4.4</v>
+      </c>
+      <c r="BO18">
+        <v>3.7</v>
+      </c>
+      <c r="BP18">
+        <v>8</v>
+      </c>
+      <c r="BQ18">
+        <v>6.6</v>
+      </c>
+      <c r="BR18">
+        <v>19.5</v>
+      </c>
+      <c r="BS18">
+        <v>7.2</v>
+      </c>
+      <c r="BT18">
+        <v>13</v>
+      </c>
+      <c r="BU18">
+        <v>5.6</v>
+      </c>
+      <c r="BV18">
         <v>65</v>
       </c>
-      <c r="BF18">
-        <v>3.85</v>
-      </c>
-      <c r="BG18">
-        <v>65</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.26</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.56</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.04</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>3.65</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>1.56</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>1.04</v>
-      </c>
-      <c r="BT18">
-        <v>1000</v>
-      </c>
-      <c r="BU18">
-        <v>1.04</v>
-      </c>
-      <c r="BV18">
-        <v>1000</v>
-      </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB18" t="s">
         <v>211</v>
@@ -5357,226 +5357,226 @@
         <v>187</v>
       </c>
       <c r="F19">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G19">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H19">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J19">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K19">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O19">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="Q19">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="S19">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="T19">
+        <v>1.58</v>
+      </c>
+      <c r="U19">
+        <v>2.58</v>
+      </c>
+      <c r="V19">
+        <v>1.45</v>
+      </c>
+      <c r="W19">
         <v>1.7</v>
       </c>
-      <c r="U19">
-        <v>2.26</v>
-      </c>
-      <c r="V19">
-        <v>1.44</v>
-      </c>
-      <c r="W19">
-        <v>1.68</v>
-      </c>
       <c r="X19">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y19">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z19">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA19">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AB19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC19">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE19">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AF19">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG19">
         <v>11</v>
       </c>
       <c r="AH19">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI19">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AJ19">
         <v>34</v>
       </c>
       <c r="AK19">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL19">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM19">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AN19">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AO19">
+        <v>23</v>
+      </c>
+      <c r="AP19">
+        <v>17</v>
+      </c>
+      <c r="AQ19">
+        <v>14</v>
+      </c>
+      <c r="AR19">
+        <v>21</v>
+      </c>
+      <c r="AS19">
         <v>48</v>
       </c>
-      <c r="AP19">
-        <v>13.5</v>
-      </c>
-      <c r="AQ19">
-        <v>12.5</v>
-      </c>
-      <c r="AR19">
-        <v>20</v>
-      </c>
-      <c r="AS19">
-        <v>40</v>
-      </c>
       <c r="AT19">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AU19">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV19">
         <v>12.5</v>
       </c>
       <c r="AW19">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX19">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA19">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BB19">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BC19">
+        <v>18</v>
+      </c>
+      <c r="BD19">
+        <v>27</v>
+      </c>
+      <c r="BE19">
+        <v>60</v>
+      </c>
+      <c r="BF19">
+        <v>13.5</v>
+      </c>
+      <c r="BG19">
         <v>21</v>
       </c>
-      <c r="BD19">
-        <v>30</v>
-      </c>
-      <c r="BE19">
-        <v>40</v>
-      </c>
-      <c r="BF19">
+      <c r="BH19">
+        <v>4.1</v>
+      </c>
+      <c r="BI19">
+        <v>3.15</v>
+      </c>
+      <c r="BJ19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK19">
+        <v>4.8</v>
+      </c>
+      <c r="BL19">
+        <v>90</v>
+      </c>
+      <c r="BM19">
+        <v>19</v>
+      </c>
+      <c r="BN19">
+        <v>5.8</v>
+      </c>
+      <c r="BO19">
+        <v>4.3</v>
+      </c>
+      <c r="BP19">
         <v>17.5</v>
       </c>
-      <c r="BG19">
-        <v>22</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.04</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.04</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.04</v>
-      </c>
-      <c r="BN19">
-        <v>1000</v>
-      </c>
-      <c r="BO19">
-        <v>1.04</v>
-      </c>
-      <c r="BP19">
-        <v>1000</v>
-      </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="CB19" t="s">
         <v>211</v>
@@ -5602,19 +5602,19 @@
         <v>2.12</v>
       </c>
       <c r="G20">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H20">
         <v>3.3</v>
       </c>
       <c r="I20">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
         <v>1.26</v>
@@ -5626,7 +5626,7 @@
         <v>6.4</v>
       </c>
       <c r="O20">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P20">
         <v>2.84</v>
@@ -5635,22 +5635,22 @@
         <v>1.5</v>
       </c>
       <c r="R20">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T20">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="U20">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V20">
         <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X20">
         <v>950</v>
@@ -5734,7 +5734,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY20">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20">
         <v>7.6</v>
@@ -5841,58 +5841,58 @@
         <v>189</v>
       </c>
       <c r="F21">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="G21">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H21">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="I21">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J21">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L21">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M21">
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>1.18</v>
       </c>
       <c r="P21">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q21">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R21">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S21">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T21">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U21">
         <v>2.64</v>
       </c>
       <c r="V21">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="W21">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X21">
         <v>950</v>
@@ -5901,10 +5901,10 @@
         <v>970</v>
       </c>
       <c r="Z21">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA21">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AB21">
         <v>950</v>
@@ -5913,13 +5913,13 @@
         <v>970</v>
       </c>
       <c r="AD21">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE21">
         <v>970</v>
       </c>
       <c r="AF21">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AG21">
         <v>970</v>
@@ -5928,16 +5928,16 @@
         <v>970</v>
       </c>
       <c r="AI21">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ21">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AK21">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AL21">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM21">
         <v>580</v>
@@ -5955,25 +5955,25 @@
         <v>6.8</v>
       </c>
       <c r="AR21">
-        <v>1.68</v>
+        <v>7.4</v>
       </c>
       <c r="AS21">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AT21">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AU21">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV21">
         <v>5.2</v>
       </c>
       <c r="AW21">
-        <v>7.6</v>
+        <v>1.81</v>
       </c>
       <c r="AX21">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AY21">
         <v>6.6</v>
@@ -5982,85 +5982,85 @@
         <v>8.6</v>
       </c>
       <c r="BA21">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="BB21">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="BC21">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="BD21">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="BE21">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="BF21">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="BG21">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB21" t="s">
         <v>211</v>
@@ -6086,16 +6086,16 @@
         <v>1.6</v>
       </c>
       <c r="G22">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H22">
         <v>6.8</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J22">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K22">
         <v>4.2</v>
@@ -6107,88 +6107,88 @@
         <v>1.07</v>
       </c>
       <c r="N22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P22">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q22">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S22">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T22">
         <v>2</v>
       </c>
       <c r="U22">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V22">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W22">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X22">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y22">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Z22">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AA22">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="AB22">
+        <v>9</v>
+      </c>
+      <c r="AC22">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AC22">
-        <v>9.4</v>
       </c>
       <c r="AD22">
         <v>27</v>
       </c>
       <c r="AE22">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF22">
         <v>11</v>
       </c>
       <c r="AG22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH22">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI22">
         <v>240</v>
       </c>
       <c r="AJ22">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK22">
         <v>22</v>
       </c>
       <c r="AL22">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM22">
-        <v>140</v>
+        <v>390</v>
       </c>
       <c r="AN22">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AO22">
-        <v>530</v>
+        <v>190</v>
       </c>
       <c r="AP22">
         <v>13</v>
@@ -6200,28 +6200,28 @@
         <v>46</v>
       </c>
       <c r="AS22">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AT22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU22">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW22">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX22">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY22">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA22">
         <v>55</v>
@@ -6233,16 +6233,16 @@
         <v>15</v>
       </c>
       <c r="BD22">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BE22">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="BF22">
         <v>8.199999999999999</v>
       </c>
       <c r="BG22">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6325,13 +6325,13 @@
         <v>191</v>
       </c>
       <c r="F23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G23">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H23">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="I23">
         <v>2.02</v>
@@ -6343,7 +6343,7 @@
         <v>3.75</v>
       </c>
       <c r="L23">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M23">
         <v>1.07</v>
@@ -6352,7 +6352,7 @@
         <v>3.75</v>
       </c>
       <c r="O23">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P23">
         <v>1.92</v>
@@ -6364,40 +6364,40 @@
         <v>1.35</v>
       </c>
       <c r="S23">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T23">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U23">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V23">
         <v>1.98</v>
       </c>
       <c r="W23">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X23">
         <v>14</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z23">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AA23">
         <v>26</v>
       </c>
       <c r="AB23">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC23">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD23">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE23">
         <v>27</v>
@@ -6406,7 +6406,7 @@
         <v>38</v>
       </c>
       <c r="AG23">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH23">
         <v>24</v>
@@ -6424,16 +6424,16 @@
         <v>80</v>
       </c>
       <c r="AM23">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN23">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO23">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ23">
         <v>8.199999999999999</v>
@@ -6445,106 +6445,106 @@
         <v>20</v>
       </c>
       <c r="AT23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU23">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV23">
         <v>8.4</v>
       </c>
       <c r="AW23">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AX23">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AY23">
         <v>14.5</v>
       </c>
       <c r="AZ23">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA23">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB23">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BC23">
         <v>42</v>
       </c>
       <c r="BD23">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE23">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="BF23">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG23">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB23" t="s">
         <v>211</v>
@@ -6567,25 +6567,25 @@
         <v>192</v>
       </c>
       <c r="F24">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G24">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H24">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I24">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J24">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L24">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M24">
         <v>1.06</v>
@@ -6597,55 +6597,55 @@
         <v>1.3</v>
       </c>
       <c r="P24">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q24">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R24">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S24">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T24">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U24">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W24">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X24">
         <v>22</v>
       </c>
       <c r="Y24">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Z24">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA24">
         <v>440</v>
       </c>
       <c r="AB24">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AC24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD24">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AE24">
         <v>85</v>
       </c>
       <c r="AF24">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AG24">
         <v>17</v>
@@ -6657,13 +6657,13 @@
         <v>150</v>
       </c>
       <c r="AJ24">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AK24">
         <v>40</v>
       </c>
       <c r="AL24">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AM24">
         <v>500</v>
@@ -6675,28 +6675,28 @@
         <v>600</v>
       </c>
       <c r="AP24">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ24">
         <v>10.5</v>
       </c>
       <c r="AR24">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS24">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT24">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU24">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX24">
         <v>11.5</v>
@@ -6708,79 +6708,79 @@
         <v>14</v>
       </c>
       <c r="BA24">
+        <v>32</v>
+      </c>
+      <c r="BB24">
+        <v>22</v>
+      </c>
+      <c r="BC24">
+        <v>18</v>
+      </c>
+      <c r="BD24">
+        <v>27</v>
+      </c>
+      <c r="BE24">
+        <v>44</v>
+      </c>
+      <c r="BF24">
+        <v>12.5</v>
+      </c>
+      <c r="BG24">
+        <v>13.5</v>
+      </c>
+      <c r="BH24">
+        <v>3.95</v>
+      </c>
+      <c r="BI24">
+        <v>2.92</v>
+      </c>
+      <c r="BJ24">
+        <v>11</v>
+      </c>
+      <c r="BK24">
+        <v>7.2</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>5.5</v>
+      </c>
+      <c r="BN24">
+        <v>6</v>
+      </c>
+      <c r="BO24">
+        <v>4.2</v>
+      </c>
+      <c r="BP24">
+        <v>19.5</v>
+      </c>
+      <c r="BQ24">
+        <v>4.4</v>
+      </c>
+      <c r="BR24">
+        <v>34</v>
+      </c>
+      <c r="BS24">
+        <v>4.9</v>
+      </c>
+      <c r="BT24">
+        <v>7.4</v>
+      </c>
+      <c r="BU24">
+        <v>5.2</v>
+      </c>
+      <c r="BV24">
         <v>30</v>
       </c>
-      <c r="BB24">
-        <v>21</v>
-      </c>
-      <c r="BC24">
-        <v>17.5</v>
-      </c>
-      <c r="BD24">
-        <v>26</v>
-      </c>
-      <c r="BE24">
-        <v>38</v>
-      </c>
-      <c r="BF24">
-        <v>12</v>
-      </c>
-      <c r="BG24">
-        <v>20</v>
-      </c>
-      <c r="BH24">
-        <v>1000</v>
-      </c>
-      <c r="BI24">
-        <v>1.04</v>
-      </c>
-      <c r="BJ24">
-        <v>1000</v>
-      </c>
-      <c r="BK24">
-        <v>1.04</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>1.04</v>
-      </c>
-      <c r="BN24">
-        <v>1000</v>
-      </c>
-      <c r="BO24">
-        <v>1.04</v>
-      </c>
-      <c r="BP24">
-        <v>1000</v>
-      </c>
-      <c r="BQ24">
-        <v>1.04</v>
-      </c>
-      <c r="BR24">
-        <v>1000</v>
-      </c>
-      <c r="BS24">
-        <v>1.04</v>
-      </c>
-      <c r="BT24">
-        <v>1000</v>
-      </c>
-      <c r="BU24">
-        <v>1.04</v>
-      </c>
-      <c r="BV24">
-        <v>1000</v>
-      </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6812,19 +6812,19 @@
         <v>3.3</v>
       </c>
       <c r="G25">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H25">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I25">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J25">
         <v>2.78</v>
       </c>
       <c r="K25">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L25">
         <v>1.61</v>
@@ -6833,7 +6833,7 @@
         <v>1.14</v>
       </c>
       <c r="N25">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="O25">
         <v>1.6</v>
@@ -6842,13 +6842,13 @@
         <v>1.49</v>
       </c>
       <c r="Q25">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R25">
         <v>1.17</v>
       </c>
       <c r="S25">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T25">
         <v>1.8</v>
@@ -6860,7 +6860,7 @@
         <v>1.56</v>
       </c>
       <c r="W25">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X25">
         <v>970</v>
@@ -6884,10 +6884,10 @@
         <v>970</v>
       </c>
       <c r="AE25">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AF25">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AG25">
         <v>970</v>
@@ -6896,13 +6896,13 @@
         <v>950</v>
       </c>
       <c r="AI25">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AJ25">
         <v>900</v>
       </c>
       <c r="AK25">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AL25">
         <v>540</v>
@@ -6947,19 +6947,19 @@
         <v>7.4</v>
       </c>
       <c r="AZ25">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="BA25">
         <v>1.52</v>
       </c>
       <c r="BB25">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BC25">
         <v>1.52</v>
       </c>
       <c r="BD25">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BE25">
         <v>1.53</v>
@@ -7051,7 +7051,7 @@
         <v>194</v>
       </c>
       <c r="F26">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G26">
         <v>2.98</v>
@@ -7060,79 +7060,79 @@
         <v>2.72</v>
       </c>
       <c r="I26">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J26">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K26">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L26">
         <v>1.52</v>
       </c>
       <c r="M26">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N26">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O26">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P26">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q26">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R26">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S26">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T26">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U26">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V26">
         <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X26">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y26">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="Z26">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AA26">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="AB26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC26">
+        <v>10</v>
+      </c>
+      <c r="AD26">
         <v>13</v>
       </c>
-      <c r="AC26">
-        <v>11</v>
-      </c>
-      <c r="AD26">
-        <v>21</v>
-      </c>
       <c r="AE26">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AF26">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AG26">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AH26">
         <v>34</v>
@@ -7141,10 +7141,10 @@
         <v>290</v>
       </c>
       <c r="AJ26">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AK26">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AL26">
         <v>290</v>
@@ -7159,58 +7159,58 @@
         <v>600</v>
       </c>
       <c r="AP26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ26">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AR26">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS26">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AT26">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU26">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW26">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AX26">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY26">
         <v>10.5</v>
       </c>
       <c r="AZ26">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB26">
+        <v>34</v>
+      </c>
+      <c r="BC26">
+        <v>29</v>
+      </c>
+      <c r="BD26">
         <v>36</v>
       </c>
-      <c r="BC26">
+      <c r="BE26">
+        <v>55</v>
+      </c>
+      <c r="BF26">
+        <v>23</v>
+      </c>
+      <c r="BG26">
         <v>27</v>
-      </c>
-      <c r="BD26">
-        <v>40</v>
-      </c>
-      <c r="BE26">
-        <v>60</v>
-      </c>
-      <c r="BF26">
-        <v>30</v>
-      </c>
-      <c r="BG26">
-        <v>17.5</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7293,13 +7293,13 @@
         <v>195</v>
       </c>
       <c r="F27">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G27">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H27">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I27">
         <v>2.62</v>
@@ -7308,7 +7308,7 @@
         <v>3.1</v>
       </c>
       <c r="K27">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="L27">
         <v>1.6</v>
@@ -7317,7 +7317,7 @@
         <v>1.12</v>
       </c>
       <c r="N27">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O27">
         <v>1.57</v>
@@ -7326,19 +7326,19 @@
         <v>1.51</v>
       </c>
       <c r="Q27">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R27">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S27">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="U27">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V27">
         <v>1.62</v>
@@ -7347,7 +7347,7 @@
         <v>1.38</v>
       </c>
       <c r="X27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y27">
         <v>12.5</v>
@@ -7362,7 +7362,7 @@
         <v>15</v>
       </c>
       <c r="AC27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD27">
         <v>23</v>
@@ -7401,25 +7401,25 @@
         <v>600</v>
       </c>
       <c r="AP27">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AQ27">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR27">
         <v>7.2</v>
       </c>
       <c r="AS27">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AT27">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU27">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AV27">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AW27">
         <v>18.5</v>
@@ -7428,7 +7428,7 @@
         <v>11.5</v>
       </c>
       <c r="AY27">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27">
         <v>20</v>
@@ -7437,7 +7437,7 @@
         <v>46</v>
       </c>
       <c r="BB27">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BC27">
         <v>36</v>
@@ -7455,64 +7455,64 @@
         <v>27</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI27">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK27">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO27">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ27">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS27">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU27">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW27">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY27">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA27">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB27" t="s">
         <v>211</v>
@@ -7547,7 +7547,7 @@
         <v>2.62</v>
       </c>
       <c r="J28">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K28">
         <v>5.1</v>
@@ -7556,13 +7556,13 @@
         <v>1.22</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N28">
         <v>7.2</v>
       </c>
       <c r="O28">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P28">
         <v>3.2</v>
@@ -7574,10 +7574,10 @@
         <v>1.87</v>
       </c>
       <c r="S28">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T28">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U28">
         <v>1.11</v>
@@ -7589,172 +7589,172 @@
         <v>1.56</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI28">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK28">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO28">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU28">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY28">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA28">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB28" t="s">
         <v>211</v>
@@ -7780,19 +7780,19 @@
         <v>2.8</v>
       </c>
       <c r="G29">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H29">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I29">
         <v>2.3</v>
       </c>
       <c r="J29">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K29">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L29">
         <v>1.13</v>
@@ -7801,28 +7801,28 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="O29">
         <v>1.05</v>
       </c>
       <c r="P29">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>1.19</v>
       </c>
       <c r="R29">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="S29">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="U29">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="V29">
         <v>1.01</v>
@@ -7846,25 +7846,25 @@
         <v>100</v>
       </c>
       <c r="AC29">
+        <v>21</v>
+      </c>
+      <c r="AD29">
         <v>20</v>
       </c>
-      <c r="AD29">
-        <v>17</v>
-      </c>
       <c r="AE29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF29">
         <v>95</v>
       </c>
       <c r="AG29">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH29">
         <v>15.5</v>
       </c>
       <c r="AI29">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AJ29">
         <v>140</v>
@@ -7876,10 +7876,10 @@
         <v>28</v>
       </c>
       <c r="AM29">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AN29">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO29">
         <v>5.7</v>
@@ -7897,22 +7897,22 @@
         <v>32</v>
       </c>
       <c r="AT29">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AU29">
+        <v>14.5</v>
+      </c>
+      <c r="AV29">
+        <v>13</v>
+      </c>
+      <c r="AW29">
+        <v>17</v>
+      </c>
+      <c r="AX29">
+        <v>32</v>
+      </c>
+      <c r="AY29">
         <v>14</v>
-      </c>
-      <c r="AV29">
-        <v>12.5</v>
-      </c>
-      <c r="AW29">
-        <v>16.5</v>
-      </c>
-      <c r="AX29">
-        <v>34</v>
-      </c>
-      <c r="AY29">
-        <v>13.5</v>
       </c>
       <c r="AZ29">
         <v>11</v>
@@ -7930,67 +7930,67 @@
         <v>15.5</v>
       </c>
       <c r="BE29">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BF29">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG29">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BI29">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK29">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL29">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BM29">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO29">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ29">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS29">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU29">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW29">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BY29">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BZ29">
         <v>0</v>
@@ -8019,94 +8019,94 @@
         <v>198</v>
       </c>
       <c r="F30">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G30">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="H30">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I30">
         <v>5.5</v>
       </c>
       <c r="J30">
+        <v>3.4</v>
+      </c>
+      <c r="K30">
         <v>3.45</v>
       </c>
-      <c r="K30">
-        <v>3.5</v>
-      </c>
       <c r="L30">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M30">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N30">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="O30">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="P30">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="Q30">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R30">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S30">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T30">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="U30">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="V30">
         <v>1.22</v>
       </c>
       <c r="W30">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X30">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA30">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AC30">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD30">
         <v>22</v>
       </c>
       <c r="AE30">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AF30">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG30">
         <v>11</v>
       </c>
       <c r="AH30">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI30">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="AJ30">
         <v>21</v>
@@ -8115,112 +8115,112 @@
         <v>25</v>
       </c>
       <c r="AL30">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM30">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="AN30">
-        <v>600</v>
+        <v>22</v>
       </c>
       <c r="AO30">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AP30">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR30">
         <v>34</v>
       </c>
       <c r="AS30">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AT30">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU30">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV30">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW30">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AX30">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ30">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA30">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB30">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC30">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD30">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BE30">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="BF30">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BG30">
-        <v>17.5</v>
+        <v>70</v>
       </c>
       <c r="BH30">
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="BN30">
         <v>1000</v>
       </c>
       <c r="BO30">
-        <v>1.06</v>
+        <v>3.35</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BT30">
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BV30">
         <v>1000</v>
@@ -8232,7 +8232,7 @@
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
@@ -8273,7 +8273,7 @@
         <v>2.52</v>
       </c>
       <c r="J31">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K31">
         <v>3.65</v>
@@ -8291,7 +8291,7 @@
         <v>1.35</v>
       </c>
       <c r="P31">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q31">
         <v>2</v>
@@ -8306,7 +8306,7 @@
         <v>1.74</v>
       </c>
       <c r="U31">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="V31">
         <v>1.66</v>
@@ -8315,43 +8315,43 @@
         <v>1.4</v>
       </c>
       <c r="X31">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y31">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z31">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AA31">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="AB31">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC31">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="AD31">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE31">
         <v>90</v>
       </c>
       <c r="AF31">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AG31">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AH31">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AI31">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ31">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AK31">
         <v>110</v>
@@ -8366,121 +8366,121 @@
         <v>600</v>
       </c>
       <c r="AO31">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP31">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AQ31">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR31">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AS31">
-        <v>1.97</v>
+        <v>23</v>
       </c>
       <c r="AT31">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AU31">
+        <v>6.8</v>
+      </c>
+      <c r="AV31">
+        <v>9.6</v>
+      </c>
+      <c r="AW31">
+        <v>19</v>
+      </c>
+      <c r="AX31">
+        <v>19.5</v>
+      </c>
+      <c r="AY31">
+        <v>12</v>
+      </c>
+      <c r="AZ31">
+        <v>14.5</v>
+      </c>
+      <c r="BA31">
+        <v>29</v>
+      </c>
+      <c r="BB31">
+        <v>40</v>
+      </c>
+      <c r="BC31">
+        <v>27</v>
+      </c>
+      <c r="BD31">
+        <v>34</v>
+      </c>
+      <c r="BE31">
+        <v>48</v>
+      </c>
+      <c r="BF31">
+        <v>24</v>
+      </c>
+      <c r="BG31">
+        <v>17</v>
+      </c>
+      <c r="BH31">
+        <v>3.8</v>
+      </c>
+      <c r="BI31">
+        <v>2.8</v>
+      </c>
+      <c r="BJ31">
+        <v>11</v>
+      </c>
+      <c r="BK31">
+        <v>3.75</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>5.5</v>
+      </c>
+      <c r="BN31">
+        <v>7.4</v>
+      </c>
+      <c r="BO31">
+        <v>5.1</v>
+      </c>
+      <c r="BP31">
+        <v>30</v>
+      </c>
+      <c r="BQ31">
+        <v>4.8</v>
+      </c>
+      <c r="BR31">
+        <v>44</v>
+      </c>
+      <c r="BS31">
+        <v>5</v>
+      </c>
+      <c r="BT31">
+        <v>6</v>
+      </c>
+      <c r="BU31">
         <v>4.2</v>
       </c>
-      <c r="AV31">
-        <v>5.2</v>
-      </c>
-      <c r="AW31">
-        <v>1.97</v>
-      </c>
-      <c r="AX31">
-        <v>9</v>
-      </c>
-      <c r="AY31">
-        <v>6.6</v>
-      </c>
-      <c r="AZ31">
-        <v>7.6</v>
-      </c>
-      <c r="BA31">
-        <v>1.98</v>
-      </c>
-      <c r="BB31">
-        <v>1.99</v>
-      </c>
-      <c r="BC31">
-        <v>1.98</v>
-      </c>
-      <c r="BD31">
-        <v>1.99</v>
-      </c>
-      <c r="BE31">
-        <v>2</v>
-      </c>
-      <c r="BF31">
-        <v>1.95</v>
-      </c>
-      <c r="BG31">
-        <v>1.95</v>
-      </c>
-      <c r="BH31">
-        <v>1000</v>
-      </c>
-      <c r="BI31">
-        <v>1.04</v>
-      </c>
-      <c r="BJ31">
-        <v>1000</v>
-      </c>
-      <c r="BK31">
-        <v>1.04</v>
-      </c>
-      <c r="BL31">
-        <v>1000</v>
-      </c>
-      <c r="BM31">
-        <v>1.04</v>
-      </c>
-      <c r="BN31">
-        <v>1000</v>
-      </c>
-      <c r="BO31">
-        <v>1.04</v>
-      </c>
-      <c r="BP31">
-        <v>1000</v>
-      </c>
-      <c r="BQ31">
-        <v>1.04</v>
-      </c>
-      <c r="BR31">
-        <v>1000</v>
-      </c>
-      <c r="BS31">
-        <v>1.04</v>
-      </c>
-      <c r="BT31">
-        <v>1000</v>
-      </c>
-      <c r="BU31">
-        <v>1.04</v>
-      </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW31">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY31">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA31">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB31" t="s">
         <v>211</v>
@@ -8503,16 +8503,16 @@
         <v>200</v>
       </c>
       <c r="F32">
+        <v>2.02</v>
+      </c>
+      <c r="G32">
         <v>2.06</v>
       </c>
-      <c r="G32">
-        <v>2.1</v>
-      </c>
       <c r="H32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I32">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J32">
         <v>3.5</v>
@@ -8530,13 +8530,13 @@
         <v>3.05</v>
       </c>
       <c r="O32">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P32">
         <v>1.67</v>
       </c>
       <c r="Q32">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R32">
         <v>1.24</v>
@@ -8548,31 +8548,31 @@
         <v>2</v>
       </c>
       <c r="U32">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V32">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W32">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X32">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="Y32">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="Z32">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AA32">
         <v>500</v>
       </c>
       <c r="AB32">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AC32">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD32">
         <v>970</v>
@@ -8581,22 +8581,22 @@
         <v>500</v>
       </c>
       <c r="AF32">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG32">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AH32">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AI32">
         <v>500</v>
       </c>
       <c r="AJ32">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AK32">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AL32">
         <v>500</v>
@@ -8608,13 +8608,13 @@
         <v>600</v>
       </c>
       <c r="AO32">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AP32">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ32">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AR32">
         <v>15</v>
@@ -8623,22 +8623,22 @@
         <v>28</v>
       </c>
       <c r="AT32">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU32">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV32">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW32">
         <v>27</v>
       </c>
       <c r="AX32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY32">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ32">
         <v>18</v>
@@ -8647,7 +8647,7 @@
         <v>32</v>
       </c>
       <c r="BB32">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BC32">
         <v>13.5</v>
@@ -8659,7 +8659,7 @@
         <v>28</v>
       </c>
       <c r="BF32">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BG32">
         <v>36</v>
@@ -8745,16 +8745,16 @@
         <v>201</v>
       </c>
       <c r="F33">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G33">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="H33">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="I33">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="J33">
         <v>3.6</v>
@@ -8763,10 +8763,10 @@
         <v>3.95</v>
       </c>
       <c r="L33">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N33">
         <v>3.95</v>
@@ -8775,136 +8775,136 @@
         <v>1.32</v>
       </c>
       <c r="P33">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q33">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R33">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S33">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U33">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V33">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="W33">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X33">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Y33">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z33">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AA33">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AB33">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AC33">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="AD33">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE33">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AF33">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AG33">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AH33">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AI33">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ33">
         <v>900</v>
       </c>
       <c r="AK33">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AL33">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AM33">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN33">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO33">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="AP33">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AQ33">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR33">
+        <v>5.8</v>
+      </c>
+      <c r="AS33">
         <v>9.6</v>
       </c>
-      <c r="AS33">
-        <v>16.5</v>
-      </c>
       <c r="AT33">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU33">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AV33">
+        <v>5.8</v>
+      </c>
+      <c r="AW33">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX33">
+        <v>2.2</v>
+      </c>
+      <c r="AY33">
+        <v>7.4</v>
+      </c>
+      <c r="AZ33">
         <v>8.4</v>
       </c>
-      <c r="AW33">
-        <v>14</v>
-      </c>
-      <c r="AX33">
-        <v>27</v>
-      </c>
-      <c r="AY33">
-        <v>14</v>
-      </c>
-      <c r="AZ33">
-        <v>14.5</v>
-      </c>
       <c r="BA33">
-        <v>24</v>
+        <v>2.22</v>
       </c>
       <c r="BB33">
-        <v>55</v>
+        <v>1.94</v>
       </c>
       <c r="BC33">
-        <v>36</v>
+        <v>1.92</v>
       </c>
       <c r="BD33">
-        <v>38</v>
+        <v>1.93</v>
       </c>
       <c r="BE33">
-        <v>30</v>
+        <v>1.93</v>
       </c>
       <c r="BF33">
-        <v>32</v>
+        <v>1.95</v>
       </c>
       <c r="BG33">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8987,7 +8987,7 @@
         <v>202</v>
       </c>
       <c r="F34">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G34">
         <v>2.54</v>
@@ -8999,10 +8999,10 @@
         <v>3.75</v>
       </c>
       <c r="J34">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K34">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L34">
         <v>1.52</v>
@@ -9011,28 +9011,28 @@
         <v>1.11</v>
       </c>
       <c r="N34">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O34">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P34">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q34">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R34">
         <v>1.23</v>
       </c>
       <c r="S34">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T34">
         <v>1.11</v>
       </c>
       <c r="U34">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V34">
         <v>1.37</v>
@@ -9101,22 +9101,22 @@
         <v>5.8</v>
       </c>
       <c r="AR34">
-        <v>1.81</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS34">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AT34">
-        <v>1.79</v>
+        <v>3.7</v>
       </c>
       <c r="AU34">
         <v>4.2</v>
       </c>
       <c r="AV34">
-        <v>1.75</v>
+        <v>6.2</v>
       </c>
       <c r="AW34">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AX34">
         <v>7</v>
@@ -9125,28 +9125,28 @@
         <v>7</v>
       </c>
       <c r="AZ34">
-        <v>1.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA34">
+        <v>1.83</v>
+      </c>
+      <c r="BB34">
+        <v>1.81</v>
+      </c>
+      <c r="BC34">
+        <v>1.81</v>
+      </c>
+      <c r="BD34">
         <v>1.84</v>
       </c>
-      <c r="BB34">
-        <v>1.82</v>
-      </c>
-      <c r="BC34">
-        <v>1.83</v>
-      </c>
-      <c r="BD34">
-        <v>1.83</v>
-      </c>
       <c r="BE34">
-        <v>1.86</v>
+        <v>110</v>
       </c>
       <c r="BF34">
         <v>5.5</v>
       </c>
       <c r="BG34">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9164,7 +9164,7 @@
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.04</v>
+        <v>140</v>
       </c>
       <c r="BN34">
         <v>1000</v>
@@ -9232,22 +9232,22 @@
         <v>3.45</v>
       </c>
       <c r="G35">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H35">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I35">
         <v>2.66</v>
       </c>
       <c r="J35">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K35">
         <v>3.05</v>
       </c>
       <c r="L35">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M35">
         <v>1.14</v>
@@ -9262,7 +9262,7 @@
         <v>1.49</v>
       </c>
       <c r="Q35">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R35">
         <v>1.17</v>
@@ -9271,22 +9271,22 @@
         <v>6.4</v>
       </c>
       <c r="T35">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U35">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V35">
         <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X35">
         <v>8.199999999999999</v>
       </c>
       <c r="Y35">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="Z35">
         <v>15</v>
@@ -9298,7 +9298,7 @@
         <v>9.4</v>
       </c>
       <c r="AC35">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD35">
         <v>14.5</v>
@@ -9328,7 +9328,7 @@
         <v>95</v>
       </c>
       <c r="AM35">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN35">
         <v>90</v>
@@ -9337,7 +9337,7 @@
         <v>120</v>
       </c>
       <c r="AP35">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ35">
         <v>6.8</v>
@@ -9349,7 +9349,7 @@
         <v>34</v>
       </c>
       <c r="AT35">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU35">
         <v>6.4</v>
@@ -9373,7 +9373,7 @@
         <v>60</v>
       </c>
       <c r="BB35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC35">
         <v>42</v>
@@ -9382,73 +9382,73 @@
         <v>60</v>
       </c>
       <c r="BE35">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="BF35">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BG35">
         <v>40</v>
       </c>
       <c r="BH35">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="BI35">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ35">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK35">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="BN35">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO35">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP35">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ35">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR35">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS35">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BT35">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU35">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV35">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW35">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX35">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY35">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BZ35">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA35">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB35" t="s">
         <v>211</v>
@@ -9471,19 +9471,19 @@
         <v>204</v>
       </c>
       <c r="F36">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
         <v>2.94</v>
-      </c>
-      <c r="H36">
-        <v>2.9</v>
       </c>
       <c r="I36">
         <v>3.15</v>
       </c>
       <c r="J36">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K36">
         <v>3.25</v>
@@ -9504,7 +9504,7 @@
         <v>1.56</v>
       </c>
       <c r="Q36">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R36">
         <v>1.14</v>
@@ -9513,7 +9513,7 @@
         <v>1.02</v>
       </c>
       <c r="T36">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U36">
         <v>1.83</v>
@@ -9525,37 +9525,37 @@
         <v>1.01</v>
       </c>
       <c r="X36">
-        <v>16.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y36">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Z36">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AA36">
         <v>900</v>
       </c>
       <c r="AB36">
-        <v>48</v>
+        <v>8.6</v>
       </c>
       <c r="AC36">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="AD36">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE36">
         <v>500</v>
       </c>
       <c r="AF36">
-        <v>970</v>
+        <v>75</v>
       </c>
       <c r="AG36">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="AH36">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI36">
         <v>500</v>
@@ -9579,58 +9579,58 @@
         <v>600</v>
       </c>
       <c r="AP36">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ36">
-        <v>2.74</v>
+        <v>7.8</v>
       </c>
       <c r="AR36">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="AS36">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT36">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="AU36">
-        <v>2.98</v>
+        <v>6.2</v>
       </c>
       <c r="AV36">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="AW36">
+        <v>25</v>
+      </c>
+      <c r="AX36">
+        <v>6</v>
+      </c>
+      <c r="AY36">
+        <v>11.5</v>
+      </c>
+      <c r="AZ36">
+        <v>6.6</v>
+      </c>
+      <c r="BA36">
         <v>8</v>
       </c>
-      <c r="AX36">
-        <v>5.3</v>
-      </c>
-      <c r="AY36">
-        <v>4.3</v>
-      </c>
-      <c r="AZ36">
-        <v>8</v>
-      </c>
-      <c r="BA36">
-        <v>11</v>
-      </c>
       <c r="BB36">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BC36">
         <v>7.2</v>
       </c>
       <c r="BD36">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BE36">
-        <v>1.75</v>
+        <v>38</v>
       </c>
       <c r="BF36">
-        <v>1.75</v>
+        <v>7.4</v>
       </c>
       <c r="BG36">
-        <v>1.75</v>
+        <v>7.8</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9713,25 +9713,25 @@
         <v>205</v>
       </c>
       <c r="F37">
+        <v>1.8</v>
+      </c>
+      <c r="G37">
         <v>1.82</v>
       </c>
-      <c r="G37">
-        <v>1.87</v>
-      </c>
       <c r="H37">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="I37">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J37">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K37">
         <v>3.65</v>
       </c>
       <c r="L37">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M37">
         <v>1.1</v>
@@ -9749,28 +9749,28 @@
         <v>2.32</v>
       </c>
       <c r="R37">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S37">
         <v>4.4</v>
       </c>
       <c r="T37">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U37">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V37">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W37">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="X37">
         <v>11</v>
       </c>
       <c r="Y37">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Z37">
         <v>42</v>
@@ -9779,22 +9779,22 @@
         <v>160</v>
       </c>
       <c r="AB37">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC37">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD37">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AE37">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AF37">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG37">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH37">
         <v>55</v>
@@ -9815,10 +9815,10 @@
         <v>180</v>
       </c>
       <c r="AN37">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AO37">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP37">
         <v>7.6</v>
@@ -9830,7 +9830,7 @@
         <v>34</v>
       </c>
       <c r="AS37">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AT37">
         <v>6.6</v>
@@ -9854,10 +9854,10 @@
         <v>22</v>
       </c>
       <c r="BA37">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB37">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BC37">
         <v>12</v>
@@ -9866,13 +9866,13 @@
         <v>36</v>
       </c>
       <c r="BE37">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="BF37">
         <v>14</v>
       </c>
       <c r="BG37">
-        <v>4.8</v>
+        <v>18.5</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9890,7 +9890,7 @@
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="BN37">
         <v>1000</v>
@@ -9902,7 +9902,7 @@
         <v>1000</v>
       </c>
       <c r="BQ37">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR37">
         <v>1000</v>
@@ -9914,7 +9914,7 @@
         <v>1000</v>
       </c>
       <c r="BU37">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV37">
         <v>1000</v>
@@ -9955,7 +9955,7 @@
         <v>206</v>
       </c>
       <c r="F38">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G38">
         <v>3.6</v>
@@ -9967,7 +9967,7 @@
         <v>2.74</v>
       </c>
       <c r="J38">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K38">
         <v>3.35</v>
@@ -9979,16 +9979,16 @@
         <v>1.11</v>
       </c>
       <c r="N38">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O38">
         <v>1.47</v>
       </c>
       <c r="P38">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="Q38">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R38">
         <v>1.21</v>
@@ -9997,52 +9997,52 @@
         <v>4.7</v>
       </c>
       <c r="T38">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="U38">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V38">
         <v>1.58</v>
       </c>
       <c r="W38">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X38">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Y38">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z38">
         <v>970</v>
       </c>
       <c r="AA38">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB38">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC38">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="AD38">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE38">
         <v>500</v>
       </c>
       <c r="AF38">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AG38">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH38">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AI38">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ38">
         <v>900</v>
@@ -10060,58 +10060,58 @@
         <v>600</v>
       </c>
       <c r="AO38">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP38">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ38">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR38">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AS38">
-        <v>1.98</v>
+        <v>5.3</v>
       </c>
       <c r="AT38">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU38">
+        <v>6.2</v>
+      </c>
+      <c r="AV38">
+        <v>10.5</v>
+      </c>
+      <c r="AW38">
+        <v>14.5</v>
+      </c>
+      <c r="AX38">
+        <v>18.5</v>
+      </c>
+      <c r="AY38">
+        <v>12.5</v>
+      </c>
+      <c r="AZ38">
+        <v>4.8</v>
+      </c>
+      <c r="BA38">
+        <v>5.3</v>
+      </c>
+      <c r="BB38">
+        <v>5.5</v>
+      </c>
+      <c r="BC38">
+        <v>5.5</v>
+      </c>
+      <c r="BD38">
+        <v>5.2</v>
+      </c>
+      <c r="BE38">
+        <v>120</v>
+      </c>
+      <c r="BF38">
         <v>5.6</v>
-      </c>
-      <c r="AU38">
-        <v>4.2</v>
-      </c>
-      <c r="AV38">
-        <v>7</v>
-      </c>
-      <c r="AW38">
-        <v>1.97</v>
-      </c>
-      <c r="AX38">
-        <v>2.06</v>
-      </c>
-      <c r="AY38">
-        <v>2.02</v>
-      </c>
-      <c r="AZ38">
-        <v>1.95</v>
-      </c>
-      <c r="BA38">
-        <v>2</v>
-      </c>
-      <c r="BB38">
-        <v>2</v>
-      </c>
-      <c r="BC38">
-        <v>1.99</v>
-      </c>
-      <c r="BD38">
-        <v>2</v>
-      </c>
-      <c r="BE38">
-        <v>2.02</v>
-      </c>
-      <c r="BF38">
-        <v>2.04</v>
       </c>
       <c r="BG38">
         <v>6.8</v>
@@ -10132,7 +10132,7 @@
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.04</v>
+        <v>150</v>
       </c>
       <c r="BN38">
         <v>1000</v>
@@ -10197,22 +10197,22 @@
         <v>207</v>
       </c>
       <c r="F39">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G39">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H39">
         <v>5.1</v>
       </c>
       <c r="I39">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J39">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K39">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L39">
         <v>1.4</v>
@@ -10224,19 +10224,19 @@
         <v>3.9</v>
       </c>
       <c r="O39">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P39">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q39">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R39">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S39">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T39">
         <v>1.55</v>
@@ -10245,7 +10245,7 @@
         <v>1.51</v>
       </c>
       <c r="V39">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W39">
         <v>2.36</v>
@@ -10290,7 +10290,7 @@
         <v>1000</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL39">
         <v>1000</v>
@@ -10305,118 +10305,118 @@
         <v>1000</v>
       </c>
       <c r="AP39">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV39">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC39">
         <v>1.01</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH39">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI39">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ39">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK39">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN39">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO39">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP39">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ39">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BR39">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS39">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT39">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU39">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BV39">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW39">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BZ39">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA39">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB39" t="s">
         <v>211</v>
@@ -10445,16 +10445,16 @@
         <v>3.9</v>
       </c>
       <c r="H40">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I40">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J40">
         <v>3.75</v>
       </c>
       <c r="K40">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L40">
         <v>1.44</v>
@@ -10469,19 +10469,19 @@
         <v>1.33</v>
       </c>
       <c r="P40">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q40">
         <v>2</v>
       </c>
       <c r="R40">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S40">
         <v>3.6</v>
       </c>
       <c r="T40">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U40">
         <v>1.85</v>
@@ -10511,7 +10511,7 @@
         <v>1000</v>
       </c>
       <c r="AD40">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE40">
         <v>1000</v>
@@ -10547,58 +10547,58 @@
         <v>1000</v>
       </c>
       <c r="AP40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AQ40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AR40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AS40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AT40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AU40">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AV40">
         <v>1.01</v>
       </c>
       <c r="AW40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AX40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AY40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AZ40">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BA40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BB40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BC40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BD40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BE40">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BF40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BG40">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10681,16 +10681,16 @@
         <v>209</v>
       </c>
       <c r="F41">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="G41">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H41">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="I41">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J41">
         <v>3.25</v>
@@ -10699,208 +10699,208 @@
         <v>3.45</v>
       </c>
       <c r="L41">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M41">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N41">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O41">
         <v>1.38</v>
       </c>
       <c r="P41">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q41">
         <v>2.16</v>
       </c>
       <c r="R41">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S41">
         <v>4</v>
       </c>
       <c r="T41">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U41">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W41">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X41">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y41">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z41">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA41">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB41">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC41">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD41">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE41">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF41">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG41">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH41">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI41">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ41">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK41">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL41">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM41">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN41">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO41">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP41">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ41">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR41">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS41">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT41">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU41">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV41">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW41">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AX41">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY41">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ41">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA41">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BB41">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BC41">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD41">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE41">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BF41">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG41">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BH41">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI41">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ41">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK41">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN41">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO41">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP41">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ41">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR41">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS41">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT41">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU41">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV41">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW41">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX41">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY41">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ41">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA41">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB41" t="s">
         <v>211</v>
@@ -10923,22 +10923,22 @@
         <v>210</v>
       </c>
       <c r="F42">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="G42">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="H42">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I42">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J42">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K42">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L42">
         <v>1.6</v>
@@ -10947,34 +10947,34 @@
         <v>1.13</v>
       </c>
       <c r="N42">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O42">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P42">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q42">
         <v>2.74</v>
       </c>
       <c r="R42">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S42">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T42">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="U42">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="V42">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W42">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="X42">
         <v>1000</v>
